--- a/minio-report-tracker/xlxs/collab.xlsx
+++ b/minio-report-tracker/xlxs/collab.xlsx
@@ -598,7 +598,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AI8"/>
+  <dimension ref="A1:Q8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="15" customWidth="1" min="1" max="1"/>
@@ -614,28 +614,10 @@
     <col width="12" customWidth="1" min="11" max="11"/>
     <col width="5" customWidth="1" min="12" max="12"/>
     <col width="5" customWidth="1" min="13" max="13"/>
-    <col width="4" customWidth="1" min="14" max="14"/>
+    <col width="5" customWidth="1" min="14" max="14"/>
     <col width="5" customWidth="1" min="15" max="15"/>
-    <col width="4" customWidth="1" min="16" max="16"/>
-    <col width="4" customWidth="1" min="17" max="17"/>
-    <col width="2" customWidth="1" min="18" max="18"/>
-    <col width="15" customWidth="1" min="19" max="19"/>
-    <col width="12" customWidth="1" min="20" max="20"/>
-    <col width="5" customWidth="1" min="21" max="21"/>
-    <col width="5" customWidth="1" min="22" max="22"/>
-    <col width="4" customWidth="1" min="23" max="23"/>
-    <col width="5" customWidth="1" min="24" max="24"/>
-    <col width="4" customWidth="1" min="25" max="25"/>
-    <col width="4" customWidth="1" min="26" max="26"/>
-    <col width="2" customWidth="1" min="27" max="27"/>
-    <col width="15" customWidth="1" min="28" max="28"/>
-    <col width="12" customWidth="1" min="29" max="29"/>
-    <col width="5" customWidth="1" min="30" max="30"/>
-    <col width="5" customWidth="1" min="31" max="31"/>
-    <col width="5" customWidth="1" min="32" max="32"/>
-    <col width="5" customWidth="1" min="33" max="33"/>
-    <col width="5" customWidth="1" min="34" max="34"/>
-    <col width="5" customWidth="1" min="35" max="35"/>
+    <col width="5" customWidth="1" min="16" max="16"/>
+    <col width="5" customWidth="1" min="17" max="17"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -719,244 +701,84 @@
           <t>KI</t>
         </is>
       </c>
-      <c r="S1" s="1" t="inlineStr">
-        <is>
-          <t>Date</t>
-        </is>
-      </c>
-      <c r="T1" s="1" t="inlineStr">
-        <is>
-          <t>Module</t>
-        </is>
-      </c>
-      <c r="U1" s="1" t="inlineStr">
-        <is>
-          <t>T</t>
-        </is>
-      </c>
-      <c r="V1" s="1" t="inlineStr">
-        <is>
-          <t>P</t>
-        </is>
-      </c>
-      <c r="W1" s="1" t="inlineStr">
-        <is>
-          <t>S</t>
-        </is>
-      </c>
-      <c r="X1" s="1" t="inlineStr">
-        <is>
-          <t>F</t>
-        </is>
-      </c>
-      <c r="Y1" s="1" t="inlineStr">
-        <is>
-          <t>I</t>
-        </is>
-      </c>
-      <c r="Z1" s="1" t="inlineStr">
-        <is>
-          <t>KI</t>
-        </is>
-      </c>
-      <c r="AB1" s="1" t="inlineStr">
-        <is>
-          <t>Date</t>
-        </is>
-      </c>
-      <c r="AC1" s="1" t="inlineStr">
-        <is>
-          <t>Module</t>
-        </is>
-      </c>
-      <c r="AD1" s="1" t="inlineStr">
-        <is>
-          <t>T</t>
-        </is>
-      </c>
-      <c r="AE1" s="1" t="inlineStr">
-        <is>
-          <t>P</t>
-        </is>
-      </c>
-      <c r="AF1" s="1" t="inlineStr">
-        <is>
-          <t>S</t>
-        </is>
-      </c>
-      <c r="AG1" s="1" t="inlineStr">
-        <is>
-          <t>F</t>
-        </is>
-      </c>
-      <c r="AH1" s="1" t="inlineStr">
-        <is>
-          <t>I</t>
-        </is>
-      </c>
-      <c r="AI1" s="1" t="inlineStr">
-        <is>
-          <t>KI</t>
-        </is>
-      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
+          <t>30-March-2026</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>auth</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>254</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>71</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>70</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>113</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
           <t>27-March-2026</t>
         </is>
       </c>
-      <c r="B2" t="inlineStr">
-        <is>
-          <t>auth</t>
-        </is>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>254</t>
-        </is>
-      </c>
-      <c r="D2" t="inlineStr">
-        <is>
-          <t>71</t>
-        </is>
-      </c>
-      <c r="E2" t="inlineStr">
-        <is>
-          <t>70</t>
-        </is>
-      </c>
-      <c r="F2" t="inlineStr">
-        <is>
-          <t>113</t>
-        </is>
-      </c>
-      <c r="G2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="J2" t="inlineStr">
-        <is>
-          <t>26-March-2026</t>
-        </is>
-      </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>auth</t>
+          <t>esignet</t>
         </is>
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>254</t>
+          <t>375</t>
         </is>
       </c>
       <c r="M2" t="inlineStr">
         <is>
-          <t>71</t>
+          <t>221</t>
         </is>
       </c>
       <c r="N2" t="inlineStr">
         <is>
-          <t>70</t>
+          <t>62</t>
         </is>
       </c>
       <c r="O2" t="inlineStr">
         <is>
-          <t>113</t>
+          <t>65</t>
         </is>
       </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>27</t>
         </is>
       </c>
       <c r="Q2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="S2" t="inlineStr">
-        <is>
-          <t>25-March-2026</t>
-        </is>
-      </c>
-      <c r="T2" t="inlineStr">
-        <is>
-          <t>auth</t>
-        </is>
-      </c>
-      <c r="U2" t="inlineStr">
-        <is>
-          <t>254</t>
-        </is>
-      </c>
-      <c r="V2" t="inlineStr">
-        <is>
-          <t>71</t>
-        </is>
-      </c>
-      <c r="W2" t="inlineStr">
-        <is>
-          <t>70</t>
-        </is>
-      </c>
-      <c r="X2" t="inlineStr">
-        <is>
-          <t>113</t>
-        </is>
-      </c>
-      <c r="Y2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>24-March-2026</t>
-        </is>
-      </c>
-      <c r="AC2" t="inlineStr">
-        <is>
-          <t>esignet</t>
-        </is>
-      </c>
-      <c r="AD2" t="inlineStr">
-        <is>
-          <t>375</t>
-        </is>
-      </c>
-      <c r="AE2" t="inlineStr">
-        <is>
-          <t>221</t>
-        </is>
-      </c>
-      <c r="AF2" t="inlineStr">
-        <is>
-          <t>62</t>
-        </is>
-      </c>
-      <c r="AG2" t="inlineStr">
-        <is>
-          <t>65</t>
-        </is>
-      </c>
-      <c r="AH2" t="inlineStr">
-        <is>
-          <t>27</t>
-        </is>
-      </c>
-      <c r="AI2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
@@ -965,160 +787,80 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
+          <t>30-March-2026</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>esignet</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>375</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>221</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>62</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>65</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>27</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
           <t>27-March-2026</t>
         </is>
       </c>
-      <c r="B3" t="inlineStr">
-        <is>
-          <t>esignet</t>
-        </is>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>375</t>
-        </is>
-      </c>
-      <c r="D3" t="inlineStr">
-        <is>
-          <t>221</t>
-        </is>
-      </c>
-      <c r="E3" t="inlineStr">
-        <is>
-          <t>62</t>
-        </is>
-      </c>
-      <c r="F3" t="inlineStr">
-        <is>
-          <t>65</t>
-        </is>
-      </c>
-      <c r="G3" t="inlineStr">
-        <is>
-          <t>27</t>
-        </is>
-      </c>
-      <c r="H3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="J3" t="inlineStr">
-        <is>
-          <t>26-March-2026</t>
-        </is>
-      </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>esignet</t>
+          <t>injiverify</t>
         </is>
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>375</t>
+          <t>35</t>
         </is>
       </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>221</t>
+          <t>35</t>
         </is>
       </c>
       <c r="N3" t="inlineStr">
         <is>
-          <t>62</t>
+          <t>0</t>
         </is>
       </c>
       <c r="O3" t="inlineStr">
         <is>
-          <t>65</t>
+          <t>0</t>
         </is>
       </c>
       <c r="P3" t="inlineStr">
         <is>
-          <t>27</t>
+          <t>0</t>
         </is>
       </c>
       <c r="Q3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="S3" t="inlineStr">
-        <is>
-          <t>25-March-2026</t>
-        </is>
-      </c>
-      <c r="T3" t="inlineStr">
-        <is>
-          <t>esignet</t>
-        </is>
-      </c>
-      <c r="U3" t="inlineStr">
-        <is>
-          <t>375</t>
-        </is>
-      </c>
-      <c r="V3" t="inlineStr">
-        <is>
-          <t>221</t>
-        </is>
-      </c>
-      <c r="W3" t="inlineStr">
-        <is>
-          <t>62</t>
-        </is>
-      </c>
-      <c r="X3" t="inlineStr">
-        <is>
-          <t>65</t>
-        </is>
-      </c>
-      <c r="Y3" t="inlineStr">
-        <is>
-          <t>27</t>
-        </is>
-      </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>24-March-2026</t>
-        </is>
-      </c>
-      <c r="AC3" t="inlineStr">
-        <is>
-          <t>injiverify</t>
-        </is>
-      </c>
-      <c r="AD3" t="inlineStr">
-        <is>
-          <t>35</t>
-        </is>
-      </c>
-      <c r="AE3" t="inlineStr">
-        <is>
-          <t>35</t>
-        </is>
-      </c>
-      <c r="AF3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AG3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AH3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AI3" t="inlineStr">
         <is>
           <t>0</t>
         </is>
@@ -1127,160 +869,80 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
+          <t>30-March-2026</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>idrepo</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>152</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>101</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>51</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
           <t>27-March-2026</t>
         </is>
       </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>idrepo</t>
-        </is>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>152</t>
-        </is>
-      </c>
-      <c r="D4" t="inlineStr">
-        <is>
-          <t>101</t>
-        </is>
-      </c>
-      <c r="E4" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F4" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="G4" t="inlineStr">
-        <is>
-          <t>51</t>
-        </is>
-      </c>
-      <c r="H4" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="J4" t="inlineStr">
-        <is>
-          <t>26-March-2026</t>
-        </is>
-      </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>idrepo</t>
+          <t>prereg</t>
         </is>
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>152</t>
+          <t>104</t>
         </is>
       </c>
       <c r="M4" t="inlineStr">
         <is>
-          <t>101</t>
+          <t>3</t>
         </is>
       </c>
       <c r="N4" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>70</t>
         </is>
       </c>
       <c r="O4" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>30</t>
         </is>
       </c>
       <c r="P4" t="inlineStr">
         <is>
-          <t>51</t>
+          <t>0</t>
         </is>
       </c>
       <c r="Q4" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="S4" t="inlineStr">
-        <is>
-          <t>25-March-2026</t>
-        </is>
-      </c>
-      <c r="T4" t="inlineStr">
-        <is>
-          <t>idrepo</t>
-        </is>
-      </c>
-      <c r="U4" t="inlineStr">
-        <is>
-          <t>152</t>
-        </is>
-      </c>
-      <c r="V4" t="inlineStr">
-        <is>
-          <t>101</t>
-        </is>
-      </c>
-      <c r="W4" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="X4" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="Y4" t="inlineStr">
-        <is>
-          <t>51</t>
-        </is>
-      </c>
-      <c r="Z4" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB4" t="inlineStr">
-        <is>
-          <t>24-March-2026</t>
-        </is>
-      </c>
-      <c r="AC4" t="inlineStr">
-        <is>
-          <t>prereg</t>
-        </is>
-      </c>
-      <c r="AD4" t="inlineStr">
-        <is>
-          <t>104</t>
-        </is>
-      </c>
-      <c r="AE4" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="AF4" t="inlineStr">
-        <is>
-          <t>70</t>
-        </is>
-      </c>
-      <c r="AG4" t="inlineStr">
-        <is>
-          <t>30</t>
-        </is>
-      </c>
-      <c r="AH4" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AI4" t="inlineStr">
         <is>
           <t>1</t>
         </is>
@@ -1289,72 +951,72 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
+          <t>30-March-2026</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>injiverify</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>35</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>35</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
           <t>27-March-2026</t>
         </is>
       </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>injiverify</t>
-        </is>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>35</t>
-        </is>
-      </c>
-      <c r="D5" t="inlineStr">
-        <is>
-          <t>35</t>
-        </is>
-      </c>
-      <c r="E5" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F5" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="G5" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H5" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="J5" t="inlineStr">
-        <is>
-          <t>26-March-2026</t>
-        </is>
-      </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>injiverify</t>
+          <t>residentui</t>
         </is>
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>35</t>
+          <t>33</t>
         </is>
       </c>
       <c r="M5" t="inlineStr">
         <is>
-          <t>35</t>
+          <t>10</t>
         </is>
       </c>
       <c r="N5" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>5</t>
         </is>
       </c>
       <c r="O5" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>18</t>
         </is>
       </c>
       <c r="P5" t="inlineStr">
@@ -1363,86 +1025,6 @@
         </is>
       </c>
       <c r="Q5" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="S5" t="inlineStr">
-        <is>
-          <t>25-March-2026</t>
-        </is>
-      </c>
-      <c r="T5" t="inlineStr">
-        <is>
-          <t>injiverify</t>
-        </is>
-      </c>
-      <c r="U5" t="inlineStr">
-        <is>
-          <t>35</t>
-        </is>
-      </c>
-      <c r="V5" t="inlineStr">
-        <is>
-          <t>35</t>
-        </is>
-      </c>
-      <c r="W5" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="X5" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="Y5" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="Z5" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB5" t="inlineStr">
-        <is>
-          <t>24-March-2026</t>
-        </is>
-      </c>
-      <c r="AC5" t="inlineStr">
-        <is>
-          <t>residentui</t>
-        </is>
-      </c>
-      <c r="AD5" t="inlineStr">
-        <is>
-          <t>33</t>
-        </is>
-      </c>
-      <c r="AE5" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="AF5" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="AG5" t="inlineStr">
-        <is>
-          <t>18</t>
-        </is>
-      </c>
-      <c r="AH5" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AI5" t="inlineStr">
         <is>
           <t>0</t>
         </is>
@@ -1451,7 +1033,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>27-March-2026</t>
+          <t>30-March-2026</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -1466,7 +1048,7 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>56</t>
+          <t>57</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -1476,7 +1058,7 @@
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>6</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
@@ -1489,115 +1071,35 @@
           <t>2</t>
         </is>
       </c>
-      <c r="J6" t="inlineStr">
-        <is>
-          <t>26-March-2026</t>
-        </is>
-      </c>
-      <c r="K6" t="inlineStr">
-        <is>
-          <t>mimoto</t>
-        </is>
-      </c>
-      <c r="L6" t="inlineStr">
-        <is>
-          <t>79</t>
-        </is>
-      </c>
-      <c r="M6" t="inlineStr">
-        <is>
-          <t>57</t>
-        </is>
-      </c>
-      <c r="N6" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="O6" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="P6" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="Q6" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="S6" t="inlineStr">
-        <is>
-          <t>25-March-2026</t>
-        </is>
-      </c>
-      <c r="T6" t="inlineStr">
-        <is>
-          <t>mimoto</t>
-        </is>
-      </c>
-      <c r="U6" t="inlineStr">
-        <is>
-          <t>79</t>
-        </is>
-      </c>
-      <c r="V6" t="inlineStr">
-        <is>
-          <t>57</t>
-        </is>
-      </c>
-      <c r="W6" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="X6" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="Y6" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="Z6" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="AB6" t="n">
-        <v/>
-      </c>
-      <c r="AC6" t="n">
-        <v/>
-      </c>
-      <c r="AD6" t="n">
-        <v/>
-      </c>
-      <c r="AE6" t="n">
-        <v/>
-      </c>
-      <c r="AF6" t="n">
-        <v/>
-      </c>
-      <c r="AG6" t="n">
-        <v/>
-      </c>
-      <c r="AH6" t="n">
-        <v/>
-      </c>
-      <c r="AI6" t="n">
+      <c r="J6" t="n">
+        <v/>
+      </c>
+      <c r="K6" t="n">
+        <v/>
+      </c>
+      <c r="L6" t="n">
+        <v/>
+      </c>
+      <c r="M6" t="n">
+        <v/>
+      </c>
+      <c r="N6" t="n">
+        <v/>
+      </c>
+      <c r="O6" t="n">
+        <v/>
+      </c>
+      <c r="P6" t="n">
+        <v/>
+      </c>
+      <c r="Q6" t="n">
         <v/>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>27-March-2026</t>
+          <t>30-March-2026</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -1635,115 +1137,35 @@
           <t>1</t>
         </is>
       </c>
-      <c r="J7" t="inlineStr">
-        <is>
-          <t>26-March-2026</t>
-        </is>
-      </c>
-      <c r="K7" t="inlineStr">
-        <is>
-          <t>prereg</t>
-        </is>
-      </c>
-      <c r="L7" t="inlineStr">
-        <is>
-          <t>104</t>
-        </is>
-      </c>
-      <c r="M7" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="N7" t="inlineStr">
-        <is>
-          <t>70</t>
-        </is>
-      </c>
-      <c r="O7" t="inlineStr">
-        <is>
-          <t>30</t>
-        </is>
-      </c>
-      <c r="P7" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="Q7" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="S7" t="inlineStr">
-        <is>
-          <t>25-March-2026</t>
-        </is>
-      </c>
-      <c r="T7" t="inlineStr">
-        <is>
-          <t>prereg</t>
-        </is>
-      </c>
-      <c r="U7" t="inlineStr">
-        <is>
-          <t>104</t>
-        </is>
-      </c>
-      <c r="V7" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="W7" t="inlineStr">
-        <is>
-          <t>70</t>
-        </is>
-      </c>
-      <c r="X7" t="inlineStr">
-        <is>
-          <t>30</t>
-        </is>
-      </c>
-      <c r="Y7" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="Z7" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="AB7" t="n">
-        <v/>
-      </c>
-      <c r="AC7" t="n">
-        <v/>
-      </c>
-      <c r="AD7" t="n">
-        <v/>
-      </c>
-      <c r="AE7" t="n">
-        <v/>
-      </c>
-      <c r="AF7" t="n">
-        <v/>
-      </c>
-      <c r="AG7" t="n">
-        <v/>
-      </c>
-      <c r="AH7" t="n">
-        <v/>
-      </c>
-      <c r="AI7" t="n">
+      <c r="J7" t="n">
+        <v/>
+      </c>
+      <c r="K7" t="n">
+        <v/>
+      </c>
+      <c r="L7" t="n">
+        <v/>
+      </c>
+      <c r="M7" t="n">
+        <v/>
+      </c>
+      <c r="N7" t="n">
+        <v/>
+      </c>
+      <c r="O7" t="n">
+        <v/>
+      </c>
+      <c r="P7" t="n">
+        <v/>
+      </c>
+      <c r="Q7" t="n">
         <v/>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>27-March-2026</t>
+          <t>30-March-2026</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1781,108 +1203,28 @@
           <t>0</t>
         </is>
       </c>
-      <c r="J8" t="inlineStr">
-        <is>
-          <t>26-March-2026</t>
-        </is>
-      </c>
-      <c r="K8" t="inlineStr">
-        <is>
-          <t>residentui</t>
-        </is>
-      </c>
-      <c r="L8" t="inlineStr">
-        <is>
-          <t>33</t>
-        </is>
-      </c>
-      <c r="M8" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="N8" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="O8" t="inlineStr">
-        <is>
-          <t>18</t>
-        </is>
-      </c>
-      <c r="P8" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="Q8" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="S8" t="inlineStr">
-        <is>
-          <t>25-March-2026</t>
-        </is>
-      </c>
-      <c r="T8" t="inlineStr">
-        <is>
-          <t>residentui</t>
-        </is>
-      </c>
-      <c r="U8" t="inlineStr">
-        <is>
-          <t>33</t>
-        </is>
-      </c>
-      <c r="V8" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="W8" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="X8" t="inlineStr">
-        <is>
-          <t>18</t>
-        </is>
-      </c>
-      <c r="Y8" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="Z8" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB8" t="n">
-        <v/>
-      </c>
-      <c r="AC8" t="n">
-        <v/>
-      </c>
-      <c r="AD8" t="n">
-        <v/>
-      </c>
-      <c r="AE8" t="n">
-        <v/>
-      </c>
-      <c r="AF8" t="n">
-        <v/>
-      </c>
-      <c r="AG8" t="n">
-        <v/>
-      </c>
-      <c r="AH8" t="n">
-        <v/>
-      </c>
-      <c r="AI8" t="n">
+      <c r="J8" t="n">
+        <v/>
+      </c>
+      <c r="K8" t="n">
+        <v/>
+      </c>
+      <c r="L8" t="n">
+        <v/>
+      </c>
+      <c r="M8" t="n">
+        <v/>
+      </c>
+      <c r="N8" t="n">
+        <v/>
+      </c>
+      <c r="O8" t="n">
+        <v/>
+      </c>
+      <c r="P8" t="n">
+        <v/>
+      </c>
+      <c r="Q8" t="n">
         <v/>
       </c>
     </row>

--- a/minio-report-tracker/xlxs/collab.xlsx
+++ b/minio-report-tracker/xlxs/collab.xlsx
@@ -614,10 +614,10 @@
     <col width="12" customWidth="1" min="11" max="11"/>
     <col width="5" customWidth="1" min="12" max="12"/>
     <col width="5" customWidth="1" min="13" max="13"/>
-    <col width="5" customWidth="1" min="14" max="14"/>
+    <col width="4" customWidth="1" min="14" max="14"/>
     <col width="5" customWidth="1" min="15" max="15"/>
-    <col width="5" customWidth="1" min="16" max="16"/>
-    <col width="5" customWidth="1" min="17" max="17"/>
+    <col width="4" customWidth="1" min="16" max="16"/>
+    <col width="4" customWidth="1" min="17" max="17"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -705,77 +705,77 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
+          <t>31-March-2026</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>auth</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>254</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>71</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>70</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>113</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
           <t>30-March-2026</t>
         </is>
       </c>
-      <c r="B2" t="inlineStr">
+      <c r="K2" t="inlineStr">
         <is>
           <t>auth</t>
         </is>
       </c>
-      <c r="C2" t="inlineStr">
+      <c r="L2" t="inlineStr">
         <is>
           <t>254</t>
         </is>
       </c>
-      <c r="D2" t="inlineStr">
+      <c r="M2" t="inlineStr">
         <is>
           <t>71</t>
         </is>
       </c>
-      <c r="E2" t="inlineStr">
+      <c r="N2" t="inlineStr">
         <is>
           <t>70</t>
         </is>
       </c>
-      <c r="F2" t="inlineStr">
+      <c r="O2" t="inlineStr">
         <is>
           <t>113</t>
         </is>
       </c>
-      <c r="G2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="J2" t="inlineStr">
-        <is>
-          <t>27-March-2026</t>
-        </is>
-      </c>
-      <c r="K2" t="inlineStr">
-        <is>
-          <t>esignet</t>
-        </is>
-      </c>
-      <c r="L2" t="inlineStr">
-        <is>
-          <t>375</t>
-        </is>
-      </c>
-      <c r="M2" t="inlineStr">
-        <is>
-          <t>221</t>
-        </is>
-      </c>
-      <c r="N2" t="inlineStr">
-        <is>
-          <t>62</t>
-        </is>
-      </c>
-      <c r="O2" t="inlineStr">
-        <is>
-          <t>65</t>
-        </is>
-      </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>27</t>
+          <t>0</t>
         </is>
       </c>
       <c r="Q2" t="inlineStr">
@@ -787,77 +787,77 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
+          <t>31-March-2026</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>esignet</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>375</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>221</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>62</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>65</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>27</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
           <t>30-March-2026</t>
         </is>
       </c>
-      <c r="B3" t="inlineStr">
+      <c r="K3" t="inlineStr">
         <is>
           <t>esignet</t>
         </is>
       </c>
-      <c r="C3" t="inlineStr">
+      <c r="L3" t="inlineStr">
         <is>
           <t>375</t>
         </is>
       </c>
-      <c r="D3" t="inlineStr">
+      <c r="M3" t="inlineStr">
         <is>
           <t>221</t>
         </is>
       </c>
-      <c r="E3" t="inlineStr">
+      <c r="N3" t="inlineStr">
         <is>
           <t>62</t>
         </is>
       </c>
-      <c r="F3" t="inlineStr">
+      <c r="O3" t="inlineStr">
         <is>
           <t>65</t>
         </is>
       </c>
-      <c r="G3" t="inlineStr">
+      <c r="P3" t="inlineStr">
         <is>
           <t>27</t>
-        </is>
-      </c>
-      <c r="H3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="J3" t="inlineStr">
-        <is>
-          <t>27-March-2026</t>
-        </is>
-      </c>
-      <c r="K3" t="inlineStr">
-        <is>
-          <t>injiverify</t>
-        </is>
-      </c>
-      <c r="L3" t="inlineStr">
-        <is>
-          <t>35</t>
-        </is>
-      </c>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>35</t>
-        </is>
-      </c>
-      <c r="N3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="O3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="P3" t="inlineStr">
-        <is>
-          <t>0</t>
         </is>
       </c>
       <c r="Q3" t="inlineStr">
@@ -869,154 +869,154 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
+          <t>31-March-2026</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>idrepo</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>152</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>101</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>51</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
           <t>30-March-2026</t>
         </is>
       </c>
-      <c r="B4" t="inlineStr">
+      <c r="K4" t="inlineStr">
         <is>
           <t>idrepo</t>
         </is>
       </c>
-      <c r="C4" t="inlineStr">
+      <c r="L4" t="inlineStr">
         <is>
           <t>152</t>
         </is>
       </c>
-      <c r="D4" t="inlineStr">
+      <c r="M4" t="inlineStr">
         <is>
           <t>101</t>
         </is>
       </c>
-      <c r="E4" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F4" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="G4" t="inlineStr">
+      <c r="N4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P4" t="inlineStr">
         <is>
           <t>51</t>
         </is>
       </c>
-      <c r="H4" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="J4" t="inlineStr">
-        <is>
-          <t>27-March-2026</t>
-        </is>
-      </c>
-      <c r="K4" t="inlineStr">
-        <is>
-          <t>prereg</t>
-        </is>
-      </c>
-      <c r="L4" t="inlineStr">
-        <is>
-          <t>104</t>
-        </is>
-      </c>
-      <c r="M4" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="N4" t="inlineStr">
-        <is>
-          <t>70</t>
-        </is>
-      </c>
-      <c r="O4" t="inlineStr">
-        <is>
-          <t>30</t>
-        </is>
-      </c>
-      <c r="P4" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
       <c r="Q4" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
+          <t>31-March-2026</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>injiverify</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>35</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>35</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
           <t>30-March-2026</t>
         </is>
       </c>
-      <c r="B5" t="inlineStr">
+      <c r="K5" t="inlineStr">
         <is>
           <t>injiverify</t>
         </is>
       </c>
-      <c r="C5" t="inlineStr">
+      <c r="L5" t="inlineStr">
         <is>
           <t>35</t>
         </is>
       </c>
-      <c r="D5" t="inlineStr">
+      <c r="M5" t="inlineStr">
         <is>
           <t>35</t>
         </is>
       </c>
-      <c r="E5" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F5" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="G5" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H5" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="J5" t="inlineStr">
-        <is>
-          <t>27-March-2026</t>
-        </is>
-      </c>
-      <c r="K5" t="inlineStr">
-        <is>
-          <t>residentui</t>
-        </is>
-      </c>
-      <c r="L5" t="inlineStr">
-        <is>
-          <t>33</t>
-        </is>
-      </c>
-      <c r="M5" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
       <c r="N5" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>0</t>
         </is>
       </c>
       <c r="O5" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>0</t>
         </is>
       </c>
       <c r="P5" t="inlineStr">
@@ -1033,199 +1033,247 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
+          <t>31-March-2026</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>mimoto</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>79</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>57</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
           <t>30-March-2026</t>
         </is>
       </c>
-      <c r="B6" t="inlineStr">
+      <c r="K6" t="inlineStr">
         <is>
           <t>mimoto</t>
         </is>
       </c>
-      <c r="C6" t="inlineStr">
+      <c r="L6" t="inlineStr">
         <is>
           <t>79</t>
         </is>
       </c>
-      <c r="D6" t="inlineStr">
+      <c r="M6" t="inlineStr">
         <is>
           <t>57</t>
         </is>
       </c>
-      <c r="E6" t="inlineStr">
+      <c r="N6" t="inlineStr">
         <is>
           <t>4</t>
         </is>
       </c>
-      <c r="F6" t="inlineStr">
+      <c r="O6" t="inlineStr">
         <is>
           <t>6</t>
         </is>
       </c>
-      <c r="G6" t="inlineStr">
+      <c r="P6" t="inlineStr">
         <is>
           <t>10</t>
         </is>
       </c>
-      <c r="H6" t="inlineStr">
+      <c r="Q6" t="inlineStr">
         <is>
           <t>2</t>
         </is>
-      </c>
-      <c r="J6" t="n">
-        <v/>
-      </c>
-      <c r="K6" t="n">
-        <v/>
-      </c>
-      <c r="L6" t="n">
-        <v/>
-      </c>
-      <c r="M6" t="n">
-        <v/>
-      </c>
-      <c r="N6" t="n">
-        <v/>
-      </c>
-      <c r="O6" t="n">
-        <v/>
-      </c>
-      <c r="P6" t="n">
-        <v/>
-      </c>
-      <c r="Q6" t="n">
-        <v/>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
+          <t>31-March-2026</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>prereg</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>104</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>70</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
           <t>30-March-2026</t>
         </is>
       </c>
-      <c r="B7" t="inlineStr">
+      <c r="K7" t="inlineStr">
         <is>
           <t>prereg</t>
         </is>
       </c>
-      <c r="C7" t="inlineStr">
+      <c r="L7" t="inlineStr">
         <is>
           <t>104</t>
         </is>
       </c>
-      <c r="D7" t="inlineStr">
+      <c r="M7" t="inlineStr">
         <is>
           <t>3</t>
         </is>
       </c>
-      <c r="E7" t="inlineStr">
+      <c r="N7" t="inlineStr">
         <is>
           <t>70</t>
         </is>
       </c>
-      <c r="F7" t="inlineStr">
+      <c r="O7" t="inlineStr">
         <is>
           <t>30</t>
         </is>
       </c>
-      <c r="G7" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H7" t="inlineStr">
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Q7" t="inlineStr">
         <is>
           <t>1</t>
         </is>
-      </c>
-      <c r="J7" t="n">
-        <v/>
-      </c>
-      <c r="K7" t="n">
-        <v/>
-      </c>
-      <c r="L7" t="n">
-        <v/>
-      </c>
-      <c r="M7" t="n">
-        <v/>
-      </c>
-      <c r="N7" t="n">
-        <v/>
-      </c>
-      <c r="O7" t="n">
-        <v/>
-      </c>
-      <c r="P7" t="n">
-        <v/>
-      </c>
-      <c r="Q7" t="n">
-        <v/>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
+          <t>31-March-2026</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>residentui</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>33</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>18</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
           <t>30-March-2026</t>
         </is>
       </c>
-      <c r="B8" t="inlineStr">
+      <c r="K8" t="inlineStr">
         <is>
           <t>residentui</t>
         </is>
       </c>
-      <c r="C8" t="inlineStr">
+      <c r="L8" t="inlineStr">
         <is>
           <t>33</t>
         </is>
       </c>
-      <c r="D8" t="inlineStr">
+      <c r="M8" t="inlineStr">
         <is>
           <t>10</t>
         </is>
       </c>
-      <c r="E8" t="inlineStr">
+      <c r="N8" t="inlineStr">
         <is>
           <t>5</t>
         </is>
       </c>
-      <c r="F8" t="inlineStr">
+      <c r="O8" t="inlineStr">
         <is>
           <t>18</t>
         </is>
       </c>
-      <c r="G8" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H8" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="J8" t="n">
-        <v/>
-      </c>
-      <c r="K8" t="n">
-        <v/>
-      </c>
-      <c r="L8" t="n">
-        <v/>
-      </c>
-      <c r="M8" t="n">
-        <v/>
-      </c>
-      <c r="N8" t="n">
-        <v/>
-      </c>
-      <c r="O8" t="n">
-        <v/>
-      </c>
-      <c r="P8" t="n">
-        <v/>
-      </c>
-      <c r="Q8" t="n">
-        <v/>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Q8" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
     </row>
   </sheetData>

--- a/minio-report-tracker/xlxs/collab.xlsx
+++ b/minio-report-tracker/xlxs/collab.xlsx
@@ -598,17 +598,17 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q8"/>
+  <dimension ref="A1:Z8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="15" customWidth="1" min="1" max="1"/>
     <col width="12" customWidth="1" min="2" max="2"/>
     <col width="5" customWidth="1" min="3" max="3"/>
     <col width="5" customWidth="1" min="4" max="4"/>
-    <col width="4" customWidth="1" min="5" max="5"/>
+    <col width="5" customWidth="1" min="5" max="5"/>
     <col width="5" customWidth="1" min="6" max="6"/>
-    <col width="4" customWidth="1" min="7" max="7"/>
-    <col width="4" customWidth="1" min="8" max="8"/>
+    <col width="5" customWidth="1" min="7" max="7"/>
+    <col width="5" customWidth="1" min="8" max="8"/>
     <col width="2" customWidth="1" min="9" max="9"/>
     <col width="15" customWidth="1" min="10" max="10"/>
     <col width="12" customWidth="1" min="11" max="11"/>
@@ -618,6 +618,15 @@
     <col width="5" customWidth="1" min="15" max="15"/>
     <col width="4" customWidth="1" min="16" max="16"/>
     <col width="4" customWidth="1" min="17" max="17"/>
+    <col width="2" customWidth="1" min="18" max="18"/>
+    <col width="15" customWidth="1" min="19" max="19"/>
+    <col width="12" customWidth="1" min="20" max="20"/>
+    <col width="5" customWidth="1" min="21" max="21"/>
+    <col width="5" customWidth="1" min="22" max="22"/>
+    <col width="4" customWidth="1" min="23" max="23"/>
+    <col width="5" customWidth="1" min="24" max="24"/>
+    <col width="4" customWidth="1" min="25" max="25"/>
+    <col width="4" customWidth="1" min="26" max="26"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -701,84 +710,164 @@
           <t>KI</t>
         </is>
       </c>
+      <c r="S1" s="1" t="inlineStr">
+        <is>
+          <t>Date</t>
+        </is>
+      </c>
+      <c r="T1" s="1" t="inlineStr">
+        <is>
+          <t>Module</t>
+        </is>
+      </c>
+      <c r="U1" s="1" t="inlineStr">
+        <is>
+          <t>T</t>
+        </is>
+      </c>
+      <c r="V1" s="1" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
+      <c r="W1" s="1" t="inlineStr">
+        <is>
+          <t>S</t>
+        </is>
+      </c>
+      <c r="X1" s="1" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
+      <c r="Y1" s="1" t="inlineStr">
+        <is>
+          <t>I</t>
+        </is>
+      </c>
+      <c r="Z1" s="1" t="inlineStr">
+        <is>
+          <t>KI</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
+          <t>01-April-2026</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>auth</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>254</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>142</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>72</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>40</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
           <t>31-March-2026</t>
         </is>
       </c>
-      <c r="B2" t="inlineStr">
+      <c r="K2" t="inlineStr">
         <is>
           <t>auth</t>
         </is>
       </c>
-      <c r="C2" t="inlineStr">
+      <c r="L2" t="inlineStr">
         <is>
           <t>254</t>
         </is>
       </c>
-      <c r="D2" t="inlineStr">
+      <c r="M2" t="inlineStr">
         <is>
           <t>71</t>
         </is>
       </c>
-      <c r="E2" t="inlineStr">
+      <c r="N2" t="inlineStr">
         <is>
           <t>70</t>
         </is>
       </c>
-      <c r="F2" t="inlineStr">
+      <c r="O2" t="inlineStr">
         <is>
           <t>113</t>
         </is>
       </c>
-      <c r="G2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="J2" t="inlineStr">
+      <c r="P2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Q2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="S2" t="inlineStr">
         <is>
           <t>30-March-2026</t>
         </is>
       </c>
-      <c r="K2" t="inlineStr">
+      <c r="T2" t="inlineStr">
         <is>
           <t>auth</t>
         </is>
       </c>
-      <c r="L2" t="inlineStr">
+      <c r="U2" t="inlineStr">
         <is>
           <t>254</t>
         </is>
       </c>
-      <c r="M2" t="inlineStr">
+      <c r="V2" t="inlineStr">
         <is>
           <t>71</t>
         </is>
       </c>
-      <c r="N2" t="inlineStr">
+      <c r="W2" t="inlineStr">
         <is>
           <t>70</t>
         </is>
       </c>
-      <c r="O2" t="inlineStr">
+      <c r="X2" t="inlineStr">
         <is>
           <t>113</t>
         </is>
       </c>
-      <c r="P2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="Q2" t="inlineStr">
+      <c r="Y2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Z2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
@@ -787,80 +876,120 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
+          <t>01-April-2026</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>idrepo</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>152</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>101</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>51</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
           <t>31-March-2026</t>
         </is>
       </c>
-      <c r="B3" t="inlineStr">
+      <c r="K3" t="inlineStr">
         <is>
           <t>esignet</t>
         </is>
       </c>
-      <c r="C3" t="inlineStr">
+      <c r="L3" t="inlineStr">
         <is>
           <t>375</t>
         </is>
       </c>
-      <c r="D3" t="inlineStr">
+      <c r="M3" t="inlineStr">
         <is>
           <t>221</t>
         </is>
       </c>
-      <c r="E3" t="inlineStr">
+      <c r="N3" t="inlineStr">
         <is>
           <t>62</t>
         </is>
       </c>
-      <c r="F3" t="inlineStr">
+      <c r="O3" t="inlineStr">
         <is>
           <t>65</t>
         </is>
       </c>
-      <c r="G3" t="inlineStr">
+      <c r="P3" t="inlineStr">
         <is>
           <t>27</t>
         </is>
       </c>
-      <c r="H3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="J3" t="inlineStr">
+      <c r="Q3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="S3" t="inlineStr">
         <is>
           <t>30-March-2026</t>
         </is>
       </c>
-      <c r="K3" t="inlineStr">
+      <c r="T3" t="inlineStr">
         <is>
           <t>esignet</t>
         </is>
       </c>
-      <c r="L3" t="inlineStr">
+      <c r="U3" t="inlineStr">
         <is>
           <t>375</t>
         </is>
       </c>
-      <c r="M3" t="inlineStr">
+      <c r="V3" t="inlineStr">
         <is>
           <t>221</t>
         </is>
       </c>
-      <c r="N3" t="inlineStr">
+      <c r="W3" t="inlineStr">
         <is>
           <t>62</t>
         </is>
       </c>
-      <c r="O3" t="inlineStr">
+      <c r="X3" t="inlineStr">
         <is>
           <t>65</t>
         </is>
       </c>
-      <c r="P3" t="inlineStr">
+      <c r="Y3" t="inlineStr">
         <is>
           <t>27</t>
         </is>
       </c>
-      <c r="Q3" t="inlineStr">
+      <c r="Z3" t="inlineStr">
         <is>
           <t>0</t>
         </is>
@@ -869,80 +998,120 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
+          <t>01-April-2026</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>injiverify</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>35</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>35</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
           <t>31-March-2026</t>
         </is>
       </c>
-      <c r="B4" t="inlineStr">
+      <c r="K4" t="inlineStr">
         <is>
           <t>idrepo</t>
         </is>
       </c>
-      <c r="C4" t="inlineStr">
+      <c r="L4" t="inlineStr">
         <is>
           <t>152</t>
         </is>
       </c>
-      <c r="D4" t="inlineStr">
+      <c r="M4" t="inlineStr">
         <is>
           <t>101</t>
         </is>
       </c>
-      <c r="E4" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F4" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="G4" t="inlineStr">
+      <c r="N4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P4" t="inlineStr">
         <is>
           <t>51</t>
         </is>
       </c>
-      <c r="H4" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="J4" t="inlineStr">
+      <c r="Q4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="S4" t="inlineStr">
         <is>
           <t>30-March-2026</t>
         </is>
       </c>
-      <c r="K4" t="inlineStr">
+      <c r="T4" t="inlineStr">
         <is>
           <t>idrepo</t>
         </is>
       </c>
-      <c r="L4" t="inlineStr">
+      <c r="U4" t="inlineStr">
         <is>
           <t>152</t>
         </is>
       </c>
-      <c r="M4" t="inlineStr">
+      <c r="V4" t="inlineStr">
         <is>
           <t>101</t>
         </is>
       </c>
-      <c r="N4" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="O4" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="P4" t="inlineStr">
+      <c r="W4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="X4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Y4" t="inlineStr">
         <is>
           <t>51</t>
         </is>
       </c>
-      <c r="Q4" t="inlineStr">
+      <c r="Z4" t="inlineStr">
         <is>
           <t>0</t>
         </is>
@@ -951,80 +1120,120 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
+          <t>01-April-2026</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>mimoto</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>79</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>59</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
           <t>31-March-2026</t>
         </is>
       </c>
-      <c r="B5" t="inlineStr">
+      <c r="K5" t="inlineStr">
         <is>
           <t>injiverify</t>
         </is>
       </c>
-      <c r="C5" t="inlineStr">
+      <c r="L5" t="inlineStr">
         <is>
           <t>35</t>
         </is>
       </c>
-      <c r="D5" t="inlineStr">
+      <c r="M5" t="inlineStr">
         <is>
           <t>35</t>
         </is>
       </c>
-      <c r="E5" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F5" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="G5" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H5" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="J5" t="inlineStr">
+      <c r="N5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Q5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="S5" t="inlineStr">
         <is>
           <t>30-March-2026</t>
         </is>
       </c>
-      <c r="K5" t="inlineStr">
+      <c r="T5" t="inlineStr">
         <is>
           <t>injiverify</t>
         </is>
       </c>
-      <c r="L5" t="inlineStr">
+      <c r="U5" t="inlineStr">
         <is>
           <t>35</t>
         </is>
       </c>
-      <c r="M5" t="inlineStr">
+      <c r="V5" t="inlineStr">
         <is>
           <t>35</t>
         </is>
       </c>
-      <c r="N5" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="O5" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="P5" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="Q5" t="inlineStr">
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="X5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Z5" t="inlineStr">
         <is>
           <t>0</t>
         </is>
@@ -1033,80 +1242,120 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
+          <t>01-April-2026</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>prereg</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>104</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>70</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
           <t>31-March-2026</t>
         </is>
       </c>
-      <c r="B6" t="inlineStr">
+      <c r="K6" t="inlineStr">
         <is>
           <t>mimoto</t>
         </is>
       </c>
-      <c r="C6" t="inlineStr">
+      <c r="L6" t="inlineStr">
         <is>
           <t>79</t>
         </is>
       </c>
-      <c r="D6" t="inlineStr">
+      <c r="M6" t="inlineStr">
         <is>
           <t>57</t>
         </is>
       </c>
-      <c r="E6" t="inlineStr">
+      <c r="N6" t="inlineStr">
         <is>
           <t>4</t>
         </is>
       </c>
-      <c r="F6" t="inlineStr">
+      <c r="O6" t="inlineStr">
         <is>
           <t>6</t>
         </is>
       </c>
-      <c r="G6" t="inlineStr">
+      <c r="P6" t="inlineStr">
         <is>
           <t>10</t>
         </is>
       </c>
-      <c r="H6" t="inlineStr">
+      <c r="Q6" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="J6" t="inlineStr">
+      <c r="S6" t="inlineStr">
         <is>
           <t>30-March-2026</t>
         </is>
       </c>
-      <c r="K6" t="inlineStr">
+      <c r="T6" t="inlineStr">
         <is>
           <t>mimoto</t>
         </is>
       </c>
-      <c r="L6" t="inlineStr">
+      <c r="U6" t="inlineStr">
         <is>
           <t>79</t>
         </is>
       </c>
-      <c r="M6" t="inlineStr">
+      <c r="V6" t="inlineStr">
         <is>
           <t>57</t>
         </is>
       </c>
-      <c r="N6" t="inlineStr">
+      <c r="W6" t="inlineStr">
         <is>
           <t>4</t>
         </is>
       </c>
-      <c r="O6" t="inlineStr">
+      <c r="X6" t="inlineStr">
         <is>
           <t>6</t>
         </is>
       </c>
-      <c r="P6" t="inlineStr">
+      <c r="Y6" t="inlineStr">
         <is>
           <t>10</t>
         </is>
       </c>
-      <c r="Q6" t="inlineStr">
+      <c r="Z6" t="inlineStr">
         <is>
           <t>2</t>
         </is>
@@ -1115,162 +1364,226 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
+          <t>01-April-2026</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>residentui</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>33</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
           <t>31-March-2026</t>
         </is>
       </c>
-      <c r="B7" t="inlineStr">
+      <c r="K7" t="inlineStr">
         <is>
           <t>prereg</t>
         </is>
       </c>
-      <c r="C7" t="inlineStr">
+      <c r="L7" t="inlineStr">
         <is>
           <t>104</t>
         </is>
       </c>
-      <c r="D7" t="inlineStr">
+      <c r="M7" t="inlineStr">
         <is>
           <t>3</t>
         </is>
       </c>
-      <c r="E7" t="inlineStr">
+      <c r="N7" t="inlineStr">
         <is>
           <t>70</t>
         </is>
       </c>
-      <c r="F7" t="inlineStr">
+      <c r="O7" t="inlineStr">
         <is>
           <t>30</t>
         </is>
       </c>
-      <c r="G7" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H7" t="inlineStr">
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Q7" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="J7" t="inlineStr">
+      <c r="S7" t="inlineStr">
         <is>
           <t>30-March-2026</t>
         </is>
       </c>
-      <c r="K7" t="inlineStr">
+      <c r="T7" t="inlineStr">
         <is>
           <t>prereg</t>
         </is>
       </c>
-      <c r="L7" t="inlineStr">
+      <c r="U7" t="inlineStr">
         <is>
           <t>104</t>
         </is>
       </c>
-      <c r="M7" t="inlineStr">
+      <c r="V7" t="inlineStr">
         <is>
           <t>3</t>
         </is>
       </c>
-      <c r="N7" t="inlineStr">
+      <c r="W7" t="inlineStr">
         <is>
           <t>70</t>
         </is>
       </c>
-      <c r="O7" t="inlineStr">
+      <c r="X7" t="inlineStr">
         <is>
           <t>30</t>
         </is>
       </c>
-      <c r="P7" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="Q7" t="inlineStr">
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Z7" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
     </row>
     <row r="8">
-      <c r="A8" t="inlineStr">
+      <c r="A8" t="n">
+        <v/>
+      </c>
+      <c r="B8" t="n">
+        <v/>
+      </c>
+      <c r="C8" t="n">
+        <v/>
+      </c>
+      <c r="D8" t="n">
+        <v/>
+      </c>
+      <c r="E8" t="n">
+        <v/>
+      </c>
+      <c r="F8" t="n">
+        <v/>
+      </c>
+      <c r="G8" t="n">
+        <v/>
+      </c>
+      <c r="H8" t="n">
+        <v/>
+      </c>
+      <c r="J8" t="inlineStr">
         <is>
           <t>31-March-2026</t>
         </is>
       </c>
-      <c r="B8" t="inlineStr">
+      <c r="K8" t="inlineStr">
         <is>
           <t>residentui</t>
         </is>
       </c>
-      <c r="C8" t="inlineStr">
+      <c r="L8" t="inlineStr">
         <is>
           <t>33</t>
         </is>
       </c>
-      <c r="D8" t="inlineStr">
+      <c r="M8" t="inlineStr">
         <is>
           <t>10</t>
         </is>
       </c>
-      <c r="E8" t="inlineStr">
+      <c r="N8" t="inlineStr">
         <is>
           <t>5</t>
         </is>
       </c>
-      <c r="F8" t="inlineStr">
+      <c r="O8" t="inlineStr">
         <is>
           <t>18</t>
         </is>
       </c>
-      <c r="G8" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H8" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="J8" t="inlineStr">
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Q8" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="S8" t="inlineStr">
         <is>
           <t>30-March-2026</t>
         </is>
       </c>
-      <c r="K8" t="inlineStr">
+      <c r="T8" t="inlineStr">
         <is>
           <t>residentui</t>
         </is>
       </c>
-      <c r="L8" t="inlineStr">
+      <c r="U8" t="inlineStr">
         <is>
           <t>33</t>
         </is>
       </c>
-      <c r="M8" t="inlineStr">
+      <c r="V8" t="inlineStr">
         <is>
           <t>10</t>
         </is>
       </c>
-      <c r="N8" t="inlineStr">
+      <c r="W8" t="inlineStr">
         <is>
           <t>5</t>
         </is>
       </c>
-      <c r="O8" t="inlineStr">
+      <c r="X8" t="inlineStr">
         <is>
           <t>18</t>
         </is>
       </c>
-      <c r="P8" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="Q8" t="inlineStr">
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Z8" t="inlineStr">
         <is>
           <t>0</t>
         </is>

--- a/minio-report-tracker/xlxs/collab.xlsx
+++ b/minio-report-tracker/xlxs/collab.xlsx
@@ -598,26 +598,26 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Z8"/>
+  <dimension ref="A1:AI8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="15" customWidth="1" min="1" max="1"/>
     <col width="12" customWidth="1" min="2" max="2"/>
     <col width="5" customWidth="1" min="3" max="3"/>
     <col width="5" customWidth="1" min="4" max="4"/>
-    <col width="5" customWidth="1" min="5" max="5"/>
-    <col width="5" customWidth="1" min="6" max="6"/>
-    <col width="5" customWidth="1" min="7" max="7"/>
-    <col width="5" customWidth="1" min="8" max="8"/>
+    <col width="4" customWidth="1" min="5" max="5"/>
+    <col width="4" customWidth="1" min="6" max="6"/>
+    <col width="4" customWidth="1" min="7" max="7"/>
+    <col width="4" customWidth="1" min="8" max="8"/>
     <col width="2" customWidth="1" min="9" max="9"/>
     <col width="15" customWidth="1" min="10" max="10"/>
     <col width="12" customWidth="1" min="11" max="11"/>
     <col width="5" customWidth="1" min="12" max="12"/>
     <col width="5" customWidth="1" min="13" max="13"/>
-    <col width="4" customWidth="1" min="14" max="14"/>
+    <col width="5" customWidth="1" min="14" max="14"/>
     <col width="5" customWidth="1" min="15" max="15"/>
-    <col width="4" customWidth="1" min="16" max="16"/>
-    <col width="4" customWidth="1" min="17" max="17"/>
+    <col width="5" customWidth="1" min="16" max="16"/>
+    <col width="5" customWidth="1" min="17" max="17"/>
     <col width="2" customWidth="1" min="18" max="18"/>
     <col width="15" customWidth="1" min="19" max="19"/>
     <col width="12" customWidth="1" min="20" max="20"/>
@@ -627,6 +627,15 @@
     <col width="5" customWidth="1" min="24" max="24"/>
     <col width="4" customWidth="1" min="25" max="25"/>
     <col width="4" customWidth="1" min="26" max="26"/>
+    <col width="2" customWidth="1" min="27" max="27"/>
+    <col width="15" customWidth="1" min="28" max="28"/>
+    <col width="12" customWidth="1" min="29" max="29"/>
+    <col width="5" customWidth="1" min="30" max="30"/>
+    <col width="5" customWidth="1" min="31" max="31"/>
+    <col width="5" customWidth="1" min="32" max="32"/>
+    <col width="5" customWidth="1" min="33" max="33"/>
+    <col width="5" customWidth="1" min="34" max="34"/>
+    <col width="5" customWidth="1" min="35" max="35"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -750,124 +759,204 @@
           <t>KI</t>
         </is>
       </c>
+      <c r="AB1" s="1" t="inlineStr">
+        <is>
+          <t>Date</t>
+        </is>
+      </c>
+      <c r="AC1" s="1" t="inlineStr">
+        <is>
+          <t>Module</t>
+        </is>
+      </c>
+      <c r="AD1" s="1" t="inlineStr">
+        <is>
+          <t>T</t>
+        </is>
+      </c>
+      <c r="AE1" s="1" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
+      <c r="AF1" s="1" t="inlineStr">
+        <is>
+          <t>S</t>
+        </is>
+      </c>
+      <c r="AG1" s="1" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
+      <c r="AH1" s="1" t="inlineStr">
+        <is>
+          <t>I</t>
+        </is>
+      </c>
+      <c r="AI1" s="1" t="inlineStr">
+        <is>
+          <t>KI</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
+          <t>02-April-2026</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>auth</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>254</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>140</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>72</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>42</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
           <t>01-April-2026</t>
         </is>
       </c>
-      <c r="B2" t="inlineStr">
+      <c r="K2" t="inlineStr">
         <is>
           <t>auth</t>
         </is>
       </c>
-      <c r="C2" t="inlineStr">
+      <c r="L2" t="inlineStr">
         <is>
           <t>254</t>
         </is>
       </c>
-      <c r="D2" t="inlineStr">
+      <c r="M2" t="inlineStr">
         <is>
           <t>142</t>
         </is>
       </c>
-      <c r="E2" t="inlineStr">
+      <c r="N2" t="inlineStr">
         <is>
           <t>72</t>
         </is>
       </c>
-      <c r="F2" t="inlineStr">
+      <c r="O2" t="inlineStr">
         <is>
           <t>40</t>
         </is>
       </c>
-      <c r="G2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="J2" t="inlineStr">
+      <c r="P2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Q2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="S2" t="inlineStr">
         <is>
           <t>31-March-2026</t>
         </is>
       </c>
-      <c r="K2" t="inlineStr">
+      <c r="T2" t="inlineStr">
         <is>
           <t>auth</t>
         </is>
       </c>
-      <c r="L2" t="inlineStr">
+      <c r="U2" t="inlineStr">
         <is>
           <t>254</t>
         </is>
       </c>
-      <c r="M2" t="inlineStr">
+      <c r="V2" t="inlineStr">
         <is>
           <t>71</t>
         </is>
       </c>
-      <c r="N2" t="inlineStr">
+      <c r="W2" t="inlineStr">
         <is>
           <t>70</t>
         </is>
       </c>
-      <c r="O2" t="inlineStr">
+      <c r="X2" t="inlineStr">
         <is>
           <t>113</t>
         </is>
       </c>
-      <c r="P2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="Q2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="S2" t="inlineStr">
+      <c r="Y2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Z2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB2" t="inlineStr">
         <is>
           <t>30-March-2026</t>
         </is>
       </c>
-      <c r="T2" t="inlineStr">
-        <is>
-          <t>auth</t>
-        </is>
-      </c>
-      <c r="U2" t="inlineStr">
-        <is>
-          <t>254</t>
-        </is>
-      </c>
-      <c r="V2" t="inlineStr">
-        <is>
-          <t>71</t>
-        </is>
-      </c>
-      <c r="W2" t="inlineStr">
-        <is>
-          <t>70</t>
-        </is>
-      </c>
-      <c r="X2" t="inlineStr">
-        <is>
-          <t>113</t>
-        </is>
-      </c>
-      <c r="Y2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="Z2" t="inlineStr">
+      <c r="AC2" t="inlineStr">
+        <is>
+          <t>esignet</t>
+        </is>
+      </c>
+      <c r="AD2" t="inlineStr">
+        <is>
+          <t>375</t>
+        </is>
+      </c>
+      <c r="AE2" t="inlineStr">
+        <is>
+          <t>221</t>
+        </is>
+      </c>
+      <c r="AF2" t="inlineStr">
+        <is>
+          <t>62</t>
+        </is>
+      </c>
+      <c r="AG2" t="inlineStr">
+        <is>
+          <t>65</t>
+        </is>
+      </c>
+      <c r="AH2" t="inlineStr">
+        <is>
+          <t>27</t>
+        </is>
+      </c>
+      <c r="AI2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
@@ -876,120 +965,160 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
+          <t>02-April-2026</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>esignet</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>375</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>247</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>46</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>55</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>27</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
           <t>01-April-2026</t>
         </is>
       </c>
-      <c r="B3" t="inlineStr">
+      <c r="K3" t="inlineStr">
         <is>
           <t>idrepo</t>
         </is>
       </c>
-      <c r="C3" t="inlineStr">
+      <c r="L3" t="inlineStr">
         <is>
           <t>152</t>
         </is>
       </c>
-      <c r="D3" t="inlineStr">
+      <c r="M3" t="inlineStr">
         <is>
           <t>101</t>
         </is>
       </c>
-      <c r="E3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="G3" t="inlineStr">
+      <c r="N3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P3" t="inlineStr">
         <is>
           <t>51</t>
         </is>
       </c>
-      <c r="H3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="J3" t="inlineStr">
+      <c r="Q3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="S3" t="inlineStr">
         <is>
           <t>31-March-2026</t>
         </is>
       </c>
-      <c r="K3" t="inlineStr">
+      <c r="T3" t="inlineStr">
         <is>
           <t>esignet</t>
         </is>
       </c>
-      <c r="L3" t="inlineStr">
+      <c r="U3" t="inlineStr">
         <is>
           <t>375</t>
         </is>
       </c>
-      <c r="M3" t="inlineStr">
+      <c r="V3" t="inlineStr">
         <is>
           <t>221</t>
         </is>
       </c>
-      <c r="N3" t="inlineStr">
+      <c r="W3" t="inlineStr">
         <is>
           <t>62</t>
         </is>
       </c>
-      <c r="O3" t="inlineStr">
+      <c r="X3" t="inlineStr">
         <is>
           <t>65</t>
         </is>
       </c>
-      <c r="P3" t="inlineStr">
+      <c r="Y3" t="inlineStr">
         <is>
           <t>27</t>
         </is>
       </c>
-      <c r="Q3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="S3" t="inlineStr">
+      <c r="Z3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB3" t="inlineStr">
         <is>
           <t>30-March-2026</t>
         </is>
       </c>
-      <c r="T3" t="inlineStr">
-        <is>
-          <t>esignet</t>
-        </is>
-      </c>
-      <c r="U3" t="inlineStr">
-        <is>
-          <t>375</t>
-        </is>
-      </c>
-      <c r="V3" t="inlineStr">
-        <is>
-          <t>221</t>
-        </is>
-      </c>
-      <c r="W3" t="inlineStr">
-        <is>
-          <t>62</t>
-        </is>
-      </c>
-      <c r="X3" t="inlineStr">
-        <is>
-          <t>65</t>
-        </is>
-      </c>
-      <c r="Y3" t="inlineStr">
-        <is>
-          <t>27</t>
-        </is>
-      </c>
-      <c r="Z3" t="inlineStr">
+      <c r="AC3" t="inlineStr">
+        <is>
+          <t>injiverify</t>
+        </is>
+      </c>
+      <c r="AD3" t="inlineStr">
+        <is>
+          <t>35</t>
+        </is>
+      </c>
+      <c r="AE3" t="inlineStr">
+        <is>
+          <t>35</t>
+        </is>
+      </c>
+      <c r="AF3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AG3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AH3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AI3" t="inlineStr">
         <is>
           <t>0</t>
         </is>
@@ -998,242 +1127,322 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
+          <t>02-April-2026</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>idrepo</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>152</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>101</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>51</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
           <t>01-April-2026</t>
         </is>
       </c>
-      <c r="B4" t="inlineStr">
+      <c r="K4" t="inlineStr">
         <is>
           <t>injiverify</t>
         </is>
       </c>
-      <c r="C4" t="inlineStr">
+      <c r="L4" t="inlineStr">
         <is>
           <t>35</t>
         </is>
       </c>
-      <c r="D4" t="inlineStr">
+      <c r="M4" t="inlineStr">
         <is>
           <t>35</t>
         </is>
       </c>
-      <c r="E4" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F4" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="G4" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H4" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="J4" t="inlineStr">
+      <c r="N4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Q4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="S4" t="inlineStr">
         <is>
           <t>31-March-2026</t>
         </is>
       </c>
-      <c r="K4" t="inlineStr">
+      <c r="T4" t="inlineStr">
         <is>
           <t>idrepo</t>
         </is>
       </c>
-      <c r="L4" t="inlineStr">
+      <c r="U4" t="inlineStr">
         <is>
           <t>152</t>
         </is>
       </c>
-      <c r="M4" t="inlineStr">
+      <c r="V4" t="inlineStr">
         <is>
           <t>101</t>
         </is>
       </c>
-      <c r="N4" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="O4" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="P4" t="inlineStr">
+      <c r="W4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="X4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Y4" t="inlineStr">
         <is>
           <t>51</t>
         </is>
       </c>
-      <c r="Q4" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="S4" t="inlineStr">
+      <c r="Z4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB4" t="inlineStr">
         <is>
           <t>30-March-2026</t>
         </is>
       </c>
-      <c r="T4" t="inlineStr">
-        <is>
-          <t>idrepo</t>
-        </is>
-      </c>
-      <c r="U4" t="inlineStr">
-        <is>
-          <t>152</t>
-        </is>
-      </c>
-      <c r="V4" t="inlineStr">
-        <is>
-          <t>101</t>
-        </is>
-      </c>
-      <c r="W4" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="X4" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="Y4" t="inlineStr">
-        <is>
-          <t>51</t>
-        </is>
-      </c>
-      <c r="Z4" t="inlineStr">
-        <is>
-          <t>0</t>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t>prereg</t>
+        </is>
+      </c>
+      <c r="AD4" t="inlineStr">
+        <is>
+          <t>104</t>
+        </is>
+      </c>
+      <c r="AE4" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AF4" t="inlineStr">
+        <is>
+          <t>70</t>
+        </is>
+      </c>
+      <c r="AG4" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="AH4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AI4" t="inlineStr">
+        <is>
+          <t>1</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
+          <t>02-April-2026</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>injiverify</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>35</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>35</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
           <t>01-April-2026</t>
         </is>
       </c>
-      <c r="B5" t="inlineStr">
+      <c r="K5" t="inlineStr">
         <is>
           <t>mimoto</t>
         </is>
       </c>
-      <c r="C5" t="inlineStr">
+      <c r="L5" t="inlineStr">
         <is>
           <t>79</t>
         </is>
       </c>
-      <c r="D5" t="inlineStr">
+      <c r="M5" t="inlineStr">
         <is>
           <t>59</t>
         </is>
       </c>
-      <c r="E5" t="inlineStr">
+      <c r="N5" t="inlineStr">
         <is>
           <t>4</t>
         </is>
       </c>
-      <c r="F5" t="inlineStr">
+      <c r="O5" t="inlineStr">
         <is>
           <t>4</t>
         </is>
       </c>
-      <c r="G5" t="inlineStr">
+      <c r="P5" t="inlineStr">
         <is>
           <t>10</t>
         </is>
       </c>
-      <c r="H5" t="inlineStr">
+      <c r="Q5" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="J5" t="inlineStr">
+      <c r="S5" t="inlineStr">
         <is>
           <t>31-March-2026</t>
         </is>
       </c>
-      <c r="K5" t="inlineStr">
+      <c r="T5" t="inlineStr">
         <is>
           <t>injiverify</t>
         </is>
       </c>
-      <c r="L5" t="inlineStr">
+      <c r="U5" t="inlineStr">
         <is>
           <t>35</t>
         </is>
       </c>
-      <c r="M5" t="inlineStr">
+      <c r="V5" t="inlineStr">
         <is>
           <t>35</t>
         </is>
       </c>
-      <c r="N5" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="O5" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="P5" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="Q5" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="S5" t="inlineStr">
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="X5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Z5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB5" t="inlineStr">
         <is>
           <t>30-March-2026</t>
         </is>
       </c>
-      <c r="T5" t="inlineStr">
-        <is>
-          <t>injiverify</t>
-        </is>
-      </c>
-      <c r="U5" t="inlineStr">
-        <is>
-          <t>35</t>
-        </is>
-      </c>
-      <c r="V5" t="inlineStr">
-        <is>
-          <t>35</t>
-        </is>
-      </c>
-      <c r="W5" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="X5" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="Y5" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="Z5" t="inlineStr">
+      <c r="AC5" t="inlineStr">
+        <is>
+          <t>residentui</t>
+        </is>
+      </c>
+      <c r="AD5" t="inlineStr">
+        <is>
+          <t>33</t>
+        </is>
+      </c>
+      <c r="AE5" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="AF5" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AG5" t="inlineStr">
+        <is>
+          <t>18</t>
+        </is>
+      </c>
+      <c r="AH5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AI5" t="inlineStr">
         <is>
           <t>0</t>
         </is>
@@ -1242,342 +1451,390 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
+          <t>02-April-2026</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>mimoto</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>79</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>58</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
           <t>01-April-2026</t>
         </is>
       </c>
-      <c r="B6" t="inlineStr">
+      <c r="K6" t="inlineStr">
         <is>
           <t>prereg</t>
         </is>
       </c>
-      <c r="C6" t="inlineStr">
+      <c r="L6" t="inlineStr">
         <is>
           <t>104</t>
         </is>
       </c>
-      <c r="D6" t="inlineStr">
+      <c r="M6" t="inlineStr">
         <is>
           <t>3</t>
         </is>
       </c>
-      <c r="E6" t="inlineStr">
+      <c r="N6" t="inlineStr">
         <is>
           <t>70</t>
         </is>
       </c>
-      <c r="F6" t="inlineStr">
+      <c r="O6" t="inlineStr">
         <is>
           <t>30</t>
         </is>
       </c>
-      <c r="G6" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H6" t="inlineStr">
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Q6" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="J6" t="inlineStr">
+      <c r="S6" t="inlineStr">
         <is>
           <t>31-March-2026</t>
         </is>
       </c>
-      <c r="K6" t="inlineStr">
+      <c r="T6" t="inlineStr">
         <is>
           <t>mimoto</t>
         </is>
       </c>
-      <c r="L6" t="inlineStr">
+      <c r="U6" t="inlineStr">
         <is>
           <t>79</t>
         </is>
       </c>
-      <c r="M6" t="inlineStr">
+      <c r="V6" t="inlineStr">
         <is>
           <t>57</t>
         </is>
       </c>
-      <c r="N6" t="inlineStr">
+      <c r="W6" t="inlineStr">
         <is>
           <t>4</t>
         </is>
       </c>
-      <c r="O6" t="inlineStr">
+      <c r="X6" t="inlineStr">
         <is>
           <t>6</t>
         </is>
       </c>
-      <c r="P6" t="inlineStr">
+      <c r="Y6" t="inlineStr">
         <is>
           <t>10</t>
         </is>
       </c>
-      <c r="Q6" t="inlineStr">
+      <c r="Z6" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="S6" t="inlineStr">
-        <is>
-          <t>30-March-2026</t>
-        </is>
-      </c>
-      <c r="T6" t="inlineStr">
-        <is>
-          <t>mimoto</t>
-        </is>
-      </c>
-      <c r="U6" t="inlineStr">
-        <is>
-          <t>79</t>
-        </is>
-      </c>
-      <c r="V6" t="inlineStr">
-        <is>
-          <t>57</t>
-        </is>
-      </c>
-      <c r="W6" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="X6" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="Y6" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="Z6" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
+      <c r="AB6" t="n">
+        <v/>
+      </c>
+      <c r="AC6" t="n">
+        <v/>
+      </c>
+      <c r="AD6" t="n">
+        <v/>
+      </c>
+      <c r="AE6" t="n">
+        <v/>
+      </c>
+      <c r="AF6" t="n">
+        <v/>
+      </c>
+      <c r="AG6" t="n">
+        <v/>
+      </c>
+      <c r="AH6" t="n">
+        <v/>
+      </c>
+      <c r="AI6" t="n">
+        <v/>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
+          <t>02-April-2026</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>prereg</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>104</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>70</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
           <t>01-April-2026</t>
         </is>
       </c>
-      <c r="B7" t="inlineStr">
+      <c r="K7" t="inlineStr">
         <is>
           <t>residentui</t>
         </is>
       </c>
-      <c r="C7" t="inlineStr">
+      <c r="L7" t="inlineStr">
         <is>
           <t>33</t>
         </is>
       </c>
-      <c r="D7" t="inlineStr">
+      <c r="M7" t="inlineStr">
         <is>
           <t>12</t>
         </is>
       </c>
-      <c r="E7" t="inlineStr">
+      <c r="N7" t="inlineStr">
         <is>
           <t>5</t>
         </is>
       </c>
-      <c r="F7" t="inlineStr">
+      <c r="O7" t="inlineStr">
         <is>
           <t>16</t>
         </is>
       </c>
-      <c r="G7" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H7" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="J7" t="inlineStr">
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Q7" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="S7" t="inlineStr">
         <is>
           <t>31-March-2026</t>
         </is>
       </c>
-      <c r="K7" t="inlineStr">
+      <c r="T7" t="inlineStr">
         <is>
           <t>prereg</t>
         </is>
       </c>
-      <c r="L7" t="inlineStr">
+      <c r="U7" t="inlineStr">
         <is>
           <t>104</t>
         </is>
       </c>
-      <c r="M7" t="inlineStr">
+      <c r="V7" t="inlineStr">
         <is>
           <t>3</t>
         </is>
       </c>
-      <c r="N7" t="inlineStr">
+      <c r="W7" t="inlineStr">
         <is>
           <t>70</t>
         </is>
       </c>
-      <c r="O7" t="inlineStr">
+      <c r="X7" t="inlineStr">
         <is>
           <t>30</t>
         </is>
       </c>
-      <c r="P7" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="Q7" t="inlineStr">
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Z7" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="S7" t="inlineStr">
-        <is>
-          <t>30-March-2026</t>
-        </is>
-      </c>
-      <c r="T7" t="inlineStr">
-        <is>
-          <t>prereg</t>
-        </is>
-      </c>
-      <c r="U7" t="inlineStr">
-        <is>
-          <t>104</t>
-        </is>
-      </c>
-      <c r="V7" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="W7" t="inlineStr">
-        <is>
-          <t>70</t>
-        </is>
-      </c>
-      <c r="X7" t="inlineStr">
-        <is>
-          <t>30</t>
-        </is>
-      </c>
-      <c r="Y7" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="Z7" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
+      <c r="AB7" t="n">
+        <v/>
+      </c>
+      <c r="AC7" t="n">
+        <v/>
+      </c>
+      <c r="AD7" t="n">
+        <v/>
+      </c>
+      <c r="AE7" t="n">
+        <v/>
+      </c>
+      <c r="AF7" t="n">
+        <v/>
+      </c>
+      <c r="AG7" t="n">
+        <v/>
+      </c>
+      <c r="AH7" t="n">
+        <v/>
+      </c>
+      <c r="AI7" t="n">
+        <v/>
       </c>
     </row>
     <row r="8">
-      <c r="A8" t="n">
-        <v/>
-      </c>
-      <c r="B8" t="n">
-        <v/>
-      </c>
-      <c r="C8" t="n">
-        <v/>
-      </c>
-      <c r="D8" t="n">
-        <v/>
-      </c>
-      <c r="E8" t="n">
-        <v/>
-      </c>
-      <c r="F8" t="n">
-        <v/>
-      </c>
-      <c r="G8" t="n">
-        <v/>
-      </c>
-      <c r="H8" t="n">
-        <v/>
-      </c>
-      <c r="J8" t="inlineStr">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>02-April-2026</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>residentui</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>33</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J8" t="n">
+        <v/>
+      </c>
+      <c r="K8" t="n">
+        <v/>
+      </c>
+      <c r="L8" t="n">
+        <v/>
+      </c>
+      <c r="M8" t="n">
+        <v/>
+      </c>
+      <c r="N8" t="n">
+        <v/>
+      </c>
+      <c r="O8" t="n">
+        <v/>
+      </c>
+      <c r="P8" t="n">
+        <v/>
+      </c>
+      <c r="Q8" t="n">
+        <v/>
+      </c>
+      <c r="S8" t="inlineStr">
         <is>
           <t>31-March-2026</t>
         </is>
       </c>
-      <c r="K8" t="inlineStr">
+      <c r="T8" t="inlineStr">
         <is>
           <t>residentui</t>
         </is>
       </c>
-      <c r="L8" t="inlineStr">
+      <c r="U8" t="inlineStr">
         <is>
           <t>33</t>
         </is>
       </c>
-      <c r="M8" t="inlineStr">
+      <c r="V8" t="inlineStr">
         <is>
           <t>10</t>
         </is>
       </c>
-      <c r="N8" t="inlineStr">
+      <c r="W8" t="inlineStr">
         <is>
           <t>5</t>
         </is>
       </c>
-      <c r="O8" t="inlineStr">
+      <c r="X8" t="inlineStr">
         <is>
           <t>18</t>
         </is>
       </c>
-      <c r="P8" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="Q8" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="S8" t="inlineStr">
-        <is>
-          <t>30-March-2026</t>
-        </is>
-      </c>
-      <c r="T8" t="inlineStr">
-        <is>
-          <t>residentui</t>
-        </is>
-      </c>
-      <c r="U8" t="inlineStr">
-        <is>
-          <t>33</t>
-        </is>
-      </c>
-      <c r="V8" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="W8" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="X8" t="inlineStr">
-        <is>
-          <t>18</t>
-        </is>
-      </c>
       <c r="Y8" t="inlineStr">
         <is>
           <t>0</t>
@@ -1587,6 +1844,30 @@
         <is>
           <t>0</t>
         </is>
+      </c>
+      <c r="AB8" t="n">
+        <v/>
+      </c>
+      <c r="AC8" t="n">
+        <v/>
+      </c>
+      <c r="AD8" t="n">
+        <v/>
+      </c>
+      <c r="AE8" t="n">
+        <v/>
+      </c>
+      <c r="AF8" t="n">
+        <v/>
+      </c>
+      <c r="AG8" t="n">
+        <v/>
+      </c>
+      <c r="AH8" t="n">
+        <v/>
+      </c>
+      <c r="AI8" t="n">
+        <v/>
       </c>
     </row>
   </sheetData>

--- a/minio-report-tracker/xlxs/collab.xlsx
+++ b/minio-report-tracker/xlxs/collab.xlsx
@@ -614,19 +614,19 @@
     <col width="12" customWidth="1" min="11" max="11"/>
     <col width="5" customWidth="1" min="12" max="12"/>
     <col width="5" customWidth="1" min="13" max="13"/>
-    <col width="5" customWidth="1" min="14" max="14"/>
-    <col width="5" customWidth="1" min="15" max="15"/>
-    <col width="5" customWidth="1" min="16" max="16"/>
-    <col width="5" customWidth="1" min="17" max="17"/>
+    <col width="4" customWidth="1" min="14" max="14"/>
+    <col width="4" customWidth="1" min="15" max="15"/>
+    <col width="4" customWidth="1" min="16" max="16"/>
+    <col width="4" customWidth="1" min="17" max="17"/>
     <col width="2" customWidth="1" min="18" max="18"/>
     <col width="15" customWidth="1" min="19" max="19"/>
     <col width="12" customWidth="1" min="20" max="20"/>
     <col width="5" customWidth="1" min="21" max="21"/>
     <col width="5" customWidth="1" min="22" max="22"/>
-    <col width="4" customWidth="1" min="23" max="23"/>
+    <col width="5" customWidth="1" min="23" max="23"/>
     <col width="5" customWidth="1" min="24" max="24"/>
-    <col width="4" customWidth="1" min="25" max="25"/>
-    <col width="4" customWidth="1" min="26" max="26"/>
+    <col width="5" customWidth="1" min="25" max="25"/>
+    <col width="5" customWidth="1" min="26" max="26"/>
     <col width="2" customWidth="1" min="27" max="27"/>
     <col width="15" customWidth="1" min="28" max="28"/>
     <col width="12" customWidth="1" min="29" max="29"/>
@@ -803,127 +803,127 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
+          <t>03-April-2026</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>auth</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>254</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>140</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>72</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>42</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
           <t>02-April-2026</t>
         </is>
       </c>
-      <c r="B2" t="inlineStr">
+      <c r="K2" t="inlineStr">
         <is>
           <t>auth</t>
         </is>
       </c>
-      <c r="C2" t="inlineStr">
+      <c r="L2" t="inlineStr">
         <is>
           <t>254</t>
         </is>
       </c>
-      <c r="D2" t="inlineStr">
+      <c r="M2" t="inlineStr">
         <is>
           <t>140</t>
         </is>
       </c>
-      <c r="E2" t="inlineStr">
+      <c r="N2" t="inlineStr">
         <is>
           <t>72</t>
         </is>
       </c>
-      <c r="F2" t="inlineStr">
+      <c r="O2" t="inlineStr">
         <is>
           <t>42</t>
         </is>
       </c>
-      <c r="G2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="J2" t="inlineStr">
+      <c r="P2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Q2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="S2" t="inlineStr">
         <is>
           <t>01-April-2026</t>
         </is>
       </c>
-      <c r="K2" t="inlineStr">
+      <c r="T2" t="inlineStr">
         <is>
           <t>auth</t>
         </is>
       </c>
-      <c r="L2" t="inlineStr">
+      <c r="U2" t="inlineStr">
         <is>
           <t>254</t>
         </is>
       </c>
-      <c r="M2" t="inlineStr">
+      <c r="V2" t="inlineStr">
         <is>
           <t>142</t>
         </is>
       </c>
-      <c r="N2" t="inlineStr">
+      <c r="W2" t="inlineStr">
         <is>
           <t>72</t>
         </is>
       </c>
-      <c r="O2" t="inlineStr">
+      <c r="X2" t="inlineStr">
         <is>
           <t>40</t>
         </is>
       </c>
-      <c r="P2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="Q2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="S2" t="inlineStr">
+      <c r="Y2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Z2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB2" t="inlineStr">
         <is>
           <t>31-March-2026</t>
-        </is>
-      </c>
-      <c r="T2" t="inlineStr">
-        <is>
-          <t>auth</t>
-        </is>
-      </c>
-      <c r="U2" t="inlineStr">
-        <is>
-          <t>254</t>
-        </is>
-      </c>
-      <c r="V2" t="inlineStr">
-        <is>
-          <t>71</t>
-        </is>
-      </c>
-      <c r="W2" t="inlineStr">
-        <is>
-          <t>70</t>
-        </is>
-      </c>
-      <c r="X2" t="inlineStr">
-        <is>
-          <t>113</t>
-        </is>
-      </c>
-      <c r="Y2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>30-March-2026</t>
         </is>
       </c>
       <c r="AC2" t="inlineStr">
@@ -965,127 +965,127 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
+          <t>03-April-2026</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>esignet</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>375</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>267</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>32</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>49</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>27</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
           <t>02-April-2026</t>
         </is>
       </c>
-      <c r="B3" t="inlineStr">
+      <c r="K3" t="inlineStr">
         <is>
           <t>esignet</t>
         </is>
       </c>
-      <c r="C3" t="inlineStr">
+      <c r="L3" t="inlineStr">
         <is>
           <t>375</t>
         </is>
       </c>
-      <c r="D3" t="inlineStr">
+      <c r="M3" t="inlineStr">
         <is>
           <t>247</t>
         </is>
       </c>
-      <c r="E3" t="inlineStr">
+      <c r="N3" t="inlineStr">
         <is>
           <t>46</t>
         </is>
       </c>
-      <c r="F3" t="inlineStr">
+      <c r="O3" t="inlineStr">
         <is>
           <t>55</t>
         </is>
       </c>
-      <c r="G3" t="inlineStr">
+      <c r="P3" t="inlineStr">
         <is>
           <t>27</t>
         </is>
       </c>
-      <c r="H3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="J3" t="inlineStr">
+      <c r="Q3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="S3" t="inlineStr">
         <is>
           <t>01-April-2026</t>
         </is>
       </c>
-      <c r="K3" t="inlineStr">
+      <c r="T3" t="inlineStr">
         <is>
           <t>idrepo</t>
         </is>
       </c>
-      <c r="L3" t="inlineStr">
+      <c r="U3" t="inlineStr">
         <is>
           <t>152</t>
         </is>
       </c>
-      <c r="M3" t="inlineStr">
+      <c r="V3" t="inlineStr">
         <is>
           <t>101</t>
         </is>
       </c>
-      <c r="N3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="O3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="P3" t="inlineStr">
+      <c r="W3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="X3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Y3" t="inlineStr">
         <is>
           <t>51</t>
         </is>
       </c>
-      <c r="Q3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="S3" t="inlineStr">
+      <c r="Z3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB3" t="inlineStr">
         <is>
           <t>31-March-2026</t>
-        </is>
-      </c>
-      <c r="T3" t="inlineStr">
-        <is>
-          <t>esignet</t>
-        </is>
-      </c>
-      <c r="U3" t="inlineStr">
-        <is>
-          <t>375</t>
-        </is>
-      </c>
-      <c r="V3" t="inlineStr">
-        <is>
-          <t>221</t>
-        </is>
-      </c>
-      <c r="W3" t="inlineStr">
-        <is>
-          <t>62</t>
-        </is>
-      </c>
-      <c r="X3" t="inlineStr">
-        <is>
-          <t>65</t>
-        </is>
-      </c>
-      <c r="Y3" t="inlineStr">
-        <is>
-          <t>27</t>
-        </is>
-      </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>30-March-2026</t>
         </is>
       </c>
       <c r="AC3" t="inlineStr">
@@ -1127,127 +1127,127 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
+          <t>03-April-2026</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>idrepo</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>152</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>101</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>51</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
           <t>02-April-2026</t>
         </is>
       </c>
-      <c r="B4" t="inlineStr">
+      <c r="K4" t="inlineStr">
         <is>
           <t>idrepo</t>
         </is>
       </c>
-      <c r="C4" t="inlineStr">
+      <c r="L4" t="inlineStr">
         <is>
           <t>152</t>
         </is>
       </c>
-      <c r="D4" t="inlineStr">
+      <c r="M4" t="inlineStr">
         <is>
           <t>101</t>
         </is>
       </c>
-      <c r="E4" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F4" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="G4" t="inlineStr">
+      <c r="N4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P4" t="inlineStr">
         <is>
           <t>51</t>
         </is>
       </c>
-      <c r="H4" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="J4" t="inlineStr">
+      <c r="Q4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="S4" t="inlineStr">
         <is>
           <t>01-April-2026</t>
         </is>
       </c>
-      <c r="K4" t="inlineStr">
+      <c r="T4" t="inlineStr">
         <is>
           <t>injiverify</t>
         </is>
       </c>
-      <c r="L4" t="inlineStr">
+      <c r="U4" t="inlineStr">
         <is>
           <t>35</t>
         </is>
       </c>
-      <c r="M4" t="inlineStr">
+      <c r="V4" t="inlineStr">
         <is>
           <t>35</t>
         </is>
       </c>
-      <c r="N4" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="O4" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="P4" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="Q4" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="S4" t="inlineStr">
+      <c r="W4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="X4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Z4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB4" t="inlineStr">
         <is>
           <t>31-March-2026</t>
-        </is>
-      </c>
-      <c r="T4" t="inlineStr">
-        <is>
-          <t>idrepo</t>
-        </is>
-      </c>
-      <c r="U4" t="inlineStr">
-        <is>
-          <t>152</t>
-        </is>
-      </c>
-      <c r="V4" t="inlineStr">
-        <is>
-          <t>101</t>
-        </is>
-      </c>
-      <c r="W4" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="X4" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="Y4" t="inlineStr">
-        <is>
-          <t>51</t>
-        </is>
-      </c>
-      <c r="Z4" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB4" t="inlineStr">
-        <is>
-          <t>30-March-2026</t>
         </is>
       </c>
       <c r="AC4" t="inlineStr">
@@ -1289,127 +1289,127 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
+          <t>03-April-2026</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>injiverify</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>53</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>53</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
           <t>02-April-2026</t>
         </is>
       </c>
-      <c r="B5" t="inlineStr">
+      <c r="K5" t="inlineStr">
         <is>
           <t>injiverify</t>
         </is>
       </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>35</t>
-        </is>
-      </c>
-      <c r="D5" t="inlineStr">
-        <is>
-          <t>35</t>
-        </is>
-      </c>
-      <c r="E5" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F5" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="G5" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H5" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="J5" t="inlineStr">
+      <c r="L5" t="inlineStr">
+        <is>
+          <t>53</t>
+        </is>
+      </c>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>53</t>
+        </is>
+      </c>
+      <c r="N5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Q5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="S5" t="inlineStr">
         <is>
           <t>01-April-2026</t>
         </is>
       </c>
-      <c r="K5" t="inlineStr">
+      <c r="T5" t="inlineStr">
         <is>
           <t>mimoto</t>
         </is>
       </c>
-      <c r="L5" t="inlineStr">
+      <c r="U5" t="inlineStr">
         <is>
           <t>79</t>
         </is>
       </c>
-      <c r="M5" t="inlineStr">
+      <c r="V5" t="inlineStr">
         <is>
           <t>59</t>
         </is>
       </c>
-      <c r="N5" t="inlineStr">
+      <c r="W5" t="inlineStr">
         <is>
           <t>4</t>
         </is>
       </c>
-      <c r="O5" t="inlineStr">
+      <c r="X5" t="inlineStr">
         <is>
           <t>4</t>
         </is>
       </c>
-      <c r="P5" t="inlineStr">
+      <c r="Y5" t="inlineStr">
         <is>
           <t>10</t>
         </is>
       </c>
-      <c r="Q5" t="inlineStr">
+      <c r="Z5" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="S5" t="inlineStr">
+      <c r="AB5" t="inlineStr">
         <is>
           <t>31-March-2026</t>
-        </is>
-      </c>
-      <c r="T5" t="inlineStr">
-        <is>
-          <t>injiverify</t>
-        </is>
-      </c>
-      <c r="U5" t="inlineStr">
-        <is>
-          <t>35</t>
-        </is>
-      </c>
-      <c r="V5" t="inlineStr">
-        <is>
-          <t>35</t>
-        </is>
-      </c>
-      <c r="W5" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="X5" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="Y5" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="Z5" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB5" t="inlineStr">
-        <is>
-          <t>30-March-2026</t>
         </is>
       </c>
       <c r="AC5" t="inlineStr">
@@ -1451,122 +1451,122 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
+          <t>03-April-2026</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>mimoto</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>79</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>47</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
           <t>02-April-2026</t>
         </is>
       </c>
-      <c r="B6" t="inlineStr">
+      <c r="K6" t="inlineStr">
         <is>
           <t>mimoto</t>
         </is>
       </c>
-      <c r="C6" t="inlineStr">
+      <c r="L6" t="inlineStr">
         <is>
           <t>79</t>
         </is>
       </c>
-      <c r="D6" t="inlineStr">
+      <c r="M6" t="inlineStr">
         <is>
           <t>58</t>
         </is>
       </c>
-      <c r="E6" t="inlineStr">
+      <c r="N6" t="inlineStr">
         <is>
           <t>4</t>
         </is>
       </c>
-      <c r="F6" t="inlineStr">
+      <c r="O6" t="inlineStr">
         <is>
           <t>5</t>
         </is>
       </c>
-      <c r="G6" t="inlineStr">
+      <c r="P6" t="inlineStr">
         <is>
           <t>10</t>
         </is>
       </c>
-      <c r="H6" t="inlineStr">
+      <c r="Q6" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="J6" t="inlineStr">
+      <c r="S6" t="inlineStr">
         <is>
           <t>01-April-2026</t>
         </is>
       </c>
-      <c r="K6" t="inlineStr">
+      <c r="T6" t="inlineStr">
         <is>
           <t>prereg</t>
         </is>
       </c>
-      <c r="L6" t="inlineStr">
+      <c r="U6" t="inlineStr">
         <is>
           <t>104</t>
         </is>
       </c>
-      <c r="M6" t="inlineStr">
+      <c r="V6" t="inlineStr">
         <is>
           <t>3</t>
         </is>
       </c>
-      <c r="N6" t="inlineStr">
+      <c r="W6" t="inlineStr">
         <is>
           <t>70</t>
         </is>
       </c>
-      <c r="O6" t="inlineStr">
+      <c r="X6" t="inlineStr">
         <is>
           <t>30</t>
         </is>
       </c>
-      <c r="P6" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="Q6" t="inlineStr">
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Z6" t="inlineStr">
         <is>
           <t>1</t>
-        </is>
-      </c>
-      <c r="S6" t="inlineStr">
-        <is>
-          <t>31-March-2026</t>
-        </is>
-      </c>
-      <c r="T6" t="inlineStr">
-        <is>
-          <t>mimoto</t>
-        </is>
-      </c>
-      <c r="U6" t="inlineStr">
-        <is>
-          <t>79</t>
-        </is>
-      </c>
-      <c r="V6" t="inlineStr">
-        <is>
-          <t>57</t>
-        </is>
-      </c>
-      <c r="W6" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="X6" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="Y6" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="Z6" t="inlineStr">
-        <is>
-          <t>2</t>
         </is>
       </c>
       <c r="AB6" t="n">
@@ -1597,114 +1597,114 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
+          <t>03-April-2026</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>prereg</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>104</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>70</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
           <t>02-April-2026</t>
         </is>
       </c>
-      <c r="B7" t="inlineStr">
+      <c r="K7" t="inlineStr">
         <is>
           <t>prereg</t>
         </is>
       </c>
-      <c r="C7" t="inlineStr">
+      <c r="L7" t="inlineStr">
         <is>
           <t>104</t>
         </is>
       </c>
-      <c r="D7" t="inlineStr">
+      <c r="M7" t="inlineStr">
         <is>
           <t>3</t>
         </is>
       </c>
-      <c r="E7" t="inlineStr">
+      <c r="N7" t="inlineStr">
         <is>
           <t>70</t>
         </is>
       </c>
-      <c r="F7" t="inlineStr">
+      <c r="O7" t="inlineStr">
         <is>
           <t>30</t>
         </is>
       </c>
-      <c r="G7" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H7" t="inlineStr">
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Q7" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="J7" t="inlineStr">
+      <c r="S7" t="inlineStr">
         <is>
           <t>01-April-2026</t>
         </is>
       </c>
-      <c r="K7" t="inlineStr">
+      <c r="T7" t="inlineStr">
         <is>
           <t>residentui</t>
         </is>
       </c>
-      <c r="L7" t="inlineStr">
+      <c r="U7" t="inlineStr">
         <is>
           <t>33</t>
         </is>
       </c>
-      <c r="M7" t="inlineStr">
+      <c r="V7" t="inlineStr">
         <is>
           <t>12</t>
         </is>
       </c>
-      <c r="N7" t="inlineStr">
+      <c r="W7" t="inlineStr">
         <is>
           <t>5</t>
         </is>
       </c>
-      <c r="O7" t="inlineStr">
+      <c r="X7" t="inlineStr">
         <is>
           <t>16</t>
         </is>
       </c>
-      <c r="P7" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="Q7" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="S7" t="inlineStr">
-        <is>
-          <t>31-March-2026</t>
-        </is>
-      </c>
-      <c r="T7" t="inlineStr">
-        <is>
-          <t>prereg</t>
-        </is>
-      </c>
-      <c r="U7" t="inlineStr">
-        <is>
-          <t>104</t>
-        </is>
-      </c>
-      <c r="V7" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="W7" t="inlineStr">
-        <is>
-          <t>70</t>
-        </is>
-      </c>
-      <c r="X7" t="inlineStr">
-        <is>
-          <t>30</t>
-        </is>
-      </c>
       <c r="Y7" t="inlineStr">
         <is>
           <t>0</t>
@@ -1712,7 +1712,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="AB7" t="n">
@@ -1743,107 +1743,107 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
+          <t>03-April-2026</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>residentui</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>33</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
           <t>02-April-2026</t>
         </is>
       </c>
-      <c r="B8" t="inlineStr">
+      <c r="K8" t="inlineStr">
         <is>
           <t>residentui</t>
         </is>
       </c>
-      <c r="C8" t="inlineStr">
+      <c r="L8" t="inlineStr">
         <is>
           <t>33</t>
         </is>
       </c>
-      <c r="D8" t="inlineStr">
+      <c r="M8" t="inlineStr">
         <is>
           <t>12</t>
         </is>
       </c>
-      <c r="E8" t="inlineStr">
+      <c r="N8" t="inlineStr">
         <is>
           <t>5</t>
         </is>
       </c>
-      <c r="F8" t="inlineStr">
+      <c r="O8" t="inlineStr">
         <is>
           <t>16</t>
         </is>
       </c>
-      <c r="G8" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H8" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="J8" t="n">
-        <v/>
-      </c>
-      <c r="K8" t="n">
-        <v/>
-      </c>
-      <c r="L8" t="n">
-        <v/>
-      </c>
-      <c r="M8" t="n">
-        <v/>
-      </c>
-      <c r="N8" t="n">
-        <v/>
-      </c>
-      <c r="O8" t="n">
-        <v/>
-      </c>
-      <c r="P8" t="n">
-        <v/>
-      </c>
-      <c r="Q8" t="n">
-        <v/>
-      </c>
-      <c r="S8" t="inlineStr">
-        <is>
-          <t>31-March-2026</t>
-        </is>
-      </c>
-      <c r="T8" t="inlineStr">
-        <is>
-          <t>residentui</t>
-        </is>
-      </c>
-      <c r="U8" t="inlineStr">
-        <is>
-          <t>33</t>
-        </is>
-      </c>
-      <c r="V8" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="W8" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="X8" t="inlineStr">
-        <is>
-          <t>18</t>
-        </is>
-      </c>
-      <c r="Y8" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="Z8" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Q8" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="S8" t="n">
+        <v/>
+      </c>
+      <c r="T8" t="n">
+        <v/>
+      </c>
+      <c r="U8" t="n">
+        <v/>
+      </c>
+      <c r="V8" t="n">
+        <v/>
+      </c>
+      <c r="W8" t="n">
+        <v/>
+      </c>
+      <c r="X8" t="n">
+        <v/>
+      </c>
+      <c r="Y8" t="n">
+        <v/>
+      </c>
+      <c r="Z8" t="n">
+        <v/>
       </c>
       <c r="AB8" t="n">
         <v/>

--- a/minio-report-tracker/xlxs/collab.xlsx
+++ b/minio-report-tracker/xlxs/collab.xlsx
@@ -598,7 +598,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AI8"/>
+  <dimension ref="A1:Q8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="15" customWidth="1" min="1" max="1"/>
@@ -614,28 +614,10 @@
     <col width="12" customWidth="1" min="11" max="11"/>
     <col width="5" customWidth="1" min="12" max="12"/>
     <col width="5" customWidth="1" min="13" max="13"/>
-    <col width="4" customWidth="1" min="14" max="14"/>
-    <col width="4" customWidth="1" min="15" max="15"/>
-    <col width="4" customWidth="1" min="16" max="16"/>
-    <col width="4" customWidth="1" min="17" max="17"/>
-    <col width="2" customWidth="1" min="18" max="18"/>
-    <col width="15" customWidth="1" min="19" max="19"/>
-    <col width="12" customWidth="1" min="20" max="20"/>
-    <col width="5" customWidth="1" min="21" max="21"/>
-    <col width="5" customWidth="1" min="22" max="22"/>
-    <col width="5" customWidth="1" min="23" max="23"/>
-    <col width="5" customWidth="1" min="24" max="24"/>
-    <col width="5" customWidth="1" min="25" max="25"/>
-    <col width="5" customWidth="1" min="26" max="26"/>
-    <col width="2" customWidth="1" min="27" max="27"/>
-    <col width="15" customWidth="1" min="28" max="28"/>
-    <col width="12" customWidth="1" min="29" max="29"/>
-    <col width="5" customWidth="1" min="30" max="30"/>
-    <col width="5" customWidth="1" min="31" max="31"/>
-    <col width="5" customWidth="1" min="32" max="32"/>
-    <col width="5" customWidth="1" min="33" max="33"/>
-    <col width="5" customWidth="1" min="34" max="34"/>
-    <col width="5" customWidth="1" min="35" max="35"/>
+    <col width="5" customWidth="1" min="14" max="14"/>
+    <col width="5" customWidth="1" min="15" max="15"/>
+    <col width="5" customWidth="1" min="16" max="16"/>
+    <col width="5" customWidth="1" min="17" max="17"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -719,244 +701,84 @@
           <t>KI</t>
         </is>
       </c>
-      <c r="S1" s="1" t="inlineStr">
-        <is>
-          <t>Date</t>
-        </is>
-      </c>
-      <c r="T1" s="1" t="inlineStr">
-        <is>
-          <t>Module</t>
-        </is>
-      </c>
-      <c r="U1" s="1" t="inlineStr">
-        <is>
-          <t>T</t>
-        </is>
-      </c>
-      <c r="V1" s="1" t="inlineStr">
-        <is>
-          <t>P</t>
-        </is>
-      </c>
-      <c r="W1" s="1" t="inlineStr">
-        <is>
-          <t>S</t>
-        </is>
-      </c>
-      <c r="X1" s="1" t="inlineStr">
-        <is>
-          <t>F</t>
-        </is>
-      </c>
-      <c r="Y1" s="1" t="inlineStr">
-        <is>
-          <t>I</t>
-        </is>
-      </c>
-      <c r="Z1" s="1" t="inlineStr">
-        <is>
-          <t>KI</t>
-        </is>
-      </c>
-      <c r="AB1" s="1" t="inlineStr">
-        <is>
-          <t>Date</t>
-        </is>
-      </c>
-      <c r="AC1" s="1" t="inlineStr">
-        <is>
-          <t>Module</t>
-        </is>
-      </c>
-      <c r="AD1" s="1" t="inlineStr">
-        <is>
-          <t>T</t>
-        </is>
-      </c>
-      <c r="AE1" s="1" t="inlineStr">
-        <is>
-          <t>P</t>
-        </is>
-      </c>
-      <c r="AF1" s="1" t="inlineStr">
-        <is>
-          <t>S</t>
-        </is>
-      </c>
-      <c r="AG1" s="1" t="inlineStr">
-        <is>
-          <t>F</t>
-        </is>
-      </c>
-      <c r="AH1" s="1" t="inlineStr">
-        <is>
-          <t>I</t>
-        </is>
-      </c>
-      <c r="AI1" s="1" t="inlineStr">
-        <is>
-          <t>KI</t>
-        </is>
-      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
+          <t>06-April-2026</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>auth</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>254</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>184</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>64</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
           <t>03-April-2026</t>
         </is>
       </c>
-      <c r="B2" t="inlineStr">
-        <is>
-          <t>auth</t>
-        </is>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>254</t>
-        </is>
-      </c>
-      <c r="D2" t="inlineStr">
-        <is>
-          <t>140</t>
-        </is>
-      </c>
-      <c r="E2" t="inlineStr">
-        <is>
-          <t>72</t>
-        </is>
-      </c>
-      <c r="F2" t="inlineStr">
-        <is>
-          <t>42</t>
-        </is>
-      </c>
-      <c r="G2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="J2" t="inlineStr">
-        <is>
-          <t>02-April-2026</t>
-        </is>
-      </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>auth</t>
+          <t>esignet</t>
         </is>
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>254</t>
+          <t>375</t>
         </is>
       </c>
       <c r="M2" t="inlineStr">
         <is>
-          <t>140</t>
+          <t>267</t>
         </is>
       </c>
       <c r="N2" t="inlineStr">
         <is>
-          <t>72</t>
+          <t>32</t>
         </is>
       </c>
       <c r="O2" t="inlineStr">
         <is>
-          <t>42</t>
+          <t>49</t>
         </is>
       </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>27</t>
         </is>
       </c>
       <c r="Q2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="S2" t="inlineStr">
-        <is>
-          <t>01-April-2026</t>
-        </is>
-      </c>
-      <c r="T2" t="inlineStr">
-        <is>
-          <t>auth</t>
-        </is>
-      </c>
-      <c r="U2" t="inlineStr">
-        <is>
-          <t>254</t>
-        </is>
-      </c>
-      <c r="V2" t="inlineStr">
-        <is>
-          <t>142</t>
-        </is>
-      </c>
-      <c r="W2" t="inlineStr">
-        <is>
-          <t>72</t>
-        </is>
-      </c>
-      <c r="X2" t="inlineStr">
-        <is>
-          <t>40</t>
-        </is>
-      </c>
-      <c r="Y2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>31-March-2026</t>
-        </is>
-      </c>
-      <c r="AC2" t="inlineStr">
-        <is>
-          <t>esignet</t>
-        </is>
-      </c>
-      <c r="AD2" t="inlineStr">
-        <is>
-          <t>375</t>
-        </is>
-      </c>
-      <c r="AE2" t="inlineStr">
-        <is>
-          <t>221</t>
-        </is>
-      </c>
-      <c r="AF2" t="inlineStr">
-        <is>
-          <t>62</t>
-        </is>
-      </c>
-      <c r="AG2" t="inlineStr">
-        <is>
-          <t>65</t>
-        </is>
-      </c>
-      <c r="AH2" t="inlineStr">
-        <is>
-          <t>27</t>
-        </is>
-      </c>
-      <c r="AI2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
@@ -965,160 +787,80 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
+          <t>06-April-2026</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>esignet</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>375</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>274</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>28</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>46</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>27</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
           <t>03-April-2026</t>
         </is>
       </c>
-      <c r="B3" t="inlineStr">
-        <is>
-          <t>esignet</t>
-        </is>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>375</t>
-        </is>
-      </c>
-      <c r="D3" t="inlineStr">
-        <is>
-          <t>267</t>
-        </is>
-      </c>
-      <c r="E3" t="inlineStr">
-        <is>
-          <t>32</t>
-        </is>
-      </c>
-      <c r="F3" t="inlineStr">
-        <is>
-          <t>49</t>
-        </is>
-      </c>
-      <c r="G3" t="inlineStr">
-        <is>
-          <t>27</t>
-        </is>
-      </c>
-      <c r="H3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="J3" t="inlineStr">
-        <is>
-          <t>02-April-2026</t>
-        </is>
-      </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>esignet</t>
+          <t>injiverify</t>
         </is>
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>375</t>
+          <t>53</t>
         </is>
       </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>247</t>
+          <t>53</t>
         </is>
       </c>
       <c r="N3" t="inlineStr">
         <is>
-          <t>46</t>
+          <t>0</t>
         </is>
       </c>
       <c r="O3" t="inlineStr">
         <is>
-          <t>55</t>
+          <t>0</t>
         </is>
       </c>
       <c r="P3" t="inlineStr">
         <is>
-          <t>27</t>
+          <t>0</t>
         </is>
       </c>
       <c r="Q3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="S3" t="inlineStr">
-        <is>
-          <t>01-April-2026</t>
-        </is>
-      </c>
-      <c r="T3" t="inlineStr">
-        <is>
-          <t>idrepo</t>
-        </is>
-      </c>
-      <c r="U3" t="inlineStr">
-        <is>
-          <t>152</t>
-        </is>
-      </c>
-      <c r="V3" t="inlineStr">
-        <is>
-          <t>101</t>
-        </is>
-      </c>
-      <c r="W3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="X3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="Y3" t="inlineStr">
-        <is>
-          <t>51</t>
-        </is>
-      </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>31-March-2026</t>
-        </is>
-      </c>
-      <c r="AC3" t="inlineStr">
-        <is>
-          <t>injiverify</t>
-        </is>
-      </c>
-      <c r="AD3" t="inlineStr">
-        <is>
-          <t>35</t>
-        </is>
-      </c>
-      <c r="AE3" t="inlineStr">
-        <is>
-          <t>35</t>
-        </is>
-      </c>
-      <c r="AF3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AG3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AH3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AI3" t="inlineStr">
         <is>
           <t>0</t>
         </is>
@@ -1127,160 +869,80 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
+          <t>06-April-2026</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>idrepo</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>152</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>101</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>51</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
           <t>03-April-2026</t>
         </is>
       </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>idrepo</t>
-        </is>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>152</t>
-        </is>
-      </c>
-      <c r="D4" t="inlineStr">
-        <is>
-          <t>101</t>
-        </is>
-      </c>
-      <c r="E4" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F4" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="G4" t="inlineStr">
-        <is>
-          <t>51</t>
-        </is>
-      </c>
-      <c r="H4" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="J4" t="inlineStr">
-        <is>
-          <t>02-April-2026</t>
-        </is>
-      </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>idrepo</t>
+          <t>prereg</t>
         </is>
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>152</t>
+          <t>104</t>
         </is>
       </c>
       <c r="M4" t="inlineStr">
         <is>
-          <t>101</t>
+          <t>3</t>
         </is>
       </c>
       <c r="N4" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>70</t>
         </is>
       </c>
       <c r="O4" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>30</t>
         </is>
       </c>
       <c r="P4" t="inlineStr">
         <is>
-          <t>51</t>
+          <t>0</t>
         </is>
       </c>
       <c r="Q4" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="S4" t="inlineStr">
-        <is>
-          <t>01-April-2026</t>
-        </is>
-      </c>
-      <c r="T4" t="inlineStr">
-        <is>
-          <t>injiverify</t>
-        </is>
-      </c>
-      <c r="U4" t="inlineStr">
-        <is>
-          <t>35</t>
-        </is>
-      </c>
-      <c r="V4" t="inlineStr">
-        <is>
-          <t>35</t>
-        </is>
-      </c>
-      <c r="W4" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="X4" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="Y4" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="Z4" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB4" t="inlineStr">
-        <is>
-          <t>31-March-2026</t>
-        </is>
-      </c>
-      <c r="AC4" t="inlineStr">
-        <is>
-          <t>prereg</t>
-        </is>
-      </c>
-      <c r="AD4" t="inlineStr">
-        <is>
-          <t>104</t>
-        </is>
-      </c>
-      <c r="AE4" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="AF4" t="inlineStr">
-        <is>
-          <t>70</t>
-        </is>
-      </c>
-      <c r="AG4" t="inlineStr">
-        <is>
-          <t>30</t>
-        </is>
-      </c>
-      <c r="AH4" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AI4" t="inlineStr">
         <is>
           <t>1</t>
         </is>
@@ -1289,72 +951,72 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
+          <t>06-April-2026</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>injiverify</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>53</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>53</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
           <t>03-April-2026</t>
         </is>
       </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>injiverify</t>
-        </is>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>53</t>
-        </is>
-      </c>
-      <c r="D5" t="inlineStr">
-        <is>
-          <t>53</t>
-        </is>
-      </c>
-      <c r="E5" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F5" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="G5" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H5" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="J5" t="inlineStr">
-        <is>
-          <t>02-April-2026</t>
-        </is>
-      </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>injiverify</t>
+          <t>residentui</t>
         </is>
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>53</t>
+          <t>33</t>
         </is>
       </c>
       <c r="M5" t="inlineStr">
         <is>
-          <t>53</t>
+          <t>12</t>
         </is>
       </c>
       <c r="N5" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>5</t>
         </is>
       </c>
       <c r="O5" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>16</t>
         </is>
       </c>
       <c r="P5" t="inlineStr">
@@ -1363,86 +1025,6 @@
         </is>
       </c>
       <c r="Q5" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="S5" t="inlineStr">
-        <is>
-          <t>01-April-2026</t>
-        </is>
-      </c>
-      <c r="T5" t="inlineStr">
-        <is>
-          <t>mimoto</t>
-        </is>
-      </c>
-      <c r="U5" t="inlineStr">
-        <is>
-          <t>79</t>
-        </is>
-      </c>
-      <c r="V5" t="inlineStr">
-        <is>
-          <t>59</t>
-        </is>
-      </c>
-      <c r="W5" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="X5" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="Y5" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="Z5" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="AB5" t="inlineStr">
-        <is>
-          <t>31-March-2026</t>
-        </is>
-      </c>
-      <c r="AC5" t="inlineStr">
-        <is>
-          <t>residentui</t>
-        </is>
-      </c>
-      <c r="AD5" t="inlineStr">
-        <is>
-          <t>33</t>
-        </is>
-      </c>
-      <c r="AE5" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="AF5" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="AG5" t="inlineStr">
-        <is>
-          <t>18</t>
-        </is>
-      </c>
-      <c r="AH5" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AI5" t="inlineStr">
         <is>
           <t>0</t>
         </is>
@@ -1451,7 +1033,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>03-April-2026</t>
+          <t>06-April-2026</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -1466,17 +1048,17 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>47</t>
+          <t>66</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>0</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>1</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
@@ -1489,115 +1071,35 @@
           <t>2</t>
         </is>
       </c>
-      <c r="J6" t="inlineStr">
-        <is>
-          <t>02-April-2026</t>
-        </is>
-      </c>
-      <c r="K6" t="inlineStr">
-        <is>
-          <t>mimoto</t>
-        </is>
-      </c>
-      <c r="L6" t="inlineStr">
-        <is>
-          <t>79</t>
-        </is>
-      </c>
-      <c r="M6" t="inlineStr">
-        <is>
-          <t>58</t>
-        </is>
-      </c>
-      <c r="N6" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="O6" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="P6" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="Q6" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="S6" t="inlineStr">
-        <is>
-          <t>01-April-2026</t>
-        </is>
-      </c>
-      <c r="T6" t="inlineStr">
-        <is>
-          <t>prereg</t>
-        </is>
-      </c>
-      <c r="U6" t="inlineStr">
-        <is>
-          <t>104</t>
-        </is>
-      </c>
-      <c r="V6" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="W6" t="inlineStr">
-        <is>
-          <t>70</t>
-        </is>
-      </c>
-      <c r="X6" t="inlineStr">
-        <is>
-          <t>30</t>
-        </is>
-      </c>
-      <c r="Y6" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="Z6" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="AB6" t="n">
-        <v/>
-      </c>
-      <c r="AC6" t="n">
-        <v/>
-      </c>
-      <c r="AD6" t="n">
-        <v/>
-      </c>
-      <c r="AE6" t="n">
-        <v/>
-      </c>
-      <c r="AF6" t="n">
-        <v/>
-      </c>
-      <c r="AG6" t="n">
-        <v/>
-      </c>
-      <c r="AH6" t="n">
-        <v/>
-      </c>
-      <c r="AI6" t="n">
+      <c r="J6" t="n">
+        <v/>
+      </c>
+      <c r="K6" t="n">
+        <v/>
+      </c>
+      <c r="L6" t="n">
+        <v/>
+      </c>
+      <c r="M6" t="n">
+        <v/>
+      </c>
+      <c r="N6" t="n">
+        <v/>
+      </c>
+      <c r="O6" t="n">
+        <v/>
+      </c>
+      <c r="P6" t="n">
+        <v/>
+      </c>
+      <c r="Q6" t="n">
         <v/>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>03-April-2026</t>
+          <t>06-April-2026</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -1635,115 +1137,35 @@
           <t>1</t>
         </is>
       </c>
-      <c r="J7" t="inlineStr">
-        <is>
-          <t>02-April-2026</t>
-        </is>
-      </c>
-      <c r="K7" t="inlineStr">
-        <is>
-          <t>prereg</t>
-        </is>
-      </c>
-      <c r="L7" t="inlineStr">
-        <is>
-          <t>104</t>
-        </is>
-      </c>
-      <c r="M7" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="N7" t="inlineStr">
-        <is>
-          <t>70</t>
-        </is>
-      </c>
-      <c r="O7" t="inlineStr">
-        <is>
-          <t>30</t>
-        </is>
-      </c>
-      <c r="P7" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="Q7" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="S7" t="inlineStr">
-        <is>
-          <t>01-April-2026</t>
-        </is>
-      </c>
-      <c r="T7" t="inlineStr">
-        <is>
-          <t>residentui</t>
-        </is>
-      </c>
-      <c r="U7" t="inlineStr">
-        <is>
-          <t>33</t>
-        </is>
-      </c>
-      <c r="V7" t="inlineStr">
-        <is>
-          <t>12</t>
-        </is>
-      </c>
-      <c r="W7" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="X7" t="inlineStr">
-        <is>
-          <t>16</t>
-        </is>
-      </c>
-      <c r="Y7" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="Z7" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB7" t="n">
-        <v/>
-      </c>
-      <c r="AC7" t="n">
-        <v/>
-      </c>
-      <c r="AD7" t="n">
-        <v/>
-      </c>
-      <c r="AE7" t="n">
-        <v/>
-      </c>
-      <c r="AF7" t="n">
-        <v/>
-      </c>
-      <c r="AG7" t="n">
-        <v/>
-      </c>
-      <c r="AH7" t="n">
-        <v/>
-      </c>
-      <c r="AI7" t="n">
+      <c r="J7" t="n">
+        <v/>
+      </c>
+      <c r="K7" t="n">
+        <v/>
+      </c>
+      <c r="L7" t="n">
+        <v/>
+      </c>
+      <c r="M7" t="n">
+        <v/>
+      </c>
+      <c r="N7" t="n">
+        <v/>
+      </c>
+      <c r="O7" t="n">
+        <v/>
+      </c>
+      <c r="P7" t="n">
+        <v/>
+      </c>
+      <c r="Q7" t="n">
         <v/>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>03-April-2026</t>
+          <t>06-April-2026</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1781,92 +1203,28 @@
           <t>0</t>
         </is>
       </c>
-      <c r="J8" t="inlineStr">
-        <is>
-          <t>02-April-2026</t>
-        </is>
-      </c>
-      <c r="K8" t="inlineStr">
-        <is>
-          <t>residentui</t>
-        </is>
-      </c>
-      <c r="L8" t="inlineStr">
-        <is>
-          <t>33</t>
-        </is>
-      </c>
-      <c r="M8" t="inlineStr">
-        <is>
-          <t>12</t>
-        </is>
-      </c>
-      <c r="N8" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="O8" t="inlineStr">
-        <is>
-          <t>16</t>
-        </is>
-      </c>
-      <c r="P8" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="Q8" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="S8" t="n">
-        <v/>
-      </c>
-      <c r="T8" t="n">
-        <v/>
-      </c>
-      <c r="U8" t="n">
-        <v/>
-      </c>
-      <c r="V8" t="n">
-        <v/>
-      </c>
-      <c r="W8" t="n">
-        <v/>
-      </c>
-      <c r="X8" t="n">
-        <v/>
-      </c>
-      <c r="Y8" t="n">
-        <v/>
-      </c>
-      <c r="Z8" t="n">
-        <v/>
-      </c>
-      <c r="AB8" t="n">
-        <v/>
-      </c>
-      <c r="AC8" t="n">
-        <v/>
-      </c>
-      <c r="AD8" t="n">
-        <v/>
-      </c>
-      <c r="AE8" t="n">
-        <v/>
-      </c>
-      <c r="AF8" t="n">
-        <v/>
-      </c>
-      <c r="AG8" t="n">
-        <v/>
-      </c>
-      <c r="AH8" t="n">
-        <v/>
-      </c>
-      <c r="AI8" t="n">
+      <c r="J8" t="n">
+        <v/>
+      </c>
+      <c r="K8" t="n">
+        <v/>
+      </c>
+      <c r="L8" t="n">
+        <v/>
+      </c>
+      <c r="M8" t="n">
+        <v/>
+      </c>
+      <c r="N8" t="n">
+        <v/>
+      </c>
+      <c r="O8" t="n">
+        <v/>
+      </c>
+      <c r="P8" t="n">
+        <v/>
+      </c>
+      <c r="Q8" t="n">
         <v/>
       </c>
     </row>

--- a/minio-report-tracker/xlxs/collab.xlsx
+++ b/minio-report-tracker/xlxs/collab.xlsx
@@ -614,10 +614,10 @@
     <col width="12" customWidth="1" min="11" max="11"/>
     <col width="5" customWidth="1" min="12" max="12"/>
     <col width="5" customWidth="1" min="13" max="13"/>
-    <col width="5" customWidth="1" min="14" max="14"/>
-    <col width="5" customWidth="1" min="15" max="15"/>
-    <col width="5" customWidth="1" min="16" max="16"/>
-    <col width="5" customWidth="1" min="17" max="17"/>
+    <col width="4" customWidth="1" min="14" max="14"/>
+    <col width="4" customWidth="1" min="15" max="15"/>
+    <col width="4" customWidth="1" min="16" max="16"/>
+    <col width="4" customWidth="1" min="17" max="17"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -705,77 +705,77 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
+          <t>07-April-2026</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>auth</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>254</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>184</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>64</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
           <t>06-April-2026</t>
         </is>
       </c>
-      <c r="B2" t="inlineStr">
+      <c r="K2" t="inlineStr">
         <is>
           <t>auth</t>
         </is>
       </c>
-      <c r="C2" t="inlineStr">
+      <c r="L2" t="inlineStr">
         <is>
           <t>254</t>
         </is>
       </c>
-      <c r="D2" t="inlineStr">
+      <c r="M2" t="inlineStr">
         <is>
           <t>184</t>
         </is>
       </c>
-      <c r="E2" t="inlineStr">
+      <c r="N2" t="inlineStr">
         <is>
           <t>6</t>
         </is>
       </c>
-      <c r="F2" t="inlineStr">
+      <c r="O2" t="inlineStr">
         <is>
           <t>64</t>
         </is>
       </c>
-      <c r="G2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="J2" t="inlineStr">
-        <is>
-          <t>03-April-2026</t>
-        </is>
-      </c>
-      <c r="K2" t="inlineStr">
-        <is>
-          <t>esignet</t>
-        </is>
-      </c>
-      <c r="L2" t="inlineStr">
-        <is>
-          <t>375</t>
-        </is>
-      </c>
-      <c r="M2" t="inlineStr">
-        <is>
-          <t>267</t>
-        </is>
-      </c>
-      <c r="N2" t="inlineStr">
-        <is>
-          <t>32</t>
-        </is>
-      </c>
-      <c r="O2" t="inlineStr">
-        <is>
-          <t>49</t>
-        </is>
-      </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>27</t>
+          <t>0</t>
         </is>
       </c>
       <c r="Q2" t="inlineStr">
@@ -787,77 +787,77 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
+          <t>07-April-2026</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>esignet</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>375</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>285</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>21</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>42</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>27</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
           <t>06-April-2026</t>
         </is>
       </c>
-      <c r="B3" t="inlineStr">
+      <c r="K3" t="inlineStr">
         <is>
           <t>esignet</t>
         </is>
       </c>
-      <c r="C3" t="inlineStr">
+      <c r="L3" t="inlineStr">
         <is>
           <t>375</t>
         </is>
       </c>
-      <c r="D3" t="inlineStr">
+      <c r="M3" t="inlineStr">
         <is>
           <t>274</t>
         </is>
       </c>
-      <c r="E3" t="inlineStr">
+      <c r="N3" t="inlineStr">
         <is>
           <t>28</t>
         </is>
       </c>
-      <c r="F3" t="inlineStr">
+      <c r="O3" t="inlineStr">
         <is>
           <t>46</t>
         </is>
       </c>
-      <c r="G3" t="inlineStr">
+      <c r="P3" t="inlineStr">
         <is>
           <t>27</t>
-        </is>
-      </c>
-      <c r="H3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="J3" t="inlineStr">
-        <is>
-          <t>03-April-2026</t>
-        </is>
-      </c>
-      <c r="K3" t="inlineStr">
-        <is>
-          <t>injiverify</t>
-        </is>
-      </c>
-      <c r="L3" t="inlineStr">
-        <is>
-          <t>53</t>
-        </is>
-      </c>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>53</t>
-        </is>
-      </c>
-      <c r="N3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="O3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="P3" t="inlineStr">
-        <is>
-          <t>0</t>
         </is>
       </c>
       <c r="Q3" t="inlineStr">
@@ -869,154 +869,154 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
+          <t>07-April-2026</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>idrepo</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>152</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>101</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>51</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
           <t>06-April-2026</t>
         </is>
       </c>
-      <c r="B4" t="inlineStr">
+      <c r="K4" t="inlineStr">
         <is>
           <t>idrepo</t>
         </is>
       </c>
-      <c r="C4" t="inlineStr">
+      <c r="L4" t="inlineStr">
         <is>
           <t>152</t>
         </is>
       </c>
-      <c r="D4" t="inlineStr">
+      <c r="M4" t="inlineStr">
         <is>
           <t>101</t>
         </is>
       </c>
-      <c r="E4" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F4" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="G4" t="inlineStr">
+      <c r="N4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P4" t="inlineStr">
         <is>
           <t>51</t>
         </is>
       </c>
-      <c r="H4" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="J4" t="inlineStr">
-        <is>
-          <t>03-April-2026</t>
-        </is>
-      </c>
-      <c r="K4" t="inlineStr">
-        <is>
-          <t>prereg</t>
-        </is>
-      </c>
-      <c r="L4" t="inlineStr">
-        <is>
-          <t>104</t>
-        </is>
-      </c>
-      <c r="M4" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="N4" t="inlineStr">
-        <is>
-          <t>70</t>
-        </is>
-      </c>
-      <c r="O4" t="inlineStr">
-        <is>
-          <t>30</t>
-        </is>
-      </c>
-      <c r="P4" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
       <c r="Q4" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
+          <t>07-April-2026</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>injiverify</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>53</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>23</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
           <t>06-April-2026</t>
         </is>
       </c>
-      <c r="B5" t="inlineStr">
+      <c r="K5" t="inlineStr">
         <is>
           <t>injiverify</t>
         </is>
       </c>
-      <c r="C5" t="inlineStr">
+      <c r="L5" t="inlineStr">
         <is>
           <t>53</t>
         </is>
       </c>
-      <c r="D5" t="inlineStr">
+      <c r="M5" t="inlineStr">
         <is>
           <t>53</t>
         </is>
       </c>
-      <c r="E5" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F5" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="G5" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H5" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="J5" t="inlineStr">
-        <is>
-          <t>03-April-2026</t>
-        </is>
-      </c>
-      <c r="K5" t="inlineStr">
-        <is>
-          <t>residentui</t>
-        </is>
-      </c>
-      <c r="L5" t="inlineStr">
-        <is>
-          <t>33</t>
-        </is>
-      </c>
-      <c r="M5" t="inlineStr">
-        <is>
-          <t>12</t>
-        </is>
-      </c>
       <c r="N5" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>0</t>
         </is>
       </c>
       <c r="O5" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>0</t>
         </is>
       </c>
       <c r="P5" t="inlineStr">
@@ -1033,199 +1033,247 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
+          <t>07-April-2026</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>mimoto</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>79</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>66</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
           <t>06-April-2026</t>
         </is>
       </c>
-      <c r="B6" t="inlineStr">
+      <c r="K6" t="inlineStr">
         <is>
           <t>mimoto</t>
         </is>
       </c>
-      <c r="C6" t="inlineStr">
+      <c r="L6" t="inlineStr">
         <is>
           <t>79</t>
         </is>
       </c>
-      <c r="D6" t="inlineStr">
+      <c r="M6" t="inlineStr">
         <is>
           <t>66</t>
         </is>
       </c>
-      <c r="E6" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F6" t="inlineStr">
+      <c r="N6" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O6" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="G6" t="inlineStr">
+      <c r="P6" t="inlineStr">
         <is>
           <t>10</t>
         </is>
       </c>
-      <c r="H6" t="inlineStr">
+      <c r="Q6" t="inlineStr">
         <is>
           <t>2</t>
         </is>
-      </c>
-      <c r="J6" t="n">
-        <v/>
-      </c>
-      <c r="K6" t="n">
-        <v/>
-      </c>
-      <c r="L6" t="n">
-        <v/>
-      </c>
-      <c r="M6" t="n">
-        <v/>
-      </c>
-      <c r="N6" t="n">
-        <v/>
-      </c>
-      <c r="O6" t="n">
-        <v/>
-      </c>
-      <c r="P6" t="n">
-        <v/>
-      </c>
-      <c r="Q6" t="n">
-        <v/>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
+          <t>07-April-2026</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>prereg</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>104</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>70</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
           <t>06-April-2026</t>
         </is>
       </c>
-      <c r="B7" t="inlineStr">
+      <c r="K7" t="inlineStr">
         <is>
           <t>prereg</t>
         </is>
       </c>
-      <c r="C7" t="inlineStr">
+      <c r="L7" t="inlineStr">
         <is>
           <t>104</t>
         </is>
       </c>
-      <c r="D7" t="inlineStr">
+      <c r="M7" t="inlineStr">
         <is>
           <t>3</t>
         </is>
       </c>
-      <c r="E7" t="inlineStr">
+      <c r="N7" t="inlineStr">
         <is>
           <t>70</t>
         </is>
       </c>
-      <c r="F7" t="inlineStr">
+      <c r="O7" t="inlineStr">
         <is>
           <t>30</t>
         </is>
       </c>
-      <c r="G7" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H7" t="inlineStr">
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Q7" t="inlineStr">
         <is>
           <t>1</t>
         </is>
-      </c>
-      <c r="J7" t="n">
-        <v/>
-      </c>
-      <c r="K7" t="n">
-        <v/>
-      </c>
-      <c r="L7" t="n">
-        <v/>
-      </c>
-      <c r="M7" t="n">
-        <v/>
-      </c>
-      <c r="N7" t="n">
-        <v/>
-      </c>
-      <c r="O7" t="n">
-        <v/>
-      </c>
-      <c r="P7" t="n">
-        <v/>
-      </c>
-      <c r="Q7" t="n">
-        <v/>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
+          <t>07-April-2026</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>residentui</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>33</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
           <t>06-April-2026</t>
         </is>
       </c>
-      <c r="B8" t="inlineStr">
+      <c r="K8" t="inlineStr">
         <is>
           <t>residentui</t>
         </is>
       </c>
-      <c r="C8" t="inlineStr">
+      <c r="L8" t="inlineStr">
         <is>
           <t>33</t>
         </is>
       </c>
-      <c r="D8" t="inlineStr">
+      <c r="M8" t="inlineStr">
         <is>
           <t>12</t>
         </is>
       </c>
-      <c r="E8" t="inlineStr">
+      <c r="N8" t="inlineStr">
         <is>
           <t>5</t>
         </is>
       </c>
-      <c r="F8" t="inlineStr">
+      <c r="O8" t="inlineStr">
         <is>
           <t>16</t>
         </is>
       </c>
-      <c r="G8" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H8" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="J8" t="n">
-        <v/>
-      </c>
-      <c r="K8" t="n">
-        <v/>
-      </c>
-      <c r="L8" t="n">
-        <v/>
-      </c>
-      <c r="M8" t="n">
-        <v/>
-      </c>
-      <c r="N8" t="n">
-        <v/>
-      </c>
-      <c r="O8" t="n">
-        <v/>
-      </c>
-      <c r="P8" t="n">
-        <v/>
-      </c>
-      <c r="Q8" t="n">
-        <v/>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Q8" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
     </row>
   </sheetData>

--- a/minio-report-tracker/xlxs/collab.xlsx
+++ b/minio-report-tracker/xlxs/collab.xlsx
@@ -598,7 +598,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q8"/>
+  <dimension ref="A1:Z8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="15" customWidth="1" min="1" max="1"/>
@@ -618,6 +618,15 @@
     <col width="4" customWidth="1" min="15" max="15"/>
     <col width="4" customWidth="1" min="16" max="16"/>
     <col width="4" customWidth="1" min="17" max="17"/>
+    <col width="2" customWidth="1" min="18" max="18"/>
+    <col width="15" customWidth="1" min="19" max="19"/>
+    <col width="12" customWidth="1" min="20" max="20"/>
+    <col width="5" customWidth="1" min="21" max="21"/>
+    <col width="5" customWidth="1" min="22" max="22"/>
+    <col width="4" customWidth="1" min="23" max="23"/>
+    <col width="4" customWidth="1" min="24" max="24"/>
+    <col width="4" customWidth="1" min="25" max="25"/>
+    <col width="4" customWidth="1" min="26" max="26"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -701,84 +710,164 @@
           <t>KI</t>
         </is>
       </c>
+      <c r="S1" s="1" t="inlineStr">
+        <is>
+          <t>Date</t>
+        </is>
+      </c>
+      <c r="T1" s="1" t="inlineStr">
+        <is>
+          <t>Module</t>
+        </is>
+      </c>
+      <c r="U1" s="1" t="inlineStr">
+        <is>
+          <t>T</t>
+        </is>
+      </c>
+      <c r="V1" s="1" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
+      <c r="W1" s="1" t="inlineStr">
+        <is>
+          <t>S</t>
+        </is>
+      </c>
+      <c r="X1" s="1" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
+      <c r="Y1" s="1" t="inlineStr">
+        <is>
+          <t>I</t>
+        </is>
+      </c>
+      <c r="Z1" s="1" t="inlineStr">
+        <is>
+          <t>KI</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
+          <t>08-April-2026</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>auth</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>254</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>142</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>72</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>40</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
           <t>07-April-2026</t>
         </is>
       </c>
-      <c r="B2" t="inlineStr">
+      <c r="K2" t="inlineStr">
         <is>
           <t>auth</t>
         </is>
       </c>
-      <c r="C2" t="inlineStr">
+      <c r="L2" t="inlineStr">
         <is>
           <t>254</t>
         </is>
       </c>
-      <c r="D2" t="inlineStr">
+      <c r="M2" t="inlineStr">
         <is>
           <t>184</t>
         </is>
       </c>
-      <c r="E2" t="inlineStr">
+      <c r="N2" t="inlineStr">
         <is>
           <t>6</t>
         </is>
       </c>
-      <c r="F2" t="inlineStr">
+      <c r="O2" t="inlineStr">
         <is>
           <t>64</t>
         </is>
       </c>
-      <c r="G2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="J2" t="inlineStr">
+      <c r="P2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Q2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="S2" t="inlineStr">
         <is>
           <t>06-April-2026</t>
         </is>
       </c>
-      <c r="K2" t="inlineStr">
+      <c r="T2" t="inlineStr">
         <is>
           <t>auth</t>
         </is>
       </c>
-      <c r="L2" t="inlineStr">
+      <c r="U2" t="inlineStr">
         <is>
           <t>254</t>
         </is>
       </c>
-      <c r="M2" t="inlineStr">
+      <c r="V2" t="inlineStr">
         <is>
           <t>184</t>
         </is>
       </c>
-      <c r="N2" t="inlineStr">
+      <c r="W2" t="inlineStr">
         <is>
           <t>6</t>
         </is>
       </c>
-      <c r="O2" t="inlineStr">
+      <c r="X2" t="inlineStr">
         <is>
           <t>64</t>
         </is>
       </c>
-      <c r="P2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="Q2" t="inlineStr">
+      <c r="Y2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Z2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
@@ -787,80 +876,120 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
+          <t>08-April-2026</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>esignet</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>375</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>267</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>32</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>49</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>27</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
           <t>07-April-2026</t>
         </is>
       </c>
-      <c r="B3" t="inlineStr">
+      <c r="K3" t="inlineStr">
         <is>
           <t>esignet</t>
         </is>
       </c>
-      <c r="C3" t="inlineStr">
+      <c r="L3" t="inlineStr">
         <is>
           <t>375</t>
         </is>
       </c>
-      <c r="D3" t="inlineStr">
+      <c r="M3" t="inlineStr">
         <is>
           <t>285</t>
         </is>
       </c>
-      <c r="E3" t="inlineStr">
+      <c r="N3" t="inlineStr">
         <is>
           <t>21</t>
         </is>
       </c>
-      <c r="F3" t="inlineStr">
+      <c r="O3" t="inlineStr">
         <is>
           <t>42</t>
         </is>
       </c>
-      <c r="G3" t="inlineStr">
+      <c r="P3" t="inlineStr">
         <is>
           <t>27</t>
         </is>
       </c>
-      <c r="H3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="J3" t="inlineStr">
+      <c r="Q3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="S3" t="inlineStr">
         <is>
           <t>06-April-2026</t>
         </is>
       </c>
-      <c r="K3" t="inlineStr">
+      <c r="T3" t="inlineStr">
         <is>
           <t>esignet</t>
         </is>
       </c>
-      <c r="L3" t="inlineStr">
+      <c r="U3" t="inlineStr">
         <is>
           <t>375</t>
         </is>
       </c>
-      <c r="M3" t="inlineStr">
+      <c r="V3" t="inlineStr">
         <is>
           <t>274</t>
         </is>
       </c>
-      <c r="N3" t="inlineStr">
+      <c r="W3" t="inlineStr">
         <is>
           <t>28</t>
         </is>
       </c>
-      <c r="O3" t="inlineStr">
+      <c r="X3" t="inlineStr">
         <is>
           <t>46</t>
         </is>
       </c>
-      <c r="P3" t="inlineStr">
+      <c r="Y3" t="inlineStr">
         <is>
           <t>27</t>
         </is>
       </c>
-      <c r="Q3" t="inlineStr">
+      <c r="Z3" t="inlineStr">
         <is>
           <t>0</t>
         </is>
@@ -869,80 +998,120 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
+          <t>08-April-2026</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>idrepo</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>152</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>101</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>51</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
           <t>07-April-2026</t>
         </is>
       </c>
-      <c r="B4" t="inlineStr">
+      <c r="K4" t="inlineStr">
         <is>
           <t>idrepo</t>
         </is>
       </c>
-      <c r="C4" t="inlineStr">
+      <c r="L4" t="inlineStr">
         <is>
           <t>152</t>
         </is>
       </c>
-      <c r="D4" t="inlineStr">
+      <c r="M4" t="inlineStr">
         <is>
           <t>101</t>
         </is>
       </c>
-      <c r="E4" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F4" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="G4" t="inlineStr">
+      <c r="N4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P4" t="inlineStr">
         <is>
           <t>51</t>
         </is>
       </c>
-      <c r="H4" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="J4" t="inlineStr">
+      <c r="Q4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="S4" t="inlineStr">
         <is>
           <t>06-April-2026</t>
         </is>
       </c>
-      <c r="K4" t="inlineStr">
+      <c r="T4" t="inlineStr">
         <is>
           <t>idrepo</t>
         </is>
       </c>
-      <c r="L4" t="inlineStr">
+      <c r="U4" t="inlineStr">
         <is>
           <t>152</t>
         </is>
       </c>
-      <c r="M4" t="inlineStr">
+      <c r="V4" t="inlineStr">
         <is>
           <t>101</t>
         </is>
       </c>
-      <c r="N4" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="O4" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="P4" t="inlineStr">
+      <c r="W4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="X4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Y4" t="inlineStr">
         <is>
           <t>51</t>
         </is>
       </c>
-      <c r="Q4" t="inlineStr">
+      <c r="Z4" t="inlineStr">
         <is>
           <t>0</t>
         </is>
@@ -951,80 +1120,120 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
+          <t>08-April-2026</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>injiverify</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>53</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>23</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
           <t>07-April-2026</t>
         </is>
       </c>
-      <c r="B5" t="inlineStr">
+      <c r="K5" t="inlineStr">
         <is>
           <t>injiverify</t>
         </is>
       </c>
-      <c r="C5" t="inlineStr">
+      <c r="L5" t="inlineStr">
         <is>
           <t>53</t>
         </is>
       </c>
-      <c r="D5" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="E5" t="inlineStr">
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="N5" t="inlineStr">
         <is>
           <t>23</t>
         </is>
       </c>
-      <c r="F5" t="inlineStr">
+      <c r="O5" t="inlineStr">
         <is>
           <t>30</t>
         </is>
       </c>
-      <c r="G5" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H5" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="J5" t="inlineStr">
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Q5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="S5" t="inlineStr">
         <is>
           <t>06-April-2026</t>
         </is>
       </c>
-      <c r="K5" t="inlineStr">
+      <c r="T5" t="inlineStr">
         <is>
           <t>injiverify</t>
         </is>
       </c>
-      <c r="L5" t="inlineStr">
+      <c r="U5" t="inlineStr">
         <is>
           <t>53</t>
         </is>
       </c>
-      <c r="M5" t="inlineStr">
+      <c r="V5" t="inlineStr">
         <is>
           <t>53</t>
         </is>
       </c>
-      <c r="N5" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="O5" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="P5" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="Q5" t="inlineStr">
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="X5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Z5" t="inlineStr">
         <is>
           <t>0</t>
         </is>
@@ -1033,80 +1242,120 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
+          <t>08-April-2026</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>mimoto</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>79</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>65</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
           <t>07-April-2026</t>
         </is>
       </c>
-      <c r="B6" t="inlineStr">
+      <c r="K6" t="inlineStr">
         <is>
           <t>mimoto</t>
         </is>
       </c>
-      <c r="C6" t="inlineStr">
+      <c r="L6" t="inlineStr">
         <is>
           <t>79</t>
         </is>
       </c>
-      <c r="D6" t="inlineStr">
+      <c r="M6" t="inlineStr">
         <is>
           <t>66</t>
         </is>
       </c>
-      <c r="E6" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F6" t="inlineStr">
+      <c r="N6" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O6" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="G6" t="inlineStr">
+      <c r="P6" t="inlineStr">
         <is>
           <t>10</t>
         </is>
       </c>
-      <c r="H6" t="inlineStr">
+      <c r="Q6" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="J6" t="inlineStr">
+      <c r="S6" t="inlineStr">
         <is>
           <t>06-April-2026</t>
         </is>
       </c>
-      <c r="K6" t="inlineStr">
+      <c r="T6" t="inlineStr">
         <is>
           <t>mimoto</t>
         </is>
       </c>
-      <c r="L6" t="inlineStr">
+      <c r="U6" t="inlineStr">
         <is>
           <t>79</t>
         </is>
       </c>
-      <c r="M6" t="inlineStr">
+      <c r="V6" t="inlineStr">
         <is>
           <t>66</t>
         </is>
       </c>
-      <c r="N6" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="O6" t="inlineStr">
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="X6" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="P6" t="inlineStr">
+      <c r="Y6" t="inlineStr">
         <is>
           <t>10</t>
         </is>
       </c>
-      <c r="Q6" t="inlineStr">
+      <c r="Z6" t="inlineStr">
         <is>
           <t>2</t>
         </is>
@@ -1115,80 +1364,120 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
+          <t>08-April-2026</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>prereg</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>104</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>70</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
           <t>07-April-2026</t>
         </is>
       </c>
-      <c r="B7" t="inlineStr">
+      <c r="K7" t="inlineStr">
         <is>
           <t>prereg</t>
         </is>
       </c>
-      <c r="C7" t="inlineStr">
+      <c r="L7" t="inlineStr">
         <is>
           <t>104</t>
         </is>
       </c>
-      <c r="D7" t="inlineStr">
+      <c r="M7" t="inlineStr">
         <is>
           <t>3</t>
         </is>
       </c>
-      <c r="E7" t="inlineStr">
+      <c r="N7" t="inlineStr">
         <is>
           <t>70</t>
         </is>
       </c>
-      <c r="F7" t="inlineStr">
+      <c r="O7" t="inlineStr">
         <is>
           <t>30</t>
         </is>
       </c>
-      <c r="G7" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H7" t="inlineStr">
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Q7" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="J7" t="inlineStr">
+      <c r="S7" t="inlineStr">
         <is>
           <t>06-April-2026</t>
         </is>
       </c>
-      <c r="K7" t="inlineStr">
+      <c r="T7" t="inlineStr">
         <is>
           <t>prereg</t>
         </is>
       </c>
-      <c r="L7" t="inlineStr">
+      <c r="U7" t="inlineStr">
         <is>
           <t>104</t>
         </is>
       </c>
-      <c r="M7" t="inlineStr">
+      <c r="V7" t="inlineStr">
         <is>
           <t>3</t>
         </is>
       </c>
-      <c r="N7" t="inlineStr">
+      <c r="W7" t="inlineStr">
         <is>
           <t>70</t>
         </is>
       </c>
-      <c r="O7" t="inlineStr">
+      <c r="X7" t="inlineStr">
         <is>
           <t>30</t>
         </is>
       </c>
-      <c r="P7" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="Q7" t="inlineStr">
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Z7" t="inlineStr">
         <is>
           <t>1</t>
         </is>
@@ -1197,80 +1486,120 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
+          <t>08-April-2026</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>residentui</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>33</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
           <t>07-April-2026</t>
         </is>
       </c>
-      <c r="B8" t="inlineStr">
+      <c r="K8" t="inlineStr">
         <is>
           <t>residentui</t>
         </is>
       </c>
-      <c r="C8" t="inlineStr">
+      <c r="L8" t="inlineStr">
         <is>
           <t>33</t>
         </is>
       </c>
-      <c r="D8" t="inlineStr">
+      <c r="M8" t="inlineStr">
         <is>
           <t>12</t>
         </is>
       </c>
-      <c r="E8" t="inlineStr">
+      <c r="N8" t="inlineStr">
         <is>
           <t>5</t>
         </is>
       </c>
-      <c r="F8" t="inlineStr">
+      <c r="O8" t="inlineStr">
         <is>
           <t>16</t>
         </is>
       </c>
-      <c r="G8" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H8" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="J8" t="inlineStr">
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Q8" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="S8" t="inlineStr">
         <is>
           <t>06-April-2026</t>
         </is>
       </c>
-      <c r="K8" t="inlineStr">
+      <c r="T8" t="inlineStr">
         <is>
           <t>residentui</t>
         </is>
       </c>
-      <c r="L8" t="inlineStr">
+      <c r="U8" t="inlineStr">
         <is>
           <t>33</t>
         </is>
       </c>
-      <c r="M8" t="inlineStr">
+      <c r="V8" t="inlineStr">
         <is>
           <t>12</t>
         </is>
       </c>
-      <c r="N8" t="inlineStr">
+      <c r="W8" t="inlineStr">
         <is>
           <t>5</t>
         </is>
       </c>
-      <c r="O8" t="inlineStr">
+      <c r="X8" t="inlineStr">
         <is>
           <t>16</t>
         </is>
       </c>
-      <c r="P8" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="Q8" t="inlineStr">
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Z8" t="inlineStr">
         <is>
           <t>0</t>
         </is>

--- a/minio-report-tracker/xlxs/collab.xlsx
+++ b/minio-report-tracker/xlxs/collab.xlsx
@@ -598,7 +598,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Z8"/>
+  <dimension ref="A1:AI8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="15" customWidth="1" min="1" max="1"/>
@@ -627,6 +627,15 @@
     <col width="4" customWidth="1" min="24" max="24"/>
     <col width="4" customWidth="1" min="25" max="25"/>
     <col width="4" customWidth="1" min="26" max="26"/>
+    <col width="2" customWidth="1" min="27" max="27"/>
+    <col width="15" customWidth="1" min="28" max="28"/>
+    <col width="12" customWidth="1" min="29" max="29"/>
+    <col width="5" customWidth="1" min="30" max="30"/>
+    <col width="5" customWidth="1" min="31" max="31"/>
+    <col width="5" customWidth="1" min="32" max="32"/>
+    <col width="5" customWidth="1" min="33" max="33"/>
+    <col width="5" customWidth="1" min="34" max="34"/>
+    <col width="5" customWidth="1" min="35" max="35"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -750,124 +759,204 @@
           <t>KI</t>
         </is>
       </c>
+      <c r="AB1" s="1" t="inlineStr">
+        <is>
+          <t>Date</t>
+        </is>
+      </c>
+      <c r="AC1" s="1" t="inlineStr">
+        <is>
+          <t>Module</t>
+        </is>
+      </c>
+      <c r="AD1" s="1" t="inlineStr">
+        <is>
+          <t>T</t>
+        </is>
+      </c>
+      <c r="AE1" s="1" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
+      <c r="AF1" s="1" t="inlineStr">
+        <is>
+          <t>S</t>
+        </is>
+      </c>
+      <c r="AG1" s="1" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
+      <c r="AH1" s="1" t="inlineStr">
+        <is>
+          <t>I</t>
+        </is>
+      </c>
+      <c r="AI1" s="1" t="inlineStr">
+        <is>
+          <t>KI</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
+          <t>09-April-2026</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>auth</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>254</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>140</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>72</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>42</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
           <t>08-April-2026</t>
         </is>
       </c>
-      <c r="B2" t="inlineStr">
+      <c r="K2" t="inlineStr">
         <is>
           <t>auth</t>
         </is>
       </c>
-      <c r="C2" t="inlineStr">
+      <c r="L2" t="inlineStr">
         <is>
           <t>254</t>
         </is>
       </c>
-      <c r="D2" t="inlineStr">
+      <c r="M2" t="inlineStr">
         <is>
           <t>142</t>
         </is>
       </c>
-      <c r="E2" t="inlineStr">
+      <c r="N2" t="inlineStr">
         <is>
           <t>72</t>
         </is>
       </c>
-      <c r="F2" t="inlineStr">
+      <c r="O2" t="inlineStr">
         <is>
           <t>40</t>
         </is>
       </c>
-      <c r="G2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="J2" t="inlineStr">
+      <c r="P2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Q2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="S2" t="inlineStr">
         <is>
           <t>07-April-2026</t>
         </is>
       </c>
-      <c r="K2" t="inlineStr">
+      <c r="T2" t="inlineStr">
         <is>
           <t>auth</t>
         </is>
       </c>
-      <c r="L2" t="inlineStr">
+      <c r="U2" t="inlineStr">
         <is>
           <t>254</t>
         </is>
       </c>
-      <c r="M2" t="inlineStr">
+      <c r="V2" t="inlineStr">
         <is>
           <t>184</t>
         </is>
       </c>
-      <c r="N2" t="inlineStr">
+      <c r="W2" t="inlineStr">
         <is>
           <t>6</t>
         </is>
       </c>
-      <c r="O2" t="inlineStr">
+      <c r="X2" t="inlineStr">
         <is>
           <t>64</t>
         </is>
       </c>
-      <c r="P2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="Q2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="S2" t="inlineStr">
+      <c r="Y2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Z2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB2" t="inlineStr">
         <is>
           <t>06-April-2026</t>
         </is>
       </c>
-      <c r="T2" t="inlineStr">
-        <is>
-          <t>auth</t>
-        </is>
-      </c>
-      <c r="U2" t="inlineStr">
-        <is>
-          <t>254</t>
-        </is>
-      </c>
-      <c r="V2" t="inlineStr">
-        <is>
-          <t>184</t>
-        </is>
-      </c>
-      <c r="W2" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="X2" t="inlineStr">
-        <is>
-          <t>64</t>
-        </is>
-      </c>
-      <c r="Y2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="Z2" t="inlineStr">
+      <c r="AC2" t="inlineStr">
+        <is>
+          <t>esignet</t>
+        </is>
+      </c>
+      <c r="AD2" t="inlineStr">
+        <is>
+          <t>375</t>
+        </is>
+      </c>
+      <c r="AE2" t="inlineStr">
+        <is>
+          <t>274</t>
+        </is>
+      </c>
+      <c r="AF2" t="inlineStr">
+        <is>
+          <t>28</t>
+        </is>
+      </c>
+      <c r="AG2" t="inlineStr">
+        <is>
+          <t>46</t>
+        </is>
+      </c>
+      <c r="AH2" t="inlineStr">
+        <is>
+          <t>27</t>
+        </is>
+      </c>
+      <c r="AI2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
@@ -876,120 +965,160 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
+          <t>09-April-2026</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>esignet</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>375</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>290</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>31</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>27</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>27</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
           <t>08-April-2026</t>
         </is>
       </c>
-      <c r="B3" t="inlineStr">
+      <c r="K3" t="inlineStr">
         <is>
           <t>esignet</t>
         </is>
       </c>
-      <c r="C3" t="inlineStr">
+      <c r="L3" t="inlineStr">
         <is>
           <t>375</t>
         </is>
       </c>
-      <c r="D3" t="inlineStr">
+      <c r="M3" t="inlineStr">
         <is>
           <t>267</t>
         </is>
       </c>
-      <c r="E3" t="inlineStr">
+      <c r="N3" t="inlineStr">
         <is>
           <t>32</t>
         </is>
       </c>
-      <c r="F3" t="inlineStr">
+      <c r="O3" t="inlineStr">
         <is>
           <t>49</t>
         </is>
       </c>
-      <c r="G3" t="inlineStr">
+      <c r="P3" t="inlineStr">
         <is>
           <t>27</t>
         </is>
       </c>
-      <c r="H3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="J3" t="inlineStr">
+      <c r="Q3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="S3" t="inlineStr">
         <is>
           <t>07-April-2026</t>
         </is>
       </c>
-      <c r="K3" t="inlineStr">
+      <c r="T3" t="inlineStr">
         <is>
           <t>esignet</t>
         </is>
       </c>
-      <c r="L3" t="inlineStr">
+      <c r="U3" t="inlineStr">
         <is>
           <t>375</t>
         </is>
       </c>
-      <c r="M3" t="inlineStr">
+      <c r="V3" t="inlineStr">
         <is>
           <t>285</t>
         </is>
       </c>
-      <c r="N3" t="inlineStr">
+      <c r="W3" t="inlineStr">
         <is>
           <t>21</t>
         </is>
       </c>
-      <c r="O3" t="inlineStr">
+      <c r="X3" t="inlineStr">
         <is>
           <t>42</t>
         </is>
       </c>
-      <c r="P3" t="inlineStr">
+      <c r="Y3" t="inlineStr">
         <is>
           <t>27</t>
         </is>
       </c>
-      <c r="Q3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="S3" t="inlineStr">
+      <c r="Z3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB3" t="inlineStr">
         <is>
           <t>06-April-2026</t>
         </is>
       </c>
-      <c r="T3" t="inlineStr">
-        <is>
-          <t>esignet</t>
-        </is>
-      </c>
-      <c r="U3" t="inlineStr">
-        <is>
-          <t>375</t>
-        </is>
-      </c>
-      <c r="V3" t="inlineStr">
-        <is>
-          <t>274</t>
-        </is>
-      </c>
-      <c r="W3" t="inlineStr">
-        <is>
-          <t>28</t>
-        </is>
-      </c>
-      <c r="X3" t="inlineStr">
-        <is>
-          <t>46</t>
-        </is>
-      </c>
-      <c r="Y3" t="inlineStr">
-        <is>
-          <t>27</t>
-        </is>
-      </c>
-      <c r="Z3" t="inlineStr">
+      <c r="AC3" t="inlineStr">
+        <is>
+          <t>injiverify</t>
+        </is>
+      </c>
+      <c r="AD3" t="inlineStr">
+        <is>
+          <t>53</t>
+        </is>
+      </c>
+      <c r="AE3" t="inlineStr">
+        <is>
+          <t>53</t>
+        </is>
+      </c>
+      <c r="AF3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AG3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AH3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AI3" t="inlineStr">
         <is>
           <t>0</t>
         </is>
@@ -998,242 +1127,322 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
+          <t>09-April-2026</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>idrepo</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>152</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>101</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>51</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
           <t>08-April-2026</t>
         </is>
       </c>
-      <c r="B4" t="inlineStr">
+      <c r="K4" t="inlineStr">
         <is>
           <t>idrepo</t>
         </is>
       </c>
-      <c r="C4" t="inlineStr">
+      <c r="L4" t="inlineStr">
         <is>
           <t>152</t>
         </is>
       </c>
-      <c r="D4" t="inlineStr">
+      <c r="M4" t="inlineStr">
         <is>
           <t>101</t>
         </is>
       </c>
-      <c r="E4" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F4" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="G4" t="inlineStr">
+      <c r="N4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P4" t="inlineStr">
         <is>
           <t>51</t>
         </is>
       </c>
-      <c r="H4" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="J4" t="inlineStr">
+      <c r="Q4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="S4" t="inlineStr">
         <is>
           <t>07-April-2026</t>
         </is>
       </c>
-      <c r="K4" t="inlineStr">
+      <c r="T4" t="inlineStr">
         <is>
           <t>idrepo</t>
         </is>
       </c>
-      <c r="L4" t="inlineStr">
+      <c r="U4" t="inlineStr">
         <is>
           <t>152</t>
         </is>
       </c>
-      <c r="M4" t="inlineStr">
+      <c r="V4" t="inlineStr">
         <is>
           <t>101</t>
         </is>
       </c>
-      <c r="N4" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="O4" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="P4" t="inlineStr">
+      <c r="W4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="X4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Y4" t="inlineStr">
         <is>
           <t>51</t>
         </is>
       </c>
-      <c r="Q4" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="S4" t="inlineStr">
+      <c r="Z4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB4" t="inlineStr">
         <is>
           <t>06-April-2026</t>
         </is>
       </c>
-      <c r="T4" t="inlineStr">
-        <is>
-          <t>idrepo</t>
-        </is>
-      </c>
-      <c r="U4" t="inlineStr">
-        <is>
-          <t>152</t>
-        </is>
-      </c>
-      <c r="V4" t="inlineStr">
-        <is>
-          <t>101</t>
-        </is>
-      </c>
-      <c r="W4" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="X4" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="Y4" t="inlineStr">
-        <is>
-          <t>51</t>
-        </is>
-      </c>
-      <c r="Z4" t="inlineStr">
-        <is>
-          <t>0</t>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t>prereg</t>
+        </is>
+      </c>
+      <c r="AD4" t="inlineStr">
+        <is>
+          <t>104</t>
+        </is>
+      </c>
+      <c r="AE4" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AF4" t="inlineStr">
+        <is>
+          <t>70</t>
+        </is>
+      </c>
+      <c r="AG4" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="AH4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AI4" t="inlineStr">
+        <is>
+          <t>1</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
+          <t>09-April-2026</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>injiverify</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>53</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>23</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
           <t>08-April-2026</t>
         </is>
       </c>
-      <c r="B5" t="inlineStr">
+      <c r="K5" t="inlineStr">
         <is>
           <t>injiverify</t>
         </is>
       </c>
-      <c r="C5" t="inlineStr">
+      <c r="L5" t="inlineStr">
         <is>
           <t>53</t>
         </is>
       </c>
-      <c r="D5" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="E5" t="inlineStr">
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="N5" t="inlineStr">
         <is>
           <t>23</t>
         </is>
       </c>
-      <c r="F5" t="inlineStr">
+      <c r="O5" t="inlineStr">
         <is>
           <t>30</t>
         </is>
       </c>
-      <c r="G5" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H5" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="J5" t="inlineStr">
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Q5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="S5" t="inlineStr">
         <is>
           <t>07-April-2026</t>
         </is>
       </c>
-      <c r="K5" t="inlineStr">
+      <c r="T5" t="inlineStr">
         <is>
           <t>injiverify</t>
         </is>
       </c>
-      <c r="L5" t="inlineStr">
+      <c r="U5" t="inlineStr">
         <is>
           <t>53</t>
         </is>
       </c>
-      <c r="M5" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="N5" t="inlineStr">
+      <c r="V5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="W5" t="inlineStr">
         <is>
           <t>23</t>
         </is>
       </c>
-      <c r="O5" t="inlineStr">
+      <c r="X5" t="inlineStr">
         <is>
           <t>30</t>
         </is>
       </c>
-      <c r="P5" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="Q5" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="S5" t="inlineStr">
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Z5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB5" t="inlineStr">
         <is>
           <t>06-April-2026</t>
         </is>
       </c>
-      <c r="T5" t="inlineStr">
-        <is>
-          <t>injiverify</t>
-        </is>
-      </c>
-      <c r="U5" t="inlineStr">
-        <is>
-          <t>53</t>
-        </is>
-      </c>
-      <c r="V5" t="inlineStr">
-        <is>
-          <t>53</t>
-        </is>
-      </c>
-      <c r="W5" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="X5" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="Y5" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="Z5" t="inlineStr">
+      <c r="AC5" t="inlineStr">
+        <is>
+          <t>residentui</t>
+        </is>
+      </c>
+      <c r="AD5" t="inlineStr">
+        <is>
+          <t>33</t>
+        </is>
+      </c>
+      <c r="AE5" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="AF5" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AG5" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="AH5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AI5" t="inlineStr">
         <is>
           <t>0</t>
         </is>
@@ -1242,358 +1451,406 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
+          <t>09-April-2026</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>mimoto</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>79</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>59</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
           <t>08-April-2026</t>
         </is>
       </c>
-      <c r="B6" t="inlineStr">
+      <c r="K6" t="inlineStr">
         <is>
           <t>mimoto</t>
         </is>
       </c>
-      <c r="C6" t="inlineStr">
+      <c r="L6" t="inlineStr">
         <is>
           <t>79</t>
         </is>
       </c>
-      <c r="D6" t="inlineStr">
+      <c r="M6" t="inlineStr">
         <is>
           <t>65</t>
         </is>
       </c>
-      <c r="E6" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F6" t="inlineStr">
+      <c r="N6" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O6" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="G6" t="inlineStr">
+      <c r="P6" t="inlineStr">
         <is>
           <t>10</t>
         </is>
       </c>
-      <c r="H6" t="inlineStr">
+      <c r="Q6" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="J6" t="inlineStr">
+      <c r="S6" t="inlineStr">
         <is>
           <t>07-April-2026</t>
         </is>
       </c>
-      <c r="K6" t="inlineStr">
+      <c r="T6" t="inlineStr">
         <is>
           <t>mimoto</t>
         </is>
       </c>
-      <c r="L6" t="inlineStr">
+      <c r="U6" t="inlineStr">
         <is>
           <t>79</t>
         </is>
       </c>
-      <c r="M6" t="inlineStr">
+      <c r="V6" t="inlineStr">
         <is>
           <t>66</t>
         </is>
       </c>
-      <c r="N6" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="O6" t="inlineStr">
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="X6" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="P6" t="inlineStr">
+      <c r="Y6" t="inlineStr">
         <is>
           <t>10</t>
         </is>
       </c>
-      <c r="Q6" t="inlineStr">
+      <c r="Z6" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="S6" t="inlineStr">
-        <is>
-          <t>06-April-2026</t>
-        </is>
-      </c>
-      <c r="T6" t="inlineStr">
-        <is>
-          <t>mimoto</t>
-        </is>
-      </c>
-      <c r="U6" t="inlineStr">
-        <is>
-          <t>79</t>
-        </is>
-      </c>
-      <c r="V6" t="inlineStr">
-        <is>
-          <t>66</t>
-        </is>
-      </c>
-      <c r="W6" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="X6" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="Y6" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="Z6" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
+      <c r="AB6" t="n">
+        <v/>
+      </c>
+      <c r="AC6" t="n">
+        <v/>
+      </c>
+      <c r="AD6" t="n">
+        <v/>
+      </c>
+      <c r="AE6" t="n">
+        <v/>
+      </c>
+      <c r="AF6" t="n">
+        <v/>
+      </c>
+      <c r="AG6" t="n">
+        <v/>
+      </c>
+      <c r="AH6" t="n">
+        <v/>
+      </c>
+      <c r="AI6" t="n">
+        <v/>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
+          <t>09-April-2026</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>prereg</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>104</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>70</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
           <t>08-April-2026</t>
         </is>
       </c>
-      <c r="B7" t="inlineStr">
+      <c r="K7" t="inlineStr">
         <is>
           <t>prereg</t>
         </is>
       </c>
-      <c r="C7" t="inlineStr">
+      <c r="L7" t="inlineStr">
         <is>
           <t>104</t>
         </is>
       </c>
-      <c r="D7" t="inlineStr">
+      <c r="M7" t="inlineStr">
         <is>
           <t>3</t>
         </is>
       </c>
-      <c r="E7" t="inlineStr">
+      <c r="N7" t="inlineStr">
         <is>
           <t>70</t>
         </is>
       </c>
-      <c r="F7" t="inlineStr">
+      <c r="O7" t="inlineStr">
         <is>
           <t>30</t>
         </is>
       </c>
-      <c r="G7" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H7" t="inlineStr">
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Q7" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="J7" t="inlineStr">
+      <c r="S7" t="inlineStr">
         <is>
           <t>07-April-2026</t>
         </is>
       </c>
-      <c r="K7" t="inlineStr">
+      <c r="T7" t="inlineStr">
         <is>
           <t>prereg</t>
         </is>
       </c>
-      <c r="L7" t="inlineStr">
+      <c r="U7" t="inlineStr">
         <is>
           <t>104</t>
         </is>
       </c>
-      <c r="M7" t="inlineStr">
+      <c r="V7" t="inlineStr">
         <is>
           <t>3</t>
         </is>
       </c>
-      <c r="N7" t="inlineStr">
+      <c r="W7" t="inlineStr">
         <is>
           <t>70</t>
         </is>
       </c>
-      <c r="O7" t="inlineStr">
+      <c r="X7" t="inlineStr">
         <is>
           <t>30</t>
         </is>
       </c>
-      <c r="P7" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="Q7" t="inlineStr">
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Z7" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="S7" t="inlineStr">
-        <is>
-          <t>06-April-2026</t>
-        </is>
-      </c>
-      <c r="T7" t="inlineStr">
-        <is>
-          <t>prereg</t>
-        </is>
-      </c>
-      <c r="U7" t="inlineStr">
-        <is>
-          <t>104</t>
-        </is>
-      </c>
-      <c r="V7" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="W7" t="inlineStr">
-        <is>
-          <t>70</t>
-        </is>
-      </c>
-      <c r="X7" t="inlineStr">
-        <is>
-          <t>30</t>
-        </is>
-      </c>
-      <c r="Y7" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="Z7" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
+      <c r="AB7" t="n">
+        <v/>
+      </c>
+      <c r="AC7" t="n">
+        <v/>
+      </c>
+      <c r="AD7" t="n">
+        <v/>
+      </c>
+      <c r="AE7" t="n">
+        <v/>
+      </c>
+      <c r="AF7" t="n">
+        <v/>
+      </c>
+      <c r="AG7" t="n">
+        <v/>
+      </c>
+      <c r="AH7" t="n">
+        <v/>
+      </c>
+      <c r="AI7" t="n">
+        <v/>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
+          <t>09-April-2026</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>residentui</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>33</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
           <t>08-April-2026</t>
         </is>
       </c>
-      <c r="B8" t="inlineStr">
+      <c r="K8" t="inlineStr">
         <is>
           <t>residentui</t>
         </is>
       </c>
-      <c r="C8" t="inlineStr">
+      <c r="L8" t="inlineStr">
         <is>
           <t>33</t>
         </is>
       </c>
-      <c r="D8" t="inlineStr">
+      <c r="M8" t="inlineStr">
         <is>
           <t>12</t>
         </is>
       </c>
-      <c r="E8" t="inlineStr">
+      <c r="N8" t="inlineStr">
         <is>
           <t>5</t>
         </is>
       </c>
-      <c r="F8" t="inlineStr">
+      <c r="O8" t="inlineStr">
         <is>
           <t>16</t>
         </is>
       </c>
-      <c r="G8" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H8" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="J8" t="inlineStr">
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Q8" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="S8" t="inlineStr">
         <is>
           <t>07-April-2026</t>
         </is>
       </c>
-      <c r="K8" t="inlineStr">
+      <c r="T8" t="inlineStr">
         <is>
           <t>residentui</t>
         </is>
       </c>
-      <c r="L8" t="inlineStr">
+      <c r="U8" t="inlineStr">
         <is>
           <t>33</t>
         </is>
       </c>
-      <c r="M8" t="inlineStr">
+      <c r="V8" t="inlineStr">
         <is>
           <t>12</t>
         </is>
       </c>
-      <c r="N8" t="inlineStr">
+      <c r="W8" t="inlineStr">
         <is>
           <t>5</t>
         </is>
       </c>
-      <c r="O8" t="inlineStr">
+      <c r="X8" t="inlineStr">
         <is>
           <t>16</t>
         </is>
       </c>
-      <c r="P8" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="Q8" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="S8" t="inlineStr">
-        <is>
-          <t>06-April-2026</t>
-        </is>
-      </c>
-      <c r="T8" t="inlineStr">
-        <is>
-          <t>residentui</t>
-        </is>
-      </c>
-      <c r="U8" t="inlineStr">
-        <is>
-          <t>33</t>
-        </is>
-      </c>
-      <c r="V8" t="inlineStr">
-        <is>
-          <t>12</t>
-        </is>
-      </c>
-      <c r="W8" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="X8" t="inlineStr">
-        <is>
-          <t>16</t>
-        </is>
-      </c>
       <c r="Y8" t="inlineStr">
         <is>
           <t>0</t>
@@ -1603,6 +1860,30 @@
         <is>
           <t>0</t>
         </is>
+      </c>
+      <c r="AB8" t="n">
+        <v/>
+      </c>
+      <c r="AC8" t="n">
+        <v/>
+      </c>
+      <c r="AD8" t="n">
+        <v/>
+      </c>
+      <c r="AE8" t="n">
+        <v/>
+      </c>
+      <c r="AF8" t="n">
+        <v/>
+      </c>
+      <c r="AG8" t="n">
+        <v/>
+      </c>
+      <c r="AH8" t="n">
+        <v/>
+      </c>
+      <c r="AI8" t="n">
+        <v/>
       </c>
     </row>
   </sheetData>

--- a/minio-report-tracker/xlxs/collab.xlsx
+++ b/minio-report-tracker/xlxs/collab.xlsx
@@ -803,129 +803,129 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
+          <t>10-April-2026</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>auth</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>254</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>184</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>64</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
           <t>09-April-2026</t>
         </is>
       </c>
-      <c r="B2" t="inlineStr">
+      <c r="K2" t="inlineStr">
         <is>
           <t>auth</t>
         </is>
       </c>
-      <c r="C2" t="inlineStr">
+      <c r="L2" t="inlineStr">
         <is>
           <t>254</t>
         </is>
       </c>
-      <c r="D2" t="inlineStr">
+      <c r="M2" t="inlineStr">
         <is>
           <t>140</t>
         </is>
       </c>
-      <c r="E2" t="inlineStr">
+      <c r="N2" t="inlineStr">
         <is>
           <t>72</t>
         </is>
       </c>
-      <c r="F2" t="inlineStr">
+      <c r="O2" t="inlineStr">
         <is>
           <t>42</t>
         </is>
       </c>
-      <c r="G2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="J2" t="inlineStr">
+      <c r="P2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Q2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="S2" t="inlineStr">
         <is>
           <t>08-April-2026</t>
         </is>
       </c>
-      <c r="K2" t="inlineStr">
+      <c r="T2" t="inlineStr">
         <is>
           <t>auth</t>
         </is>
       </c>
-      <c r="L2" t="inlineStr">
+      <c r="U2" t="inlineStr">
         <is>
           <t>254</t>
         </is>
       </c>
-      <c r="M2" t="inlineStr">
+      <c r="V2" t="inlineStr">
         <is>
           <t>142</t>
         </is>
       </c>
-      <c r="N2" t="inlineStr">
+      <c r="W2" t="inlineStr">
         <is>
           <t>72</t>
         </is>
       </c>
-      <c r="O2" t="inlineStr">
+      <c r="X2" t="inlineStr">
         <is>
           <t>40</t>
         </is>
       </c>
-      <c r="P2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="Q2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="S2" t="inlineStr">
+      <c r="Y2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Z2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB2" t="inlineStr">
         <is>
           <t>07-April-2026</t>
         </is>
       </c>
-      <c r="T2" t="inlineStr">
-        <is>
-          <t>auth</t>
-        </is>
-      </c>
-      <c r="U2" t="inlineStr">
-        <is>
-          <t>254</t>
-        </is>
-      </c>
-      <c r="V2" t="inlineStr">
-        <is>
-          <t>184</t>
-        </is>
-      </c>
-      <c r="W2" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="X2" t="inlineStr">
-        <is>
-          <t>64</t>
-        </is>
-      </c>
-      <c r="Y2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>06-April-2026</t>
-        </is>
-      </c>
       <c r="AC2" t="inlineStr">
         <is>
           <t>esignet</t>
@@ -938,17 +938,17 @@
       </c>
       <c r="AE2" t="inlineStr">
         <is>
-          <t>274</t>
+          <t>285</t>
         </is>
       </c>
       <c r="AF2" t="inlineStr">
         <is>
-          <t>28</t>
+          <t>21</t>
         </is>
       </c>
       <c r="AG2" t="inlineStr">
         <is>
-          <t>46</t>
+          <t>42</t>
         </is>
       </c>
       <c r="AH2" t="inlineStr">
@@ -965,129 +965,129 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
+          <t>10-April-2026</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>esignet</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>375</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>253</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>41</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>54</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>27</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
           <t>09-April-2026</t>
         </is>
       </c>
-      <c r="B3" t="inlineStr">
+      <c r="K3" t="inlineStr">
         <is>
           <t>esignet</t>
         </is>
       </c>
-      <c r="C3" t="inlineStr">
+      <c r="L3" t="inlineStr">
         <is>
           <t>375</t>
         </is>
       </c>
-      <c r="D3" t="inlineStr">
+      <c r="M3" t="inlineStr">
         <is>
           <t>290</t>
         </is>
       </c>
-      <c r="E3" t="inlineStr">
+      <c r="N3" t="inlineStr">
         <is>
           <t>31</t>
         </is>
       </c>
-      <c r="F3" t="inlineStr">
+      <c r="O3" t="inlineStr">
         <is>
           <t>27</t>
         </is>
       </c>
-      <c r="G3" t="inlineStr">
+      <c r="P3" t="inlineStr">
         <is>
           <t>27</t>
         </is>
       </c>
-      <c r="H3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="J3" t="inlineStr">
+      <c r="Q3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="S3" t="inlineStr">
         <is>
           <t>08-April-2026</t>
         </is>
       </c>
-      <c r="K3" t="inlineStr">
+      <c r="T3" t="inlineStr">
         <is>
           <t>esignet</t>
         </is>
       </c>
-      <c r="L3" t="inlineStr">
+      <c r="U3" t="inlineStr">
         <is>
           <t>375</t>
         </is>
       </c>
-      <c r="M3" t="inlineStr">
+      <c r="V3" t="inlineStr">
         <is>
           <t>267</t>
         </is>
       </c>
-      <c r="N3" t="inlineStr">
+      <c r="W3" t="inlineStr">
         <is>
           <t>32</t>
         </is>
       </c>
-      <c r="O3" t="inlineStr">
+      <c r="X3" t="inlineStr">
         <is>
           <t>49</t>
         </is>
       </c>
-      <c r="P3" t="inlineStr">
+      <c r="Y3" t="inlineStr">
         <is>
           <t>27</t>
         </is>
       </c>
-      <c r="Q3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="S3" t="inlineStr">
+      <c r="Z3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB3" t="inlineStr">
         <is>
           <t>07-April-2026</t>
         </is>
       </c>
-      <c r="T3" t="inlineStr">
-        <is>
-          <t>esignet</t>
-        </is>
-      </c>
-      <c r="U3" t="inlineStr">
-        <is>
-          <t>375</t>
-        </is>
-      </c>
-      <c r="V3" t="inlineStr">
-        <is>
-          <t>285</t>
-        </is>
-      </c>
-      <c r="W3" t="inlineStr">
-        <is>
-          <t>21</t>
-        </is>
-      </c>
-      <c r="X3" t="inlineStr">
-        <is>
-          <t>42</t>
-        </is>
-      </c>
-      <c r="Y3" t="inlineStr">
-        <is>
-          <t>27</t>
-        </is>
-      </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>06-April-2026</t>
-        </is>
-      </c>
       <c r="AC3" t="inlineStr">
         <is>
           <t>injiverify</t>
@@ -1100,17 +1100,17 @@
       </c>
       <c r="AE3" t="inlineStr">
         <is>
-          <t>53</t>
+          <t>0</t>
         </is>
       </c>
       <c r="AF3" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>23</t>
         </is>
       </c>
       <c r="AG3" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>30</t>
         </is>
       </c>
       <c r="AH3" t="inlineStr">
@@ -1127,127 +1127,127 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
+          <t>10-April-2026</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>idrepo</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>152</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>101</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>51</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
           <t>09-April-2026</t>
         </is>
       </c>
-      <c r="B4" t="inlineStr">
+      <c r="K4" t="inlineStr">
         <is>
           <t>idrepo</t>
         </is>
       </c>
-      <c r="C4" t="inlineStr">
+      <c r="L4" t="inlineStr">
         <is>
           <t>152</t>
         </is>
       </c>
-      <c r="D4" t="inlineStr">
+      <c r="M4" t="inlineStr">
         <is>
           <t>101</t>
         </is>
       </c>
-      <c r="E4" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F4" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="G4" t="inlineStr">
+      <c r="N4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P4" t="inlineStr">
         <is>
           <t>51</t>
         </is>
       </c>
-      <c r="H4" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="J4" t="inlineStr">
+      <c r="Q4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="S4" t="inlineStr">
         <is>
           <t>08-April-2026</t>
         </is>
       </c>
-      <c r="K4" t="inlineStr">
+      <c r="T4" t="inlineStr">
         <is>
           <t>idrepo</t>
         </is>
       </c>
-      <c r="L4" t="inlineStr">
+      <c r="U4" t="inlineStr">
         <is>
           <t>152</t>
         </is>
       </c>
-      <c r="M4" t="inlineStr">
+      <c r="V4" t="inlineStr">
         <is>
           <t>101</t>
         </is>
       </c>
-      <c r="N4" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="O4" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="P4" t="inlineStr">
+      <c r="W4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="X4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Y4" t="inlineStr">
         <is>
           <t>51</t>
         </is>
       </c>
-      <c r="Q4" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="S4" t="inlineStr">
+      <c r="Z4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB4" t="inlineStr">
         <is>
           <t>07-April-2026</t>
-        </is>
-      </c>
-      <c r="T4" t="inlineStr">
-        <is>
-          <t>idrepo</t>
-        </is>
-      </c>
-      <c r="U4" t="inlineStr">
-        <is>
-          <t>152</t>
-        </is>
-      </c>
-      <c r="V4" t="inlineStr">
-        <is>
-          <t>101</t>
-        </is>
-      </c>
-      <c r="W4" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="X4" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="Y4" t="inlineStr">
-        <is>
-          <t>51</t>
-        </is>
-      </c>
-      <c r="Z4" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB4" t="inlineStr">
-        <is>
-          <t>06-April-2026</t>
         </is>
       </c>
       <c r="AC4" t="inlineStr">
@@ -1289,127 +1289,127 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
+          <t>10-April-2026</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>injiverify</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>53</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>23</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
           <t>09-April-2026</t>
         </is>
       </c>
-      <c r="B5" t="inlineStr">
+      <c r="K5" t="inlineStr">
         <is>
           <t>injiverify</t>
         </is>
       </c>
-      <c r="C5" t="inlineStr">
+      <c r="L5" t="inlineStr">
         <is>
           <t>53</t>
         </is>
       </c>
-      <c r="D5" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="E5" t="inlineStr">
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="N5" t="inlineStr">
         <is>
           <t>23</t>
         </is>
       </c>
-      <c r="F5" t="inlineStr">
+      <c r="O5" t="inlineStr">
         <is>
           <t>30</t>
         </is>
       </c>
-      <c r="G5" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H5" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="J5" t="inlineStr">
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Q5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="S5" t="inlineStr">
         <is>
           <t>08-April-2026</t>
         </is>
       </c>
-      <c r="K5" t="inlineStr">
+      <c r="T5" t="inlineStr">
         <is>
           <t>injiverify</t>
         </is>
       </c>
-      <c r="L5" t="inlineStr">
+      <c r="U5" t="inlineStr">
         <is>
           <t>53</t>
         </is>
       </c>
-      <c r="M5" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="N5" t="inlineStr">
+      <c r="V5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="W5" t="inlineStr">
         <is>
           <t>23</t>
         </is>
       </c>
-      <c r="O5" t="inlineStr">
+      <c r="X5" t="inlineStr">
         <is>
           <t>30</t>
         </is>
       </c>
-      <c r="P5" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="Q5" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="S5" t="inlineStr">
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Z5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB5" t="inlineStr">
         <is>
           <t>07-April-2026</t>
-        </is>
-      </c>
-      <c r="T5" t="inlineStr">
-        <is>
-          <t>injiverify</t>
-        </is>
-      </c>
-      <c r="U5" t="inlineStr">
-        <is>
-          <t>53</t>
-        </is>
-      </c>
-      <c r="V5" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="W5" t="inlineStr">
-        <is>
-          <t>23</t>
-        </is>
-      </c>
-      <c r="X5" t="inlineStr">
-        <is>
-          <t>30</t>
-        </is>
-      </c>
-      <c r="Y5" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="Z5" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB5" t="inlineStr">
-        <is>
-          <t>06-April-2026</t>
         </is>
       </c>
       <c r="AC5" t="inlineStr">
@@ -1451,112 +1451,112 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
+          <t>10-April-2026</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>mimoto</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>79</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>58</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
           <t>09-April-2026</t>
         </is>
       </c>
-      <c r="B6" t="inlineStr">
+      <c r="K6" t="inlineStr">
         <is>
           <t>mimoto</t>
         </is>
       </c>
-      <c r="C6" t="inlineStr">
+      <c r="L6" t="inlineStr">
         <is>
           <t>79</t>
         </is>
       </c>
-      <c r="D6" t="inlineStr">
+      <c r="M6" t="inlineStr">
         <is>
           <t>59</t>
         </is>
       </c>
-      <c r="E6" t="inlineStr">
+      <c r="N6" t="inlineStr">
         <is>
           <t>4</t>
         </is>
       </c>
-      <c r="F6" t="inlineStr">
+      <c r="O6" t="inlineStr">
         <is>
           <t>4</t>
         </is>
       </c>
-      <c r="G6" t="inlineStr">
+      <c r="P6" t="inlineStr">
         <is>
           <t>10</t>
         </is>
       </c>
-      <c r="H6" t="inlineStr">
+      <c r="Q6" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="J6" t="inlineStr">
+      <c r="S6" t="inlineStr">
         <is>
           <t>08-April-2026</t>
         </is>
       </c>
-      <c r="K6" t="inlineStr">
+      <c r="T6" t="inlineStr">
         <is>
           <t>mimoto</t>
         </is>
       </c>
-      <c r="L6" t="inlineStr">
+      <c r="U6" t="inlineStr">
         <is>
           <t>79</t>
         </is>
       </c>
-      <c r="M6" t="inlineStr">
+      <c r="V6" t="inlineStr">
         <is>
           <t>65</t>
         </is>
       </c>
-      <c r="N6" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="O6" t="inlineStr">
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="X6" t="inlineStr">
         <is>
           <t>2</t>
-        </is>
-      </c>
-      <c r="P6" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="Q6" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="S6" t="inlineStr">
-        <is>
-          <t>07-April-2026</t>
-        </is>
-      </c>
-      <c r="T6" t="inlineStr">
-        <is>
-          <t>mimoto</t>
-        </is>
-      </c>
-      <c r="U6" t="inlineStr">
-        <is>
-          <t>79</t>
-        </is>
-      </c>
-      <c r="V6" t="inlineStr">
-        <is>
-          <t>66</t>
-        </is>
-      </c>
-      <c r="W6" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="X6" t="inlineStr">
-        <is>
-          <t>1</t>
         </is>
       </c>
       <c r="Y6" t="inlineStr">
@@ -1597,87 +1597,87 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
+          <t>10-April-2026</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>prereg</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>104</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>70</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
           <t>09-April-2026</t>
         </is>
       </c>
-      <c r="B7" t="inlineStr">
+      <c r="K7" t="inlineStr">
         <is>
           <t>prereg</t>
         </is>
       </c>
-      <c r="C7" t="inlineStr">
+      <c r="L7" t="inlineStr">
         <is>
           <t>104</t>
         </is>
       </c>
-      <c r="D7" t="inlineStr">
+      <c r="M7" t="inlineStr">
         <is>
           <t>3</t>
         </is>
       </c>
-      <c r="E7" t="inlineStr">
+      <c r="N7" t="inlineStr">
         <is>
           <t>70</t>
         </is>
       </c>
-      <c r="F7" t="inlineStr">
+      <c r="O7" t="inlineStr">
         <is>
           <t>30</t>
         </is>
       </c>
-      <c r="G7" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H7" t="inlineStr">
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Q7" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="J7" t="inlineStr">
+      <c r="S7" t="inlineStr">
         <is>
           <t>08-April-2026</t>
-        </is>
-      </c>
-      <c r="K7" t="inlineStr">
-        <is>
-          <t>prereg</t>
-        </is>
-      </c>
-      <c r="L7" t="inlineStr">
-        <is>
-          <t>104</t>
-        </is>
-      </c>
-      <c r="M7" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="N7" t="inlineStr">
-        <is>
-          <t>70</t>
-        </is>
-      </c>
-      <c r="O7" t="inlineStr">
-        <is>
-          <t>30</t>
-        </is>
-      </c>
-      <c r="P7" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="Q7" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="S7" t="inlineStr">
-        <is>
-          <t>07-April-2026</t>
         </is>
       </c>
       <c r="T7" t="inlineStr">
@@ -1743,87 +1743,87 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
+          <t>10-April-2026</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>residentui</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>33</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
           <t>09-April-2026</t>
         </is>
       </c>
-      <c r="B8" t="inlineStr">
+      <c r="K8" t="inlineStr">
         <is>
           <t>residentui</t>
         </is>
       </c>
-      <c r="C8" t="inlineStr">
+      <c r="L8" t="inlineStr">
         <is>
           <t>33</t>
         </is>
       </c>
-      <c r="D8" t="inlineStr">
+      <c r="M8" t="inlineStr">
         <is>
           <t>12</t>
         </is>
       </c>
-      <c r="E8" t="inlineStr">
+      <c r="N8" t="inlineStr">
         <is>
           <t>5</t>
         </is>
       </c>
-      <c r="F8" t="inlineStr">
+      <c r="O8" t="inlineStr">
         <is>
           <t>16</t>
         </is>
       </c>
-      <c r="G8" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H8" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="J8" t="inlineStr">
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Q8" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="S8" t="inlineStr">
         <is>
           <t>08-April-2026</t>
-        </is>
-      </c>
-      <c r="K8" t="inlineStr">
-        <is>
-          <t>residentui</t>
-        </is>
-      </c>
-      <c r="L8" t="inlineStr">
-        <is>
-          <t>33</t>
-        </is>
-      </c>
-      <c r="M8" t="inlineStr">
-        <is>
-          <t>12</t>
-        </is>
-      </c>
-      <c r="N8" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="O8" t="inlineStr">
-        <is>
-          <t>16</t>
-        </is>
-      </c>
-      <c r="P8" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="Q8" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="S8" t="inlineStr">
-        <is>
-          <t>07-April-2026</t>
         </is>
       </c>
       <c r="T8" t="inlineStr">

--- a/minio-report-tracker/xlxs/collab.xlsx
+++ b/minio-report-tracker/xlxs/collab.xlsx
@@ -598,7 +598,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AI8"/>
+  <dimension ref="A1:Q8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="15" customWidth="1" min="1" max="1"/>
@@ -614,28 +614,10 @@
     <col width="12" customWidth="1" min="11" max="11"/>
     <col width="5" customWidth="1" min="12" max="12"/>
     <col width="5" customWidth="1" min="13" max="13"/>
-    <col width="4" customWidth="1" min="14" max="14"/>
-    <col width="4" customWidth="1" min="15" max="15"/>
-    <col width="4" customWidth="1" min="16" max="16"/>
-    <col width="4" customWidth="1" min="17" max="17"/>
-    <col width="2" customWidth="1" min="18" max="18"/>
-    <col width="15" customWidth="1" min="19" max="19"/>
-    <col width="12" customWidth="1" min="20" max="20"/>
-    <col width="5" customWidth="1" min="21" max="21"/>
-    <col width="5" customWidth="1" min="22" max="22"/>
-    <col width="4" customWidth="1" min="23" max="23"/>
-    <col width="4" customWidth="1" min="24" max="24"/>
-    <col width="4" customWidth="1" min="25" max="25"/>
-    <col width="4" customWidth="1" min="26" max="26"/>
-    <col width="2" customWidth="1" min="27" max="27"/>
-    <col width="15" customWidth="1" min="28" max="28"/>
-    <col width="12" customWidth="1" min="29" max="29"/>
-    <col width="5" customWidth="1" min="30" max="30"/>
-    <col width="5" customWidth="1" min="31" max="31"/>
-    <col width="5" customWidth="1" min="32" max="32"/>
-    <col width="5" customWidth="1" min="33" max="33"/>
-    <col width="5" customWidth="1" min="34" max="34"/>
-    <col width="5" customWidth="1" min="35" max="35"/>
+    <col width="5" customWidth="1" min="14" max="14"/>
+    <col width="5" customWidth="1" min="15" max="15"/>
+    <col width="5" customWidth="1" min="16" max="16"/>
+    <col width="5" customWidth="1" min="17" max="17"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -719,244 +701,84 @@
           <t>KI</t>
         </is>
       </c>
-      <c r="S1" s="1" t="inlineStr">
-        <is>
-          <t>Date</t>
-        </is>
-      </c>
-      <c r="T1" s="1" t="inlineStr">
-        <is>
-          <t>Module</t>
-        </is>
-      </c>
-      <c r="U1" s="1" t="inlineStr">
-        <is>
-          <t>T</t>
-        </is>
-      </c>
-      <c r="V1" s="1" t="inlineStr">
-        <is>
-          <t>P</t>
-        </is>
-      </c>
-      <c r="W1" s="1" t="inlineStr">
-        <is>
-          <t>S</t>
-        </is>
-      </c>
-      <c r="X1" s="1" t="inlineStr">
-        <is>
-          <t>F</t>
-        </is>
-      </c>
-      <c r="Y1" s="1" t="inlineStr">
-        <is>
-          <t>I</t>
-        </is>
-      </c>
-      <c r="Z1" s="1" t="inlineStr">
-        <is>
-          <t>KI</t>
-        </is>
-      </c>
-      <c r="AB1" s="1" t="inlineStr">
-        <is>
-          <t>Date</t>
-        </is>
-      </c>
-      <c r="AC1" s="1" t="inlineStr">
-        <is>
-          <t>Module</t>
-        </is>
-      </c>
-      <c r="AD1" s="1" t="inlineStr">
-        <is>
-          <t>T</t>
-        </is>
-      </c>
-      <c r="AE1" s="1" t="inlineStr">
-        <is>
-          <t>P</t>
-        </is>
-      </c>
-      <c r="AF1" s="1" t="inlineStr">
-        <is>
-          <t>S</t>
-        </is>
-      </c>
-      <c r="AG1" s="1" t="inlineStr">
-        <is>
-          <t>F</t>
-        </is>
-      </c>
-      <c r="AH1" s="1" t="inlineStr">
-        <is>
-          <t>I</t>
-        </is>
-      </c>
-      <c r="AI1" s="1" t="inlineStr">
-        <is>
-          <t>KI</t>
-        </is>
-      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
+          <t>13-April-2026</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>auth</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>254</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>186</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>62</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
           <t>10-April-2026</t>
         </is>
       </c>
-      <c r="B2" t="inlineStr">
-        <is>
-          <t>auth</t>
-        </is>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>254</t>
-        </is>
-      </c>
-      <c r="D2" t="inlineStr">
-        <is>
-          <t>184</t>
-        </is>
-      </c>
-      <c r="E2" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="F2" t="inlineStr">
-        <is>
-          <t>64</t>
-        </is>
-      </c>
-      <c r="G2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="J2" t="inlineStr">
-        <is>
-          <t>09-April-2026</t>
-        </is>
-      </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>auth</t>
+          <t>esignet</t>
         </is>
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>254</t>
+          <t>375</t>
         </is>
       </c>
       <c r="M2" t="inlineStr">
         <is>
-          <t>140</t>
+          <t>253</t>
         </is>
       </c>
       <c r="N2" t="inlineStr">
         <is>
-          <t>72</t>
+          <t>41</t>
         </is>
       </c>
       <c r="O2" t="inlineStr">
         <is>
-          <t>42</t>
+          <t>54</t>
         </is>
       </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>27</t>
         </is>
       </c>
       <c r="Q2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="S2" t="inlineStr">
-        <is>
-          <t>08-April-2026</t>
-        </is>
-      </c>
-      <c r="T2" t="inlineStr">
-        <is>
-          <t>auth</t>
-        </is>
-      </c>
-      <c r="U2" t="inlineStr">
-        <is>
-          <t>254</t>
-        </is>
-      </c>
-      <c r="V2" t="inlineStr">
-        <is>
-          <t>142</t>
-        </is>
-      </c>
-      <c r="W2" t="inlineStr">
-        <is>
-          <t>72</t>
-        </is>
-      </c>
-      <c r="X2" t="inlineStr">
-        <is>
-          <t>40</t>
-        </is>
-      </c>
-      <c r="Y2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>07-April-2026</t>
-        </is>
-      </c>
-      <c r="AC2" t="inlineStr">
-        <is>
-          <t>esignet</t>
-        </is>
-      </c>
-      <c r="AD2" t="inlineStr">
-        <is>
-          <t>375</t>
-        </is>
-      </c>
-      <c r="AE2" t="inlineStr">
-        <is>
-          <t>285</t>
-        </is>
-      </c>
-      <c r="AF2" t="inlineStr">
-        <is>
-          <t>21</t>
-        </is>
-      </c>
-      <c r="AG2" t="inlineStr">
-        <is>
-          <t>42</t>
-        </is>
-      </c>
-      <c r="AH2" t="inlineStr">
-        <is>
-          <t>27</t>
-        </is>
-      </c>
-      <c r="AI2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
@@ -965,160 +787,80 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
+          <t>13-April-2026</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>esignet</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>375</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>262</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>44</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>42</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>27</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
           <t>10-April-2026</t>
         </is>
       </c>
-      <c r="B3" t="inlineStr">
-        <is>
-          <t>esignet</t>
-        </is>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>375</t>
-        </is>
-      </c>
-      <c r="D3" t="inlineStr">
-        <is>
-          <t>253</t>
-        </is>
-      </c>
-      <c r="E3" t="inlineStr">
-        <is>
-          <t>41</t>
-        </is>
-      </c>
-      <c r="F3" t="inlineStr">
-        <is>
-          <t>54</t>
-        </is>
-      </c>
-      <c r="G3" t="inlineStr">
-        <is>
-          <t>27</t>
-        </is>
-      </c>
-      <c r="H3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="J3" t="inlineStr">
-        <is>
-          <t>09-April-2026</t>
-        </is>
-      </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>esignet</t>
+          <t>injiverify</t>
         </is>
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>375</t>
+          <t>53</t>
         </is>
       </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>290</t>
+          <t>0</t>
         </is>
       </c>
       <c r="N3" t="inlineStr">
         <is>
-          <t>31</t>
+          <t>23</t>
         </is>
       </c>
       <c r="O3" t="inlineStr">
         <is>
-          <t>27</t>
+          <t>30</t>
         </is>
       </c>
       <c r="P3" t="inlineStr">
         <is>
-          <t>27</t>
+          <t>0</t>
         </is>
       </c>
       <c r="Q3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="S3" t="inlineStr">
-        <is>
-          <t>08-April-2026</t>
-        </is>
-      </c>
-      <c r="T3" t="inlineStr">
-        <is>
-          <t>esignet</t>
-        </is>
-      </c>
-      <c r="U3" t="inlineStr">
-        <is>
-          <t>375</t>
-        </is>
-      </c>
-      <c r="V3" t="inlineStr">
-        <is>
-          <t>267</t>
-        </is>
-      </c>
-      <c r="W3" t="inlineStr">
-        <is>
-          <t>32</t>
-        </is>
-      </c>
-      <c r="X3" t="inlineStr">
-        <is>
-          <t>49</t>
-        </is>
-      </c>
-      <c r="Y3" t="inlineStr">
-        <is>
-          <t>27</t>
-        </is>
-      </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>07-April-2026</t>
-        </is>
-      </c>
-      <c r="AC3" t="inlineStr">
-        <is>
-          <t>injiverify</t>
-        </is>
-      </c>
-      <c r="AD3" t="inlineStr">
-        <is>
-          <t>53</t>
-        </is>
-      </c>
-      <c r="AE3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AF3" t="inlineStr">
-        <is>
-          <t>23</t>
-        </is>
-      </c>
-      <c r="AG3" t="inlineStr">
-        <is>
-          <t>30</t>
-        </is>
-      </c>
-      <c r="AH3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AI3" t="inlineStr">
         <is>
           <t>0</t>
         </is>
@@ -1127,160 +869,80 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
+          <t>13-April-2026</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>idrepo</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>152</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>101</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>51</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
           <t>10-April-2026</t>
         </is>
       </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>idrepo</t>
-        </is>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>152</t>
-        </is>
-      </c>
-      <c r="D4" t="inlineStr">
-        <is>
-          <t>101</t>
-        </is>
-      </c>
-      <c r="E4" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F4" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="G4" t="inlineStr">
-        <is>
-          <t>51</t>
-        </is>
-      </c>
-      <c r="H4" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="J4" t="inlineStr">
-        <is>
-          <t>09-April-2026</t>
-        </is>
-      </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>idrepo</t>
+          <t>prereg</t>
         </is>
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>152</t>
+          <t>104</t>
         </is>
       </c>
       <c r="M4" t="inlineStr">
         <is>
-          <t>101</t>
+          <t>3</t>
         </is>
       </c>
       <c r="N4" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>70</t>
         </is>
       </c>
       <c r="O4" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>30</t>
         </is>
       </c>
       <c r="P4" t="inlineStr">
         <is>
-          <t>51</t>
+          <t>0</t>
         </is>
       </c>
       <c r="Q4" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="S4" t="inlineStr">
-        <is>
-          <t>08-April-2026</t>
-        </is>
-      </c>
-      <c r="T4" t="inlineStr">
-        <is>
-          <t>idrepo</t>
-        </is>
-      </c>
-      <c r="U4" t="inlineStr">
-        <is>
-          <t>152</t>
-        </is>
-      </c>
-      <c r="V4" t="inlineStr">
-        <is>
-          <t>101</t>
-        </is>
-      </c>
-      <c r="W4" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="X4" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="Y4" t="inlineStr">
-        <is>
-          <t>51</t>
-        </is>
-      </c>
-      <c r="Z4" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB4" t="inlineStr">
-        <is>
-          <t>07-April-2026</t>
-        </is>
-      </c>
-      <c r="AC4" t="inlineStr">
-        <is>
-          <t>prereg</t>
-        </is>
-      </c>
-      <c r="AD4" t="inlineStr">
-        <is>
-          <t>104</t>
-        </is>
-      </c>
-      <c r="AE4" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="AF4" t="inlineStr">
-        <is>
-          <t>70</t>
-        </is>
-      </c>
-      <c r="AG4" t="inlineStr">
-        <is>
-          <t>30</t>
-        </is>
-      </c>
-      <c r="AH4" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AI4" t="inlineStr">
         <is>
           <t>1</t>
         </is>
@@ -1289,72 +951,72 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
+          <t>13-April-2026</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>injiverify</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>53</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>23</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
           <t>10-April-2026</t>
         </is>
       </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>injiverify</t>
-        </is>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>53</t>
-        </is>
-      </c>
-      <c r="D5" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="E5" t="inlineStr">
-        <is>
-          <t>23</t>
-        </is>
-      </c>
-      <c r="F5" t="inlineStr">
-        <is>
-          <t>30</t>
-        </is>
-      </c>
-      <c r="G5" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H5" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="J5" t="inlineStr">
-        <is>
-          <t>09-April-2026</t>
-        </is>
-      </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>injiverify</t>
+          <t>residentui</t>
         </is>
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>53</t>
+          <t>33</t>
         </is>
       </c>
       <c r="M5" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>12</t>
         </is>
       </c>
       <c r="N5" t="inlineStr">
         <is>
-          <t>23</t>
+          <t>5</t>
         </is>
       </c>
       <c r="O5" t="inlineStr">
         <is>
-          <t>30</t>
+          <t>16</t>
         </is>
       </c>
       <c r="P5" t="inlineStr">
@@ -1363,86 +1025,6 @@
         </is>
       </c>
       <c r="Q5" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="S5" t="inlineStr">
-        <is>
-          <t>08-April-2026</t>
-        </is>
-      </c>
-      <c r="T5" t="inlineStr">
-        <is>
-          <t>injiverify</t>
-        </is>
-      </c>
-      <c r="U5" t="inlineStr">
-        <is>
-          <t>53</t>
-        </is>
-      </c>
-      <c r="V5" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="W5" t="inlineStr">
-        <is>
-          <t>23</t>
-        </is>
-      </c>
-      <c r="X5" t="inlineStr">
-        <is>
-          <t>30</t>
-        </is>
-      </c>
-      <c r="Y5" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="Z5" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB5" t="inlineStr">
-        <is>
-          <t>07-April-2026</t>
-        </is>
-      </c>
-      <c r="AC5" t="inlineStr">
-        <is>
-          <t>residentui</t>
-        </is>
-      </c>
-      <c r="AD5" t="inlineStr">
-        <is>
-          <t>33</t>
-        </is>
-      </c>
-      <c r="AE5" t="inlineStr">
-        <is>
-          <t>12</t>
-        </is>
-      </c>
-      <c r="AF5" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="AG5" t="inlineStr">
-        <is>
-          <t>16</t>
-        </is>
-      </c>
-      <c r="AH5" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AI5" t="inlineStr">
         <is>
           <t>0</t>
         </is>
@@ -1451,7 +1033,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>10-April-2026</t>
+          <t>13-April-2026</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -1466,17 +1048,17 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>58</t>
+          <t>65</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>0</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>2</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
@@ -1489,115 +1071,35 @@
           <t>2</t>
         </is>
       </c>
-      <c r="J6" t="inlineStr">
-        <is>
-          <t>09-April-2026</t>
-        </is>
-      </c>
-      <c r="K6" t="inlineStr">
-        <is>
-          <t>mimoto</t>
-        </is>
-      </c>
-      <c r="L6" t="inlineStr">
-        <is>
-          <t>79</t>
-        </is>
-      </c>
-      <c r="M6" t="inlineStr">
-        <is>
-          <t>59</t>
-        </is>
-      </c>
-      <c r="N6" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="O6" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="P6" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="Q6" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="S6" t="inlineStr">
-        <is>
-          <t>08-April-2026</t>
-        </is>
-      </c>
-      <c r="T6" t="inlineStr">
-        <is>
-          <t>mimoto</t>
-        </is>
-      </c>
-      <c r="U6" t="inlineStr">
-        <is>
-          <t>79</t>
-        </is>
-      </c>
-      <c r="V6" t="inlineStr">
-        <is>
-          <t>65</t>
-        </is>
-      </c>
-      <c r="W6" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="X6" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="Y6" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="Z6" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="AB6" t="n">
-        <v/>
-      </c>
-      <c r="AC6" t="n">
-        <v/>
-      </c>
-      <c r="AD6" t="n">
-        <v/>
-      </c>
-      <c r="AE6" t="n">
-        <v/>
-      </c>
-      <c r="AF6" t="n">
-        <v/>
-      </c>
-      <c r="AG6" t="n">
-        <v/>
-      </c>
-      <c r="AH6" t="n">
-        <v/>
-      </c>
-      <c r="AI6" t="n">
+      <c r="J6" t="n">
+        <v/>
+      </c>
+      <c r="K6" t="n">
+        <v/>
+      </c>
+      <c r="L6" t="n">
+        <v/>
+      </c>
+      <c r="M6" t="n">
+        <v/>
+      </c>
+      <c r="N6" t="n">
+        <v/>
+      </c>
+      <c r="O6" t="n">
+        <v/>
+      </c>
+      <c r="P6" t="n">
+        <v/>
+      </c>
+      <c r="Q6" t="n">
         <v/>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>10-April-2026</t>
+          <t>13-April-2026</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -1635,115 +1137,35 @@
           <t>1</t>
         </is>
       </c>
-      <c r="J7" t="inlineStr">
-        <is>
-          <t>09-April-2026</t>
-        </is>
-      </c>
-      <c r="K7" t="inlineStr">
-        <is>
-          <t>prereg</t>
-        </is>
-      </c>
-      <c r="L7" t="inlineStr">
-        <is>
-          <t>104</t>
-        </is>
-      </c>
-      <c r="M7" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="N7" t="inlineStr">
-        <is>
-          <t>70</t>
-        </is>
-      </c>
-      <c r="O7" t="inlineStr">
-        <is>
-          <t>30</t>
-        </is>
-      </c>
-      <c r="P7" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="Q7" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="S7" t="inlineStr">
-        <is>
-          <t>08-April-2026</t>
-        </is>
-      </c>
-      <c r="T7" t="inlineStr">
-        <is>
-          <t>prereg</t>
-        </is>
-      </c>
-      <c r="U7" t="inlineStr">
-        <is>
-          <t>104</t>
-        </is>
-      </c>
-      <c r="V7" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="W7" t="inlineStr">
-        <is>
-          <t>70</t>
-        </is>
-      </c>
-      <c r="X7" t="inlineStr">
-        <is>
-          <t>30</t>
-        </is>
-      </c>
-      <c r="Y7" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="Z7" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="AB7" t="n">
-        <v/>
-      </c>
-      <c r="AC7" t="n">
-        <v/>
-      </c>
-      <c r="AD7" t="n">
-        <v/>
-      </c>
-      <c r="AE7" t="n">
-        <v/>
-      </c>
-      <c r="AF7" t="n">
-        <v/>
-      </c>
-      <c r="AG7" t="n">
-        <v/>
-      </c>
-      <c r="AH7" t="n">
-        <v/>
-      </c>
-      <c r="AI7" t="n">
+      <c r="J7" t="n">
+        <v/>
+      </c>
+      <c r="K7" t="n">
+        <v/>
+      </c>
+      <c r="L7" t="n">
+        <v/>
+      </c>
+      <c r="M7" t="n">
+        <v/>
+      </c>
+      <c r="N7" t="n">
+        <v/>
+      </c>
+      <c r="O7" t="n">
+        <v/>
+      </c>
+      <c r="P7" t="n">
+        <v/>
+      </c>
+      <c r="Q7" t="n">
         <v/>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>10-April-2026</t>
+          <t>13-April-2026</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1781,108 +1203,28 @@
           <t>0</t>
         </is>
       </c>
-      <c r="J8" t="inlineStr">
-        <is>
-          <t>09-April-2026</t>
-        </is>
-      </c>
-      <c r="K8" t="inlineStr">
-        <is>
-          <t>residentui</t>
-        </is>
-      </c>
-      <c r="L8" t="inlineStr">
-        <is>
-          <t>33</t>
-        </is>
-      </c>
-      <c r="M8" t="inlineStr">
-        <is>
-          <t>12</t>
-        </is>
-      </c>
-      <c r="N8" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="O8" t="inlineStr">
-        <is>
-          <t>16</t>
-        </is>
-      </c>
-      <c r="P8" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="Q8" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="S8" t="inlineStr">
-        <is>
-          <t>08-April-2026</t>
-        </is>
-      </c>
-      <c r="T8" t="inlineStr">
-        <is>
-          <t>residentui</t>
-        </is>
-      </c>
-      <c r="U8" t="inlineStr">
-        <is>
-          <t>33</t>
-        </is>
-      </c>
-      <c r="V8" t="inlineStr">
-        <is>
-          <t>12</t>
-        </is>
-      </c>
-      <c r="W8" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="X8" t="inlineStr">
-        <is>
-          <t>16</t>
-        </is>
-      </c>
-      <c r="Y8" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="Z8" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB8" t="n">
-        <v/>
-      </c>
-      <c r="AC8" t="n">
-        <v/>
-      </c>
-      <c r="AD8" t="n">
-        <v/>
-      </c>
-      <c r="AE8" t="n">
-        <v/>
-      </c>
-      <c r="AF8" t="n">
-        <v/>
-      </c>
-      <c r="AG8" t="n">
-        <v/>
-      </c>
-      <c r="AH8" t="n">
-        <v/>
-      </c>
-      <c r="AI8" t="n">
+      <c r="J8" t="n">
+        <v/>
+      </c>
+      <c r="K8" t="n">
+        <v/>
+      </c>
+      <c r="L8" t="n">
+        <v/>
+      </c>
+      <c r="M8" t="n">
+        <v/>
+      </c>
+      <c r="N8" t="n">
+        <v/>
+      </c>
+      <c r="O8" t="n">
+        <v/>
+      </c>
+      <c r="P8" t="n">
+        <v/>
+      </c>
+      <c r="Q8" t="n">
         <v/>
       </c>
     </row>

--- a/minio-report-tracker/xlxs/collab.xlsx
+++ b/minio-report-tracker/xlxs/collab.xlsx
@@ -614,10 +614,10 @@
     <col width="12" customWidth="1" min="11" max="11"/>
     <col width="5" customWidth="1" min="12" max="12"/>
     <col width="5" customWidth="1" min="13" max="13"/>
-    <col width="5" customWidth="1" min="14" max="14"/>
-    <col width="5" customWidth="1" min="15" max="15"/>
-    <col width="5" customWidth="1" min="16" max="16"/>
-    <col width="5" customWidth="1" min="17" max="17"/>
+    <col width="4" customWidth="1" min="14" max="14"/>
+    <col width="4" customWidth="1" min="15" max="15"/>
+    <col width="4" customWidth="1" min="16" max="16"/>
+    <col width="4" customWidth="1" min="17" max="17"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -705,77 +705,77 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
+          <t>14-April-2026</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>auth</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>254</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>186</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>62</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
           <t>13-April-2026</t>
         </is>
       </c>
-      <c r="B2" t="inlineStr">
+      <c r="K2" t="inlineStr">
         <is>
           <t>auth</t>
         </is>
       </c>
-      <c r="C2" t="inlineStr">
+      <c r="L2" t="inlineStr">
         <is>
           <t>254</t>
         </is>
       </c>
-      <c r="D2" t="inlineStr">
+      <c r="M2" t="inlineStr">
         <is>
           <t>186</t>
         </is>
       </c>
-      <c r="E2" t="inlineStr">
+      <c r="N2" t="inlineStr">
         <is>
           <t>6</t>
         </is>
       </c>
-      <c r="F2" t="inlineStr">
+      <c r="O2" t="inlineStr">
         <is>
           <t>62</t>
         </is>
       </c>
-      <c r="G2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="J2" t="inlineStr">
-        <is>
-          <t>10-April-2026</t>
-        </is>
-      </c>
-      <c r="K2" t="inlineStr">
-        <is>
-          <t>esignet</t>
-        </is>
-      </c>
-      <c r="L2" t="inlineStr">
-        <is>
-          <t>375</t>
-        </is>
-      </c>
-      <c r="M2" t="inlineStr">
-        <is>
-          <t>253</t>
-        </is>
-      </c>
-      <c r="N2" t="inlineStr">
-        <is>
-          <t>41</t>
-        </is>
-      </c>
-      <c r="O2" t="inlineStr">
-        <is>
-          <t>54</t>
-        </is>
-      </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>27</t>
+          <t>0</t>
         </is>
       </c>
       <c r="Q2" t="inlineStr">
@@ -787,77 +787,77 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
+          <t>14-April-2026</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>esignet</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>375</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>264</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>37</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>47</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>27</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
           <t>13-April-2026</t>
         </is>
       </c>
-      <c r="B3" t="inlineStr">
+      <c r="K3" t="inlineStr">
         <is>
           <t>esignet</t>
         </is>
       </c>
-      <c r="C3" t="inlineStr">
+      <c r="L3" t="inlineStr">
         <is>
           <t>375</t>
         </is>
       </c>
-      <c r="D3" t="inlineStr">
+      <c r="M3" t="inlineStr">
         <is>
           <t>262</t>
         </is>
       </c>
-      <c r="E3" t="inlineStr">
+      <c r="N3" t="inlineStr">
         <is>
           <t>44</t>
         </is>
       </c>
-      <c r="F3" t="inlineStr">
+      <c r="O3" t="inlineStr">
         <is>
           <t>42</t>
         </is>
       </c>
-      <c r="G3" t="inlineStr">
+      <c r="P3" t="inlineStr">
         <is>
           <t>27</t>
-        </is>
-      </c>
-      <c r="H3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="J3" t="inlineStr">
-        <is>
-          <t>10-April-2026</t>
-        </is>
-      </c>
-      <c r="K3" t="inlineStr">
-        <is>
-          <t>injiverify</t>
-        </is>
-      </c>
-      <c r="L3" t="inlineStr">
-        <is>
-          <t>53</t>
-        </is>
-      </c>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="N3" t="inlineStr">
-        <is>
-          <t>23</t>
-        </is>
-      </c>
-      <c r="O3" t="inlineStr">
-        <is>
-          <t>30</t>
-        </is>
-      </c>
-      <c r="P3" t="inlineStr">
-        <is>
-          <t>0</t>
         </is>
       </c>
       <c r="Q3" t="inlineStr">
@@ -869,154 +869,154 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
+          <t>14-April-2026</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>idrepo</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>152</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>101</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>51</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
           <t>13-April-2026</t>
         </is>
       </c>
-      <c r="B4" t="inlineStr">
+      <c r="K4" t="inlineStr">
         <is>
           <t>idrepo</t>
         </is>
       </c>
-      <c r="C4" t="inlineStr">
+      <c r="L4" t="inlineStr">
         <is>
           <t>152</t>
         </is>
       </c>
-      <c r="D4" t="inlineStr">
+      <c r="M4" t="inlineStr">
         <is>
           <t>101</t>
         </is>
       </c>
-      <c r="E4" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F4" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="G4" t="inlineStr">
+      <c r="N4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P4" t="inlineStr">
         <is>
           <t>51</t>
         </is>
       </c>
-      <c r="H4" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="J4" t="inlineStr">
-        <is>
-          <t>10-April-2026</t>
-        </is>
-      </c>
-      <c r="K4" t="inlineStr">
-        <is>
-          <t>prereg</t>
-        </is>
-      </c>
-      <c r="L4" t="inlineStr">
-        <is>
-          <t>104</t>
-        </is>
-      </c>
-      <c r="M4" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="N4" t="inlineStr">
-        <is>
-          <t>70</t>
-        </is>
-      </c>
-      <c r="O4" t="inlineStr">
-        <is>
-          <t>30</t>
-        </is>
-      </c>
-      <c r="P4" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
       <c r="Q4" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
+          <t>14-April-2026</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>injiverify</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>53</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>23</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
           <t>13-April-2026</t>
         </is>
       </c>
-      <c r="B5" t="inlineStr">
+      <c r="K5" t="inlineStr">
         <is>
           <t>injiverify</t>
         </is>
       </c>
-      <c r="C5" t="inlineStr">
+      <c r="L5" t="inlineStr">
         <is>
           <t>53</t>
         </is>
       </c>
-      <c r="D5" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="E5" t="inlineStr">
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="N5" t="inlineStr">
         <is>
           <t>23</t>
         </is>
       </c>
-      <c r="F5" t="inlineStr">
+      <c r="O5" t="inlineStr">
         <is>
           <t>30</t>
-        </is>
-      </c>
-      <c r="G5" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H5" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="J5" t="inlineStr">
-        <is>
-          <t>10-April-2026</t>
-        </is>
-      </c>
-      <c r="K5" t="inlineStr">
-        <is>
-          <t>residentui</t>
-        </is>
-      </c>
-      <c r="L5" t="inlineStr">
-        <is>
-          <t>33</t>
-        </is>
-      </c>
-      <c r="M5" t="inlineStr">
-        <is>
-          <t>12</t>
-        </is>
-      </c>
-      <c r="N5" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="O5" t="inlineStr">
-        <is>
-          <t>16</t>
         </is>
       </c>
       <c r="P5" t="inlineStr">
@@ -1033,199 +1033,247 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
+          <t>14-April-2026</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>mimoto</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>79</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>66</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
           <t>13-April-2026</t>
         </is>
       </c>
-      <c r="B6" t="inlineStr">
+      <c r="K6" t="inlineStr">
         <is>
           <t>mimoto</t>
         </is>
       </c>
-      <c r="C6" t="inlineStr">
+      <c r="L6" t="inlineStr">
         <is>
           <t>79</t>
         </is>
       </c>
-      <c r="D6" t="inlineStr">
+      <c r="M6" t="inlineStr">
         <is>
           <t>65</t>
         </is>
       </c>
-      <c r="E6" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F6" t="inlineStr">
+      <c r="N6" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O6" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="G6" t="inlineStr">
+      <c r="P6" t="inlineStr">
         <is>
           <t>10</t>
         </is>
       </c>
-      <c r="H6" t="inlineStr">
+      <c r="Q6" t="inlineStr">
         <is>
           <t>2</t>
         </is>
-      </c>
-      <c r="J6" t="n">
-        <v/>
-      </c>
-      <c r="K6" t="n">
-        <v/>
-      </c>
-      <c r="L6" t="n">
-        <v/>
-      </c>
-      <c r="M6" t="n">
-        <v/>
-      </c>
-      <c r="N6" t="n">
-        <v/>
-      </c>
-      <c r="O6" t="n">
-        <v/>
-      </c>
-      <c r="P6" t="n">
-        <v/>
-      </c>
-      <c r="Q6" t="n">
-        <v/>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
+          <t>14-April-2026</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>prereg</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>104</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>70</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
           <t>13-April-2026</t>
         </is>
       </c>
-      <c r="B7" t="inlineStr">
+      <c r="K7" t="inlineStr">
         <is>
           <t>prereg</t>
         </is>
       </c>
-      <c r="C7" t="inlineStr">
+      <c r="L7" t="inlineStr">
         <is>
           <t>104</t>
         </is>
       </c>
-      <c r="D7" t="inlineStr">
+      <c r="M7" t="inlineStr">
         <is>
           <t>3</t>
         </is>
       </c>
-      <c r="E7" t="inlineStr">
+      <c r="N7" t="inlineStr">
         <is>
           <t>70</t>
         </is>
       </c>
-      <c r="F7" t="inlineStr">
+      <c r="O7" t="inlineStr">
         <is>
           <t>30</t>
         </is>
       </c>
-      <c r="G7" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H7" t="inlineStr">
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Q7" t="inlineStr">
         <is>
           <t>1</t>
         </is>
-      </c>
-      <c r="J7" t="n">
-        <v/>
-      </c>
-      <c r="K7" t="n">
-        <v/>
-      </c>
-      <c r="L7" t="n">
-        <v/>
-      </c>
-      <c r="M7" t="n">
-        <v/>
-      </c>
-      <c r="N7" t="n">
-        <v/>
-      </c>
-      <c r="O7" t="n">
-        <v/>
-      </c>
-      <c r="P7" t="n">
-        <v/>
-      </c>
-      <c r="Q7" t="n">
-        <v/>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
+          <t>14-April-2026</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>residentui</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>33</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
           <t>13-April-2026</t>
         </is>
       </c>
-      <c r="B8" t="inlineStr">
+      <c r="K8" t="inlineStr">
         <is>
           <t>residentui</t>
         </is>
       </c>
-      <c r="C8" t="inlineStr">
+      <c r="L8" t="inlineStr">
         <is>
           <t>33</t>
         </is>
       </c>
-      <c r="D8" t="inlineStr">
+      <c r="M8" t="inlineStr">
         <is>
           <t>12</t>
         </is>
       </c>
-      <c r="E8" t="inlineStr">
+      <c r="N8" t="inlineStr">
         <is>
           <t>5</t>
         </is>
       </c>
-      <c r="F8" t="inlineStr">
+      <c r="O8" t="inlineStr">
         <is>
           <t>16</t>
         </is>
       </c>
-      <c r="G8" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H8" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="J8" t="n">
-        <v/>
-      </c>
-      <c r="K8" t="n">
-        <v/>
-      </c>
-      <c r="L8" t="n">
-        <v/>
-      </c>
-      <c r="M8" t="n">
-        <v/>
-      </c>
-      <c r="N8" t="n">
-        <v/>
-      </c>
-      <c r="O8" t="n">
-        <v/>
-      </c>
-      <c r="P8" t="n">
-        <v/>
-      </c>
-      <c r="Q8" t="n">
-        <v/>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Q8" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
     </row>
   </sheetData>

--- a/minio-report-tracker/xlxs/collab.xlsx
+++ b/minio-report-tracker/xlxs/collab.xlsx
@@ -598,7 +598,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q8"/>
+  <dimension ref="A1:Z8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="15" customWidth="1" min="1" max="1"/>
@@ -618,6 +618,15 @@
     <col width="4" customWidth="1" min="15" max="15"/>
     <col width="4" customWidth="1" min="16" max="16"/>
     <col width="4" customWidth="1" min="17" max="17"/>
+    <col width="2" customWidth="1" min="18" max="18"/>
+    <col width="15" customWidth="1" min="19" max="19"/>
+    <col width="12" customWidth="1" min="20" max="20"/>
+    <col width="5" customWidth="1" min="21" max="21"/>
+    <col width="5" customWidth="1" min="22" max="22"/>
+    <col width="4" customWidth="1" min="23" max="23"/>
+    <col width="4" customWidth="1" min="24" max="24"/>
+    <col width="4" customWidth="1" min="25" max="25"/>
+    <col width="4" customWidth="1" min="26" max="26"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -701,84 +710,164 @@
           <t>KI</t>
         </is>
       </c>
+      <c r="S1" s="1" t="inlineStr">
+        <is>
+          <t>Date</t>
+        </is>
+      </c>
+      <c r="T1" s="1" t="inlineStr">
+        <is>
+          <t>Module</t>
+        </is>
+      </c>
+      <c r="U1" s="1" t="inlineStr">
+        <is>
+          <t>T</t>
+        </is>
+      </c>
+      <c r="V1" s="1" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
+      <c r="W1" s="1" t="inlineStr">
+        <is>
+          <t>S</t>
+        </is>
+      </c>
+      <c r="X1" s="1" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
+      <c r="Y1" s="1" t="inlineStr">
+        <is>
+          <t>I</t>
+        </is>
+      </c>
+      <c r="Z1" s="1" t="inlineStr">
+        <is>
+          <t>KI</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
+          <t>15-April-2026</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>auth</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>254</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>184</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>64</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
           <t>14-April-2026</t>
         </is>
       </c>
-      <c r="B2" t="inlineStr">
+      <c r="K2" t="inlineStr">
         <is>
           <t>auth</t>
         </is>
       </c>
-      <c r="C2" t="inlineStr">
+      <c r="L2" t="inlineStr">
         <is>
           <t>254</t>
         </is>
       </c>
-      <c r="D2" t="inlineStr">
+      <c r="M2" t="inlineStr">
         <is>
           <t>186</t>
         </is>
       </c>
-      <c r="E2" t="inlineStr">
+      <c r="N2" t="inlineStr">
         <is>
           <t>6</t>
         </is>
       </c>
-      <c r="F2" t="inlineStr">
+      <c r="O2" t="inlineStr">
         <is>
           <t>62</t>
         </is>
       </c>
-      <c r="G2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="J2" t="inlineStr">
+      <c r="P2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Q2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="S2" t="inlineStr">
         <is>
           <t>13-April-2026</t>
         </is>
       </c>
-      <c r="K2" t="inlineStr">
+      <c r="T2" t="inlineStr">
         <is>
           <t>auth</t>
         </is>
       </c>
-      <c r="L2" t="inlineStr">
+      <c r="U2" t="inlineStr">
         <is>
           <t>254</t>
         </is>
       </c>
-      <c r="M2" t="inlineStr">
+      <c r="V2" t="inlineStr">
         <is>
           <t>186</t>
         </is>
       </c>
-      <c r="N2" t="inlineStr">
+      <c r="W2" t="inlineStr">
         <is>
           <t>6</t>
         </is>
       </c>
-      <c r="O2" t="inlineStr">
+      <c r="X2" t="inlineStr">
         <is>
           <t>62</t>
         </is>
       </c>
-      <c r="P2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="Q2" t="inlineStr">
+      <c r="Y2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Z2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
@@ -787,80 +876,120 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
+          <t>15-April-2026</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>esignet</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>375</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>265</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>33</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>27</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
           <t>14-April-2026</t>
         </is>
       </c>
-      <c r="B3" t="inlineStr">
+      <c r="K3" t="inlineStr">
         <is>
           <t>esignet</t>
         </is>
       </c>
-      <c r="C3" t="inlineStr">
+      <c r="L3" t="inlineStr">
         <is>
           <t>375</t>
         </is>
       </c>
-      <c r="D3" t="inlineStr">
+      <c r="M3" t="inlineStr">
         <is>
           <t>264</t>
         </is>
       </c>
-      <c r="E3" t="inlineStr">
+      <c r="N3" t="inlineStr">
         <is>
           <t>37</t>
         </is>
       </c>
-      <c r="F3" t="inlineStr">
+      <c r="O3" t="inlineStr">
         <is>
           <t>47</t>
         </is>
       </c>
-      <c r="G3" t="inlineStr">
+      <c r="P3" t="inlineStr">
         <is>
           <t>27</t>
         </is>
       </c>
-      <c r="H3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="J3" t="inlineStr">
+      <c r="Q3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="S3" t="inlineStr">
         <is>
           <t>13-April-2026</t>
         </is>
       </c>
-      <c r="K3" t="inlineStr">
+      <c r="T3" t="inlineStr">
         <is>
           <t>esignet</t>
         </is>
       </c>
-      <c r="L3" t="inlineStr">
+      <c r="U3" t="inlineStr">
         <is>
           <t>375</t>
         </is>
       </c>
-      <c r="M3" t="inlineStr">
+      <c r="V3" t="inlineStr">
         <is>
           <t>262</t>
         </is>
       </c>
-      <c r="N3" t="inlineStr">
+      <c r="W3" t="inlineStr">
         <is>
           <t>44</t>
         </is>
       </c>
-      <c r="O3" t="inlineStr">
+      <c r="X3" t="inlineStr">
         <is>
           <t>42</t>
         </is>
       </c>
-      <c r="P3" t="inlineStr">
+      <c r="Y3" t="inlineStr">
         <is>
           <t>27</t>
         </is>
       </c>
-      <c r="Q3" t="inlineStr">
+      <c r="Z3" t="inlineStr">
         <is>
           <t>0</t>
         </is>
@@ -869,80 +998,120 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
+          <t>15-April-2026</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>idrepo</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>152</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>101</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>51</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
           <t>14-April-2026</t>
         </is>
       </c>
-      <c r="B4" t="inlineStr">
+      <c r="K4" t="inlineStr">
         <is>
           <t>idrepo</t>
         </is>
       </c>
-      <c r="C4" t="inlineStr">
+      <c r="L4" t="inlineStr">
         <is>
           <t>152</t>
         </is>
       </c>
-      <c r="D4" t="inlineStr">
+      <c r="M4" t="inlineStr">
         <is>
           <t>101</t>
         </is>
       </c>
-      <c r="E4" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F4" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="G4" t="inlineStr">
+      <c r="N4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P4" t="inlineStr">
         <is>
           <t>51</t>
         </is>
       </c>
-      <c r="H4" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="J4" t="inlineStr">
+      <c r="Q4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="S4" t="inlineStr">
         <is>
           <t>13-April-2026</t>
         </is>
       </c>
-      <c r="K4" t="inlineStr">
+      <c r="T4" t="inlineStr">
         <is>
           <t>idrepo</t>
         </is>
       </c>
-      <c r="L4" t="inlineStr">
+      <c r="U4" t="inlineStr">
         <is>
           <t>152</t>
         </is>
       </c>
-      <c r="M4" t="inlineStr">
+      <c r="V4" t="inlineStr">
         <is>
           <t>101</t>
         </is>
       </c>
-      <c r="N4" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="O4" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="P4" t="inlineStr">
+      <c r="W4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="X4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Y4" t="inlineStr">
         <is>
           <t>51</t>
         </is>
       </c>
-      <c r="Q4" t="inlineStr">
+      <c r="Z4" t="inlineStr">
         <is>
           <t>0</t>
         </is>
@@ -951,80 +1120,120 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
+          <t>15-April-2026</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>injiverify</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>53</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>23</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
           <t>14-April-2026</t>
         </is>
       </c>
-      <c r="B5" t="inlineStr">
+      <c r="K5" t="inlineStr">
         <is>
           <t>injiverify</t>
         </is>
       </c>
-      <c r="C5" t="inlineStr">
+      <c r="L5" t="inlineStr">
         <is>
           <t>53</t>
         </is>
       </c>
-      <c r="D5" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="E5" t="inlineStr">
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="N5" t="inlineStr">
         <is>
           <t>23</t>
         </is>
       </c>
-      <c r="F5" t="inlineStr">
+      <c r="O5" t="inlineStr">
         <is>
           <t>30</t>
         </is>
       </c>
-      <c r="G5" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H5" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="J5" t="inlineStr">
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Q5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="S5" t="inlineStr">
         <is>
           <t>13-April-2026</t>
         </is>
       </c>
-      <c r="K5" t="inlineStr">
+      <c r="T5" t="inlineStr">
         <is>
           <t>injiverify</t>
         </is>
       </c>
-      <c r="L5" t="inlineStr">
+      <c r="U5" t="inlineStr">
         <is>
           <t>53</t>
         </is>
       </c>
-      <c r="M5" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="N5" t="inlineStr">
+      <c r="V5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="W5" t="inlineStr">
         <is>
           <t>23</t>
         </is>
       </c>
-      <c r="O5" t="inlineStr">
+      <c r="X5" t="inlineStr">
         <is>
           <t>30</t>
         </is>
       </c>
-      <c r="P5" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="Q5" t="inlineStr">
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Z5" t="inlineStr">
         <is>
           <t>0</t>
         </is>
@@ -1033,80 +1242,120 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
+          <t>15-April-2026</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>mimoto</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>79</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>66</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
           <t>14-April-2026</t>
         </is>
       </c>
-      <c r="B6" t="inlineStr">
+      <c r="K6" t="inlineStr">
         <is>
           <t>mimoto</t>
         </is>
       </c>
-      <c r="C6" t="inlineStr">
+      <c r="L6" t="inlineStr">
         <is>
           <t>79</t>
         </is>
       </c>
-      <c r="D6" t="inlineStr">
+      <c r="M6" t="inlineStr">
         <is>
           <t>66</t>
         </is>
       </c>
-      <c r="E6" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F6" t="inlineStr">
+      <c r="N6" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O6" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="G6" t="inlineStr">
+      <c r="P6" t="inlineStr">
         <is>
           <t>10</t>
         </is>
       </c>
-      <c r="H6" t="inlineStr">
+      <c r="Q6" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="J6" t="inlineStr">
+      <c r="S6" t="inlineStr">
         <is>
           <t>13-April-2026</t>
         </is>
       </c>
-      <c r="K6" t="inlineStr">
+      <c r="T6" t="inlineStr">
         <is>
           <t>mimoto</t>
         </is>
       </c>
-      <c r="L6" t="inlineStr">
+      <c r="U6" t="inlineStr">
         <is>
           <t>79</t>
         </is>
       </c>
-      <c r="M6" t="inlineStr">
+      <c r="V6" t="inlineStr">
         <is>
           <t>65</t>
         </is>
       </c>
-      <c r="N6" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="O6" t="inlineStr">
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="X6" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="P6" t="inlineStr">
+      <c r="Y6" t="inlineStr">
         <is>
           <t>10</t>
         </is>
       </c>
-      <c r="Q6" t="inlineStr">
+      <c r="Z6" t="inlineStr">
         <is>
           <t>2</t>
         </is>
@@ -1115,80 +1364,120 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
+          <t>15-April-2026</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>prereg</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>104</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>70</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
           <t>14-April-2026</t>
         </is>
       </c>
-      <c r="B7" t="inlineStr">
+      <c r="K7" t="inlineStr">
         <is>
           <t>prereg</t>
         </is>
       </c>
-      <c r="C7" t="inlineStr">
+      <c r="L7" t="inlineStr">
         <is>
           <t>104</t>
         </is>
       </c>
-      <c r="D7" t="inlineStr">
+      <c r="M7" t="inlineStr">
         <is>
           <t>3</t>
         </is>
       </c>
-      <c r="E7" t="inlineStr">
+      <c r="N7" t="inlineStr">
         <is>
           <t>70</t>
         </is>
       </c>
-      <c r="F7" t="inlineStr">
+      <c r="O7" t="inlineStr">
         <is>
           <t>30</t>
         </is>
       </c>
-      <c r="G7" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H7" t="inlineStr">
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Q7" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="J7" t="inlineStr">
+      <c r="S7" t="inlineStr">
         <is>
           <t>13-April-2026</t>
         </is>
       </c>
-      <c r="K7" t="inlineStr">
+      <c r="T7" t="inlineStr">
         <is>
           <t>prereg</t>
         </is>
       </c>
-      <c r="L7" t="inlineStr">
+      <c r="U7" t="inlineStr">
         <is>
           <t>104</t>
         </is>
       </c>
-      <c r="M7" t="inlineStr">
+      <c r="V7" t="inlineStr">
         <is>
           <t>3</t>
         </is>
       </c>
-      <c r="N7" t="inlineStr">
+      <c r="W7" t="inlineStr">
         <is>
           <t>70</t>
         </is>
       </c>
-      <c r="O7" t="inlineStr">
+      <c r="X7" t="inlineStr">
         <is>
           <t>30</t>
         </is>
       </c>
-      <c r="P7" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="Q7" t="inlineStr">
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Z7" t="inlineStr">
         <is>
           <t>1</t>
         </is>
@@ -1197,80 +1486,120 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
+          <t>15-April-2026</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>residentui</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>33</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
           <t>14-April-2026</t>
         </is>
       </c>
-      <c r="B8" t="inlineStr">
+      <c r="K8" t="inlineStr">
         <is>
           <t>residentui</t>
         </is>
       </c>
-      <c r="C8" t="inlineStr">
+      <c r="L8" t="inlineStr">
         <is>
           <t>33</t>
         </is>
       </c>
-      <c r="D8" t="inlineStr">
+      <c r="M8" t="inlineStr">
         <is>
           <t>12</t>
         </is>
       </c>
-      <c r="E8" t="inlineStr">
+      <c r="N8" t="inlineStr">
         <is>
           <t>5</t>
         </is>
       </c>
-      <c r="F8" t="inlineStr">
+      <c r="O8" t="inlineStr">
         <is>
           <t>16</t>
         </is>
       </c>
-      <c r="G8" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H8" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="J8" t="inlineStr">
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Q8" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="S8" t="inlineStr">
         <is>
           <t>13-April-2026</t>
         </is>
       </c>
-      <c r="K8" t="inlineStr">
+      <c r="T8" t="inlineStr">
         <is>
           <t>residentui</t>
         </is>
       </c>
-      <c r="L8" t="inlineStr">
+      <c r="U8" t="inlineStr">
         <is>
           <t>33</t>
         </is>
       </c>
-      <c r="M8" t="inlineStr">
+      <c r="V8" t="inlineStr">
         <is>
           <t>12</t>
         </is>
       </c>
-      <c r="N8" t="inlineStr">
+      <c r="W8" t="inlineStr">
         <is>
           <t>5</t>
         </is>
       </c>
-      <c r="O8" t="inlineStr">
+      <c r="X8" t="inlineStr">
         <is>
           <t>16</t>
         </is>
       </c>
-      <c r="P8" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="Q8" t="inlineStr">
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Z8" t="inlineStr">
         <is>
           <t>0</t>
         </is>

--- a/minio-report-tracker/xlxs/collab.xlsx
+++ b/minio-report-tracker/xlxs/collab.xlsx
@@ -598,7 +598,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Z8"/>
+  <dimension ref="A1:AI8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="15" customWidth="1" min="1" max="1"/>
@@ -627,6 +627,15 @@
     <col width="4" customWidth="1" min="24" max="24"/>
     <col width="4" customWidth="1" min="25" max="25"/>
     <col width="4" customWidth="1" min="26" max="26"/>
+    <col width="2" customWidth="1" min="27" max="27"/>
+    <col width="15" customWidth="1" min="28" max="28"/>
+    <col width="12" customWidth="1" min="29" max="29"/>
+    <col width="5" customWidth="1" min="30" max="30"/>
+    <col width="5" customWidth="1" min="31" max="31"/>
+    <col width="5" customWidth="1" min="32" max="32"/>
+    <col width="5" customWidth="1" min="33" max="33"/>
+    <col width="5" customWidth="1" min="34" max="34"/>
+    <col width="5" customWidth="1" min="35" max="35"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -750,124 +759,204 @@
           <t>KI</t>
         </is>
       </c>
+      <c r="AB1" s="1" t="inlineStr">
+        <is>
+          <t>Date</t>
+        </is>
+      </c>
+      <c r="AC1" s="1" t="inlineStr">
+        <is>
+          <t>Module</t>
+        </is>
+      </c>
+      <c r="AD1" s="1" t="inlineStr">
+        <is>
+          <t>T</t>
+        </is>
+      </c>
+      <c r="AE1" s="1" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
+      <c r="AF1" s="1" t="inlineStr">
+        <is>
+          <t>S</t>
+        </is>
+      </c>
+      <c r="AG1" s="1" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
+      <c r="AH1" s="1" t="inlineStr">
+        <is>
+          <t>I</t>
+        </is>
+      </c>
+      <c r="AI1" s="1" t="inlineStr">
+        <is>
+          <t>KI</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
+          <t>16-April-2026</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>auth</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>254</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>186</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>62</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
           <t>15-April-2026</t>
         </is>
       </c>
-      <c r="B2" t="inlineStr">
+      <c r="K2" t="inlineStr">
         <is>
           <t>auth</t>
         </is>
       </c>
-      <c r="C2" t="inlineStr">
+      <c r="L2" t="inlineStr">
         <is>
           <t>254</t>
         </is>
       </c>
-      <c r="D2" t="inlineStr">
+      <c r="M2" t="inlineStr">
         <is>
           <t>184</t>
         </is>
       </c>
-      <c r="E2" t="inlineStr">
+      <c r="N2" t="inlineStr">
         <is>
           <t>6</t>
         </is>
       </c>
-      <c r="F2" t="inlineStr">
+      <c r="O2" t="inlineStr">
         <is>
           <t>64</t>
         </is>
       </c>
-      <c r="G2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="J2" t="inlineStr">
+      <c r="P2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Q2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="S2" t="inlineStr">
         <is>
           <t>14-April-2026</t>
         </is>
       </c>
-      <c r="K2" t="inlineStr">
+      <c r="T2" t="inlineStr">
         <is>
           <t>auth</t>
         </is>
       </c>
-      <c r="L2" t="inlineStr">
+      <c r="U2" t="inlineStr">
         <is>
           <t>254</t>
         </is>
       </c>
-      <c r="M2" t="inlineStr">
+      <c r="V2" t="inlineStr">
         <is>
           <t>186</t>
         </is>
       </c>
-      <c r="N2" t="inlineStr">
+      <c r="W2" t="inlineStr">
         <is>
           <t>6</t>
         </is>
       </c>
-      <c r="O2" t="inlineStr">
+      <c r="X2" t="inlineStr">
         <is>
           <t>62</t>
         </is>
       </c>
-      <c r="P2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="Q2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="S2" t="inlineStr">
+      <c r="Y2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Z2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB2" t="inlineStr">
         <is>
           <t>13-April-2026</t>
         </is>
       </c>
-      <c r="T2" t="inlineStr">
-        <is>
-          <t>auth</t>
-        </is>
-      </c>
-      <c r="U2" t="inlineStr">
-        <is>
-          <t>254</t>
-        </is>
-      </c>
-      <c r="V2" t="inlineStr">
-        <is>
-          <t>186</t>
-        </is>
-      </c>
-      <c r="W2" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="X2" t="inlineStr">
-        <is>
-          <t>62</t>
-        </is>
-      </c>
-      <c r="Y2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="Z2" t="inlineStr">
+      <c r="AC2" t="inlineStr">
+        <is>
+          <t>esignet</t>
+        </is>
+      </c>
+      <c r="AD2" t="inlineStr">
+        <is>
+          <t>375</t>
+        </is>
+      </c>
+      <c r="AE2" t="inlineStr">
+        <is>
+          <t>262</t>
+        </is>
+      </c>
+      <c r="AF2" t="inlineStr">
+        <is>
+          <t>44</t>
+        </is>
+      </c>
+      <c r="AG2" t="inlineStr">
+        <is>
+          <t>42</t>
+        </is>
+      </c>
+      <c r="AH2" t="inlineStr">
+        <is>
+          <t>27</t>
+        </is>
+      </c>
+      <c r="AI2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
@@ -876,120 +965,160 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
+          <t>16-April-2026</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>esignet</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>375</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>272</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>46</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>27</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
           <t>15-April-2026</t>
         </is>
       </c>
-      <c r="B3" t="inlineStr">
+      <c r="K3" t="inlineStr">
         <is>
           <t>esignet</t>
         </is>
       </c>
-      <c r="C3" t="inlineStr">
+      <c r="L3" t="inlineStr">
         <is>
           <t>375</t>
         </is>
       </c>
-      <c r="D3" t="inlineStr">
+      <c r="M3" t="inlineStr">
         <is>
           <t>265</t>
         </is>
       </c>
-      <c r="E3" t="inlineStr">
+      <c r="N3" t="inlineStr">
         <is>
           <t>33</t>
         </is>
       </c>
-      <c r="F3" t="inlineStr">
+      <c r="O3" t="inlineStr">
         <is>
           <t>50</t>
         </is>
       </c>
-      <c r="G3" t="inlineStr">
+      <c r="P3" t="inlineStr">
         <is>
           <t>27</t>
         </is>
       </c>
-      <c r="H3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="J3" t="inlineStr">
+      <c r="Q3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="S3" t="inlineStr">
         <is>
           <t>14-April-2026</t>
         </is>
       </c>
-      <c r="K3" t="inlineStr">
+      <c r="T3" t="inlineStr">
         <is>
           <t>esignet</t>
         </is>
       </c>
-      <c r="L3" t="inlineStr">
+      <c r="U3" t="inlineStr">
         <is>
           <t>375</t>
         </is>
       </c>
-      <c r="M3" t="inlineStr">
+      <c r="V3" t="inlineStr">
         <is>
           <t>264</t>
         </is>
       </c>
-      <c r="N3" t="inlineStr">
+      <c r="W3" t="inlineStr">
         <is>
           <t>37</t>
         </is>
       </c>
-      <c r="O3" t="inlineStr">
+      <c r="X3" t="inlineStr">
         <is>
           <t>47</t>
         </is>
       </c>
-      <c r="P3" t="inlineStr">
+      <c r="Y3" t="inlineStr">
         <is>
           <t>27</t>
         </is>
       </c>
-      <c r="Q3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="S3" t="inlineStr">
+      <c r="Z3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB3" t="inlineStr">
         <is>
           <t>13-April-2026</t>
         </is>
       </c>
-      <c r="T3" t="inlineStr">
-        <is>
-          <t>esignet</t>
-        </is>
-      </c>
-      <c r="U3" t="inlineStr">
-        <is>
-          <t>375</t>
-        </is>
-      </c>
-      <c r="V3" t="inlineStr">
-        <is>
-          <t>262</t>
-        </is>
-      </c>
-      <c r="W3" t="inlineStr">
-        <is>
-          <t>44</t>
-        </is>
-      </c>
-      <c r="X3" t="inlineStr">
-        <is>
-          <t>42</t>
-        </is>
-      </c>
-      <c r="Y3" t="inlineStr">
-        <is>
-          <t>27</t>
-        </is>
-      </c>
-      <c r="Z3" t="inlineStr">
+      <c r="AC3" t="inlineStr">
+        <is>
+          <t>injiverify</t>
+        </is>
+      </c>
+      <c r="AD3" t="inlineStr">
+        <is>
+          <t>53</t>
+        </is>
+      </c>
+      <c r="AE3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AF3" t="inlineStr">
+        <is>
+          <t>23</t>
+        </is>
+      </c>
+      <c r="AG3" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="AH3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AI3" t="inlineStr">
         <is>
           <t>0</t>
         </is>
@@ -998,242 +1127,322 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
+          <t>16-April-2026</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>idrepo</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>152</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>101</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>51</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
           <t>15-April-2026</t>
         </is>
       </c>
-      <c r="B4" t="inlineStr">
+      <c r="K4" t="inlineStr">
         <is>
           <t>idrepo</t>
         </is>
       </c>
-      <c r="C4" t="inlineStr">
+      <c r="L4" t="inlineStr">
         <is>
           <t>152</t>
         </is>
       </c>
-      <c r="D4" t="inlineStr">
+      <c r="M4" t="inlineStr">
         <is>
           <t>101</t>
         </is>
       </c>
-      <c r="E4" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F4" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="G4" t="inlineStr">
+      <c r="N4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P4" t="inlineStr">
         <is>
           <t>51</t>
         </is>
       </c>
-      <c r="H4" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="J4" t="inlineStr">
+      <c r="Q4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="S4" t="inlineStr">
         <is>
           <t>14-April-2026</t>
         </is>
       </c>
-      <c r="K4" t="inlineStr">
+      <c r="T4" t="inlineStr">
         <is>
           <t>idrepo</t>
         </is>
       </c>
-      <c r="L4" t="inlineStr">
+      <c r="U4" t="inlineStr">
         <is>
           <t>152</t>
         </is>
       </c>
-      <c r="M4" t="inlineStr">
+      <c r="V4" t="inlineStr">
         <is>
           <t>101</t>
         </is>
       </c>
-      <c r="N4" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="O4" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="P4" t="inlineStr">
+      <c r="W4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="X4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Y4" t="inlineStr">
         <is>
           <t>51</t>
         </is>
       </c>
-      <c r="Q4" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="S4" t="inlineStr">
+      <c r="Z4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB4" t="inlineStr">
         <is>
           <t>13-April-2026</t>
         </is>
       </c>
-      <c r="T4" t="inlineStr">
-        <is>
-          <t>idrepo</t>
-        </is>
-      </c>
-      <c r="U4" t="inlineStr">
-        <is>
-          <t>152</t>
-        </is>
-      </c>
-      <c r="V4" t="inlineStr">
-        <is>
-          <t>101</t>
-        </is>
-      </c>
-      <c r="W4" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="X4" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="Y4" t="inlineStr">
-        <is>
-          <t>51</t>
-        </is>
-      </c>
-      <c r="Z4" t="inlineStr">
-        <is>
-          <t>0</t>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t>prereg</t>
+        </is>
+      </c>
+      <c r="AD4" t="inlineStr">
+        <is>
+          <t>104</t>
+        </is>
+      </c>
+      <c r="AE4" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AF4" t="inlineStr">
+        <is>
+          <t>70</t>
+        </is>
+      </c>
+      <c r="AG4" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="AH4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AI4" t="inlineStr">
+        <is>
+          <t>1</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
+          <t>16-April-2026</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>injiverify</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>53</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>23</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
           <t>15-April-2026</t>
         </is>
       </c>
-      <c r="B5" t="inlineStr">
+      <c r="K5" t="inlineStr">
         <is>
           <t>injiverify</t>
         </is>
       </c>
-      <c r="C5" t="inlineStr">
+      <c r="L5" t="inlineStr">
         <is>
           <t>53</t>
         </is>
       </c>
-      <c r="D5" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="E5" t="inlineStr">
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="N5" t="inlineStr">
         <is>
           <t>23</t>
         </is>
       </c>
-      <c r="F5" t="inlineStr">
+      <c r="O5" t="inlineStr">
         <is>
           <t>30</t>
         </is>
       </c>
-      <c r="G5" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H5" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="J5" t="inlineStr">
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Q5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="S5" t="inlineStr">
         <is>
           <t>14-April-2026</t>
         </is>
       </c>
-      <c r="K5" t="inlineStr">
+      <c r="T5" t="inlineStr">
         <is>
           <t>injiverify</t>
         </is>
       </c>
-      <c r="L5" t="inlineStr">
+      <c r="U5" t="inlineStr">
         <is>
           <t>53</t>
         </is>
       </c>
-      <c r="M5" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="N5" t="inlineStr">
+      <c r="V5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="W5" t="inlineStr">
         <is>
           <t>23</t>
         </is>
       </c>
-      <c r="O5" t="inlineStr">
+      <c r="X5" t="inlineStr">
         <is>
           <t>30</t>
         </is>
       </c>
-      <c r="P5" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="Q5" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="S5" t="inlineStr">
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Z5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB5" t="inlineStr">
         <is>
           <t>13-April-2026</t>
         </is>
       </c>
-      <c r="T5" t="inlineStr">
-        <is>
-          <t>injiverify</t>
-        </is>
-      </c>
-      <c r="U5" t="inlineStr">
-        <is>
-          <t>53</t>
-        </is>
-      </c>
-      <c r="V5" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="W5" t="inlineStr">
-        <is>
-          <t>23</t>
-        </is>
-      </c>
-      <c r="X5" t="inlineStr">
-        <is>
-          <t>30</t>
-        </is>
-      </c>
-      <c r="Y5" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="Z5" t="inlineStr">
+      <c r="AC5" t="inlineStr">
+        <is>
+          <t>residentui</t>
+        </is>
+      </c>
+      <c r="AD5" t="inlineStr">
+        <is>
+          <t>33</t>
+        </is>
+      </c>
+      <c r="AE5" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="AF5" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AG5" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="AH5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AI5" t="inlineStr">
         <is>
           <t>0</t>
         </is>
@@ -1242,358 +1451,406 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
+          <t>16-April-2026</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>mimoto</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>79</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>59</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
           <t>15-April-2026</t>
         </is>
       </c>
-      <c r="B6" t="inlineStr">
+      <c r="K6" t="inlineStr">
         <is>
           <t>mimoto</t>
         </is>
       </c>
-      <c r="C6" t="inlineStr">
+      <c r="L6" t="inlineStr">
         <is>
           <t>79</t>
         </is>
       </c>
-      <c r="D6" t="inlineStr">
+      <c r="M6" t="inlineStr">
         <is>
           <t>66</t>
         </is>
       </c>
-      <c r="E6" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F6" t="inlineStr">
+      <c r="N6" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O6" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="G6" t="inlineStr">
+      <c r="P6" t="inlineStr">
         <is>
           <t>10</t>
         </is>
       </c>
-      <c r="H6" t="inlineStr">
+      <c r="Q6" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="J6" t="inlineStr">
+      <c r="S6" t="inlineStr">
         <is>
           <t>14-April-2026</t>
         </is>
       </c>
-      <c r="K6" t="inlineStr">
+      <c r="T6" t="inlineStr">
         <is>
           <t>mimoto</t>
         </is>
       </c>
-      <c r="L6" t="inlineStr">
+      <c r="U6" t="inlineStr">
         <is>
           <t>79</t>
         </is>
       </c>
-      <c r="M6" t="inlineStr">
+      <c r="V6" t="inlineStr">
         <is>
           <t>66</t>
         </is>
       </c>
-      <c r="N6" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="O6" t="inlineStr">
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="X6" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="P6" t="inlineStr">
+      <c r="Y6" t="inlineStr">
         <is>
           <t>10</t>
         </is>
       </c>
-      <c r="Q6" t="inlineStr">
+      <c r="Z6" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="S6" t="inlineStr">
-        <is>
-          <t>13-April-2026</t>
-        </is>
-      </c>
-      <c r="T6" t="inlineStr">
-        <is>
-          <t>mimoto</t>
-        </is>
-      </c>
-      <c r="U6" t="inlineStr">
-        <is>
-          <t>79</t>
-        </is>
-      </c>
-      <c r="V6" t="inlineStr">
-        <is>
-          <t>65</t>
-        </is>
-      </c>
-      <c r="W6" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="X6" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="Y6" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="Z6" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
+      <c r="AB6" t="n">
+        <v/>
+      </c>
+      <c r="AC6" t="n">
+        <v/>
+      </c>
+      <c r="AD6" t="n">
+        <v/>
+      </c>
+      <c r="AE6" t="n">
+        <v/>
+      </c>
+      <c r="AF6" t="n">
+        <v/>
+      </c>
+      <c r="AG6" t="n">
+        <v/>
+      </c>
+      <c r="AH6" t="n">
+        <v/>
+      </c>
+      <c r="AI6" t="n">
+        <v/>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
+          <t>16-April-2026</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>prereg</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>104</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>70</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
           <t>15-April-2026</t>
         </is>
       </c>
-      <c r="B7" t="inlineStr">
+      <c r="K7" t="inlineStr">
         <is>
           <t>prereg</t>
         </is>
       </c>
-      <c r="C7" t="inlineStr">
+      <c r="L7" t="inlineStr">
         <is>
           <t>104</t>
         </is>
       </c>
-      <c r="D7" t="inlineStr">
+      <c r="M7" t="inlineStr">
         <is>
           <t>3</t>
         </is>
       </c>
-      <c r="E7" t="inlineStr">
+      <c r="N7" t="inlineStr">
         <is>
           <t>70</t>
         </is>
       </c>
-      <c r="F7" t="inlineStr">
+      <c r="O7" t="inlineStr">
         <is>
           <t>30</t>
         </is>
       </c>
-      <c r="G7" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H7" t="inlineStr">
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Q7" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="J7" t="inlineStr">
+      <c r="S7" t="inlineStr">
         <is>
           <t>14-April-2026</t>
         </is>
       </c>
-      <c r="K7" t="inlineStr">
+      <c r="T7" t="inlineStr">
         <is>
           <t>prereg</t>
         </is>
       </c>
-      <c r="L7" t="inlineStr">
+      <c r="U7" t="inlineStr">
         <is>
           <t>104</t>
         </is>
       </c>
-      <c r="M7" t="inlineStr">
+      <c r="V7" t="inlineStr">
         <is>
           <t>3</t>
         </is>
       </c>
-      <c r="N7" t="inlineStr">
+      <c r="W7" t="inlineStr">
         <is>
           <t>70</t>
         </is>
       </c>
-      <c r="O7" t="inlineStr">
+      <c r="X7" t="inlineStr">
         <is>
           <t>30</t>
         </is>
       </c>
-      <c r="P7" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="Q7" t="inlineStr">
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Z7" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="S7" t="inlineStr">
-        <is>
-          <t>13-April-2026</t>
-        </is>
-      </c>
-      <c r="T7" t="inlineStr">
-        <is>
-          <t>prereg</t>
-        </is>
-      </c>
-      <c r="U7" t="inlineStr">
-        <is>
-          <t>104</t>
-        </is>
-      </c>
-      <c r="V7" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="W7" t="inlineStr">
-        <is>
-          <t>70</t>
-        </is>
-      </c>
-      <c r="X7" t="inlineStr">
-        <is>
-          <t>30</t>
-        </is>
-      </c>
-      <c r="Y7" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="Z7" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
+      <c r="AB7" t="n">
+        <v/>
+      </c>
+      <c r="AC7" t="n">
+        <v/>
+      </c>
+      <c r="AD7" t="n">
+        <v/>
+      </c>
+      <c r="AE7" t="n">
+        <v/>
+      </c>
+      <c r="AF7" t="n">
+        <v/>
+      </c>
+      <c r="AG7" t="n">
+        <v/>
+      </c>
+      <c r="AH7" t="n">
+        <v/>
+      </c>
+      <c r="AI7" t="n">
+        <v/>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
+          <t>16-April-2026</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>residentui</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>33</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
           <t>15-April-2026</t>
         </is>
       </c>
-      <c r="B8" t="inlineStr">
+      <c r="K8" t="inlineStr">
         <is>
           <t>residentui</t>
         </is>
       </c>
-      <c r="C8" t="inlineStr">
+      <c r="L8" t="inlineStr">
         <is>
           <t>33</t>
         </is>
       </c>
-      <c r="D8" t="inlineStr">
+      <c r="M8" t="inlineStr">
         <is>
           <t>12</t>
         </is>
       </c>
-      <c r="E8" t="inlineStr">
+      <c r="N8" t="inlineStr">
         <is>
           <t>5</t>
         </is>
       </c>
-      <c r="F8" t="inlineStr">
+      <c r="O8" t="inlineStr">
         <is>
           <t>16</t>
         </is>
       </c>
-      <c r="G8" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H8" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="J8" t="inlineStr">
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Q8" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="S8" t="inlineStr">
         <is>
           <t>14-April-2026</t>
         </is>
       </c>
-      <c r="K8" t="inlineStr">
+      <c r="T8" t="inlineStr">
         <is>
           <t>residentui</t>
         </is>
       </c>
-      <c r="L8" t="inlineStr">
+      <c r="U8" t="inlineStr">
         <is>
           <t>33</t>
         </is>
       </c>
-      <c r="M8" t="inlineStr">
+      <c r="V8" t="inlineStr">
         <is>
           <t>12</t>
         </is>
       </c>
-      <c r="N8" t="inlineStr">
+      <c r="W8" t="inlineStr">
         <is>
           <t>5</t>
         </is>
       </c>
-      <c r="O8" t="inlineStr">
+      <c r="X8" t="inlineStr">
         <is>
           <t>16</t>
         </is>
       </c>
-      <c r="P8" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="Q8" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="S8" t="inlineStr">
-        <is>
-          <t>13-April-2026</t>
-        </is>
-      </c>
-      <c r="T8" t="inlineStr">
-        <is>
-          <t>residentui</t>
-        </is>
-      </c>
-      <c r="U8" t="inlineStr">
-        <is>
-          <t>33</t>
-        </is>
-      </c>
-      <c r="V8" t="inlineStr">
-        <is>
-          <t>12</t>
-        </is>
-      </c>
-      <c r="W8" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="X8" t="inlineStr">
-        <is>
-          <t>16</t>
-        </is>
-      </c>
       <c r="Y8" t="inlineStr">
         <is>
           <t>0</t>
@@ -1603,6 +1860,30 @@
         <is>
           <t>0</t>
         </is>
+      </c>
+      <c r="AB8" t="n">
+        <v/>
+      </c>
+      <c r="AC8" t="n">
+        <v/>
+      </c>
+      <c r="AD8" t="n">
+        <v/>
+      </c>
+      <c r="AE8" t="n">
+        <v/>
+      </c>
+      <c r="AF8" t="n">
+        <v/>
+      </c>
+      <c r="AG8" t="n">
+        <v/>
+      </c>
+      <c r="AH8" t="n">
+        <v/>
+      </c>
+      <c r="AI8" t="n">
+        <v/>
       </c>
     </row>
   </sheetData>

--- a/minio-report-tracker/xlxs/collab.xlsx
+++ b/minio-report-tracker/xlxs/collab.xlsx
@@ -803,129 +803,129 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
+          <t>17-April-2026</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>auth</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>254</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>186</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>62</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
           <t>16-April-2026</t>
         </is>
       </c>
-      <c r="B2" t="inlineStr">
+      <c r="K2" t="inlineStr">
         <is>
           <t>auth</t>
         </is>
       </c>
-      <c r="C2" t="inlineStr">
+      <c r="L2" t="inlineStr">
         <is>
           <t>254</t>
         </is>
       </c>
-      <c r="D2" t="inlineStr">
+      <c r="M2" t="inlineStr">
         <is>
           <t>186</t>
         </is>
       </c>
-      <c r="E2" t="inlineStr">
+      <c r="N2" t="inlineStr">
         <is>
           <t>6</t>
         </is>
       </c>
-      <c r="F2" t="inlineStr">
+      <c r="O2" t="inlineStr">
         <is>
           <t>62</t>
         </is>
       </c>
-      <c r="G2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="J2" t="inlineStr">
+      <c r="P2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Q2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="S2" t="inlineStr">
         <is>
           <t>15-April-2026</t>
         </is>
       </c>
-      <c r="K2" t="inlineStr">
+      <c r="T2" t="inlineStr">
         <is>
           <t>auth</t>
         </is>
       </c>
-      <c r="L2" t="inlineStr">
+      <c r="U2" t="inlineStr">
         <is>
           <t>254</t>
         </is>
       </c>
-      <c r="M2" t="inlineStr">
+      <c r="V2" t="inlineStr">
         <is>
           <t>184</t>
         </is>
       </c>
-      <c r="N2" t="inlineStr">
+      <c r="W2" t="inlineStr">
         <is>
           <t>6</t>
         </is>
       </c>
-      <c r="O2" t="inlineStr">
+      <c r="X2" t="inlineStr">
         <is>
           <t>64</t>
         </is>
       </c>
-      <c r="P2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="Q2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="S2" t="inlineStr">
+      <c r="Y2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Z2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB2" t="inlineStr">
         <is>
           <t>14-April-2026</t>
         </is>
       </c>
-      <c r="T2" t="inlineStr">
-        <is>
-          <t>auth</t>
-        </is>
-      </c>
-      <c r="U2" t="inlineStr">
-        <is>
-          <t>254</t>
-        </is>
-      </c>
-      <c r="V2" t="inlineStr">
-        <is>
-          <t>186</t>
-        </is>
-      </c>
-      <c r="W2" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="X2" t="inlineStr">
-        <is>
-          <t>62</t>
-        </is>
-      </c>
-      <c r="Y2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>13-April-2026</t>
-        </is>
-      </c>
       <c r="AC2" t="inlineStr">
         <is>
           <t>esignet</t>
@@ -938,17 +938,17 @@
       </c>
       <c r="AE2" t="inlineStr">
         <is>
-          <t>262</t>
+          <t>264</t>
         </is>
       </c>
       <c r="AF2" t="inlineStr">
         <is>
-          <t>44</t>
+          <t>37</t>
         </is>
       </c>
       <c r="AG2" t="inlineStr">
         <is>
-          <t>42</t>
+          <t>47</t>
         </is>
       </c>
       <c r="AH2" t="inlineStr">
@@ -965,127 +965,127 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
+          <t>17-April-2026</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>esignet</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>375</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>268</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>47</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>33</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>27</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
           <t>16-April-2026</t>
         </is>
       </c>
-      <c r="B3" t="inlineStr">
+      <c r="K3" t="inlineStr">
         <is>
           <t>esignet</t>
         </is>
       </c>
-      <c r="C3" t="inlineStr">
+      <c r="L3" t="inlineStr">
         <is>
           <t>375</t>
         </is>
       </c>
-      <c r="D3" t="inlineStr">
+      <c r="M3" t="inlineStr">
         <is>
           <t>272</t>
         </is>
       </c>
-      <c r="E3" t="inlineStr">
+      <c r="N3" t="inlineStr">
         <is>
           <t>46</t>
         </is>
       </c>
-      <c r="F3" t="inlineStr">
+      <c r="O3" t="inlineStr">
         <is>
           <t>30</t>
         </is>
       </c>
-      <c r="G3" t="inlineStr">
+      <c r="P3" t="inlineStr">
         <is>
           <t>27</t>
         </is>
       </c>
-      <c r="H3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="J3" t="inlineStr">
+      <c r="Q3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="S3" t="inlineStr">
         <is>
           <t>15-April-2026</t>
         </is>
       </c>
-      <c r="K3" t="inlineStr">
+      <c r="T3" t="inlineStr">
         <is>
           <t>esignet</t>
         </is>
       </c>
-      <c r="L3" t="inlineStr">
+      <c r="U3" t="inlineStr">
         <is>
           <t>375</t>
         </is>
       </c>
-      <c r="M3" t="inlineStr">
+      <c r="V3" t="inlineStr">
         <is>
           <t>265</t>
         </is>
       </c>
-      <c r="N3" t="inlineStr">
+      <c r="W3" t="inlineStr">
         <is>
           <t>33</t>
         </is>
       </c>
-      <c r="O3" t="inlineStr">
+      <c r="X3" t="inlineStr">
         <is>
           <t>50</t>
         </is>
       </c>
-      <c r="P3" t="inlineStr">
+      <c r="Y3" t="inlineStr">
         <is>
           <t>27</t>
         </is>
       </c>
-      <c r="Q3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="S3" t="inlineStr">
+      <c r="Z3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB3" t="inlineStr">
         <is>
           <t>14-April-2026</t>
-        </is>
-      </c>
-      <c r="T3" t="inlineStr">
-        <is>
-          <t>esignet</t>
-        </is>
-      </c>
-      <c r="U3" t="inlineStr">
-        <is>
-          <t>375</t>
-        </is>
-      </c>
-      <c r="V3" t="inlineStr">
-        <is>
-          <t>264</t>
-        </is>
-      </c>
-      <c r="W3" t="inlineStr">
-        <is>
-          <t>37</t>
-        </is>
-      </c>
-      <c r="X3" t="inlineStr">
-        <is>
-          <t>47</t>
-        </is>
-      </c>
-      <c r="Y3" t="inlineStr">
-        <is>
-          <t>27</t>
-        </is>
-      </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>13-April-2026</t>
         </is>
       </c>
       <c r="AC3" t="inlineStr">
@@ -1127,127 +1127,127 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
+          <t>17-April-2026</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>idrepo</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>152</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>101</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>51</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
           <t>16-April-2026</t>
         </is>
       </c>
-      <c r="B4" t="inlineStr">
+      <c r="K4" t="inlineStr">
         <is>
           <t>idrepo</t>
         </is>
       </c>
-      <c r="C4" t="inlineStr">
+      <c r="L4" t="inlineStr">
         <is>
           <t>152</t>
         </is>
       </c>
-      <c r="D4" t="inlineStr">
+      <c r="M4" t="inlineStr">
         <is>
           <t>101</t>
         </is>
       </c>
-      <c r="E4" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F4" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="G4" t="inlineStr">
+      <c r="N4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P4" t="inlineStr">
         <is>
           <t>51</t>
         </is>
       </c>
-      <c r="H4" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="J4" t="inlineStr">
+      <c r="Q4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="S4" t="inlineStr">
         <is>
           <t>15-April-2026</t>
         </is>
       </c>
-      <c r="K4" t="inlineStr">
+      <c r="T4" t="inlineStr">
         <is>
           <t>idrepo</t>
         </is>
       </c>
-      <c r="L4" t="inlineStr">
+      <c r="U4" t="inlineStr">
         <is>
           <t>152</t>
         </is>
       </c>
-      <c r="M4" t="inlineStr">
+      <c r="V4" t="inlineStr">
         <is>
           <t>101</t>
         </is>
       </c>
-      <c r="N4" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="O4" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="P4" t="inlineStr">
+      <c r="W4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="X4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Y4" t="inlineStr">
         <is>
           <t>51</t>
         </is>
       </c>
-      <c r="Q4" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="S4" t="inlineStr">
+      <c r="Z4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB4" t="inlineStr">
         <is>
           <t>14-April-2026</t>
-        </is>
-      </c>
-      <c r="T4" t="inlineStr">
-        <is>
-          <t>idrepo</t>
-        </is>
-      </c>
-      <c r="U4" t="inlineStr">
-        <is>
-          <t>152</t>
-        </is>
-      </c>
-      <c r="V4" t="inlineStr">
-        <is>
-          <t>101</t>
-        </is>
-      </c>
-      <c r="W4" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="X4" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="Y4" t="inlineStr">
-        <is>
-          <t>51</t>
-        </is>
-      </c>
-      <c r="Z4" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB4" t="inlineStr">
-        <is>
-          <t>13-April-2026</t>
         </is>
       </c>
       <c r="AC4" t="inlineStr">
@@ -1289,127 +1289,127 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
+          <t>17-April-2026</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>injiverify</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>53</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>23</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
           <t>16-April-2026</t>
         </is>
       </c>
-      <c r="B5" t="inlineStr">
+      <c r="K5" t="inlineStr">
         <is>
           <t>injiverify</t>
         </is>
       </c>
-      <c r="C5" t="inlineStr">
+      <c r="L5" t="inlineStr">
         <is>
           <t>53</t>
         </is>
       </c>
-      <c r="D5" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="E5" t="inlineStr">
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="N5" t="inlineStr">
         <is>
           <t>23</t>
         </is>
       </c>
-      <c r="F5" t="inlineStr">
+      <c r="O5" t="inlineStr">
         <is>
           <t>30</t>
         </is>
       </c>
-      <c r="G5" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H5" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="J5" t="inlineStr">
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Q5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="S5" t="inlineStr">
         <is>
           <t>15-April-2026</t>
         </is>
       </c>
-      <c r="K5" t="inlineStr">
+      <c r="T5" t="inlineStr">
         <is>
           <t>injiverify</t>
         </is>
       </c>
-      <c r="L5" t="inlineStr">
+      <c r="U5" t="inlineStr">
         <is>
           <t>53</t>
         </is>
       </c>
-      <c r="M5" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="N5" t="inlineStr">
+      <c r="V5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="W5" t="inlineStr">
         <is>
           <t>23</t>
         </is>
       </c>
-      <c r="O5" t="inlineStr">
+      <c r="X5" t="inlineStr">
         <is>
           <t>30</t>
         </is>
       </c>
-      <c r="P5" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="Q5" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="S5" t="inlineStr">
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Z5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB5" t="inlineStr">
         <is>
           <t>14-April-2026</t>
-        </is>
-      </c>
-      <c r="T5" t="inlineStr">
-        <is>
-          <t>injiverify</t>
-        </is>
-      </c>
-      <c r="U5" t="inlineStr">
-        <is>
-          <t>53</t>
-        </is>
-      </c>
-      <c r="V5" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="W5" t="inlineStr">
-        <is>
-          <t>23</t>
-        </is>
-      </c>
-      <c r="X5" t="inlineStr">
-        <is>
-          <t>30</t>
-        </is>
-      </c>
-      <c r="Y5" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="Z5" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB5" t="inlineStr">
-        <is>
-          <t>13-April-2026</t>
         </is>
       </c>
       <c r="AC5" t="inlineStr">
@@ -1451,87 +1451,87 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
+          <t>17-April-2026</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>mimoto</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>79</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>66</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
           <t>16-April-2026</t>
         </is>
       </c>
-      <c r="B6" t="inlineStr">
+      <c r="K6" t="inlineStr">
         <is>
           <t>mimoto</t>
         </is>
       </c>
-      <c r="C6" t="inlineStr">
+      <c r="L6" t="inlineStr">
         <is>
           <t>79</t>
         </is>
       </c>
-      <c r="D6" t="inlineStr">
+      <c r="M6" t="inlineStr">
         <is>
           <t>59</t>
         </is>
       </c>
-      <c r="E6" t="inlineStr">
+      <c r="N6" t="inlineStr">
         <is>
           <t>4</t>
         </is>
       </c>
-      <c r="F6" t="inlineStr">
+      <c r="O6" t="inlineStr">
         <is>
           <t>4</t>
         </is>
       </c>
-      <c r="G6" t="inlineStr">
+      <c r="P6" t="inlineStr">
         <is>
           <t>10</t>
         </is>
       </c>
-      <c r="H6" t="inlineStr">
+      <c r="Q6" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="J6" t="inlineStr">
+      <c r="S6" t="inlineStr">
         <is>
           <t>15-April-2026</t>
-        </is>
-      </c>
-      <c r="K6" t="inlineStr">
-        <is>
-          <t>mimoto</t>
-        </is>
-      </c>
-      <c r="L6" t="inlineStr">
-        <is>
-          <t>79</t>
-        </is>
-      </c>
-      <c r="M6" t="inlineStr">
-        <is>
-          <t>66</t>
-        </is>
-      </c>
-      <c r="N6" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="O6" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="P6" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="Q6" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="S6" t="inlineStr">
-        <is>
-          <t>14-April-2026</t>
         </is>
       </c>
       <c r="T6" t="inlineStr">
@@ -1597,87 +1597,87 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
+          <t>17-April-2026</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>prereg</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>104</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>70</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
           <t>16-April-2026</t>
         </is>
       </c>
-      <c r="B7" t="inlineStr">
+      <c r="K7" t="inlineStr">
         <is>
           <t>prereg</t>
         </is>
       </c>
-      <c r="C7" t="inlineStr">
+      <c r="L7" t="inlineStr">
         <is>
           <t>104</t>
         </is>
       </c>
-      <c r="D7" t="inlineStr">
+      <c r="M7" t="inlineStr">
         <is>
           <t>3</t>
         </is>
       </c>
-      <c r="E7" t="inlineStr">
+      <c r="N7" t="inlineStr">
         <is>
           <t>70</t>
         </is>
       </c>
-      <c r="F7" t="inlineStr">
+      <c r="O7" t="inlineStr">
         <is>
           <t>30</t>
         </is>
       </c>
-      <c r="G7" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H7" t="inlineStr">
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Q7" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="J7" t="inlineStr">
+      <c r="S7" t="inlineStr">
         <is>
           <t>15-April-2026</t>
-        </is>
-      </c>
-      <c r="K7" t="inlineStr">
-        <is>
-          <t>prereg</t>
-        </is>
-      </c>
-      <c r="L7" t="inlineStr">
-        <is>
-          <t>104</t>
-        </is>
-      </c>
-      <c r="M7" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="N7" t="inlineStr">
-        <is>
-          <t>70</t>
-        </is>
-      </c>
-      <c r="O7" t="inlineStr">
-        <is>
-          <t>30</t>
-        </is>
-      </c>
-      <c r="P7" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="Q7" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="S7" t="inlineStr">
-        <is>
-          <t>14-April-2026</t>
         </is>
       </c>
       <c r="T7" t="inlineStr">
@@ -1743,87 +1743,87 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
+          <t>17-April-2026</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>residentui</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>33</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
           <t>16-April-2026</t>
         </is>
       </c>
-      <c r="B8" t="inlineStr">
+      <c r="K8" t="inlineStr">
         <is>
           <t>residentui</t>
         </is>
       </c>
-      <c r="C8" t="inlineStr">
+      <c r="L8" t="inlineStr">
         <is>
           <t>33</t>
         </is>
       </c>
-      <c r="D8" t="inlineStr">
+      <c r="M8" t="inlineStr">
         <is>
           <t>12</t>
         </is>
       </c>
-      <c r="E8" t="inlineStr">
+      <c r="N8" t="inlineStr">
         <is>
           <t>5</t>
         </is>
       </c>
-      <c r="F8" t="inlineStr">
+      <c r="O8" t="inlineStr">
         <is>
           <t>16</t>
         </is>
       </c>
-      <c r="G8" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H8" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="J8" t="inlineStr">
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Q8" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="S8" t="inlineStr">
         <is>
           <t>15-April-2026</t>
-        </is>
-      </c>
-      <c r="K8" t="inlineStr">
-        <is>
-          <t>residentui</t>
-        </is>
-      </c>
-      <c r="L8" t="inlineStr">
-        <is>
-          <t>33</t>
-        </is>
-      </c>
-      <c r="M8" t="inlineStr">
-        <is>
-          <t>12</t>
-        </is>
-      </c>
-      <c r="N8" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="O8" t="inlineStr">
-        <is>
-          <t>16</t>
-        </is>
-      </c>
-      <c r="P8" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="Q8" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="S8" t="inlineStr">
-        <is>
-          <t>14-April-2026</t>
         </is>
       </c>
       <c r="T8" t="inlineStr">

--- a/minio-report-tracker/xlxs/collab.xlsx
+++ b/minio-report-tracker/xlxs/collab.xlsx
@@ -598,7 +598,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AI8"/>
+  <dimension ref="A1:Z8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="15" customWidth="1" min="1" max="1"/>
@@ -623,19 +623,10 @@
     <col width="12" customWidth="1" min="20" max="20"/>
     <col width="5" customWidth="1" min="21" max="21"/>
     <col width="5" customWidth="1" min="22" max="22"/>
-    <col width="4" customWidth="1" min="23" max="23"/>
-    <col width="4" customWidth="1" min="24" max="24"/>
-    <col width="4" customWidth="1" min="25" max="25"/>
-    <col width="4" customWidth="1" min="26" max="26"/>
-    <col width="2" customWidth="1" min="27" max="27"/>
-    <col width="15" customWidth="1" min="28" max="28"/>
-    <col width="12" customWidth="1" min="29" max="29"/>
-    <col width="5" customWidth="1" min="30" max="30"/>
-    <col width="5" customWidth="1" min="31" max="31"/>
-    <col width="5" customWidth="1" min="32" max="32"/>
-    <col width="5" customWidth="1" min="33" max="33"/>
-    <col width="5" customWidth="1" min="34" max="34"/>
-    <col width="5" customWidth="1" min="35" max="35"/>
+    <col width="5" customWidth="1" min="23" max="23"/>
+    <col width="5" customWidth="1" min="24" max="24"/>
+    <col width="5" customWidth="1" min="25" max="25"/>
+    <col width="5" customWidth="1" min="26" max="26"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -759,46 +750,6 @@
           <t>KI</t>
         </is>
       </c>
-      <c r="AB1" s="1" t="inlineStr">
-        <is>
-          <t>Date</t>
-        </is>
-      </c>
-      <c r="AC1" s="1" t="inlineStr">
-        <is>
-          <t>Module</t>
-        </is>
-      </c>
-      <c r="AD1" s="1" t="inlineStr">
-        <is>
-          <t>T</t>
-        </is>
-      </c>
-      <c r="AE1" s="1" t="inlineStr">
-        <is>
-          <t>P</t>
-        </is>
-      </c>
-      <c r="AF1" s="1" t="inlineStr">
-        <is>
-          <t>S</t>
-        </is>
-      </c>
-      <c r="AG1" s="1" t="inlineStr">
-        <is>
-          <t>F</t>
-        </is>
-      </c>
-      <c r="AH1" s="1" t="inlineStr">
-        <is>
-          <t>I</t>
-        </is>
-      </c>
-      <c r="AI1" s="1" t="inlineStr">
-        <is>
-          <t>KI</t>
-        </is>
-      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -888,75 +839,35 @@
       </c>
       <c r="T2" t="inlineStr">
         <is>
-          <t>auth</t>
+          <t>esignet</t>
         </is>
       </c>
       <c r="U2" t="inlineStr">
         <is>
-          <t>254</t>
+          <t>375</t>
         </is>
       </c>
       <c r="V2" t="inlineStr">
         <is>
-          <t>184</t>
+          <t>265</t>
         </is>
       </c>
       <c r="W2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>33</t>
         </is>
       </c>
       <c r="X2" t="inlineStr">
         <is>
-          <t>64</t>
+          <t>50</t>
         </is>
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>27</t>
         </is>
       </c>
       <c r="Z2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>14-April-2026</t>
-        </is>
-      </c>
-      <c r="AC2" t="inlineStr">
-        <is>
-          <t>esignet</t>
-        </is>
-      </c>
-      <c r="AD2" t="inlineStr">
-        <is>
-          <t>375</t>
-        </is>
-      </c>
-      <c r="AE2" t="inlineStr">
-        <is>
-          <t>264</t>
-        </is>
-      </c>
-      <c r="AF2" t="inlineStr">
-        <is>
-          <t>37</t>
-        </is>
-      </c>
-      <c r="AG2" t="inlineStr">
-        <is>
-          <t>47</t>
-        </is>
-      </c>
-      <c r="AH2" t="inlineStr">
-        <is>
-          <t>27</t>
-        </is>
-      </c>
-      <c r="AI2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
@@ -1050,75 +961,35 @@
       </c>
       <c r="T3" t="inlineStr">
         <is>
-          <t>esignet</t>
+          <t>injiverify</t>
         </is>
       </c>
       <c r="U3" t="inlineStr">
         <is>
-          <t>375</t>
+          <t>53</t>
         </is>
       </c>
       <c r="V3" t="inlineStr">
         <is>
-          <t>265</t>
+          <t>0</t>
         </is>
       </c>
       <c r="W3" t="inlineStr">
         <is>
-          <t>33</t>
+          <t>23</t>
         </is>
       </c>
       <c r="X3" t="inlineStr">
         <is>
-          <t>50</t>
+          <t>30</t>
         </is>
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>27</t>
+          <t>0</t>
         </is>
       </c>
       <c r="Z3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>14-April-2026</t>
-        </is>
-      </c>
-      <c r="AC3" t="inlineStr">
-        <is>
-          <t>injiverify</t>
-        </is>
-      </c>
-      <c r="AD3" t="inlineStr">
-        <is>
-          <t>53</t>
-        </is>
-      </c>
-      <c r="AE3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AF3" t="inlineStr">
-        <is>
-          <t>23</t>
-        </is>
-      </c>
-      <c r="AG3" t="inlineStr">
-        <is>
-          <t>30</t>
-        </is>
-      </c>
-      <c r="AH3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AI3" t="inlineStr">
         <is>
           <t>0</t>
         </is>
@@ -1212,75 +1083,35 @@
       </c>
       <c r="T4" t="inlineStr">
         <is>
-          <t>idrepo</t>
+          <t>prereg</t>
         </is>
       </c>
       <c r="U4" t="inlineStr">
         <is>
-          <t>152</t>
+          <t>104</t>
         </is>
       </c>
       <c r="V4" t="inlineStr">
         <is>
-          <t>101</t>
+          <t>3</t>
         </is>
       </c>
       <c r="W4" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>70</t>
         </is>
       </c>
       <c r="X4" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>30</t>
         </is>
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>51</t>
+          <t>0</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB4" t="inlineStr">
-        <is>
-          <t>14-April-2026</t>
-        </is>
-      </c>
-      <c r="AC4" t="inlineStr">
-        <is>
-          <t>prereg</t>
-        </is>
-      </c>
-      <c r="AD4" t="inlineStr">
-        <is>
-          <t>104</t>
-        </is>
-      </c>
-      <c r="AE4" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="AF4" t="inlineStr">
-        <is>
-          <t>70</t>
-        </is>
-      </c>
-      <c r="AG4" t="inlineStr">
-        <is>
-          <t>30</t>
-        </is>
-      </c>
-      <c r="AH4" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AI4" t="inlineStr">
         <is>
           <t>1</t>
         </is>
@@ -1374,27 +1205,27 @@
       </c>
       <c r="T5" t="inlineStr">
         <is>
-          <t>injiverify</t>
+          <t>residentui</t>
         </is>
       </c>
       <c r="U5" t="inlineStr">
         <is>
-          <t>53</t>
+          <t>33</t>
         </is>
       </c>
       <c r="V5" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>12</t>
         </is>
       </c>
       <c r="W5" t="inlineStr">
         <is>
-          <t>23</t>
+          <t>5</t>
         </is>
       </c>
       <c r="X5" t="inlineStr">
         <is>
-          <t>30</t>
+          <t>16</t>
         </is>
       </c>
       <c r="Y5" t="inlineStr">
@@ -1403,46 +1234,6 @@
         </is>
       </c>
       <c r="Z5" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB5" t="inlineStr">
-        <is>
-          <t>14-April-2026</t>
-        </is>
-      </c>
-      <c r="AC5" t="inlineStr">
-        <is>
-          <t>residentui</t>
-        </is>
-      </c>
-      <c r="AD5" t="inlineStr">
-        <is>
-          <t>33</t>
-        </is>
-      </c>
-      <c r="AE5" t="inlineStr">
-        <is>
-          <t>12</t>
-        </is>
-      </c>
-      <c r="AF5" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="AG5" t="inlineStr">
-        <is>
-          <t>16</t>
-        </is>
-      </c>
-      <c r="AH5" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AI5" t="inlineStr">
         <is>
           <t>0</t>
         </is>
@@ -1529,68 +1320,28 @@
           <t>2</t>
         </is>
       </c>
-      <c r="S6" t="inlineStr">
-        <is>
-          <t>15-April-2026</t>
-        </is>
-      </c>
-      <c r="T6" t="inlineStr">
-        <is>
-          <t>mimoto</t>
-        </is>
-      </c>
-      <c r="U6" t="inlineStr">
-        <is>
-          <t>79</t>
-        </is>
-      </c>
-      <c r="V6" t="inlineStr">
-        <is>
-          <t>66</t>
-        </is>
-      </c>
-      <c r="W6" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="X6" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="Y6" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="Z6" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="AB6" t="n">
-        <v/>
-      </c>
-      <c r="AC6" t="n">
-        <v/>
-      </c>
-      <c r="AD6" t="n">
-        <v/>
-      </c>
-      <c r="AE6" t="n">
-        <v/>
-      </c>
-      <c r="AF6" t="n">
-        <v/>
-      </c>
-      <c r="AG6" t="n">
-        <v/>
-      </c>
-      <c r="AH6" t="n">
-        <v/>
-      </c>
-      <c r="AI6" t="n">
+      <c r="S6" t="n">
+        <v/>
+      </c>
+      <c r="T6" t="n">
+        <v/>
+      </c>
+      <c r="U6" t="n">
+        <v/>
+      </c>
+      <c r="V6" t="n">
+        <v/>
+      </c>
+      <c r="W6" t="n">
+        <v/>
+      </c>
+      <c r="X6" t="n">
+        <v/>
+      </c>
+      <c r="Y6" t="n">
+        <v/>
+      </c>
+      <c r="Z6" t="n">
         <v/>
       </c>
     </row>
@@ -1675,68 +1426,28 @@
           <t>1</t>
         </is>
       </c>
-      <c r="S7" t="inlineStr">
-        <is>
-          <t>15-April-2026</t>
-        </is>
-      </c>
-      <c r="T7" t="inlineStr">
-        <is>
-          <t>prereg</t>
-        </is>
-      </c>
-      <c r="U7" t="inlineStr">
-        <is>
-          <t>104</t>
-        </is>
-      </c>
-      <c r="V7" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="W7" t="inlineStr">
-        <is>
-          <t>70</t>
-        </is>
-      </c>
-      <c r="X7" t="inlineStr">
-        <is>
-          <t>30</t>
-        </is>
-      </c>
-      <c r="Y7" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="Z7" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="AB7" t="n">
-        <v/>
-      </c>
-      <c r="AC7" t="n">
-        <v/>
-      </c>
-      <c r="AD7" t="n">
-        <v/>
-      </c>
-      <c r="AE7" t="n">
-        <v/>
-      </c>
-      <c r="AF7" t="n">
-        <v/>
-      </c>
-      <c r="AG7" t="n">
-        <v/>
-      </c>
-      <c r="AH7" t="n">
-        <v/>
-      </c>
-      <c r="AI7" t="n">
+      <c r="S7" t="n">
+        <v/>
+      </c>
+      <c r="T7" t="n">
+        <v/>
+      </c>
+      <c r="U7" t="n">
+        <v/>
+      </c>
+      <c r="V7" t="n">
+        <v/>
+      </c>
+      <c r="W7" t="n">
+        <v/>
+      </c>
+      <c r="X7" t="n">
+        <v/>
+      </c>
+      <c r="Y7" t="n">
+        <v/>
+      </c>
+      <c r="Z7" t="n">
         <v/>
       </c>
     </row>
@@ -1821,68 +1532,28 @@
           <t>0</t>
         </is>
       </c>
-      <c r="S8" t="inlineStr">
-        <is>
-          <t>15-April-2026</t>
-        </is>
-      </c>
-      <c r="T8" t="inlineStr">
-        <is>
-          <t>residentui</t>
-        </is>
-      </c>
-      <c r="U8" t="inlineStr">
-        <is>
-          <t>33</t>
-        </is>
-      </c>
-      <c r="V8" t="inlineStr">
-        <is>
-          <t>12</t>
-        </is>
-      </c>
-      <c r="W8" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="X8" t="inlineStr">
-        <is>
-          <t>16</t>
-        </is>
-      </c>
-      <c r="Y8" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="Z8" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB8" t="n">
-        <v/>
-      </c>
-      <c r="AC8" t="n">
-        <v/>
-      </c>
-      <c r="AD8" t="n">
-        <v/>
-      </c>
-      <c r="AE8" t="n">
-        <v/>
-      </c>
-      <c r="AF8" t="n">
-        <v/>
-      </c>
-      <c r="AG8" t="n">
-        <v/>
-      </c>
-      <c r="AH8" t="n">
-        <v/>
-      </c>
-      <c r="AI8" t="n">
+      <c r="S8" t="n">
+        <v/>
+      </c>
+      <c r="T8" t="n">
+        <v/>
+      </c>
+      <c r="U8" t="n">
+        <v/>
+      </c>
+      <c r="V8" t="n">
+        <v/>
+      </c>
+      <c r="W8" t="n">
+        <v/>
+      </c>
+      <c r="X8" t="n">
+        <v/>
+      </c>
+      <c r="Y8" t="n">
+        <v/>
+      </c>
+      <c r="Z8" t="n">
         <v/>
       </c>
     </row>

--- a/minio-report-tracker/xlxs/collab.xlsx
+++ b/minio-report-tracker/xlxs/collab.xlsx
@@ -598,7 +598,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Z8"/>
+  <dimension ref="A1:Q8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="15" customWidth="1" min="1" max="1"/>
@@ -614,19 +614,10 @@
     <col width="12" customWidth="1" min="11" max="11"/>
     <col width="5" customWidth="1" min="12" max="12"/>
     <col width="5" customWidth="1" min="13" max="13"/>
-    <col width="4" customWidth="1" min="14" max="14"/>
-    <col width="4" customWidth="1" min="15" max="15"/>
-    <col width="4" customWidth="1" min="16" max="16"/>
-    <col width="4" customWidth="1" min="17" max="17"/>
-    <col width="2" customWidth="1" min="18" max="18"/>
-    <col width="15" customWidth="1" min="19" max="19"/>
-    <col width="12" customWidth="1" min="20" max="20"/>
-    <col width="5" customWidth="1" min="21" max="21"/>
-    <col width="5" customWidth="1" min="22" max="22"/>
-    <col width="5" customWidth="1" min="23" max="23"/>
-    <col width="5" customWidth="1" min="24" max="24"/>
-    <col width="5" customWidth="1" min="25" max="25"/>
-    <col width="5" customWidth="1" min="26" max="26"/>
+    <col width="5" customWidth="1" min="14" max="14"/>
+    <col width="5" customWidth="1" min="15" max="15"/>
+    <col width="5" customWidth="1" min="16" max="16"/>
+    <col width="5" customWidth="1" min="17" max="17"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -710,164 +701,84 @@
           <t>KI</t>
         </is>
       </c>
-      <c r="S1" s="1" t="inlineStr">
-        <is>
-          <t>Date</t>
-        </is>
-      </c>
-      <c r="T1" s="1" t="inlineStr">
-        <is>
-          <t>Module</t>
-        </is>
-      </c>
-      <c r="U1" s="1" t="inlineStr">
-        <is>
-          <t>T</t>
-        </is>
-      </c>
-      <c r="V1" s="1" t="inlineStr">
-        <is>
-          <t>P</t>
-        </is>
-      </c>
-      <c r="W1" s="1" t="inlineStr">
-        <is>
-          <t>S</t>
-        </is>
-      </c>
-      <c r="X1" s="1" t="inlineStr">
-        <is>
-          <t>F</t>
-        </is>
-      </c>
-      <c r="Y1" s="1" t="inlineStr">
-        <is>
-          <t>I</t>
-        </is>
-      </c>
-      <c r="Z1" s="1" t="inlineStr">
-        <is>
-          <t>KI</t>
-        </is>
-      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
+          <t>20-April-2026</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>auth</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>254</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>140</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>72</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>42</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
           <t>17-April-2026</t>
         </is>
       </c>
-      <c r="B2" t="inlineStr">
-        <is>
-          <t>auth</t>
-        </is>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>254</t>
-        </is>
-      </c>
-      <c r="D2" t="inlineStr">
-        <is>
-          <t>186</t>
-        </is>
-      </c>
-      <c r="E2" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="F2" t="inlineStr">
-        <is>
-          <t>62</t>
-        </is>
-      </c>
-      <c r="G2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="J2" t="inlineStr">
-        <is>
-          <t>16-April-2026</t>
-        </is>
-      </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>auth</t>
+          <t>esignet</t>
         </is>
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>254</t>
+          <t>375</t>
         </is>
       </c>
       <c r="M2" t="inlineStr">
         <is>
-          <t>186</t>
+          <t>268</t>
         </is>
       </c>
       <c r="N2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>47</t>
         </is>
       </c>
       <c r="O2" t="inlineStr">
         <is>
-          <t>62</t>
+          <t>33</t>
         </is>
       </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>27</t>
         </is>
       </c>
       <c r="Q2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="S2" t="inlineStr">
-        <is>
-          <t>15-April-2026</t>
-        </is>
-      </c>
-      <c r="T2" t="inlineStr">
-        <is>
-          <t>esignet</t>
-        </is>
-      </c>
-      <c r="U2" t="inlineStr">
-        <is>
-          <t>375</t>
-        </is>
-      </c>
-      <c r="V2" t="inlineStr">
-        <is>
-          <t>265</t>
-        </is>
-      </c>
-      <c r="W2" t="inlineStr">
-        <is>
-          <t>33</t>
-        </is>
-      </c>
-      <c r="X2" t="inlineStr">
-        <is>
-          <t>50</t>
-        </is>
-      </c>
-      <c r="Y2" t="inlineStr">
-        <is>
-          <t>27</t>
-        </is>
-      </c>
-      <c r="Z2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
@@ -876,67 +787,67 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
+          <t>20-April-2026</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>esignet</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>375</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>263</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>51</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>34</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>27</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
           <t>17-April-2026</t>
         </is>
       </c>
-      <c r="B3" t="inlineStr">
-        <is>
-          <t>esignet</t>
-        </is>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>375</t>
-        </is>
-      </c>
-      <c r="D3" t="inlineStr">
-        <is>
-          <t>268</t>
-        </is>
-      </c>
-      <c r="E3" t="inlineStr">
-        <is>
-          <t>47</t>
-        </is>
-      </c>
-      <c r="F3" t="inlineStr">
-        <is>
-          <t>33</t>
-        </is>
-      </c>
-      <c r="G3" t="inlineStr">
-        <is>
-          <t>27</t>
-        </is>
-      </c>
-      <c r="H3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="J3" t="inlineStr">
-        <is>
-          <t>16-April-2026</t>
-        </is>
-      </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>esignet</t>
+          <t>injiverify</t>
         </is>
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>375</t>
+          <t>53</t>
         </is>
       </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>272</t>
+          <t>0</t>
         </is>
       </c>
       <c r="N3" t="inlineStr">
         <is>
-          <t>46</t>
+          <t>23</t>
         </is>
       </c>
       <c r="O3" t="inlineStr">
@@ -946,50 +857,10 @@
       </c>
       <c r="P3" t="inlineStr">
         <is>
-          <t>27</t>
+          <t>0</t>
         </is>
       </c>
       <c r="Q3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="S3" t="inlineStr">
-        <is>
-          <t>15-April-2026</t>
-        </is>
-      </c>
-      <c r="T3" t="inlineStr">
-        <is>
-          <t>injiverify</t>
-        </is>
-      </c>
-      <c r="U3" t="inlineStr">
-        <is>
-          <t>53</t>
-        </is>
-      </c>
-      <c r="V3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="W3" t="inlineStr">
-        <is>
-          <t>23</t>
-        </is>
-      </c>
-      <c r="X3" t="inlineStr">
-        <is>
-          <t>30</t>
-        </is>
-      </c>
-      <c r="Y3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="Z3" t="inlineStr">
         <is>
           <t>0</t>
         </is>
@@ -998,120 +869,80 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
+          <t>20-April-2026</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>idrepo</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>152</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>101</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>51</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
           <t>17-April-2026</t>
         </is>
       </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>idrepo</t>
-        </is>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>152</t>
-        </is>
-      </c>
-      <c r="D4" t="inlineStr">
-        <is>
-          <t>101</t>
-        </is>
-      </c>
-      <c r="E4" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F4" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="G4" t="inlineStr">
-        <is>
-          <t>51</t>
-        </is>
-      </c>
-      <c r="H4" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="J4" t="inlineStr">
-        <is>
-          <t>16-April-2026</t>
-        </is>
-      </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>idrepo</t>
+          <t>prereg</t>
         </is>
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>152</t>
+          <t>104</t>
         </is>
       </c>
       <c r="M4" t="inlineStr">
         <is>
-          <t>101</t>
+          <t>3</t>
         </is>
       </c>
       <c r="N4" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>70</t>
         </is>
       </c>
       <c r="O4" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>30</t>
         </is>
       </c>
       <c r="P4" t="inlineStr">
         <is>
-          <t>51</t>
+          <t>0</t>
         </is>
       </c>
       <c r="Q4" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="S4" t="inlineStr">
-        <is>
-          <t>15-April-2026</t>
-        </is>
-      </c>
-      <c r="T4" t="inlineStr">
-        <is>
-          <t>prereg</t>
-        </is>
-      </c>
-      <c r="U4" t="inlineStr">
-        <is>
-          <t>104</t>
-        </is>
-      </c>
-      <c r="V4" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="W4" t="inlineStr">
-        <is>
-          <t>70</t>
-        </is>
-      </c>
-      <c r="X4" t="inlineStr">
-        <is>
-          <t>30</t>
-        </is>
-      </c>
-      <c r="Y4" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="Z4" t="inlineStr">
         <is>
           <t>1</t>
         </is>
@@ -1120,72 +951,72 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
+          <t>20-April-2026</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>injiverify</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>53</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>23</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
           <t>17-April-2026</t>
         </is>
       </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>injiverify</t>
-        </is>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>53</t>
-        </is>
-      </c>
-      <c r="D5" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="E5" t="inlineStr">
-        <is>
-          <t>23</t>
-        </is>
-      </c>
-      <c r="F5" t="inlineStr">
-        <is>
-          <t>30</t>
-        </is>
-      </c>
-      <c r="G5" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H5" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="J5" t="inlineStr">
-        <is>
-          <t>16-April-2026</t>
-        </is>
-      </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>injiverify</t>
+          <t>residentui</t>
         </is>
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>53</t>
+          <t>33</t>
         </is>
       </c>
       <c r="M5" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>12</t>
         </is>
       </c>
       <c r="N5" t="inlineStr">
         <is>
-          <t>23</t>
+          <t>5</t>
         </is>
       </c>
       <c r="O5" t="inlineStr">
         <is>
-          <t>30</t>
+          <t>16</t>
         </is>
       </c>
       <c r="P5" t="inlineStr">
@@ -1194,46 +1025,6 @@
         </is>
       </c>
       <c r="Q5" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="S5" t="inlineStr">
-        <is>
-          <t>15-April-2026</t>
-        </is>
-      </c>
-      <c r="T5" t="inlineStr">
-        <is>
-          <t>residentui</t>
-        </is>
-      </c>
-      <c r="U5" t="inlineStr">
-        <is>
-          <t>33</t>
-        </is>
-      </c>
-      <c r="V5" t="inlineStr">
-        <is>
-          <t>12</t>
-        </is>
-      </c>
-      <c r="W5" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="X5" t="inlineStr">
-        <is>
-          <t>16</t>
-        </is>
-      </c>
-      <c r="Y5" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="Z5" t="inlineStr">
         <is>
           <t>0</t>
         </is>
@@ -1242,7 +1033,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>17-April-2026</t>
+          <t>20-April-2026</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -1280,75 +1071,35 @@
           <t>2</t>
         </is>
       </c>
-      <c r="J6" t="inlineStr">
-        <is>
-          <t>16-April-2026</t>
-        </is>
-      </c>
-      <c r="K6" t="inlineStr">
-        <is>
-          <t>mimoto</t>
-        </is>
-      </c>
-      <c r="L6" t="inlineStr">
-        <is>
-          <t>79</t>
-        </is>
-      </c>
-      <c r="M6" t="inlineStr">
-        <is>
-          <t>59</t>
-        </is>
-      </c>
-      <c r="N6" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="O6" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="P6" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="Q6" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="S6" t="n">
-        <v/>
-      </c>
-      <c r="T6" t="n">
-        <v/>
-      </c>
-      <c r="U6" t="n">
-        <v/>
-      </c>
-      <c r="V6" t="n">
-        <v/>
-      </c>
-      <c r="W6" t="n">
-        <v/>
-      </c>
-      <c r="X6" t="n">
-        <v/>
-      </c>
-      <c r="Y6" t="n">
-        <v/>
-      </c>
-      <c r="Z6" t="n">
+      <c r="J6" t="n">
+        <v/>
+      </c>
+      <c r="K6" t="n">
+        <v/>
+      </c>
+      <c r="L6" t="n">
+        <v/>
+      </c>
+      <c r="M6" t="n">
+        <v/>
+      </c>
+      <c r="N6" t="n">
+        <v/>
+      </c>
+      <c r="O6" t="n">
+        <v/>
+      </c>
+      <c r="P6" t="n">
+        <v/>
+      </c>
+      <c r="Q6" t="n">
         <v/>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>17-April-2026</t>
+          <t>20-April-2026</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -1386,75 +1137,35 @@
           <t>1</t>
         </is>
       </c>
-      <c r="J7" t="inlineStr">
-        <is>
-          <t>16-April-2026</t>
-        </is>
-      </c>
-      <c r="K7" t="inlineStr">
-        <is>
-          <t>prereg</t>
-        </is>
-      </c>
-      <c r="L7" t="inlineStr">
-        <is>
-          <t>104</t>
-        </is>
-      </c>
-      <c r="M7" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="N7" t="inlineStr">
-        <is>
-          <t>70</t>
-        </is>
-      </c>
-      <c r="O7" t="inlineStr">
-        <is>
-          <t>30</t>
-        </is>
-      </c>
-      <c r="P7" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="Q7" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="S7" t="n">
-        <v/>
-      </c>
-      <c r="T7" t="n">
-        <v/>
-      </c>
-      <c r="U7" t="n">
-        <v/>
-      </c>
-      <c r="V7" t="n">
-        <v/>
-      </c>
-      <c r="W7" t="n">
-        <v/>
-      </c>
-      <c r="X7" t="n">
-        <v/>
-      </c>
-      <c r="Y7" t="n">
-        <v/>
-      </c>
-      <c r="Z7" t="n">
+      <c r="J7" t="n">
+        <v/>
+      </c>
+      <c r="K7" t="n">
+        <v/>
+      </c>
+      <c r="L7" t="n">
+        <v/>
+      </c>
+      <c r="M7" t="n">
+        <v/>
+      </c>
+      <c r="N7" t="n">
+        <v/>
+      </c>
+      <c r="O7" t="n">
+        <v/>
+      </c>
+      <c r="P7" t="n">
+        <v/>
+      </c>
+      <c r="Q7" t="n">
         <v/>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>17-April-2026</t>
+          <t>20-April-2026</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1492,68 +1203,28 @@
           <t>0</t>
         </is>
       </c>
-      <c r="J8" t="inlineStr">
-        <is>
-          <t>16-April-2026</t>
-        </is>
-      </c>
-      <c r="K8" t="inlineStr">
-        <is>
-          <t>residentui</t>
-        </is>
-      </c>
-      <c r="L8" t="inlineStr">
-        <is>
-          <t>33</t>
-        </is>
-      </c>
-      <c r="M8" t="inlineStr">
-        <is>
-          <t>12</t>
-        </is>
-      </c>
-      <c r="N8" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="O8" t="inlineStr">
-        <is>
-          <t>16</t>
-        </is>
-      </c>
-      <c r="P8" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="Q8" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="S8" t="n">
-        <v/>
-      </c>
-      <c r="T8" t="n">
-        <v/>
-      </c>
-      <c r="U8" t="n">
-        <v/>
-      </c>
-      <c r="V8" t="n">
-        <v/>
-      </c>
-      <c r="W8" t="n">
-        <v/>
-      </c>
-      <c r="X8" t="n">
-        <v/>
-      </c>
-      <c r="Y8" t="n">
-        <v/>
-      </c>
-      <c r="Z8" t="n">
+      <c r="J8" t="n">
+        <v/>
+      </c>
+      <c r="K8" t="n">
+        <v/>
+      </c>
+      <c r="L8" t="n">
+        <v/>
+      </c>
+      <c r="M8" t="n">
+        <v/>
+      </c>
+      <c r="N8" t="n">
+        <v/>
+      </c>
+      <c r="O8" t="n">
+        <v/>
+      </c>
+      <c r="P8" t="n">
+        <v/>
+      </c>
+      <c r="Q8" t="n">
         <v/>
       </c>
     </row>

--- a/minio-report-tracker/xlxs/collab.xlsx
+++ b/minio-report-tracker/xlxs/collab.xlsx
@@ -614,10 +614,10 @@
     <col width="12" customWidth="1" min="11" max="11"/>
     <col width="5" customWidth="1" min="12" max="12"/>
     <col width="5" customWidth="1" min="13" max="13"/>
-    <col width="5" customWidth="1" min="14" max="14"/>
-    <col width="5" customWidth="1" min="15" max="15"/>
-    <col width="5" customWidth="1" min="16" max="16"/>
-    <col width="5" customWidth="1" min="17" max="17"/>
+    <col width="4" customWidth="1" min="14" max="14"/>
+    <col width="4" customWidth="1" min="15" max="15"/>
+    <col width="4" customWidth="1" min="16" max="16"/>
+    <col width="4" customWidth="1" min="17" max="17"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -705,77 +705,77 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
+          <t>21-April-2026</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>auth</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>254</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>184</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>64</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
           <t>20-April-2026</t>
         </is>
       </c>
-      <c r="B2" t="inlineStr">
+      <c r="K2" t="inlineStr">
         <is>
           <t>auth</t>
         </is>
       </c>
-      <c r="C2" t="inlineStr">
+      <c r="L2" t="inlineStr">
         <is>
           <t>254</t>
         </is>
       </c>
-      <c r="D2" t="inlineStr">
+      <c r="M2" t="inlineStr">
         <is>
           <t>140</t>
         </is>
       </c>
-      <c r="E2" t="inlineStr">
+      <c r="N2" t="inlineStr">
         <is>
           <t>72</t>
         </is>
       </c>
-      <c r="F2" t="inlineStr">
+      <c r="O2" t="inlineStr">
         <is>
           <t>42</t>
         </is>
       </c>
-      <c r="G2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="J2" t="inlineStr">
-        <is>
-          <t>17-April-2026</t>
-        </is>
-      </c>
-      <c r="K2" t="inlineStr">
-        <is>
-          <t>esignet</t>
-        </is>
-      </c>
-      <c r="L2" t="inlineStr">
-        <is>
-          <t>375</t>
-        </is>
-      </c>
-      <c r="M2" t="inlineStr">
-        <is>
-          <t>268</t>
-        </is>
-      </c>
-      <c r="N2" t="inlineStr">
-        <is>
-          <t>47</t>
-        </is>
-      </c>
-      <c r="O2" t="inlineStr">
-        <is>
-          <t>33</t>
-        </is>
-      </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>27</t>
+          <t>0</t>
         </is>
       </c>
       <c r="Q2" t="inlineStr">
@@ -787,77 +787,77 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
+          <t>21-April-2026</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>esignet</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>375</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>303</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>36</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>27</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
           <t>20-April-2026</t>
         </is>
       </c>
-      <c r="B3" t="inlineStr">
+      <c r="K3" t="inlineStr">
         <is>
           <t>esignet</t>
         </is>
       </c>
-      <c r="C3" t="inlineStr">
+      <c r="L3" t="inlineStr">
         <is>
           <t>375</t>
         </is>
       </c>
-      <c r="D3" t="inlineStr">
+      <c r="M3" t="inlineStr">
         <is>
           <t>263</t>
         </is>
       </c>
-      <c r="E3" t="inlineStr">
+      <c r="N3" t="inlineStr">
         <is>
           <t>51</t>
         </is>
       </c>
-      <c r="F3" t="inlineStr">
+      <c r="O3" t="inlineStr">
         <is>
           <t>34</t>
         </is>
       </c>
-      <c r="G3" t="inlineStr">
+      <c r="P3" t="inlineStr">
         <is>
           <t>27</t>
-        </is>
-      </c>
-      <c r="H3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="J3" t="inlineStr">
-        <is>
-          <t>17-April-2026</t>
-        </is>
-      </c>
-      <c r="K3" t="inlineStr">
-        <is>
-          <t>injiverify</t>
-        </is>
-      </c>
-      <c r="L3" t="inlineStr">
-        <is>
-          <t>53</t>
-        </is>
-      </c>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="N3" t="inlineStr">
-        <is>
-          <t>23</t>
-        </is>
-      </c>
-      <c r="O3" t="inlineStr">
-        <is>
-          <t>30</t>
-        </is>
-      </c>
-      <c r="P3" t="inlineStr">
-        <is>
-          <t>0</t>
         </is>
       </c>
       <c r="Q3" t="inlineStr">
@@ -869,154 +869,154 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
+          <t>21-April-2026</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>idrepo</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>152</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>101</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>51</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
           <t>20-April-2026</t>
         </is>
       </c>
-      <c r="B4" t="inlineStr">
+      <c r="K4" t="inlineStr">
         <is>
           <t>idrepo</t>
         </is>
       </c>
-      <c r="C4" t="inlineStr">
+      <c r="L4" t="inlineStr">
         <is>
           <t>152</t>
         </is>
       </c>
-      <c r="D4" t="inlineStr">
+      <c r="M4" t="inlineStr">
         <is>
           <t>101</t>
         </is>
       </c>
-      <c r="E4" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F4" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="G4" t="inlineStr">
+      <c r="N4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P4" t="inlineStr">
         <is>
           <t>51</t>
         </is>
       </c>
-      <c r="H4" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="J4" t="inlineStr">
-        <is>
-          <t>17-April-2026</t>
-        </is>
-      </c>
-      <c r="K4" t="inlineStr">
-        <is>
-          <t>prereg</t>
-        </is>
-      </c>
-      <c r="L4" t="inlineStr">
-        <is>
-          <t>104</t>
-        </is>
-      </c>
-      <c r="M4" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="N4" t="inlineStr">
-        <is>
-          <t>70</t>
-        </is>
-      </c>
-      <c r="O4" t="inlineStr">
-        <is>
-          <t>30</t>
-        </is>
-      </c>
-      <c r="P4" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
       <c r="Q4" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
+          <t>21-April-2026</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>injiverify</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>53</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>23</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
           <t>20-April-2026</t>
         </is>
       </c>
-      <c r="B5" t="inlineStr">
+      <c r="K5" t="inlineStr">
         <is>
           <t>injiverify</t>
         </is>
       </c>
-      <c r="C5" t="inlineStr">
+      <c r="L5" t="inlineStr">
         <is>
           <t>53</t>
         </is>
       </c>
-      <c r="D5" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="E5" t="inlineStr">
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="N5" t="inlineStr">
         <is>
           <t>23</t>
         </is>
       </c>
-      <c r="F5" t="inlineStr">
+      <c r="O5" t="inlineStr">
         <is>
           <t>30</t>
-        </is>
-      </c>
-      <c r="G5" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H5" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="J5" t="inlineStr">
-        <is>
-          <t>17-April-2026</t>
-        </is>
-      </c>
-      <c r="K5" t="inlineStr">
-        <is>
-          <t>residentui</t>
-        </is>
-      </c>
-      <c r="L5" t="inlineStr">
-        <is>
-          <t>33</t>
-        </is>
-      </c>
-      <c r="M5" t="inlineStr">
-        <is>
-          <t>12</t>
-        </is>
-      </c>
-      <c r="N5" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="O5" t="inlineStr">
-        <is>
-          <t>16</t>
         </is>
       </c>
       <c r="P5" t="inlineStr">
@@ -1033,199 +1033,247 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
+          <t>21-April-2026</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>mimoto</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>79</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>65</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
           <t>20-April-2026</t>
         </is>
       </c>
-      <c r="B6" t="inlineStr">
+      <c r="K6" t="inlineStr">
         <is>
           <t>mimoto</t>
         </is>
       </c>
-      <c r="C6" t="inlineStr">
+      <c r="L6" t="inlineStr">
         <is>
           <t>79</t>
         </is>
       </c>
-      <c r="D6" t="inlineStr">
+      <c r="M6" t="inlineStr">
         <is>
           <t>66</t>
         </is>
       </c>
-      <c r="E6" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F6" t="inlineStr">
+      <c r="N6" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O6" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="G6" t="inlineStr">
+      <c r="P6" t="inlineStr">
         <is>
           <t>10</t>
         </is>
       </c>
-      <c r="H6" t="inlineStr">
+      <c r="Q6" t="inlineStr">
         <is>
           <t>2</t>
         </is>
-      </c>
-      <c r="J6" t="n">
-        <v/>
-      </c>
-      <c r="K6" t="n">
-        <v/>
-      </c>
-      <c r="L6" t="n">
-        <v/>
-      </c>
-      <c r="M6" t="n">
-        <v/>
-      </c>
-      <c r="N6" t="n">
-        <v/>
-      </c>
-      <c r="O6" t="n">
-        <v/>
-      </c>
-      <c r="P6" t="n">
-        <v/>
-      </c>
-      <c r="Q6" t="n">
-        <v/>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
+          <t>21-April-2026</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>prereg</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>104</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>70</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
           <t>20-April-2026</t>
         </is>
       </c>
-      <c r="B7" t="inlineStr">
+      <c r="K7" t="inlineStr">
         <is>
           <t>prereg</t>
         </is>
       </c>
-      <c r="C7" t="inlineStr">
+      <c r="L7" t="inlineStr">
         <is>
           <t>104</t>
         </is>
       </c>
-      <c r="D7" t="inlineStr">
+      <c r="M7" t="inlineStr">
         <is>
           <t>3</t>
         </is>
       </c>
-      <c r="E7" t="inlineStr">
+      <c r="N7" t="inlineStr">
         <is>
           <t>70</t>
         </is>
       </c>
-      <c r="F7" t="inlineStr">
+      <c r="O7" t="inlineStr">
         <is>
           <t>30</t>
         </is>
       </c>
-      <c r="G7" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H7" t="inlineStr">
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Q7" t="inlineStr">
         <is>
           <t>1</t>
         </is>
-      </c>
-      <c r="J7" t="n">
-        <v/>
-      </c>
-      <c r="K7" t="n">
-        <v/>
-      </c>
-      <c r="L7" t="n">
-        <v/>
-      </c>
-      <c r="M7" t="n">
-        <v/>
-      </c>
-      <c r="N7" t="n">
-        <v/>
-      </c>
-      <c r="O7" t="n">
-        <v/>
-      </c>
-      <c r="P7" t="n">
-        <v/>
-      </c>
-      <c r="Q7" t="n">
-        <v/>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
+          <t>21-April-2026</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>residentui</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>33</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
           <t>20-April-2026</t>
         </is>
       </c>
-      <c r="B8" t="inlineStr">
+      <c r="K8" t="inlineStr">
         <is>
           <t>residentui</t>
         </is>
       </c>
-      <c r="C8" t="inlineStr">
+      <c r="L8" t="inlineStr">
         <is>
           <t>33</t>
         </is>
       </c>
-      <c r="D8" t="inlineStr">
+      <c r="M8" t="inlineStr">
         <is>
           <t>12</t>
         </is>
       </c>
-      <c r="E8" t="inlineStr">
+      <c r="N8" t="inlineStr">
         <is>
           <t>5</t>
         </is>
       </c>
-      <c r="F8" t="inlineStr">
+      <c r="O8" t="inlineStr">
         <is>
           <t>16</t>
         </is>
       </c>
-      <c r="G8" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H8" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="J8" t="n">
-        <v/>
-      </c>
-      <c r="K8" t="n">
-        <v/>
-      </c>
-      <c r="L8" t="n">
-        <v/>
-      </c>
-      <c r="M8" t="n">
-        <v/>
-      </c>
-      <c r="N8" t="n">
-        <v/>
-      </c>
-      <c r="O8" t="n">
-        <v/>
-      </c>
-      <c r="P8" t="n">
-        <v/>
-      </c>
-      <c r="Q8" t="n">
-        <v/>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Q8" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
     </row>
   </sheetData>

--- a/minio-report-tracker/xlxs/collab.xlsx
+++ b/minio-report-tracker/xlxs/collab.xlsx
@@ -598,7 +598,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q8"/>
+  <dimension ref="A1:Z8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="15" customWidth="1" min="1" max="1"/>
@@ -618,6 +618,15 @@
     <col width="4" customWidth="1" min="15" max="15"/>
     <col width="4" customWidth="1" min="16" max="16"/>
     <col width="4" customWidth="1" min="17" max="17"/>
+    <col width="2" customWidth="1" min="18" max="18"/>
+    <col width="15" customWidth="1" min="19" max="19"/>
+    <col width="12" customWidth="1" min="20" max="20"/>
+    <col width="5" customWidth="1" min="21" max="21"/>
+    <col width="5" customWidth="1" min="22" max="22"/>
+    <col width="4" customWidth="1" min="23" max="23"/>
+    <col width="4" customWidth="1" min="24" max="24"/>
+    <col width="4" customWidth="1" min="25" max="25"/>
+    <col width="4" customWidth="1" min="26" max="26"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -701,84 +710,164 @@
           <t>KI</t>
         </is>
       </c>
+      <c r="S1" s="1" t="inlineStr">
+        <is>
+          <t>Date</t>
+        </is>
+      </c>
+      <c r="T1" s="1" t="inlineStr">
+        <is>
+          <t>Module</t>
+        </is>
+      </c>
+      <c r="U1" s="1" t="inlineStr">
+        <is>
+          <t>T</t>
+        </is>
+      </c>
+      <c r="V1" s="1" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
+      <c r="W1" s="1" t="inlineStr">
+        <is>
+          <t>S</t>
+        </is>
+      </c>
+      <c r="X1" s="1" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
+      <c r="Y1" s="1" t="inlineStr">
+        <is>
+          <t>I</t>
+        </is>
+      </c>
+      <c r="Z1" s="1" t="inlineStr">
+        <is>
+          <t>KI</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
+          <t>22-April-2026</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>auth</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>254</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>140</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>72</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>42</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
           <t>21-April-2026</t>
         </is>
       </c>
-      <c r="B2" t="inlineStr">
+      <c r="K2" t="inlineStr">
         <is>
           <t>auth</t>
         </is>
       </c>
-      <c r="C2" t="inlineStr">
+      <c r="L2" t="inlineStr">
         <is>
           <t>254</t>
         </is>
       </c>
-      <c r="D2" t="inlineStr">
+      <c r="M2" t="inlineStr">
         <is>
           <t>184</t>
         </is>
       </c>
-      <c r="E2" t="inlineStr">
+      <c r="N2" t="inlineStr">
         <is>
           <t>6</t>
         </is>
       </c>
-      <c r="F2" t="inlineStr">
+      <c r="O2" t="inlineStr">
         <is>
           <t>64</t>
         </is>
       </c>
-      <c r="G2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="J2" t="inlineStr">
+      <c r="P2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Q2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="S2" t="inlineStr">
         <is>
           <t>20-April-2026</t>
         </is>
       </c>
-      <c r="K2" t="inlineStr">
+      <c r="T2" t="inlineStr">
         <is>
           <t>auth</t>
         </is>
       </c>
-      <c r="L2" t="inlineStr">
+      <c r="U2" t="inlineStr">
         <is>
           <t>254</t>
         </is>
       </c>
-      <c r="M2" t="inlineStr">
+      <c r="V2" t="inlineStr">
         <is>
           <t>140</t>
         </is>
       </c>
-      <c r="N2" t="inlineStr">
+      <c r="W2" t="inlineStr">
         <is>
           <t>72</t>
         </is>
       </c>
-      <c r="O2" t="inlineStr">
+      <c r="X2" t="inlineStr">
         <is>
           <t>42</t>
         </is>
       </c>
-      <c r="P2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="Q2" t="inlineStr">
+      <c r="Y2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Z2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
@@ -787,80 +876,120 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
+          <t>22-April-2026</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>esignet</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>375</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>284</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>33</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>31</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>27</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
           <t>21-April-2026</t>
         </is>
       </c>
-      <c r="B3" t="inlineStr">
+      <c r="K3" t="inlineStr">
         <is>
           <t>esignet</t>
         </is>
       </c>
-      <c r="C3" t="inlineStr">
+      <c r="L3" t="inlineStr">
         <is>
           <t>375</t>
         </is>
       </c>
-      <c r="D3" t="inlineStr">
+      <c r="M3" t="inlineStr">
         <is>
           <t>303</t>
         </is>
       </c>
-      <c r="E3" t="inlineStr">
+      <c r="N3" t="inlineStr">
         <is>
           <t>9</t>
         </is>
       </c>
-      <c r="F3" t="inlineStr">
+      <c r="O3" t="inlineStr">
         <is>
           <t>36</t>
         </is>
       </c>
-      <c r="G3" t="inlineStr">
+      <c r="P3" t="inlineStr">
         <is>
           <t>27</t>
         </is>
       </c>
-      <c r="H3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="J3" t="inlineStr">
+      <c r="Q3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="S3" t="inlineStr">
         <is>
           <t>20-April-2026</t>
         </is>
       </c>
-      <c r="K3" t="inlineStr">
+      <c r="T3" t="inlineStr">
         <is>
           <t>esignet</t>
         </is>
       </c>
-      <c r="L3" t="inlineStr">
+      <c r="U3" t="inlineStr">
         <is>
           <t>375</t>
         </is>
       </c>
-      <c r="M3" t="inlineStr">
+      <c r="V3" t="inlineStr">
         <is>
           <t>263</t>
         </is>
       </c>
-      <c r="N3" t="inlineStr">
+      <c r="W3" t="inlineStr">
         <is>
           <t>51</t>
         </is>
       </c>
-      <c r="O3" t="inlineStr">
+      <c r="X3" t="inlineStr">
         <is>
           <t>34</t>
         </is>
       </c>
-      <c r="P3" t="inlineStr">
+      <c r="Y3" t="inlineStr">
         <is>
           <t>27</t>
         </is>
       </c>
-      <c r="Q3" t="inlineStr">
+      <c r="Z3" t="inlineStr">
         <is>
           <t>0</t>
         </is>
@@ -869,80 +998,120 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
+          <t>22-April-2026</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>idrepo</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>152</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>101</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>51</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
           <t>21-April-2026</t>
         </is>
       </c>
-      <c r="B4" t="inlineStr">
+      <c r="K4" t="inlineStr">
         <is>
           <t>idrepo</t>
         </is>
       </c>
-      <c r="C4" t="inlineStr">
+      <c r="L4" t="inlineStr">
         <is>
           <t>152</t>
         </is>
       </c>
-      <c r="D4" t="inlineStr">
+      <c r="M4" t="inlineStr">
         <is>
           <t>101</t>
         </is>
       </c>
-      <c r="E4" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F4" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="G4" t="inlineStr">
+      <c r="N4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P4" t="inlineStr">
         <is>
           <t>51</t>
         </is>
       </c>
-      <c r="H4" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="J4" t="inlineStr">
+      <c r="Q4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="S4" t="inlineStr">
         <is>
           <t>20-April-2026</t>
         </is>
       </c>
-      <c r="K4" t="inlineStr">
+      <c r="T4" t="inlineStr">
         <is>
           <t>idrepo</t>
         </is>
       </c>
-      <c r="L4" t="inlineStr">
+      <c r="U4" t="inlineStr">
         <is>
           <t>152</t>
         </is>
       </c>
-      <c r="M4" t="inlineStr">
+      <c r="V4" t="inlineStr">
         <is>
           <t>101</t>
         </is>
       </c>
-      <c r="N4" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="O4" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="P4" t="inlineStr">
+      <c r="W4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="X4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Y4" t="inlineStr">
         <is>
           <t>51</t>
         </is>
       </c>
-      <c r="Q4" t="inlineStr">
+      <c r="Z4" t="inlineStr">
         <is>
           <t>0</t>
         </is>
@@ -951,80 +1120,120 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
+          <t>22-April-2026</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>injiverify</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>53</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>23</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
           <t>21-April-2026</t>
         </is>
       </c>
-      <c r="B5" t="inlineStr">
+      <c r="K5" t="inlineStr">
         <is>
           <t>injiverify</t>
         </is>
       </c>
-      <c r="C5" t="inlineStr">
+      <c r="L5" t="inlineStr">
         <is>
           <t>53</t>
         </is>
       </c>
-      <c r="D5" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="E5" t="inlineStr">
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="N5" t="inlineStr">
         <is>
           <t>23</t>
         </is>
       </c>
-      <c r="F5" t="inlineStr">
+      <c r="O5" t="inlineStr">
         <is>
           <t>30</t>
         </is>
       </c>
-      <c r="G5" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H5" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="J5" t="inlineStr">
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Q5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="S5" t="inlineStr">
         <is>
           <t>20-April-2026</t>
         </is>
       </c>
-      <c r="K5" t="inlineStr">
+      <c r="T5" t="inlineStr">
         <is>
           <t>injiverify</t>
         </is>
       </c>
-      <c r="L5" t="inlineStr">
+      <c r="U5" t="inlineStr">
         <is>
           <t>53</t>
         </is>
       </c>
-      <c r="M5" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="N5" t="inlineStr">
+      <c r="V5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="W5" t="inlineStr">
         <is>
           <t>23</t>
         </is>
       </c>
-      <c r="O5" t="inlineStr">
+      <c r="X5" t="inlineStr">
         <is>
           <t>30</t>
         </is>
       </c>
-      <c r="P5" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="Q5" t="inlineStr">
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Z5" t="inlineStr">
         <is>
           <t>0</t>
         </is>
@@ -1033,80 +1242,120 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
+          <t>22-April-2026</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>mimoto</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>79</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>65</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
           <t>21-April-2026</t>
         </is>
       </c>
-      <c r="B6" t="inlineStr">
+      <c r="K6" t="inlineStr">
         <is>
           <t>mimoto</t>
         </is>
       </c>
-      <c r="C6" t="inlineStr">
+      <c r="L6" t="inlineStr">
         <is>
           <t>79</t>
         </is>
       </c>
-      <c r="D6" t="inlineStr">
+      <c r="M6" t="inlineStr">
         <is>
           <t>65</t>
         </is>
       </c>
-      <c r="E6" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F6" t="inlineStr">
+      <c r="N6" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O6" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="G6" t="inlineStr">
+      <c r="P6" t="inlineStr">
         <is>
           <t>10</t>
         </is>
       </c>
-      <c r="H6" t="inlineStr">
+      <c r="Q6" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="J6" t="inlineStr">
+      <c r="S6" t="inlineStr">
         <is>
           <t>20-April-2026</t>
         </is>
       </c>
-      <c r="K6" t="inlineStr">
+      <c r="T6" t="inlineStr">
         <is>
           <t>mimoto</t>
         </is>
       </c>
-      <c r="L6" t="inlineStr">
+      <c r="U6" t="inlineStr">
         <is>
           <t>79</t>
         </is>
       </c>
-      <c r="M6" t="inlineStr">
+      <c r="V6" t="inlineStr">
         <is>
           <t>66</t>
         </is>
       </c>
-      <c r="N6" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="O6" t="inlineStr">
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="X6" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="P6" t="inlineStr">
+      <c r="Y6" t="inlineStr">
         <is>
           <t>10</t>
         </is>
       </c>
-      <c r="Q6" t="inlineStr">
+      <c r="Z6" t="inlineStr">
         <is>
           <t>2</t>
         </is>
@@ -1115,80 +1364,120 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
+          <t>22-April-2026</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>prereg</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>104</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>70</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
           <t>21-April-2026</t>
         </is>
       </c>
-      <c r="B7" t="inlineStr">
+      <c r="K7" t="inlineStr">
         <is>
           <t>prereg</t>
         </is>
       </c>
-      <c r="C7" t="inlineStr">
+      <c r="L7" t="inlineStr">
         <is>
           <t>104</t>
         </is>
       </c>
-      <c r="D7" t="inlineStr">
+      <c r="M7" t="inlineStr">
         <is>
           <t>3</t>
         </is>
       </c>
-      <c r="E7" t="inlineStr">
+      <c r="N7" t="inlineStr">
         <is>
           <t>70</t>
         </is>
       </c>
-      <c r="F7" t="inlineStr">
+      <c r="O7" t="inlineStr">
         <is>
           <t>30</t>
         </is>
       </c>
-      <c r="G7" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H7" t="inlineStr">
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Q7" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="J7" t="inlineStr">
+      <c r="S7" t="inlineStr">
         <is>
           <t>20-April-2026</t>
         </is>
       </c>
-      <c r="K7" t="inlineStr">
+      <c r="T7" t="inlineStr">
         <is>
           <t>prereg</t>
         </is>
       </c>
-      <c r="L7" t="inlineStr">
+      <c r="U7" t="inlineStr">
         <is>
           <t>104</t>
         </is>
       </c>
-      <c r="M7" t="inlineStr">
+      <c r="V7" t="inlineStr">
         <is>
           <t>3</t>
         </is>
       </c>
-      <c r="N7" t="inlineStr">
+      <c r="W7" t="inlineStr">
         <is>
           <t>70</t>
         </is>
       </c>
-      <c r="O7" t="inlineStr">
+      <c r="X7" t="inlineStr">
         <is>
           <t>30</t>
         </is>
       </c>
-      <c r="P7" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="Q7" t="inlineStr">
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Z7" t="inlineStr">
         <is>
           <t>1</t>
         </is>
@@ -1197,80 +1486,120 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
+          <t>22-April-2026</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>residentui</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>33</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
           <t>21-April-2026</t>
         </is>
       </c>
-      <c r="B8" t="inlineStr">
+      <c r="K8" t="inlineStr">
         <is>
           <t>residentui</t>
         </is>
       </c>
-      <c r="C8" t="inlineStr">
+      <c r="L8" t="inlineStr">
         <is>
           <t>33</t>
         </is>
       </c>
-      <c r="D8" t="inlineStr">
+      <c r="M8" t="inlineStr">
         <is>
           <t>12</t>
         </is>
       </c>
-      <c r="E8" t="inlineStr">
+      <c r="N8" t="inlineStr">
         <is>
           <t>5</t>
         </is>
       </c>
-      <c r="F8" t="inlineStr">
+      <c r="O8" t="inlineStr">
         <is>
           <t>16</t>
         </is>
       </c>
-      <c r="G8" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H8" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="J8" t="inlineStr">
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Q8" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="S8" t="inlineStr">
         <is>
           <t>20-April-2026</t>
         </is>
       </c>
-      <c r="K8" t="inlineStr">
+      <c r="T8" t="inlineStr">
         <is>
           <t>residentui</t>
         </is>
       </c>
-      <c r="L8" t="inlineStr">
+      <c r="U8" t="inlineStr">
         <is>
           <t>33</t>
         </is>
       </c>
-      <c r="M8" t="inlineStr">
+      <c r="V8" t="inlineStr">
         <is>
           <t>12</t>
         </is>
       </c>
-      <c r="N8" t="inlineStr">
+      <c r="W8" t="inlineStr">
         <is>
           <t>5</t>
         </is>
       </c>
-      <c r="O8" t="inlineStr">
+      <c r="X8" t="inlineStr">
         <is>
           <t>16</t>
         </is>
       </c>
-      <c r="P8" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="Q8" t="inlineStr">
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Z8" t="inlineStr">
         <is>
           <t>0</t>
         </is>

--- a/minio-report-tracker/xlxs/collab.xlsx
+++ b/minio-report-tracker/xlxs/collab.xlsx
@@ -598,7 +598,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Z8"/>
+  <dimension ref="A1:AI8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="15" customWidth="1" min="1" max="1"/>
@@ -627,6 +627,15 @@
     <col width="4" customWidth="1" min="24" max="24"/>
     <col width="4" customWidth="1" min="25" max="25"/>
     <col width="4" customWidth="1" min="26" max="26"/>
+    <col width="2" customWidth="1" min="27" max="27"/>
+    <col width="15" customWidth="1" min="28" max="28"/>
+    <col width="12" customWidth="1" min="29" max="29"/>
+    <col width="5" customWidth="1" min="30" max="30"/>
+    <col width="5" customWidth="1" min="31" max="31"/>
+    <col width="5" customWidth="1" min="32" max="32"/>
+    <col width="5" customWidth="1" min="33" max="33"/>
+    <col width="5" customWidth="1" min="34" max="34"/>
+    <col width="5" customWidth="1" min="35" max="35"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -750,124 +759,204 @@
           <t>KI</t>
         </is>
       </c>
+      <c r="AB1" s="1" t="inlineStr">
+        <is>
+          <t>Date</t>
+        </is>
+      </c>
+      <c r="AC1" s="1" t="inlineStr">
+        <is>
+          <t>Module</t>
+        </is>
+      </c>
+      <c r="AD1" s="1" t="inlineStr">
+        <is>
+          <t>T</t>
+        </is>
+      </c>
+      <c r="AE1" s="1" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
+      <c r="AF1" s="1" t="inlineStr">
+        <is>
+          <t>S</t>
+        </is>
+      </c>
+      <c r="AG1" s="1" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
+      <c r="AH1" s="1" t="inlineStr">
+        <is>
+          <t>I</t>
+        </is>
+      </c>
+      <c r="AI1" s="1" t="inlineStr">
+        <is>
+          <t>KI</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
+          <t>23-April-2026</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>auth</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>254</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>140</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>72</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>42</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
           <t>22-April-2026</t>
         </is>
       </c>
-      <c r="B2" t="inlineStr">
+      <c r="K2" t="inlineStr">
         <is>
           <t>auth</t>
         </is>
       </c>
-      <c r="C2" t="inlineStr">
+      <c r="L2" t="inlineStr">
         <is>
           <t>254</t>
         </is>
       </c>
-      <c r="D2" t="inlineStr">
+      <c r="M2" t="inlineStr">
         <is>
           <t>140</t>
         </is>
       </c>
-      <c r="E2" t="inlineStr">
+      <c r="N2" t="inlineStr">
         <is>
           <t>72</t>
         </is>
       </c>
-      <c r="F2" t="inlineStr">
+      <c r="O2" t="inlineStr">
         <is>
           <t>42</t>
         </is>
       </c>
-      <c r="G2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="J2" t="inlineStr">
+      <c r="P2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Q2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="S2" t="inlineStr">
         <is>
           <t>21-April-2026</t>
         </is>
       </c>
-      <c r="K2" t="inlineStr">
+      <c r="T2" t="inlineStr">
         <is>
           <t>auth</t>
         </is>
       </c>
-      <c r="L2" t="inlineStr">
+      <c r="U2" t="inlineStr">
         <is>
           <t>254</t>
         </is>
       </c>
-      <c r="M2" t="inlineStr">
+      <c r="V2" t="inlineStr">
         <is>
           <t>184</t>
         </is>
       </c>
-      <c r="N2" t="inlineStr">
+      <c r="W2" t="inlineStr">
         <is>
           <t>6</t>
         </is>
       </c>
-      <c r="O2" t="inlineStr">
+      <c r="X2" t="inlineStr">
         <is>
           <t>64</t>
         </is>
       </c>
-      <c r="P2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="Q2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="S2" t="inlineStr">
+      <c r="Y2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Z2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB2" t="inlineStr">
         <is>
           <t>20-April-2026</t>
         </is>
       </c>
-      <c r="T2" t="inlineStr">
-        <is>
-          <t>auth</t>
-        </is>
-      </c>
-      <c r="U2" t="inlineStr">
-        <is>
-          <t>254</t>
-        </is>
-      </c>
-      <c r="V2" t="inlineStr">
-        <is>
-          <t>140</t>
-        </is>
-      </c>
-      <c r="W2" t="inlineStr">
-        <is>
-          <t>72</t>
-        </is>
-      </c>
-      <c r="X2" t="inlineStr">
-        <is>
-          <t>42</t>
-        </is>
-      </c>
-      <c r="Y2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="Z2" t="inlineStr">
+      <c r="AC2" t="inlineStr">
+        <is>
+          <t>esignet</t>
+        </is>
+      </c>
+      <c r="AD2" t="inlineStr">
+        <is>
+          <t>375</t>
+        </is>
+      </c>
+      <c r="AE2" t="inlineStr">
+        <is>
+          <t>263</t>
+        </is>
+      </c>
+      <c r="AF2" t="inlineStr">
+        <is>
+          <t>51</t>
+        </is>
+      </c>
+      <c r="AG2" t="inlineStr">
+        <is>
+          <t>34</t>
+        </is>
+      </c>
+      <c r="AH2" t="inlineStr">
+        <is>
+          <t>27</t>
+        </is>
+      </c>
+      <c r="AI2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
@@ -876,120 +965,160 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
+          <t>23-April-2026</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>esignet</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>375</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>303</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>18</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>27</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>27</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
           <t>22-April-2026</t>
         </is>
       </c>
-      <c r="B3" t="inlineStr">
+      <c r="K3" t="inlineStr">
         <is>
           <t>esignet</t>
         </is>
       </c>
-      <c r="C3" t="inlineStr">
+      <c r="L3" t="inlineStr">
         <is>
           <t>375</t>
         </is>
       </c>
-      <c r="D3" t="inlineStr">
+      <c r="M3" t="inlineStr">
         <is>
           <t>284</t>
         </is>
       </c>
-      <c r="E3" t="inlineStr">
+      <c r="N3" t="inlineStr">
         <is>
           <t>33</t>
         </is>
       </c>
-      <c r="F3" t="inlineStr">
+      <c r="O3" t="inlineStr">
         <is>
           <t>31</t>
         </is>
       </c>
-      <c r="G3" t="inlineStr">
+      <c r="P3" t="inlineStr">
         <is>
           <t>27</t>
         </is>
       </c>
-      <c r="H3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="J3" t="inlineStr">
+      <c r="Q3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="S3" t="inlineStr">
         <is>
           <t>21-April-2026</t>
         </is>
       </c>
-      <c r="K3" t="inlineStr">
+      <c r="T3" t="inlineStr">
         <is>
           <t>esignet</t>
         </is>
       </c>
-      <c r="L3" t="inlineStr">
+      <c r="U3" t="inlineStr">
         <is>
           <t>375</t>
         </is>
       </c>
-      <c r="M3" t="inlineStr">
+      <c r="V3" t="inlineStr">
         <is>
           <t>303</t>
         </is>
       </c>
-      <c r="N3" t="inlineStr">
+      <c r="W3" t="inlineStr">
         <is>
           <t>9</t>
         </is>
       </c>
-      <c r="O3" t="inlineStr">
+      <c r="X3" t="inlineStr">
         <is>
           <t>36</t>
         </is>
       </c>
-      <c r="P3" t="inlineStr">
+      <c r="Y3" t="inlineStr">
         <is>
           <t>27</t>
         </is>
       </c>
-      <c r="Q3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="S3" t="inlineStr">
+      <c r="Z3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB3" t="inlineStr">
         <is>
           <t>20-April-2026</t>
         </is>
       </c>
-      <c r="T3" t="inlineStr">
-        <is>
-          <t>esignet</t>
-        </is>
-      </c>
-      <c r="U3" t="inlineStr">
-        <is>
-          <t>375</t>
-        </is>
-      </c>
-      <c r="V3" t="inlineStr">
-        <is>
-          <t>263</t>
-        </is>
-      </c>
-      <c r="W3" t="inlineStr">
-        <is>
-          <t>51</t>
-        </is>
-      </c>
-      <c r="X3" t="inlineStr">
-        <is>
-          <t>34</t>
-        </is>
-      </c>
-      <c r="Y3" t="inlineStr">
-        <is>
-          <t>27</t>
-        </is>
-      </c>
-      <c r="Z3" t="inlineStr">
+      <c r="AC3" t="inlineStr">
+        <is>
+          <t>injiverify</t>
+        </is>
+      </c>
+      <c r="AD3" t="inlineStr">
+        <is>
+          <t>53</t>
+        </is>
+      </c>
+      <c r="AE3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AF3" t="inlineStr">
+        <is>
+          <t>23</t>
+        </is>
+      </c>
+      <c r="AG3" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="AH3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AI3" t="inlineStr">
         <is>
           <t>0</t>
         </is>
@@ -998,242 +1127,322 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
+          <t>23-April-2026</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>idrepo</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>152</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>101</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>51</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
           <t>22-April-2026</t>
         </is>
       </c>
-      <c r="B4" t="inlineStr">
+      <c r="K4" t="inlineStr">
         <is>
           <t>idrepo</t>
         </is>
       </c>
-      <c r="C4" t="inlineStr">
+      <c r="L4" t="inlineStr">
         <is>
           <t>152</t>
         </is>
       </c>
-      <c r="D4" t="inlineStr">
+      <c r="M4" t="inlineStr">
         <is>
           <t>101</t>
         </is>
       </c>
-      <c r="E4" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F4" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="G4" t="inlineStr">
+      <c r="N4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P4" t="inlineStr">
         <is>
           <t>51</t>
         </is>
       </c>
-      <c r="H4" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="J4" t="inlineStr">
+      <c r="Q4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="S4" t="inlineStr">
         <is>
           <t>21-April-2026</t>
         </is>
       </c>
-      <c r="K4" t="inlineStr">
+      <c r="T4" t="inlineStr">
         <is>
           <t>idrepo</t>
         </is>
       </c>
-      <c r="L4" t="inlineStr">
+      <c r="U4" t="inlineStr">
         <is>
           <t>152</t>
         </is>
       </c>
-      <c r="M4" t="inlineStr">
+      <c r="V4" t="inlineStr">
         <is>
           <t>101</t>
         </is>
       </c>
-      <c r="N4" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="O4" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="P4" t="inlineStr">
+      <c r="W4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="X4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Y4" t="inlineStr">
         <is>
           <t>51</t>
         </is>
       </c>
-      <c r="Q4" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="S4" t="inlineStr">
+      <c r="Z4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB4" t="inlineStr">
         <is>
           <t>20-April-2026</t>
         </is>
       </c>
-      <c r="T4" t="inlineStr">
-        <is>
-          <t>idrepo</t>
-        </is>
-      </c>
-      <c r="U4" t="inlineStr">
-        <is>
-          <t>152</t>
-        </is>
-      </c>
-      <c r="V4" t="inlineStr">
-        <is>
-          <t>101</t>
-        </is>
-      </c>
-      <c r="W4" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="X4" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="Y4" t="inlineStr">
-        <is>
-          <t>51</t>
-        </is>
-      </c>
-      <c r="Z4" t="inlineStr">
-        <is>
-          <t>0</t>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t>prereg</t>
+        </is>
+      </c>
+      <c r="AD4" t="inlineStr">
+        <is>
+          <t>104</t>
+        </is>
+      </c>
+      <c r="AE4" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AF4" t="inlineStr">
+        <is>
+          <t>70</t>
+        </is>
+      </c>
+      <c r="AG4" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="AH4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AI4" t="inlineStr">
+        <is>
+          <t>1</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
+          <t>23-April-2026</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>injiverify</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>53</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>23</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
           <t>22-April-2026</t>
         </is>
       </c>
-      <c r="B5" t="inlineStr">
+      <c r="K5" t="inlineStr">
         <is>
           <t>injiverify</t>
         </is>
       </c>
-      <c r="C5" t="inlineStr">
+      <c r="L5" t="inlineStr">
         <is>
           <t>53</t>
         </is>
       </c>
-      <c r="D5" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="E5" t="inlineStr">
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="N5" t="inlineStr">
         <is>
           <t>23</t>
         </is>
       </c>
-      <c r="F5" t="inlineStr">
+      <c r="O5" t="inlineStr">
         <is>
           <t>30</t>
         </is>
       </c>
-      <c r="G5" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H5" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="J5" t="inlineStr">
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Q5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="S5" t="inlineStr">
         <is>
           <t>21-April-2026</t>
         </is>
       </c>
-      <c r="K5" t="inlineStr">
+      <c r="T5" t="inlineStr">
         <is>
           <t>injiverify</t>
         </is>
       </c>
-      <c r="L5" t="inlineStr">
+      <c r="U5" t="inlineStr">
         <is>
           <t>53</t>
         </is>
       </c>
-      <c r="M5" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="N5" t="inlineStr">
+      <c r="V5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="W5" t="inlineStr">
         <is>
           <t>23</t>
         </is>
       </c>
-      <c r="O5" t="inlineStr">
+      <c r="X5" t="inlineStr">
         <is>
           <t>30</t>
         </is>
       </c>
-      <c r="P5" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="Q5" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="S5" t="inlineStr">
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Z5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB5" t="inlineStr">
         <is>
           <t>20-April-2026</t>
         </is>
       </c>
-      <c r="T5" t="inlineStr">
-        <is>
-          <t>injiverify</t>
-        </is>
-      </c>
-      <c r="U5" t="inlineStr">
-        <is>
-          <t>53</t>
-        </is>
-      </c>
-      <c r="V5" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="W5" t="inlineStr">
-        <is>
-          <t>23</t>
-        </is>
-      </c>
-      <c r="X5" t="inlineStr">
-        <is>
-          <t>30</t>
-        </is>
-      </c>
-      <c r="Y5" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="Z5" t="inlineStr">
+      <c r="AC5" t="inlineStr">
+        <is>
+          <t>residentui</t>
+        </is>
+      </c>
+      <c r="AD5" t="inlineStr">
+        <is>
+          <t>33</t>
+        </is>
+      </c>
+      <c r="AE5" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="AF5" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AG5" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="AH5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AI5" t="inlineStr">
         <is>
           <t>0</t>
         </is>
@@ -1242,358 +1451,406 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
+          <t>23-April-2026</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>mimoto</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>79</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>66</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
           <t>22-April-2026</t>
         </is>
       </c>
-      <c r="B6" t="inlineStr">
+      <c r="K6" t="inlineStr">
         <is>
           <t>mimoto</t>
         </is>
       </c>
-      <c r="C6" t="inlineStr">
+      <c r="L6" t="inlineStr">
         <is>
           <t>79</t>
         </is>
       </c>
-      <c r="D6" t="inlineStr">
+      <c r="M6" t="inlineStr">
         <is>
           <t>65</t>
         </is>
       </c>
-      <c r="E6" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F6" t="inlineStr">
+      <c r="N6" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O6" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="G6" t="inlineStr">
+      <c r="P6" t="inlineStr">
         <is>
           <t>10</t>
         </is>
       </c>
-      <c r="H6" t="inlineStr">
+      <c r="Q6" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="J6" t="inlineStr">
+      <c r="S6" t="inlineStr">
         <is>
           <t>21-April-2026</t>
         </is>
       </c>
-      <c r="K6" t="inlineStr">
+      <c r="T6" t="inlineStr">
         <is>
           <t>mimoto</t>
         </is>
       </c>
-      <c r="L6" t="inlineStr">
+      <c r="U6" t="inlineStr">
         <is>
           <t>79</t>
         </is>
       </c>
-      <c r="M6" t="inlineStr">
+      <c r="V6" t="inlineStr">
         <is>
           <t>65</t>
         </is>
       </c>
-      <c r="N6" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="O6" t="inlineStr">
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="X6" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="P6" t="inlineStr">
+      <c r="Y6" t="inlineStr">
         <is>
           <t>10</t>
         </is>
       </c>
-      <c r="Q6" t="inlineStr">
+      <c r="Z6" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="S6" t="inlineStr">
-        <is>
-          <t>20-April-2026</t>
-        </is>
-      </c>
-      <c r="T6" t="inlineStr">
-        <is>
-          <t>mimoto</t>
-        </is>
-      </c>
-      <c r="U6" t="inlineStr">
-        <is>
-          <t>79</t>
-        </is>
-      </c>
-      <c r="V6" t="inlineStr">
-        <is>
-          <t>66</t>
-        </is>
-      </c>
-      <c r="W6" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="X6" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="Y6" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="Z6" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
+      <c r="AB6" t="n">
+        <v/>
+      </c>
+      <c r="AC6" t="n">
+        <v/>
+      </c>
+      <c r="AD6" t="n">
+        <v/>
+      </c>
+      <c r="AE6" t="n">
+        <v/>
+      </c>
+      <c r="AF6" t="n">
+        <v/>
+      </c>
+      <c r="AG6" t="n">
+        <v/>
+      </c>
+      <c r="AH6" t="n">
+        <v/>
+      </c>
+      <c r="AI6" t="n">
+        <v/>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
+          <t>23-April-2026</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>prereg</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>104</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>70</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
           <t>22-April-2026</t>
         </is>
       </c>
-      <c r="B7" t="inlineStr">
+      <c r="K7" t="inlineStr">
         <is>
           <t>prereg</t>
         </is>
       </c>
-      <c r="C7" t="inlineStr">
+      <c r="L7" t="inlineStr">
         <is>
           <t>104</t>
         </is>
       </c>
-      <c r="D7" t="inlineStr">
+      <c r="M7" t="inlineStr">
         <is>
           <t>3</t>
         </is>
       </c>
-      <c r="E7" t="inlineStr">
+      <c r="N7" t="inlineStr">
         <is>
           <t>70</t>
         </is>
       </c>
-      <c r="F7" t="inlineStr">
+      <c r="O7" t="inlineStr">
         <is>
           <t>30</t>
         </is>
       </c>
-      <c r="G7" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H7" t="inlineStr">
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Q7" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="J7" t="inlineStr">
+      <c r="S7" t="inlineStr">
         <is>
           <t>21-April-2026</t>
         </is>
       </c>
-      <c r="K7" t="inlineStr">
+      <c r="T7" t="inlineStr">
         <is>
           <t>prereg</t>
         </is>
       </c>
-      <c r="L7" t="inlineStr">
+      <c r="U7" t="inlineStr">
         <is>
           <t>104</t>
         </is>
       </c>
-      <c r="M7" t="inlineStr">
+      <c r="V7" t="inlineStr">
         <is>
           <t>3</t>
         </is>
       </c>
-      <c r="N7" t="inlineStr">
+      <c r="W7" t="inlineStr">
         <is>
           <t>70</t>
         </is>
       </c>
-      <c r="O7" t="inlineStr">
+      <c r="X7" t="inlineStr">
         <is>
           <t>30</t>
         </is>
       </c>
-      <c r="P7" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="Q7" t="inlineStr">
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Z7" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="S7" t="inlineStr">
-        <is>
-          <t>20-April-2026</t>
-        </is>
-      </c>
-      <c r="T7" t="inlineStr">
-        <is>
-          <t>prereg</t>
-        </is>
-      </c>
-      <c r="U7" t="inlineStr">
-        <is>
-          <t>104</t>
-        </is>
-      </c>
-      <c r="V7" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="W7" t="inlineStr">
-        <is>
-          <t>70</t>
-        </is>
-      </c>
-      <c r="X7" t="inlineStr">
-        <is>
-          <t>30</t>
-        </is>
-      </c>
-      <c r="Y7" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="Z7" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
+      <c r="AB7" t="n">
+        <v/>
+      </c>
+      <c r="AC7" t="n">
+        <v/>
+      </c>
+      <c r="AD7" t="n">
+        <v/>
+      </c>
+      <c r="AE7" t="n">
+        <v/>
+      </c>
+      <c r="AF7" t="n">
+        <v/>
+      </c>
+      <c r="AG7" t="n">
+        <v/>
+      </c>
+      <c r="AH7" t="n">
+        <v/>
+      </c>
+      <c r="AI7" t="n">
+        <v/>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
+          <t>23-April-2026</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>residentui</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>33</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
           <t>22-April-2026</t>
         </is>
       </c>
-      <c r="B8" t="inlineStr">
+      <c r="K8" t="inlineStr">
         <is>
           <t>residentui</t>
         </is>
       </c>
-      <c r="C8" t="inlineStr">
+      <c r="L8" t="inlineStr">
         <is>
           <t>33</t>
         </is>
       </c>
-      <c r="D8" t="inlineStr">
+      <c r="M8" t="inlineStr">
         <is>
           <t>12</t>
         </is>
       </c>
-      <c r="E8" t="inlineStr">
+      <c r="N8" t="inlineStr">
         <is>
           <t>5</t>
         </is>
       </c>
-      <c r="F8" t="inlineStr">
+      <c r="O8" t="inlineStr">
         <is>
           <t>16</t>
         </is>
       </c>
-      <c r="G8" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H8" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="J8" t="inlineStr">
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Q8" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="S8" t="inlineStr">
         <is>
           <t>21-April-2026</t>
         </is>
       </c>
-      <c r="K8" t="inlineStr">
+      <c r="T8" t="inlineStr">
         <is>
           <t>residentui</t>
         </is>
       </c>
-      <c r="L8" t="inlineStr">
+      <c r="U8" t="inlineStr">
         <is>
           <t>33</t>
         </is>
       </c>
-      <c r="M8" t="inlineStr">
+      <c r="V8" t="inlineStr">
         <is>
           <t>12</t>
         </is>
       </c>
-      <c r="N8" t="inlineStr">
+      <c r="W8" t="inlineStr">
         <is>
           <t>5</t>
         </is>
       </c>
-      <c r="O8" t="inlineStr">
+      <c r="X8" t="inlineStr">
         <is>
           <t>16</t>
         </is>
       </c>
-      <c r="P8" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="Q8" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="S8" t="inlineStr">
-        <is>
-          <t>20-April-2026</t>
-        </is>
-      </c>
-      <c r="T8" t="inlineStr">
-        <is>
-          <t>residentui</t>
-        </is>
-      </c>
-      <c r="U8" t="inlineStr">
-        <is>
-          <t>33</t>
-        </is>
-      </c>
-      <c r="V8" t="inlineStr">
-        <is>
-          <t>12</t>
-        </is>
-      </c>
-      <c r="W8" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="X8" t="inlineStr">
-        <is>
-          <t>16</t>
-        </is>
-      </c>
       <c r="Y8" t="inlineStr">
         <is>
           <t>0</t>
@@ -1603,6 +1860,30 @@
         <is>
           <t>0</t>
         </is>
+      </c>
+      <c r="AB8" t="n">
+        <v/>
+      </c>
+      <c r="AC8" t="n">
+        <v/>
+      </c>
+      <c r="AD8" t="n">
+        <v/>
+      </c>
+      <c r="AE8" t="n">
+        <v/>
+      </c>
+      <c r="AF8" t="n">
+        <v/>
+      </c>
+      <c r="AG8" t="n">
+        <v/>
+      </c>
+      <c r="AH8" t="n">
+        <v/>
+      </c>
+      <c r="AI8" t="n">
+        <v/>
       </c>
     </row>
   </sheetData>

--- a/minio-report-tracker/xlxs/collab.xlsx
+++ b/minio-report-tracker/xlxs/collab.xlsx
@@ -803,129 +803,129 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
+          <t>24-April-2026</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>auth</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>254</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>142</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>72</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>40</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
           <t>23-April-2026</t>
         </is>
       </c>
-      <c r="B2" t="inlineStr">
+      <c r="K2" t="inlineStr">
         <is>
           <t>auth</t>
         </is>
       </c>
-      <c r="C2" t="inlineStr">
+      <c r="L2" t="inlineStr">
         <is>
           <t>254</t>
         </is>
       </c>
-      <c r="D2" t="inlineStr">
+      <c r="M2" t="inlineStr">
         <is>
           <t>140</t>
         </is>
       </c>
-      <c r="E2" t="inlineStr">
+      <c r="N2" t="inlineStr">
         <is>
           <t>72</t>
         </is>
       </c>
-      <c r="F2" t="inlineStr">
+      <c r="O2" t="inlineStr">
         <is>
           <t>42</t>
         </is>
       </c>
-      <c r="G2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="J2" t="inlineStr">
+      <c r="P2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Q2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="S2" t="inlineStr">
         <is>
           <t>22-April-2026</t>
         </is>
       </c>
-      <c r="K2" t="inlineStr">
+      <c r="T2" t="inlineStr">
         <is>
           <t>auth</t>
         </is>
       </c>
-      <c r="L2" t="inlineStr">
+      <c r="U2" t="inlineStr">
         <is>
           <t>254</t>
         </is>
       </c>
-      <c r="M2" t="inlineStr">
+      <c r="V2" t="inlineStr">
         <is>
           <t>140</t>
         </is>
       </c>
-      <c r="N2" t="inlineStr">
+      <c r="W2" t="inlineStr">
         <is>
           <t>72</t>
         </is>
       </c>
-      <c r="O2" t="inlineStr">
+      <c r="X2" t="inlineStr">
         <is>
           <t>42</t>
         </is>
       </c>
-      <c r="P2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="Q2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="S2" t="inlineStr">
+      <c r="Y2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Z2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB2" t="inlineStr">
         <is>
           <t>21-April-2026</t>
         </is>
       </c>
-      <c r="T2" t="inlineStr">
-        <is>
-          <t>auth</t>
-        </is>
-      </c>
-      <c r="U2" t="inlineStr">
-        <is>
-          <t>254</t>
-        </is>
-      </c>
-      <c r="V2" t="inlineStr">
-        <is>
-          <t>184</t>
-        </is>
-      </c>
-      <c r="W2" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="X2" t="inlineStr">
-        <is>
-          <t>64</t>
-        </is>
-      </c>
-      <c r="Y2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>20-April-2026</t>
-        </is>
-      </c>
       <c r="AC2" t="inlineStr">
         <is>
           <t>esignet</t>
@@ -938,17 +938,17 @@
       </c>
       <c r="AE2" t="inlineStr">
         <is>
-          <t>263</t>
+          <t>303</t>
         </is>
       </c>
       <c r="AF2" t="inlineStr">
         <is>
-          <t>51</t>
+          <t>9</t>
         </is>
       </c>
       <c r="AG2" t="inlineStr">
         <is>
-          <t>34</t>
+          <t>36</t>
         </is>
       </c>
       <c r="AH2" t="inlineStr">
@@ -965,127 +965,127 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
+          <t>24-April-2026</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>esignet</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>375</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>292</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>26</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>27</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
           <t>23-April-2026</t>
         </is>
       </c>
-      <c r="B3" t="inlineStr">
+      <c r="K3" t="inlineStr">
         <is>
           <t>esignet</t>
         </is>
       </c>
-      <c r="C3" t="inlineStr">
+      <c r="L3" t="inlineStr">
         <is>
           <t>375</t>
         </is>
       </c>
-      <c r="D3" t="inlineStr">
+      <c r="M3" t="inlineStr">
         <is>
           <t>303</t>
         </is>
       </c>
-      <c r="E3" t="inlineStr">
+      <c r="N3" t="inlineStr">
         <is>
           <t>18</t>
         </is>
       </c>
-      <c r="F3" t="inlineStr">
+      <c r="O3" t="inlineStr">
         <is>
           <t>27</t>
         </is>
       </c>
-      <c r="G3" t="inlineStr">
+      <c r="P3" t="inlineStr">
         <is>
           <t>27</t>
         </is>
       </c>
-      <c r="H3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="J3" t="inlineStr">
+      <c r="Q3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="S3" t="inlineStr">
         <is>
           <t>22-April-2026</t>
         </is>
       </c>
-      <c r="K3" t="inlineStr">
+      <c r="T3" t="inlineStr">
         <is>
           <t>esignet</t>
         </is>
       </c>
-      <c r="L3" t="inlineStr">
+      <c r="U3" t="inlineStr">
         <is>
           <t>375</t>
         </is>
       </c>
-      <c r="M3" t="inlineStr">
+      <c r="V3" t="inlineStr">
         <is>
           <t>284</t>
         </is>
       </c>
-      <c r="N3" t="inlineStr">
+      <c r="W3" t="inlineStr">
         <is>
           <t>33</t>
         </is>
       </c>
-      <c r="O3" t="inlineStr">
+      <c r="X3" t="inlineStr">
         <is>
           <t>31</t>
         </is>
       </c>
-      <c r="P3" t="inlineStr">
+      <c r="Y3" t="inlineStr">
         <is>
           <t>27</t>
         </is>
       </c>
-      <c r="Q3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="S3" t="inlineStr">
+      <c r="Z3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB3" t="inlineStr">
         <is>
           <t>21-April-2026</t>
-        </is>
-      </c>
-      <c r="T3" t="inlineStr">
-        <is>
-          <t>esignet</t>
-        </is>
-      </c>
-      <c r="U3" t="inlineStr">
-        <is>
-          <t>375</t>
-        </is>
-      </c>
-      <c r="V3" t="inlineStr">
-        <is>
-          <t>303</t>
-        </is>
-      </c>
-      <c r="W3" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
-      </c>
-      <c r="X3" t="inlineStr">
-        <is>
-          <t>36</t>
-        </is>
-      </c>
-      <c r="Y3" t="inlineStr">
-        <is>
-          <t>27</t>
-        </is>
-      </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>20-April-2026</t>
         </is>
       </c>
       <c r="AC3" t="inlineStr">
@@ -1127,127 +1127,127 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
+          <t>24-April-2026</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>idrepo</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>152</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>101</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>51</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
           <t>23-April-2026</t>
         </is>
       </c>
-      <c r="B4" t="inlineStr">
+      <c r="K4" t="inlineStr">
         <is>
           <t>idrepo</t>
         </is>
       </c>
-      <c r="C4" t="inlineStr">
+      <c r="L4" t="inlineStr">
         <is>
           <t>152</t>
         </is>
       </c>
-      <c r="D4" t="inlineStr">
+      <c r="M4" t="inlineStr">
         <is>
           <t>101</t>
         </is>
       </c>
-      <c r="E4" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F4" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="G4" t="inlineStr">
+      <c r="N4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P4" t="inlineStr">
         <is>
           <t>51</t>
         </is>
       </c>
-      <c r="H4" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="J4" t="inlineStr">
+      <c r="Q4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="S4" t="inlineStr">
         <is>
           <t>22-April-2026</t>
         </is>
       </c>
-      <c r="K4" t="inlineStr">
+      <c r="T4" t="inlineStr">
         <is>
           <t>idrepo</t>
         </is>
       </c>
-      <c r="L4" t="inlineStr">
+      <c r="U4" t="inlineStr">
         <is>
           <t>152</t>
         </is>
       </c>
-      <c r="M4" t="inlineStr">
+      <c r="V4" t="inlineStr">
         <is>
           <t>101</t>
         </is>
       </c>
-      <c r="N4" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="O4" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="P4" t="inlineStr">
+      <c r="W4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="X4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Y4" t="inlineStr">
         <is>
           <t>51</t>
         </is>
       </c>
-      <c r="Q4" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="S4" t="inlineStr">
+      <c r="Z4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB4" t="inlineStr">
         <is>
           <t>21-April-2026</t>
-        </is>
-      </c>
-      <c r="T4" t="inlineStr">
-        <is>
-          <t>idrepo</t>
-        </is>
-      </c>
-      <c r="U4" t="inlineStr">
-        <is>
-          <t>152</t>
-        </is>
-      </c>
-      <c r="V4" t="inlineStr">
-        <is>
-          <t>101</t>
-        </is>
-      </c>
-      <c r="W4" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="X4" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="Y4" t="inlineStr">
-        <is>
-          <t>51</t>
-        </is>
-      </c>
-      <c r="Z4" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB4" t="inlineStr">
-        <is>
-          <t>20-April-2026</t>
         </is>
       </c>
       <c r="AC4" t="inlineStr">
@@ -1289,127 +1289,127 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
+          <t>24-April-2026</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>injiverify</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>53</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>23</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
           <t>23-April-2026</t>
         </is>
       </c>
-      <c r="B5" t="inlineStr">
+      <c r="K5" t="inlineStr">
         <is>
           <t>injiverify</t>
         </is>
       </c>
-      <c r="C5" t="inlineStr">
+      <c r="L5" t="inlineStr">
         <is>
           <t>53</t>
         </is>
       </c>
-      <c r="D5" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="E5" t="inlineStr">
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="N5" t="inlineStr">
         <is>
           <t>23</t>
         </is>
       </c>
-      <c r="F5" t="inlineStr">
+      <c r="O5" t="inlineStr">
         <is>
           <t>30</t>
         </is>
       </c>
-      <c r="G5" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H5" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="J5" t="inlineStr">
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Q5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="S5" t="inlineStr">
         <is>
           <t>22-April-2026</t>
         </is>
       </c>
-      <c r="K5" t="inlineStr">
+      <c r="T5" t="inlineStr">
         <is>
           <t>injiverify</t>
         </is>
       </c>
-      <c r="L5" t="inlineStr">
+      <c r="U5" t="inlineStr">
         <is>
           <t>53</t>
         </is>
       </c>
-      <c r="M5" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="N5" t="inlineStr">
+      <c r="V5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="W5" t="inlineStr">
         <is>
           <t>23</t>
         </is>
       </c>
-      <c r="O5" t="inlineStr">
+      <c r="X5" t="inlineStr">
         <is>
           <t>30</t>
         </is>
       </c>
-      <c r="P5" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="Q5" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="S5" t="inlineStr">
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Z5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB5" t="inlineStr">
         <is>
           <t>21-April-2026</t>
-        </is>
-      </c>
-      <c r="T5" t="inlineStr">
-        <is>
-          <t>injiverify</t>
-        </is>
-      </c>
-      <c r="U5" t="inlineStr">
-        <is>
-          <t>53</t>
-        </is>
-      </c>
-      <c r="V5" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="W5" t="inlineStr">
-        <is>
-          <t>23</t>
-        </is>
-      </c>
-      <c r="X5" t="inlineStr">
-        <is>
-          <t>30</t>
-        </is>
-      </c>
-      <c r="Y5" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="Z5" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB5" t="inlineStr">
-        <is>
-          <t>20-April-2026</t>
         </is>
       </c>
       <c r="AC5" t="inlineStr">
@@ -1451,87 +1451,87 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
+          <t>24-April-2026</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>mimoto</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>79</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>58</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
           <t>23-April-2026</t>
         </is>
       </c>
-      <c r="B6" t="inlineStr">
+      <c r="K6" t="inlineStr">
         <is>
           <t>mimoto</t>
         </is>
       </c>
-      <c r="C6" t="inlineStr">
+      <c r="L6" t="inlineStr">
         <is>
           <t>79</t>
         </is>
       </c>
-      <c r="D6" t="inlineStr">
+      <c r="M6" t="inlineStr">
         <is>
           <t>66</t>
         </is>
       </c>
-      <c r="E6" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F6" t="inlineStr">
+      <c r="N6" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O6" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="G6" t="inlineStr">
+      <c r="P6" t="inlineStr">
         <is>
           <t>10</t>
         </is>
       </c>
-      <c r="H6" t="inlineStr">
+      <c r="Q6" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="J6" t="inlineStr">
+      <c r="S6" t="inlineStr">
         <is>
           <t>22-April-2026</t>
-        </is>
-      </c>
-      <c r="K6" t="inlineStr">
-        <is>
-          <t>mimoto</t>
-        </is>
-      </c>
-      <c r="L6" t="inlineStr">
-        <is>
-          <t>79</t>
-        </is>
-      </c>
-      <c r="M6" t="inlineStr">
-        <is>
-          <t>65</t>
-        </is>
-      </c>
-      <c r="N6" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="O6" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="P6" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="Q6" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="S6" t="inlineStr">
-        <is>
-          <t>21-April-2026</t>
         </is>
       </c>
       <c r="T6" t="inlineStr">
@@ -1597,87 +1597,87 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
+          <t>24-April-2026</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>prereg</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>104</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>70</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
           <t>23-April-2026</t>
         </is>
       </c>
-      <c r="B7" t="inlineStr">
+      <c r="K7" t="inlineStr">
         <is>
           <t>prereg</t>
         </is>
       </c>
-      <c r="C7" t="inlineStr">
+      <c r="L7" t="inlineStr">
         <is>
           <t>104</t>
         </is>
       </c>
-      <c r="D7" t="inlineStr">
+      <c r="M7" t="inlineStr">
         <is>
           <t>3</t>
         </is>
       </c>
-      <c r="E7" t="inlineStr">
+      <c r="N7" t="inlineStr">
         <is>
           <t>70</t>
         </is>
       </c>
-      <c r="F7" t="inlineStr">
+      <c r="O7" t="inlineStr">
         <is>
           <t>30</t>
         </is>
       </c>
-      <c r="G7" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H7" t="inlineStr">
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Q7" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="J7" t="inlineStr">
+      <c r="S7" t="inlineStr">
         <is>
           <t>22-April-2026</t>
-        </is>
-      </c>
-      <c r="K7" t="inlineStr">
-        <is>
-          <t>prereg</t>
-        </is>
-      </c>
-      <c r="L7" t="inlineStr">
-        <is>
-          <t>104</t>
-        </is>
-      </c>
-      <c r="M7" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="N7" t="inlineStr">
-        <is>
-          <t>70</t>
-        </is>
-      </c>
-      <c r="O7" t="inlineStr">
-        <is>
-          <t>30</t>
-        </is>
-      </c>
-      <c r="P7" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="Q7" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="S7" t="inlineStr">
-        <is>
-          <t>21-April-2026</t>
         </is>
       </c>
       <c r="T7" t="inlineStr">
@@ -1743,87 +1743,87 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
+          <t>24-April-2026</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>residentui</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>33</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
           <t>23-April-2026</t>
         </is>
       </c>
-      <c r="B8" t="inlineStr">
+      <c r="K8" t="inlineStr">
         <is>
           <t>residentui</t>
         </is>
       </c>
-      <c r="C8" t="inlineStr">
+      <c r="L8" t="inlineStr">
         <is>
           <t>33</t>
         </is>
       </c>
-      <c r="D8" t="inlineStr">
+      <c r="M8" t="inlineStr">
         <is>
           <t>12</t>
         </is>
       </c>
-      <c r="E8" t="inlineStr">
+      <c r="N8" t="inlineStr">
         <is>
           <t>5</t>
         </is>
       </c>
-      <c r="F8" t="inlineStr">
+      <c r="O8" t="inlineStr">
         <is>
           <t>16</t>
         </is>
       </c>
-      <c r="G8" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H8" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="J8" t="inlineStr">
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Q8" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="S8" t="inlineStr">
         <is>
           <t>22-April-2026</t>
-        </is>
-      </c>
-      <c r="K8" t="inlineStr">
-        <is>
-          <t>residentui</t>
-        </is>
-      </c>
-      <c r="L8" t="inlineStr">
-        <is>
-          <t>33</t>
-        </is>
-      </c>
-      <c r="M8" t="inlineStr">
-        <is>
-          <t>12</t>
-        </is>
-      </c>
-      <c r="N8" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="O8" t="inlineStr">
-        <is>
-          <t>16</t>
-        </is>
-      </c>
-      <c r="P8" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="Q8" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="S8" t="inlineStr">
-        <is>
-          <t>21-April-2026</t>
         </is>
       </c>
       <c r="T8" t="inlineStr">

--- a/minio-report-tracker/xlxs/collab.xlsx
+++ b/minio-report-tracker/xlxs/collab.xlsx
@@ -614,10 +614,10 @@
     <col width="12" customWidth="1" min="11" max="11"/>
     <col width="5" customWidth="1" min="12" max="12"/>
     <col width="5" customWidth="1" min="13" max="13"/>
-    <col width="5" customWidth="1" min="14" max="14"/>
-    <col width="5" customWidth="1" min="15" max="15"/>
-    <col width="5" customWidth="1" min="16" max="16"/>
-    <col width="5" customWidth="1" min="17" max="17"/>
+    <col width="4" customWidth="1" min="14" max="14"/>
+    <col width="4" customWidth="1" min="15" max="15"/>
+    <col width="4" customWidth="1" min="16" max="16"/>
+    <col width="4" customWidth="1" min="17" max="17"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -705,77 +705,77 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
+          <t>28-April-2026</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>auth</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>254</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>140</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>72</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>42</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
           <t>27-April-2026</t>
         </is>
       </c>
-      <c r="B2" t="inlineStr">
+      <c r="K2" t="inlineStr">
         <is>
           <t>auth</t>
         </is>
       </c>
-      <c r="C2" t="inlineStr">
+      <c r="L2" t="inlineStr">
         <is>
           <t>254</t>
         </is>
       </c>
-      <c r="D2" t="inlineStr">
+      <c r="M2" t="inlineStr">
         <is>
           <t>142</t>
         </is>
       </c>
-      <c r="E2" t="inlineStr">
+      <c r="N2" t="inlineStr">
         <is>
           <t>72</t>
         </is>
       </c>
-      <c r="F2" t="inlineStr">
+      <c r="O2" t="inlineStr">
         <is>
           <t>40</t>
         </is>
       </c>
-      <c r="G2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="J2" t="inlineStr">
-        <is>
-          <t>24-April-2026</t>
-        </is>
-      </c>
-      <c r="K2" t="inlineStr">
-        <is>
-          <t>esignet</t>
-        </is>
-      </c>
-      <c r="L2" t="inlineStr">
-        <is>
-          <t>375</t>
-        </is>
-      </c>
-      <c r="M2" t="inlineStr">
-        <is>
-          <t>292</t>
-        </is>
-      </c>
-      <c r="N2" t="inlineStr">
-        <is>
-          <t>30</t>
-        </is>
-      </c>
-      <c r="O2" t="inlineStr">
-        <is>
-          <t>26</t>
-        </is>
-      </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>27</t>
+          <t>0</t>
         </is>
       </c>
       <c r="Q2" t="inlineStr">
@@ -787,77 +787,77 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
+          <t>28-April-2026</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>esignet</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>375</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>274</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>32</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>42</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>27</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
           <t>27-April-2026</t>
         </is>
       </c>
-      <c r="B3" t="inlineStr">
+      <c r="K3" t="inlineStr">
         <is>
           <t>esignet</t>
         </is>
       </c>
-      <c r="C3" t="inlineStr">
+      <c r="L3" t="inlineStr">
         <is>
           <t>375</t>
         </is>
       </c>
-      <c r="D3" t="inlineStr">
+      <c r="M3" t="inlineStr">
         <is>
           <t>254</t>
         </is>
       </c>
-      <c r="E3" t="inlineStr">
+      <c r="N3" t="inlineStr">
         <is>
           <t>50</t>
         </is>
       </c>
-      <c r="F3" t="inlineStr">
+      <c r="O3" t="inlineStr">
         <is>
           <t>44</t>
         </is>
       </c>
-      <c r="G3" t="inlineStr">
+      <c r="P3" t="inlineStr">
         <is>
           <t>27</t>
-        </is>
-      </c>
-      <c r="H3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="J3" t="inlineStr">
-        <is>
-          <t>24-April-2026</t>
-        </is>
-      </c>
-      <c r="K3" t="inlineStr">
-        <is>
-          <t>injiverify</t>
-        </is>
-      </c>
-      <c r="L3" t="inlineStr">
-        <is>
-          <t>53</t>
-        </is>
-      </c>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="N3" t="inlineStr">
-        <is>
-          <t>23</t>
-        </is>
-      </c>
-      <c r="O3" t="inlineStr">
-        <is>
-          <t>30</t>
-        </is>
-      </c>
-      <c r="P3" t="inlineStr">
-        <is>
-          <t>0</t>
         </is>
       </c>
       <c r="Q3" t="inlineStr">
@@ -869,154 +869,154 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
+          <t>28-April-2026</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>idrepo</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>152</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>101</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>51</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
           <t>27-April-2026</t>
         </is>
       </c>
-      <c r="B4" t="inlineStr">
+      <c r="K4" t="inlineStr">
         <is>
           <t>idrepo</t>
         </is>
       </c>
-      <c r="C4" t="inlineStr">
+      <c r="L4" t="inlineStr">
         <is>
           <t>152</t>
         </is>
       </c>
-      <c r="D4" t="inlineStr">
+      <c r="M4" t="inlineStr">
         <is>
           <t>101</t>
         </is>
       </c>
-      <c r="E4" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F4" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="G4" t="inlineStr">
+      <c r="N4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P4" t="inlineStr">
         <is>
           <t>51</t>
         </is>
       </c>
-      <c r="H4" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="J4" t="inlineStr">
-        <is>
-          <t>24-April-2026</t>
-        </is>
-      </c>
-      <c r="K4" t="inlineStr">
-        <is>
-          <t>prereg</t>
-        </is>
-      </c>
-      <c r="L4" t="inlineStr">
-        <is>
-          <t>104</t>
-        </is>
-      </c>
-      <c r="M4" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="N4" t="inlineStr">
-        <is>
-          <t>70</t>
-        </is>
-      </c>
-      <c r="O4" t="inlineStr">
-        <is>
-          <t>30</t>
-        </is>
-      </c>
-      <c r="P4" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
       <c r="Q4" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
+          <t>28-April-2026</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>injiverify</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>53</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>23</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
           <t>27-April-2026</t>
         </is>
       </c>
-      <c r="B5" t="inlineStr">
+      <c r="K5" t="inlineStr">
         <is>
           <t>injiverify</t>
         </is>
       </c>
-      <c r="C5" t="inlineStr">
+      <c r="L5" t="inlineStr">
         <is>
           <t>53</t>
         </is>
       </c>
-      <c r="D5" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="E5" t="inlineStr">
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="N5" t="inlineStr">
         <is>
           <t>23</t>
         </is>
       </c>
-      <c r="F5" t="inlineStr">
+      <c r="O5" t="inlineStr">
         <is>
           <t>30</t>
-        </is>
-      </c>
-      <c r="G5" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H5" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="J5" t="inlineStr">
-        <is>
-          <t>24-April-2026</t>
-        </is>
-      </c>
-      <c r="K5" t="inlineStr">
-        <is>
-          <t>residentui</t>
-        </is>
-      </c>
-      <c r="L5" t="inlineStr">
-        <is>
-          <t>33</t>
-        </is>
-      </c>
-      <c r="M5" t="inlineStr">
-        <is>
-          <t>12</t>
-        </is>
-      </c>
-      <c r="N5" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="O5" t="inlineStr">
-        <is>
-          <t>16</t>
         </is>
       </c>
       <c r="P5" t="inlineStr">
@@ -1033,199 +1033,247 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
+          <t>28-April-2026</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>mimoto</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>79</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>58</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
           <t>27-April-2026</t>
         </is>
       </c>
-      <c r="B6" t="inlineStr">
+      <c r="K6" t="inlineStr">
         <is>
           <t>mimoto</t>
         </is>
       </c>
-      <c r="C6" t="inlineStr">
+      <c r="L6" t="inlineStr">
         <is>
           <t>79</t>
         </is>
       </c>
-      <c r="D6" t="inlineStr">
+      <c r="M6" t="inlineStr">
         <is>
           <t>66</t>
         </is>
       </c>
-      <c r="E6" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F6" t="inlineStr">
+      <c r="N6" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O6" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="G6" t="inlineStr">
+      <c r="P6" t="inlineStr">
         <is>
           <t>10</t>
         </is>
       </c>
-      <c r="H6" t="inlineStr">
+      <c r="Q6" t="inlineStr">
         <is>
           <t>2</t>
         </is>
-      </c>
-      <c r="J6" t="n">
-        <v/>
-      </c>
-      <c r="K6" t="n">
-        <v/>
-      </c>
-      <c r="L6" t="n">
-        <v/>
-      </c>
-      <c r="M6" t="n">
-        <v/>
-      </c>
-      <c r="N6" t="n">
-        <v/>
-      </c>
-      <c r="O6" t="n">
-        <v/>
-      </c>
-      <c r="P6" t="n">
-        <v/>
-      </c>
-      <c r="Q6" t="n">
-        <v/>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
+          <t>28-April-2026</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>prereg</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>104</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>70</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
           <t>27-April-2026</t>
         </is>
       </c>
-      <c r="B7" t="inlineStr">
+      <c r="K7" t="inlineStr">
         <is>
           <t>prereg</t>
         </is>
       </c>
-      <c r="C7" t="inlineStr">
+      <c r="L7" t="inlineStr">
         <is>
           <t>104</t>
         </is>
       </c>
-      <c r="D7" t="inlineStr">
+      <c r="M7" t="inlineStr">
         <is>
           <t>3</t>
         </is>
       </c>
-      <c r="E7" t="inlineStr">
+      <c r="N7" t="inlineStr">
         <is>
           <t>70</t>
         </is>
       </c>
-      <c r="F7" t="inlineStr">
+      <c r="O7" t="inlineStr">
         <is>
           <t>30</t>
         </is>
       </c>
-      <c r="G7" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H7" t="inlineStr">
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Q7" t="inlineStr">
         <is>
           <t>1</t>
         </is>
-      </c>
-      <c r="J7" t="n">
-        <v/>
-      </c>
-      <c r="K7" t="n">
-        <v/>
-      </c>
-      <c r="L7" t="n">
-        <v/>
-      </c>
-      <c r="M7" t="n">
-        <v/>
-      </c>
-      <c r="N7" t="n">
-        <v/>
-      </c>
-      <c r="O7" t="n">
-        <v/>
-      </c>
-      <c r="P7" t="n">
-        <v/>
-      </c>
-      <c r="Q7" t="n">
-        <v/>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
+          <t>28-April-2026</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>residentui</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>33</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
           <t>27-April-2026</t>
         </is>
       </c>
-      <c r="B8" t="inlineStr">
+      <c r="K8" t="inlineStr">
         <is>
           <t>residentui</t>
         </is>
       </c>
-      <c r="C8" t="inlineStr">
+      <c r="L8" t="inlineStr">
         <is>
           <t>33</t>
         </is>
       </c>
-      <c r="D8" t="inlineStr">
+      <c r="M8" t="inlineStr">
         <is>
           <t>12</t>
         </is>
       </c>
-      <c r="E8" t="inlineStr">
+      <c r="N8" t="inlineStr">
         <is>
           <t>5</t>
         </is>
       </c>
-      <c r="F8" t="inlineStr">
+      <c r="O8" t="inlineStr">
         <is>
           <t>16</t>
         </is>
       </c>
-      <c r="G8" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H8" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="J8" t="n">
-        <v/>
-      </c>
-      <c r="K8" t="n">
-        <v/>
-      </c>
-      <c r="L8" t="n">
-        <v/>
-      </c>
-      <c r="M8" t="n">
-        <v/>
-      </c>
-      <c r="N8" t="n">
-        <v/>
-      </c>
-      <c r="O8" t="n">
-        <v/>
-      </c>
-      <c r="P8" t="n">
-        <v/>
-      </c>
-      <c r="Q8" t="n">
-        <v/>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Q8" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
     </row>
   </sheetData>

--- a/minio-report-tracker/xlxs/collab.xlsx
+++ b/minio-report-tracker/xlxs/collab.xlsx
@@ -598,7 +598,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q8"/>
+  <dimension ref="A1:Z8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="15" customWidth="1" min="1" max="1"/>
@@ -618,6 +618,15 @@
     <col width="4" customWidth="1" min="15" max="15"/>
     <col width="4" customWidth="1" min="16" max="16"/>
     <col width="4" customWidth="1" min="17" max="17"/>
+    <col width="2" customWidth="1" min="18" max="18"/>
+    <col width="15" customWidth="1" min="19" max="19"/>
+    <col width="12" customWidth="1" min="20" max="20"/>
+    <col width="5" customWidth="1" min="21" max="21"/>
+    <col width="5" customWidth="1" min="22" max="22"/>
+    <col width="4" customWidth="1" min="23" max="23"/>
+    <col width="4" customWidth="1" min="24" max="24"/>
+    <col width="4" customWidth="1" min="25" max="25"/>
+    <col width="4" customWidth="1" min="26" max="26"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -701,84 +710,164 @@
           <t>KI</t>
         </is>
       </c>
+      <c r="S1" s="1" t="inlineStr">
+        <is>
+          <t>Date</t>
+        </is>
+      </c>
+      <c r="T1" s="1" t="inlineStr">
+        <is>
+          <t>Module</t>
+        </is>
+      </c>
+      <c r="U1" s="1" t="inlineStr">
+        <is>
+          <t>T</t>
+        </is>
+      </c>
+      <c r="V1" s="1" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
+      <c r="W1" s="1" t="inlineStr">
+        <is>
+          <t>S</t>
+        </is>
+      </c>
+      <c r="X1" s="1" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
+      <c r="Y1" s="1" t="inlineStr">
+        <is>
+          <t>I</t>
+        </is>
+      </c>
+      <c r="Z1" s="1" t="inlineStr">
+        <is>
+          <t>KI</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
+          <t>29-April-2026</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>auth</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>254</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>186</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>62</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
           <t>28-April-2026</t>
         </is>
       </c>
-      <c r="B2" t="inlineStr">
+      <c r="K2" t="inlineStr">
         <is>
           <t>auth</t>
         </is>
       </c>
-      <c r="C2" t="inlineStr">
+      <c r="L2" t="inlineStr">
         <is>
           <t>254</t>
         </is>
       </c>
-      <c r="D2" t="inlineStr">
+      <c r="M2" t="inlineStr">
         <is>
           <t>140</t>
         </is>
       </c>
-      <c r="E2" t="inlineStr">
+      <c r="N2" t="inlineStr">
         <is>
           <t>72</t>
         </is>
       </c>
-      <c r="F2" t="inlineStr">
+      <c r="O2" t="inlineStr">
         <is>
           <t>42</t>
         </is>
       </c>
-      <c r="G2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="J2" t="inlineStr">
+      <c r="P2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Q2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="S2" t="inlineStr">
         <is>
           <t>27-April-2026</t>
         </is>
       </c>
-      <c r="K2" t="inlineStr">
+      <c r="T2" t="inlineStr">
         <is>
           <t>auth</t>
         </is>
       </c>
-      <c r="L2" t="inlineStr">
+      <c r="U2" t="inlineStr">
         <is>
           <t>254</t>
         </is>
       </c>
-      <c r="M2" t="inlineStr">
+      <c r="V2" t="inlineStr">
         <is>
           <t>142</t>
         </is>
       </c>
-      <c r="N2" t="inlineStr">
+      <c r="W2" t="inlineStr">
         <is>
           <t>72</t>
         </is>
       </c>
-      <c r="O2" t="inlineStr">
+      <c r="X2" t="inlineStr">
         <is>
           <t>40</t>
         </is>
       </c>
-      <c r="P2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="Q2" t="inlineStr">
+      <c r="Y2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Z2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
@@ -787,80 +876,120 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
+          <t>29-April-2026</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>esignet</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>375</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>290</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>42</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>27</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
           <t>28-April-2026</t>
         </is>
       </c>
-      <c r="B3" t="inlineStr">
+      <c r="K3" t="inlineStr">
         <is>
           <t>esignet</t>
         </is>
       </c>
-      <c r="C3" t="inlineStr">
+      <c r="L3" t="inlineStr">
         <is>
           <t>375</t>
         </is>
       </c>
-      <c r="D3" t="inlineStr">
+      <c r="M3" t="inlineStr">
         <is>
           <t>274</t>
         </is>
       </c>
-      <c r="E3" t="inlineStr">
+      <c r="N3" t="inlineStr">
         <is>
           <t>32</t>
         </is>
       </c>
-      <c r="F3" t="inlineStr">
+      <c r="O3" t="inlineStr">
         <is>
           <t>42</t>
         </is>
       </c>
-      <c r="G3" t="inlineStr">
+      <c r="P3" t="inlineStr">
         <is>
           <t>27</t>
         </is>
       </c>
-      <c r="H3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="J3" t="inlineStr">
+      <c r="Q3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="S3" t="inlineStr">
         <is>
           <t>27-April-2026</t>
         </is>
       </c>
-      <c r="K3" t="inlineStr">
+      <c r="T3" t="inlineStr">
         <is>
           <t>esignet</t>
         </is>
       </c>
-      <c r="L3" t="inlineStr">
+      <c r="U3" t="inlineStr">
         <is>
           <t>375</t>
         </is>
       </c>
-      <c r="M3" t="inlineStr">
+      <c r="V3" t="inlineStr">
         <is>
           <t>254</t>
         </is>
       </c>
-      <c r="N3" t="inlineStr">
+      <c r="W3" t="inlineStr">
         <is>
           <t>50</t>
         </is>
       </c>
-      <c r="O3" t="inlineStr">
+      <c r="X3" t="inlineStr">
         <is>
           <t>44</t>
         </is>
       </c>
-      <c r="P3" t="inlineStr">
+      <c r="Y3" t="inlineStr">
         <is>
           <t>27</t>
         </is>
       </c>
-      <c r="Q3" t="inlineStr">
+      <c r="Z3" t="inlineStr">
         <is>
           <t>0</t>
         </is>
@@ -869,80 +998,120 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
+          <t>29-April-2026</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>idrepo</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>152</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>101</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>51</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
           <t>28-April-2026</t>
         </is>
       </c>
-      <c r="B4" t="inlineStr">
+      <c r="K4" t="inlineStr">
         <is>
           <t>idrepo</t>
         </is>
       </c>
-      <c r="C4" t="inlineStr">
+      <c r="L4" t="inlineStr">
         <is>
           <t>152</t>
         </is>
       </c>
-      <c r="D4" t="inlineStr">
+      <c r="M4" t="inlineStr">
         <is>
           <t>101</t>
         </is>
       </c>
-      <c r="E4" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F4" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="G4" t="inlineStr">
+      <c r="N4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P4" t="inlineStr">
         <is>
           <t>51</t>
         </is>
       </c>
-      <c r="H4" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="J4" t="inlineStr">
+      <c r="Q4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="S4" t="inlineStr">
         <is>
           <t>27-April-2026</t>
         </is>
       </c>
-      <c r="K4" t="inlineStr">
+      <c r="T4" t="inlineStr">
         <is>
           <t>idrepo</t>
         </is>
       </c>
-      <c r="L4" t="inlineStr">
+      <c r="U4" t="inlineStr">
         <is>
           <t>152</t>
         </is>
       </c>
-      <c r="M4" t="inlineStr">
+      <c r="V4" t="inlineStr">
         <is>
           <t>101</t>
         </is>
       </c>
-      <c r="N4" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="O4" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="P4" t="inlineStr">
+      <c r="W4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="X4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Y4" t="inlineStr">
         <is>
           <t>51</t>
         </is>
       </c>
-      <c r="Q4" t="inlineStr">
+      <c r="Z4" t="inlineStr">
         <is>
           <t>0</t>
         </is>
@@ -951,80 +1120,120 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
+          <t>29-April-2026</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>injiverify</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>53</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>23</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
           <t>28-April-2026</t>
         </is>
       </c>
-      <c r="B5" t="inlineStr">
+      <c r="K5" t="inlineStr">
         <is>
           <t>injiverify</t>
         </is>
       </c>
-      <c r="C5" t="inlineStr">
+      <c r="L5" t="inlineStr">
         <is>
           <t>53</t>
         </is>
       </c>
-      <c r="D5" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="E5" t="inlineStr">
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="N5" t="inlineStr">
         <is>
           <t>23</t>
         </is>
       </c>
-      <c r="F5" t="inlineStr">
+      <c r="O5" t="inlineStr">
         <is>
           <t>30</t>
         </is>
       </c>
-      <c r="G5" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H5" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="J5" t="inlineStr">
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Q5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="S5" t="inlineStr">
         <is>
           <t>27-April-2026</t>
         </is>
       </c>
-      <c r="K5" t="inlineStr">
+      <c r="T5" t="inlineStr">
         <is>
           <t>injiverify</t>
         </is>
       </c>
-      <c r="L5" t="inlineStr">
+      <c r="U5" t="inlineStr">
         <is>
           <t>53</t>
         </is>
       </c>
-      <c r="M5" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="N5" t="inlineStr">
+      <c r="V5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="W5" t="inlineStr">
         <is>
           <t>23</t>
         </is>
       </c>
-      <c r="O5" t="inlineStr">
+      <c r="X5" t="inlineStr">
         <is>
           <t>30</t>
         </is>
       </c>
-      <c r="P5" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="Q5" t="inlineStr">
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Z5" t="inlineStr">
         <is>
           <t>0</t>
         </is>
@@ -1033,80 +1242,120 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
+          <t>29-April-2026</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>mimoto</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>79</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>58</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
           <t>28-April-2026</t>
         </is>
       </c>
-      <c r="B6" t="inlineStr">
+      <c r="K6" t="inlineStr">
         <is>
           <t>mimoto</t>
         </is>
       </c>
-      <c r="C6" t="inlineStr">
+      <c r="L6" t="inlineStr">
         <is>
           <t>79</t>
         </is>
       </c>
-      <c r="D6" t="inlineStr">
+      <c r="M6" t="inlineStr">
         <is>
           <t>58</t>
         </is>
       </c>
-      <c r="E6" t="inlineStr">
+      <c r="N6" t="inlineStr">
         <is>
           <t>4</t>
         </is>
       </c>
-      <c r="F6" t="inlineStr">
+      <c r="O6" t="inlineStr">
         <is>
           <t>5</t>
         </is>
       </c>
-      <c r="G6" t="inlineStr">
+      <c r="P6" t="inlineStr">
         <is>
           <t>10</t>
         </is>
       </c>
-      <c r="H6" t="inlineStr">
+      <c r="Q6" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="J6" t="inlineStr">
+      <c r="S6" t="inlineStr">
         <is>
           <t>27-April-2026</t>
         </is>
       </c>
-      <c r="K6" t="inlineStr">
+      <c r="T6" t="inlineStr">
         <is>
           <t>mimoto</t>
         </is>
       </c>
-      <c r="L6" t="inlineStr">
+      <c r="U6" t="inlineStr">
         <is>
           <t>79</t>
         </is>
       </c>
-      <c r="M6" t="inlineStr">
+      <c r="V6" t="inlineStr">
         <is>
           <t>66</t>
         </is>
       </c>
-      <c r="N6" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="O6" t="inlineStr">
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="X6" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="P6" t="inlineStr">
+      <c r="Y6" t="inlineStr">
         <is>
           <t>10</t>
         </is>
       </c>
-      <c r="Q6" t="inlineStr">
+      <c r="Z6" t="inlineStr">
         <is>
           <t>2</t>
         </is>
@@ -1115,80 +1364,120 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
+          <t>29-April-2026</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>prereg</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>104</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>70</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
           <t>28-April-2026</t>
         </is>
       </c>
-      <c r="B7" t="inlineStr">
+      <c r="K7" t="inlineStr">
         <is>
           <t>prereg</t>
         </is>
       </c>
-      <c r="C7" t="inlineStr">
+      <c r="L7" t="inlineStr">
         <is>
           <t>104</t>
         </is>
       </c>
-      <c r="D7" t="inlineStr">
+      <c r="M7" t="inlineStr">
         <is>
           <t>3</t>
         </is>
       </c>
-      <c r="E7" t="inlineStr">
+      <c r="N7" t="inlineStr">
         <is>
           <t>70</t>
         </is>
       </c>
-      <c r="F7" t="inlineStr">
+      <c r="O7" t="inlineStr">
         <is>
           <t>30</t>
         </is>
       </c>
-      <c r="G7" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H7" t="inlineStr">
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Q7" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="J7" t="inlineStr">
+      <c r="S7" t="inlineStr">
         <is>
           <t>27-April-2026</t>
         </is>
       </c>
-      <c r="K7" t="inlineStr">
+      <c r="T7" t="inlineStr">
         <is>
           <t>prereg</t>
         </is>
       </c>
-      <c r="L7" t="inlineStr">
+      <c r="U7" t="inlineStr">
         <is>
           <t>104</t>
         </is>
       </c>
-      <c r="M7" t="inlineStr">
+      <c r="V7" t="inlineStr">
         <is>
           <t>3</t>
         </is>
       </c>
-      <c r="N7" t="inlineStr">
+      <c r="W7" t="inlineStr">
         <is>
           <t>70</t>
         </is>
       </c>
-      <c r="O7" t="inlineStr">
+      <c r="X7" t="inlineStr">
         <is>
           <t>30</t>
         </is>
       </c>
-      <c r="P7" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="Q7" t="inlineStr">
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Z7" t="inlineStr">
         <is>
           <t>1</t>
         </is>
@@ -1197,80 +1486,120 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
+          <t>29-April-2026</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>residentui</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>33</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
           <t>28-April-2026</t>
         </is>
       </c>
-      <c r="B8" t="inlineStr">
+      <c r="K8" t="inlineStr">
         <is>
           <t>residentui</t>
         </is>
       </c>
-      <c r="C8" t="inlineStr">
+      <c r="L8" t="inlineStr">
         <is>
           <t>33</t>
         </is>
       </c>
-      <c r="D8" t="inlineStr">
+      <c r="M8" t="inlineStr">
         <is>
           <t>12</t>
         </is>
       </c>
-      <c r="E8" t="inlineStr">
+      <c r="N8" t="inlineStr">
         <is>
           <t>5</t>
         </is>
       </c>
-      <c r="F8" t="inlineStr">
+      <c r="O8" t="inlineStr">
         <is>
           <t>16</t>
         </is>
       </c>
-      <c r="G8" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H8" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="J8" t="inlineStr">
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Q8" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="S8" t="inlineStr">
         <is>
           <t>27-April-2026</t>
         </is>
       </c>
-      <c r="K8" t="inlineStr">
+      <c r="T8" t="inlineStr">
         <is>
           <t>residentui</t>
         </is>
       </c>
-      <c r="L8" t="inlineStr">
+      <c r="U8" t="inlineStr">
         <is>
           <t>33</t>
         </is>
       </c>
-      <c r="M8" t="inlineStr">
+      <c r="V8" t="inlineStr">
         <is>
           <t>12</t>
         </is>
       </c>
-      <c r="N8" t="inlineStr">
+      <c r="W8" t="inlineStr">
         <is>
           <t>5</t>
         </is>
       </c>
-      <c r="O8" t="inlineStr">
+      <c r="X8" t="inlineStr">
         <is>
           <t>16</t>
         </is>
       </c>
-      <c r="P8" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="Q8" t="inlineStr">
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Z8" t="inlineStr">
         <is>
           <t>0</t>
         </is>

--- a/minio-report-tracker/xlxs/collab.xlsx
+++ b/minio-report-tracker/xlxs/collab.xlsx
@@ -598,7 +598,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Z8"/>
+  <dimension ref="A1:AI8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="15" customWidth="1" min="1" max="1"/>
@@ -627,6 +627,15 @@
     <col width="4" customWidth="1" min="24" max="24"/>
     <col width="4" customWidth="1" min="25" max="25"/>
     <col width="4" customWidth="1" min="26" max="26"/>
+    <col width="2" customWidth="1" min="27" max="27"/>
+    <col width="15" customWidth="1" min="28" max="28"/>
+    <col width="12" customWidth="1" min="29" max="29"/>
+    <col width="5" customWidth="1" min="30" max="30"/>
+    <col width="5" customWidth="1" min="31" max="31"/>
+    <col width="5" customWidth="1" min="32" max="32"/>
+    <col width="5" customWidth="1" min="33" max="33"/>
+    <col width="5" customWidth="1" min="34" max="34"/>
+    <col width="5" customWidth="1" min="35" max="35"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -750,124 +759,204 @@
           <t>KI</t>
         </is>
       </c>
+      <c r="AB1" s="1" t="inlineStr">
+        <is>
+          <t>Date</t>
+        </is>
+      </c>
+      <c r="AC1" s="1" t="inlineStr">
+        <is>
+          <t>Module</t>
+        </is>
+      </c>
+      <c r="AD1" s="1" t="inlineStr">
+        <is>
+          <t>T</t>
+        </is>
+      </c>
+      <c r="AE1" s="1" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
+      <c r="AF1" s="1" t="inlineStr">
+        <is>
+          <t>S</t>
+        </is>
+      </c>
+      <c r="AG1" s="1" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
+      <c r="AH1" s="1" t="inlineStr">
+        <is>
+          <t>I</t>
+        </is>
+      </c>
+      <c r="AI1" s="1" t="inlineStr">
+        <is>
+          <t>KI</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
+          <t>30-April-2026</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>auth</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>254</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>184</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>64</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
           <t>29-April-2026</t>
         </is>
       </c>
-      <c r="B2" t="inlineStr">
+      <c r="K2" t="inlineStr">
         <is>
           <t>auth</t>
         </is>
       </c>
-      <c r="C2" t="inlineStr">
+      <c r="L2" t="inlineStr">
         <is>
           <t>254</t>
         </is>
       </c>
-      <c r="D2" t="inlineStr">
+      <c r="M2" t="inlineStr">
         <is>
           <t>186</t>
         </is>
       </c>
-      <c r="E2" t="inlineStr">
+      <c r="N2" t="inlineStr">
         <is>
           <t>6</t>
         </is>
       </c>
-      <c r="F2" t="inlineStr">
+      <c r="O2" t="inlineStr">
         <is>
           <t>62</t>
         </is>
       </c>
-      <c r="G2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="J2" t="inlineStr">
+      <c r="P2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Q2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="S2" t="inlineStr">
         <is>
           <t>28-April-2026</t>
         </is>
       </c>
-      <c r="K2" t="inlineStr">
+      <c r="T2" t="inlineStr">
         <is>
           <t>auth</t>
         </is>
       </c>
-      <c r="L2" t="inlineStr">
+      <c r="U2" t="inlineStr">
         <is>
           <t>254</t>
         </is>
       </c>
-      <c r="M2" t="inlineStr">
+      <c r="V2" t="inlineStr">
         <is>
           <t>140</t>
         </is>
       </c>
-      <c r="N2" t="inlineStr">
+      <c r="W2" t="inlineStr">
         <is>
           <t>72</t>
         </is>
       </c>
-      <c r="O2" t="inlineStr">
+      <c r="X2" t="inlineStr">
         <is>
           <t>42</t>
         </is>
       </c>
-      <c r="P2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="Q2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="S2" t="inlineStr">
+      <c r="Y2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Z2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB2" t="inlineStr">
         <is>
           <t>27-April-2026</t>
         </is>
       </c>
-      <c r="T2" t="inlineStr">
-        <is>
-          <t>auth</t>
-        </is>
-      </c>
-      <c r="U2" t="inlineStr">
+      <c r="AC2" t="inlineStr">
+        <is>
+          <t>esignet</t>
+        </is>
+      </c>
+      <c r="AD2" t="inlineStr">
+        <is>
+          <t>375</t>
+        </is>
+      </c>
+      <c r="AE2" t="inlineStr">
         <is>
           <t>254</t>
         </is>
       </c>
-      <c r="V2" t="inlineStr">
-        <is>
-          <t>142</t>
-        </is>
-      </c>
-      <c r="W2" t="inlineStr">
-        <is>
-          <t>72</t>
-        </is>
-      </c>
-      <c r="X2" t="inlineStr">
-        <is>
-          <t>40</t>
-        </is>
-      </c>
-      <c r="Y2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="Z2" t="inlineStr">
+      <c r="AF2" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
+      <c r="AG2" t="inlineStr">
+        <is>
+          <t>44</t>
+        </is>
+      </c>
+      <c r="AH2" t="inlineStr">
+        <is>
+          <t>27</t>
+        </is>
+      </c>
+      <c r="AI2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
@@ -876,120 +965,160 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
+          <t>30-April-2026</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>esignet</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>375</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>234</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>49</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>65</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>27</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
           <t>29-April-2026</t>
         </is>
       </c>
-      <c r="B3" t="inlineStr">
+      <c r="K3" t="inlineStr">
         <is>
           <t>esignet</t>
         </is>
       </c>
-      <c r="C3" t="inlineStr">
+      <c r="L3" t="inlineStr">
         <is>
           <t>375</t>
         </is>
       </c>
-      <c r="D3" t="inlineStr">
+      <c r="M3" t="inlineStr">
         <is>
           <t>290</t>
         </is>
       </c>
-      <c r="E3" t="inlineStr">
+      <c r="N3" t="inlineStr">
         <is>
           <t>16</t>
         </is>
       </c>
-      <c r="F3" t="inlineStr">
+      <c r="O3" t="inlineStr">
         <is>
           <t>42</t>
         </is>
       </c>
-      <c r="G3" t="inlineStr">
+      <c r="P3" t="inlineStr">
         <is>
           <t>27</t>
         </is>
       </c>
-      <c r="H3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="J3" t="inlineStr">
+      <c r="Q3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="S3" t="inlineStr">
         <is>
           <t>28-April-2026</t>
         </is>
       </c>
-      <c r="K3" t="inlineStr">
+      <c r="T3" t="inlineStr">
         <is>
           <t>esignet</t>
         </is>
       </c>
-      <c r="L3" t="inlineStr">
+      <c r="U3" t="inlineStr">
         <is>
           <t>375</t>
         </is>
       </c>
-      <c r="M3" t="inlineStr">
+      <c r="V3" t="inlineStr">
         <is>
           <t>274</t>
         </is>
       </c>
-      <c r="N3" t="inlineStr">
+      <c r="W3" t="inlineStr">
         <is>
           <t>32</t>
         </is>
       </c>
-      <c r="O3" t="inlineStr">
+      <c r="X3" t="inlineStr">
         <is>
           <t>42</t>
         </is>
       </c>
-      <c r="P3" t="inlineStr">
+      <c r="Y3" t="inlineStr">
         <is>
           <t>27</t>
         </is>
       </c>
-      <c r="Q3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="S3" t="inlineStr">
+      <c r="Z3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB3" t="inlineStr">
         <is>
           <t>27-April-2026</t>
         </is>
       </c>
-      <c r="T3" t="inlineStr">
-        <is>
-          <t>esignet</t>
-        </is>
-      </c>
-      <c r="U3" t="inlineStr">
-        <is>
-          <t>375</t>
-        </is>
-      </c>
-      <c r="V3" t="inlineStr">
-        <is>
-          <t>254</t>
-        </is>
-      </c>
-      <c r="W3" t="inlineStr">
-        <is>
-          <t>50</t>
-        </is>
-      </c>
-      <c r="X3" t="inlineStr">
-        <is>
-          <t>44</t>
-        </is>
-      </c>
-      <c r="Y3" t="inlineStr">
-        <is>
-          <t>27</t>
-        </is>
-      </c>
-      <c r="Z3" t="inlineStr">
+      <c r="AC3" t="inlineStr">
+        <is>
+          <t>injiverify</t>
+        </is>
+      </c>
+      <c r="AD3" t="inlineStr">
+        <is>
+          <t>53</t>
+        </is>
+      </c>
+      <c r="AE3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AF3" t="inlineStr">
+        <is>
+          <t>23</t>
+        </is>
+      </c>
+      <c r="AG3" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="AH3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AI3" t="inlineStr">
         <is>
           <t>0</t>
         </is>
@@ -998,242 +1127,322 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
+          <t>30-April-2026</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>idrepo</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>152</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>101</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>51</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
           <t>29-April-2026</t>
         </is>
       </c>
-      <c r="B4" t="inlineStr">
+      <c r="K4" t="inlineStr">
         <is>
           <t>idrepo</t>
         </is>
       </c>
-      <c r="C4" t="inlineStr">
+      <c r="L4" t="inlineStr">
         <is>
           <t>152</t>
         </is>
       </c>
-      <c r="D4" t="inlineStr">
+      <c r="M4" t="inlineStr">
         <is>
           <t>101</t>
         </is>
       </c>
-      <c r="E4" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F4" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="G4" t="inlineStr">
+      <c r="N4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P4" t="inlineStr">
         <is>
           <t>51</t>
         </is>
       </c>
-      <c r="H4" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="J4" t="inlineStr">
+      <c r="Q4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="S4" t="inlineStr">
         <is>
           <t>28-April-2026</t>
         </is>
       </c>
-      <c r="K4" t="inlineStr">
+      <c r="T4" t="inlineStr">
         <is>
           <t>idrepo</t>
         </is>
       </c>
-      <c r="L4" t="inlineStr">
+      <c r="U4" t="inlineStr">
         <is>
           <t>152</t>
         </is>
       </c>
-      <c r="M4" t="inlineStr">
+      <c r="V4" t="inlineStr">
         <is>
           <t>101</t>
         </is>
       </c>
-      <c r="N4" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="O4" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="P4" t="inlineStr">
+      <c r="W4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="X4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Y4" t="inlineStr">
         <is>
           <t>51</t>
         </is>
       </c>
-      <c r="Q4" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="S4" t="inlineStr">
+      <c r="Z4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB4" t="inlineStr">
         <is>
           <t>27-April-2026</t>
         </is>
       </c>
-      <c r="T4" t="inlineStr">
-        <is>
-          <t>idrepo</t>
-        </is>
-      </c>
-      <c r="U4" t="inlineStr">
-        <is>
-          <t>152</t>
-        </is>
-      </c>
-      <c r="V4" t="inlineStr">
-        <is>
-          <t>101</t>
-        </is>
-      </c>
-      <c r="W4" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="X4" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="Y4" t="inlineStr">
-        <is>
-          <t>51</t>
-        </is>
-      </c>
-      <c r="Z4" t="inlineStr">
-        <is>
-          <t>0</t>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t>prereg</t>
+        </is>
+      </c>
+      <c r="AD4" t="inlineStr">
+        <is>
+          <t>104</t>
+        </is>
+      </c>
+      <c r="AE4" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AF4" t="inlineStr">
+        <is>
+          <t>70</t>
+        </is>
+      </c>
+      <c r="AG4" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="AH4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AI4" t="inlineStr">
+        <is>
+          <t>1</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
+          <t>30-April-2026</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>injiverify</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>53</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>23</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
           <t>29-April-2026</t>
         </is>
       </c>
-      <c r="B5" t="inlineStr">
+      <c r="K5" t="inlineStr">
         <is>
           <t>injiverify</t>
         </is>
       </c>
-      <c r="C5" t="inlineStr">
+      <c r="L5" t="inlineStr">
         <is>
           <t>53</t>
         </is>
       </c>
-      <c r="D5" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="E5" t="inlineStr">
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="N5" t="inlineStr">
         <is>
           <t>23</t>
         </is>
       </c>
-      <c r="F5" t="inlineStr">
+      <c r="O5" t="inlineStr">
         <is>
           <t>30</t>
         </is>
       </c>
-      <c r="G5" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H5" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="J5" t="inlineStr">
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Q5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="S5" t="inlineStr">
         <is>
           <t>28-April-2026</t>
         </is>
       </c>
-      <c r="K5" t="inlineStr">
+      <c r="T5" t="inlineStr">
         <is>
           <t>injiverify</t>
         </is>
       </c>
-      <c r="L5" t="inlineStr">
+      <c r="U5" t="inlineStr">
         <is>
           <t>53</t>
         </is>
       </c>
-      <c r="M5" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="N5" t="inlineStr">
+      <c r="V5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="W5" t="inlineStr">
         <is>
           <t>23</t>
         </is>
       </c>
-      <c r="O5" t="inlineStr">
+      <c r="X5" t="inlineStr">
         <is>
           <t>30</t>
         </is>
       </c>
-      <c r="P5" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="Q5" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="S5" t="inlineStr">
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Z5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB5" t="inlineStr">
         <is>
           <t>27-April-2026</t>
         </is>
       </c>
-      <c r="T5" t="inlineStr">
-        <is>
-          <t>injiverify</t>
-        </is>
-      </c>
-      <c r="U5" t="inlineStr">
-        <is>
-          <t>53</t>
-        </is>
-      </c>
-      <c r="V5" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="W5" t="inlineStr">
-        <is>
-          <t>23</t>
-        </is>
-      </c>
-      <c r="X5" t="inlineStr">
-        <is>
-          <t>30</t>
-        </is>
-      </c>
-      <c r="Y5" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="Z5" t="inlineStr">
+      <c r="AC5" t="inlineStr">
+        <is>
+          <t>residentui</t>
+        </is>
+      </c>
+      <c r="AD5" t="inlineStr">
+        <is>
+          <t>33</t>
+        </is>
+      </c>
+      <c r="AE5" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="AF5" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AG5" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="AH5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AI5" t="inlineStr">
         <is>
           <t>0</t>
         </is>
@@ -1242,358 +1451,406 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
+          <t>30-April-2026</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>mimoto</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>79</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>66</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
           <t>29-April-2026</t>
         </is>
       </c>
-      <c r="B6" t="inlineStr">
+      <c r="K6" t="inlineStr">
         <is>
           <t>mimoto</t>
         </is>
       </c>
-      <c r="C6" t="inlineStr">
+      <c r="L6" t="inlineStr">
         <is>
           <t>79</t>
         </is>
       </c>
-      <c r="D6" t="inlineStr">
+      <c r="M6" t="inlineStr">
         <is>
           <t>58</t>
         </is>
       </c>
-      <c r="E6" t="inlineStr">
+      <c r="N6" t="inlineStr">
         <is>
           <t>4</t>
         </is>
       </c>
-      <c r="F6" t="inlineStr">
+      <c r="O6" t="inlineStr">
         <is>
           <t>5</t>
         </is>
       </c>
-      <c r="G6" t="inlineStr">
+      <c r="P6" t="inlineStr">
         <is>
           <t>10</t>
         </is>
       </c>
-      <c r="H6" t="inlineStr">
+      <c r="Q6" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="J6" t="inlineStr">
+      <c r="S6" t="inlineStr">
         <is>
           <t>28-April-2026</t>
         </is>
       </c>
-      <c r="K6" t="inlineStr">
+      <c r="T6" t="inlineStr">
         <is>
           <t>mimoto</t>
         </is>
       </c>
-      <c r="L6" t="inlineStr">
+      <c r="U6" t="inlineStr">
         <is>
           <t>79</t>
         </is>
       </c>
-      <c r="M6" t="inlineStr">
+      <c r="V6" t="inlineStr">
         <is>
           <t>58</t>
         </is>
       </c>
-      <c r="N6" t="inlineStr">
+      <c r="W6" t="inlineStr">
         <is>
           <t>4</t>
         </is>
       </c>
-      <c r="O6" t="inlineStr">
+      <c r="X6" t="inlineStr">
         <is>
           <t>5</t>
         </is>
       </c>
-      <c r="P6" t="inlineStr">
+      <c r="Y6" t="inlineStr">
         <is>
           <t>10</t>
         </is>
       </c>
-      <c r="Q6" t="inlineStr">
+      <c r="Z6" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="S6" t="inlineStr">
-        <is>
-          <t>27-April-2026</t>
-        </is>
-      </c>
-      <c r="T6" t="inlineStr">
-        <is>
-          <t>mimoto</t>
-        </is>
-      </c>
-      <c r="U6" t="inlineStr">
-        <is>
-          <t>79</t>
-        </is>
-      </c>
-      <c r="V6" t="inlineStr">
-        <is>
-          <t>66</t>
-        </is>
-      </c>
-      <c r="W6" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="X6" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="Y6" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="Z6" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
+      <c r="AB6" t="n">
+        <v/>
+      </c>
+      <c r="AC6" t="n">
+        <v/>
+      </c>
+      <c r="AD6" t="n">
+        <v/>
+      </c>
+      <c r="AE6" t="n">
+        <v/>
+      </c>
+      <c r="AF6" t="n">
+        <v/>
+      </c>
+      <c r="AG6" t="n">
+        <v/>
+      </c>
+      <c r="AH6" t="n">
+        <v/>
+      </c>
+      <c r="AI6" t="n">
+        <v/>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
+          <t>30-April-2026</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>prereg</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>104</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>70</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
           <t>29-April-2026</t>
         </is>
       </c>
-      <c r="B7" t="inlineStr">
+      <c r="K7" t="inlineStr">
         <is>
           <t>prereg</t>
         </is>
       </c>
-      <c r="C7" t="inlineStr">
+      <c r="L7" t="inlineStr">
         <is>
           <t>104</t>
         </is>
       </c>
-      <c r="D7" t="inlineStr">
+      <c r="M7" t="inlineStr">
         <is>
           <t>3</t>
         </is>
       </c>
-      <c r="E7" t="inlineStr">
+      <c r="N7" t="inlineStr">
         <is>
           <t>70</t>
         </is>
       </c>
-      <c r="F7" t="inlineStr">
+      <c r="O7" t="inlineStr">
         <is>
           <t>30</t>
         </is>
       </c>
-      <c r="G7" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H7" t="inlineStr">
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Q7" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="J7" t="inlineStr">
+      <c r="S7" t="inlineStr">
         <is>
           <t>28-April-2026</t>
         </is>
       </c>
-      <c r="K7" t="inlineStr">
+      <c r="T7" t="inlineStr">
         <is>
           <t>prereg</t>
         </is>
       </c>
-      <c r="L7" t="inlineStr">
+      <c r="U7" t="inlineStr">
         <is>
           <t>104</t>
         </is>
       </c>
-      <c r="M7" t="inlineStr">
+      <c r="V7" t="inlineStr">
         <is>
           <t>3</t>
         </is>
       </c>
-      <c r="N7" t="inlineStr">
+      <c r="W7" t="inlineStr">
         <is>
           <t>70</t>
         </is>
       </c>
-      <c r="O7" t="inlineStr">
+      <c r="X7" t="inlineStr">
         <is>
           <t>30</t>
         </is>
       </c>
-      <c r="P7" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="Q7" t="inlineStr">
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Z7" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="S7" t="inlineStr">
-        <is>
-          <t>27-April-2026</t>
-        </is>
-      </c>
-      <c r="T7" t="inlineStr">
-        <is>
-          <t>prereg</t>
-        </is>
-      </c>
-      <c r="U7" t="inlineStr">
-        <is>
-          <t>104</t>
-        </is>
-      </c>
-      <c r="V7" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="W7" t="inlineStr">
-        <is>
-          <t>70</t>
-        </is>
-      </c>
-      <c r="X7" t="inlineStr">
-        <is>
-          <t>30</t>
-        </is>
-      </c>
-      <c r="Y7" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="Z7" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
+      <c r="AB7" t="n">
+        <v/>
+      </c>
+      <c r="AC7" t="n">
+        <v/>
+      </c>
+      <c r="AD7" t="n">
+        <v/>
+      </c>
+      <c r="AE7" t="n">
+        <v/>
+      </c>
+      <c r="AF7" t="n">
+        <v/>
+      </c>
+      <c r="AG7" t="n">
+        <v/>
+      </c>
+      <c r="AH7" t="n">
+        <v/>
+      </c>
+      <c r="AI7" t="n">
+        <v/>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
+          <t>30-April-2026</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>residentui</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>33</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
           <t>29-April-2026</t>
         </is>
       </c>
-      <c r="B8" t="inlineStr">
+      <c r="K8" t="inlineStr">
         <is>
           <t>residentui</t>
         </is>
       </c>
-      <c r="C8" t="inlineStr">
+      <c r="L8" t="inlineStr">
         <is>
           <t>33</t>
         </is>
       </c>
-      <c r="D8" t="inlineStr">
+      <c r="M8" t="inlineStr">
         <is>
           <t>12</t>
         </is>
       </c>
-      <c r="E8" t="inlineStr">
+      <c r="N8" t="inlineStr">
         <is>
           <t>5</t>
         </is>
       </c>
-      <c r="F8" t="inlineStr">
+      <c r="O8" t="inlineStr">
         <is>
           <t>16</t>
         </is>
       </c>
-      <c r="G8" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H8" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="J8" t="inlineStr">
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Q8" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="S8" t="inlineStr">
         <is>
           <t>28-April-2026</t>
         </is>
       </c>
-      <c r="K8" t="inlineStr">
+      <c r="T8" t="inlineStr">
         <is>
           <t>residentui</t>
         </is>
       </c>
-      <c r="L8" t="inlineStr">
+      <c r="U8" t="inlineStr">
         <is>
           <t>33</t>
         </is>
       </c>
-      <c r="M8" t="inlineStr">
+      <c r="V8" t="inlineStr">
         <is>
           <t>12</t>
         </is>
       </c>
-      <c r="N8" t="inlineStr">
+      <c r="W8" t="inlineStr">
         <is>
           <t>5</t>
         </is>
       </c>
-      <c r="O8" t="inlineStr">
+      <c r="X8" t="inlineStr">
         <is>
           <t>16</t>
         </is>
       </c>
-      <c r="P8" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="Q8" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="S8" t="inlineStr">
-        <is>
-          <t>27-April-2026</t>
-        </is>
-      </c>
-      <c r="T8" t="inlineStr">
-        <is>
-          <t>residentui</t>
-        </is>
-      </c>
-      <c r="U8" t="inlineStr">
-        <is>
-          <t>33</t>
-        </is>
-      </c>
-      <c r="V8" t="inlineStr">
-        <is>
-          <t>12</t>
-        </is>
-      </c>
-      <c r="W8" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="X8" t="inlineStr">
-        <is>
-          <t>16</t>
-        </is>
-      </c>
       <c r="Y8" t="inlineStr">
         <is>
           <t>0</t>
@@ -1603,6 +1860,30 @@
         <is>
           <t>0</t>
         </is>
+      </c>
+      <c r="AB8" t="n">
+        <v/>
+      </c>
+      <c r="AC8" t="n">
+        <v/>
+      </c>
+      <c r="AD8" t="n">
+        <v/>
+      </c>
+      <c r="AE8" t="n">
+        <v/>
+      </c>
+      <c r="AF8" t="n">
+        <v/>
+      </c>
+      <c r="AG8" t="n">
+        <v/>
+      </c>
+      <c r="AH8" t="n">
+        <v/>
+      </c>
+      <c r="AI8" t="n">
+        <v/>
       </c>
     </row>
   </sheetData>

--- a/minio-report-tracker/xlxs/collab.xlsx
+++ b/minio-report-tracker/xlxs/collab.xlsx
@@ -601,7 +601,7 @@
   <dimension ref="A1:AI8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="15" customWidth="1" min="1" max="1"/>
+    <col width="13" customWidth="1" min="1" max="1"/>
     <col width="12" customWidth="1" min="2" max="2"/>
     <col width="5" customWidth="1" min="3" max="3"/>
     <col width="5" customWidth="1" min="4" max="4"/>
@@ -803,152 +803,152 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
+          <t>01-May-2026</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>auth</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>254</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>184</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>64</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
           <t>30-April-2026</t>
         </is>
       </c>
-      <c r="B2" t="inlineStr">
+      <c r="K2" t="inlineStr">
         <is>
           <t>auth</t>
         </is>
       </c>
-      <c r="C2" t="inlineStr">
+      <c r="L2" t="inlineStr">
         <is>
           <t>254</t>
         </is>
       </c>
-      <c r="D2" t="inlineStr">
+      <c r="M2" t="inlineStr">
         <is>
           <t>184</t>
         </is>
       </c>
-      <c r="E2" t="inlineStr">
+      <c r="N2" t="inlineStr">
         <is>
           <t>6</t>
         </is>
       </c>
-      <c r="F2" t="inlineStr">
+      <c r="O2" t="inlineStr">
         <is>
           <t>64</t>
         </is>
       </c>
-      <c r="G2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="J2" t="inlineStr">
+      <c r="P2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Q2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="S2" t="inlineStr">
         <is>
           <t>29-April-2026</t>
         </is>
       </c>
-      <c r="K2" t="inlineStr">
+      <c r="T2" t="inlineStr">
         <is>
           <t>auth</t>
         </is>
       </c>
-      <c r="L2" t="inlineStr">
+      <c r="U2" t="inlineStr">
         <is>
           <t>254</t>
         </is>
       </c>
-      <c r="M2" t="inlineStr">
+      <c r="V2" t="inlineStr">
         <is>
           <t>186</t>
         </is>
       </c>
-      <c r="N2" t="inlineStr">
+      <c r="W2" t="inlineStr">
         <is>
           <t>6</t>
         </is>
       </c>
-      <c r="O2" t="inlineStr">
+      <c r="X2" t="inlineStr">
         <is>
           <t>62</t>
         </is>
       </c>
-      <c r="P2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="Q2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="S2" t="inlineStr">
+      <c r="Y2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Z2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB2" t="inlineStr">
         <is>
           <t>28-April-2026</t>
         </is>
       </c>
-      <c r="T2" t="inlineStr">
-        <is>
-          <t>auth</t>
-        </is>
-      </c>
-      <c r="U2" t="inlineStr">
-        <is>
-          <t>254</t>
-        </is>
-      </c>
-      <c r="V2" t="inlineStr">
-        <is>
-          <t>140</t>
-        </is>
-      </c>
-      <c r="W2" t="inlineStr">
-        <is>
-          <t>72</t>
-        </is>
-      </c>
-      <c r="X2" t="inlineStr">
+      <c r="AC2" t="inlineStr">
+        <is>
+          <t>esignet</t>
+        </is>
+      </c>
+      <c r="AD2" t="inlineStr">
+        <is>
+          <t>375</t>
+        </is>
+      </c>
+      <c r="AE2" t="inlineStr">
+        <is>
+          <t>274</t>
+        </is>
+      </c>
+      <c r="AF2" t="inlineStr">
+        <is>
+          <t>32</t>
+        </is>
+      </c>
+      <c r="AG2" t="inlineStr">
         <is>
           <t>42</t>
-        </is>
-      </c>
-      <c r="Y2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>27-April-2026</t>
-        </is>
-      </c>
-      <c r="AC2" t="inlineStr">
-        <is>
-          <t>esignet</t>
-        </is>
-      </c>
-      <c r="AD2" t="inlineStr">
-        <is>
-          <t>375</t>
-        </is>
-      </c>
-      <c r="AE2" t="inlineStr">
-        <is>
-          <t>254</t>
-        </is>
-      </c>
-      <c r="AF2" t="inlineStr">
-        <is>
-          <t>50</t>
-        </is>
-      </c>
-      <c r="AG2" t="inlineStr">
-        <is>
-          <t>44</t>
         </is>
       </c>
       <c r="AH2" t="inlineStr">
@@ -965,127 +965,127 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
+          <t>01-May-2026</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>esignet</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>375</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>243</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>58</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>47</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>27</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
           <t>30-April-2026</t>
         </is>
       </c>
-      <c r="B3" t="inlineStr">
+      <c r="K3" t="inlineStr">
         <is>
           <t>esignet</t>
         </is>
       </c>
-      <c r="C3" t="inlineStr">
+      <c r="L3" t="inlineStr">
         <is>
           <t>375</t>
         </is>
       </c>
-      <c r="D3" t="inlineStr">
+      <c r="M3" t="inlineStr">
         <is>
           <t>234</t>
         </is>
       </c>
-      <c r="E3" t="inlineStr">
+      <c r="N3" t="inlineStr">
         <is>
           <t>49</t>
         </is>
       </c>
-      <c r="F3" t="inlineStr">
+      <c r="O3" t="inlineStr">
         <is>
           <t>65</t>
         </is>
       </c>
-      <c r="G3" t="inlineStr">
+      <c r="P3" t="inlineStr">
         <is>
           <t>27</t>
         </is>
       </c>
-      <c r="H3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="J3" t="inlineStr">
+      <c r="Q3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="S3" t="inlineStr">
         <is>
           <t>29-April-2026</t>
         </is>
       </c>
-      <c r="K3" t="inlineStr">
+      <c r="T3" t="inlineStr">
         <is>
           <t>esignet</t>
         </is>
       </c>
-      <c r="L3" t="inlineStr">
+      <c r="U3" t="inlineStr">
         <is>
           <t>375</t>
         </is>
       </c>
-      <c r="M3" t="inlineStr">
+      <c r="V3" t="inlineStr">
         <is>
           <t>290</t>
         </is>
       </c>
-      <c r="N3" t="inlineStr">
+      <c r="W3" t="inlineStr">
         <is>
           <t>16</t>
         </is>
       </c>
-      <c r="O3" t="inlineStr">
+      <c r="X3" t="inlineStr">
         <is>
           <t>42</t>
         </is>
       </c>
-      <c r="P3" t="inlineStr">
+      <c r="Y3" t="inlineStr">
         <is>
           <t>27</t>
         </is>
       </c>
-      <c r="Q3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="S3" t="inlineStr">
+      <c r="Z3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB3" t="inlineStr">
         <is>
           <t>28-April-2026</t>
-        </is>
-      </c>
-      <c r="T3" t="inlineStr">
-        <is>
-          <t>esignet</t>
-        </is>
-      </c>
-      <c r="U3" t="inlineStr">
-        <is>
-          <t>375</t>
-        </is>
-      </c>
-      <c r="V3" t="inlineStr">
-        <is>
-          <t>274</t>
-        </is>
-      </c>
-      <c r="W3" t="inlineStr">
-        <is>
-          <t>32</t>
-        </is>
-      </c>
-      <c r="X3" t="inlineStr">
-        <is>
-          <t>42</t>
-        </is>
-      </c>
-      <c r="Y3" t="inlineStr">
-        <is>
-          <t>27</t>
-        </is>
-      </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>27-April-2026</t>
         </is>
       </c>
       <c r="AC3" t="inlineStr">
@@ -1127,127 +1127,127 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
+          <t>01-May-2026</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>idrepo</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>152</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>101</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>51</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
           <t>30-April-2026</t>
         </is>
       </c>
-      <c r="B4" t="inlineStr">
+      <c r="K4" t="inlineStr">
         <is>
           <t>idrepo</t>
         </is>
       </c>
-      <c r="C4" t="inlineStr">
+      <c r="L4" t="inlineStr">
         <is>
           <t>152</t>
         </is>
       </c>
-      <c r="D4" t="inlineStr">
+      <c r="M4" t="inlineStr">
         <is>
           <t>101</t>
         </is>
       </c>
-      <c r="E4" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F4" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="G4" t="inlineStr">
+      <c r="N4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P4" t="inlineStr">
         <is>
           <t>51</t>
         </is>
       </c>
-      <c r="H4" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="J4" t="inlineStr">
+      <c r="Q4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="S4" t="inlineStr">
         <is>
           <t>29-April-2026</t>
         </is>
       </c>
-      <c r="K4" t="inlineStr">
+      <c r="T4" t="inlineStr">
         <is>
           <t>idrepo</t>
         </is>
       </c>
-      <c r="L4" t="inlineStr">
+      <c r="U4" t="inlineStr">
         <is>
           <t>152</t>
         </is>
       </c>
-      <c r="M4" t="inlineStr">
+      <c r="V4" t="inlineStr">
         <is>
           <t>101</t>
         </is>
       </c>
-      <c r="N4" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="O4" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="P4" t="inlineStr">
+      <c r="W4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="X4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Y4" t="inlineStr">
         <is>
           <t>51</t>
         </is>
       </c>
-      <c r="Q4" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="S4" t="inlineStr">
+      <c r="Z4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB4" t="inlineStr">
         <is>
           <t>28-April-2026</t>
-        </is>
-      </c>
-      <c r="T4" t="inlineStr">
-        <is>
-          <t>idrepo</t>
-        </is>
-      </c>
-      <c r="U4" t="inlineStr">
-        <is>
-          <t>152</t>
-        </is>
-      </c>
-      <c r="V4" t="inlineStr">
-        <is>
-          <t>101</t>
-        </is>
-      </c>
-      <c r="W4" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="X4" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="Y4" t="inlineStr">
-        <is>
-          <t>51</t>
-        </is>
-      </c>
-      <c r="Z4" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB4" t="inlineStr">
-        <is>
-          <t>27-April-2026</t>
         </is>
       </c>
       <c r="AC4" t="inlineStr">
@@ -1289,127 +1289,127 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
+          <t>01-May-2026</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>injiverify</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>53</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>23</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
           <t>30-April-2026</t>
         </is>
       </c>
-      <c r="B5" t="inlineStr">
+      <c r="K5" t="inlineStr">
         <is>
           <t>injiverify</t>
         </is>
       </c>
-      <c r="C5" t="inlineStr">
+      <c r="L5" t="inlineStr">
         <is>
           <t>53</t>
         </is>
       </c>
-      <c r="D5" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="E5" t="inlineStr">
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="N5" t="inlineStr">
         <is>
           <t>23</t>
         </is>
       </c>
-      <c r="F5" t="inlineStr">
+      <c r="O5" t="inlineStr">
         <is>
           <t>30</t>
         </is>
       </c>
-      <c r="G5" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H5" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="J5" t="inlineStr">
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Q5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="S5" t="inlineStr">
         <is>
           <t>29-April-2026</t>
         </is>
       </c>
-      <c r="K5" t="inlineStr">
+      <c r="T5" t="inlineStr">
         <is>
           <t>injiverify</t>
         </is>
       </c>
-      <c r="L5" t="inlineStr">
+      <c r="U5" t="inlineStr">
         <is>
           <t>53</t>
         </is>
       </c>
-      <c r="M5" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="N5" t="inlineStr">
+      <c r="V5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="W5" t="inlineStr">
         <is>
           <t>23</t>
         </is>
       </c>
-      <c r="O5" t="inlineStr">
+      <c r="X5" t="inlineStr">
         <is>
           <t>30</t>
         </is>
       </c>
-      <c r="P5" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="Q5" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="S5" t="inlineStr">
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Z5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB5" t="inlineStr">
         <is>
           <t>28-April-2026</t>
-        </is>
-      </c>
-      <c r="T5" t="inlineStr">
-        <is>
-          <t>injiverify</t>
-        </is>
-      </c>
-      <c r="U5" t="inlineStr">
-        <is>
-          <t>53</t>
-        </is>
-      </c>
-      <c r="V5" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="W5" t="inlineStr">
-        <is>
-          <t>23</t>
-        </is>
-      </c>
-      <c r="X5" t="inlineStr">
-        <is>
-          <t>30</t>
-        </is>
-      </c>
-      <c r="Y5" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="Z5" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB5" t="inlineStr">
-        <is>
-          <t>27-April-2026</t>
         </is>
       </c>
       <c r="AC5" t="inlineStr">
@@ -1451,87 +1451,87 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
+          <t>01-May-2026</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>mimoto</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>79</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>65</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
           <t>30-April-2026</t>
         </is>
       </c>
-      <c r="B6" t="inlineStr">
+      <c r="K6" t="inlineStr">
         <is>
           <t>mimoto</t>
         </is>
       </c>
-      <c r="C6" t="inlineStr">
+      <c r="L6" t="inlineStr">
         <is>
           <t>79</t>
         </is>
       </c>
-      <c r="D6" t="inlineStr">
+      <c r="M6" t="inlineStr">
         <is>
           <t>66</t>
         </is>
       </c>
-      <c r="E6" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F6" t="inlineStr">
+      <c r="N6" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O6" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="G6" t="inlineStr">
+      <c r="P6" t="inlineStr">
         <is>
           <t>10</t>
         </is>
       </c>
-      <c r="H6" t="inlineStr">
+      <c r="Q6" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="J6" t="inlineStr">
+      <c r="S6" t="inlineStr">
         <is>
           <t>29-April-2026</t>
-        </is>
-      </c>
-      <c r="K6" t="inlineStr">
-        <is>
-          <t>mimoto</t>
-        </is>
-      </c>
-      <c r="L6" t="inlineStr">
-        <is>
-          <t>79</t>
-        </is>
-      </c>
-      <c r="M6" t="inlineStr">
-        <is>
-          <t>58</t>
-        </is>
-      </c>
-      <c r="N6" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="O6" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="P6" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="Q6" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="S6" t="inlineStr">
-        <is>
-          <t>28-April-2026</t>
         </is>
       </c>
       <c r="T6" t="inlineStr">
@@ -1597,87 +1597,87 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
+          <t>01-May-2026</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>prereg</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>104</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>70</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
           <t>30-April-2026</t>
         </is>
       </c>
-      <c r="B7" t="inlineStr">
+      <c r="K7" t="inlineStr">
         <is>
           <t>prereg</t>
         </is>
       </c>
-      <c r="C7" t="inlineStr">
+      <c r="L7" t="inlineStr">
         <is>
           <t>104</t>
         </is>
       </c>
-      <c r="D7" t="inlineStr">
+      <c r="M7" t="inlineStr">
         <is>
           <t>3</t>
         </is>
       </c>
-      <c r="E7" t="inlineStr">
+      <c r="N7" t="inlineStr">
         <is>
           <t>70</t>
         </is>
       </c>
-      <c r="F7" t="inlineStr">
+      <c r="O7" t="inlineStr">
         <is>
           <t>30</t>
         </is>
       </c>
-      <c r="G7" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H7" t="inlineStr">
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Q7" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="J7" t="inlineStr">
+      <c r="S7" t="inlineStr">
         <is>
           <t>29-April-2026</t>
-        </is>
-      </c>
-      <c r="K7" t="inlineStr">
-        <is>
-          <t>prereg</t>
-        </is>
-      </c>
-      <c r="L7" t="inlineStr">
-        <is>
-          <t>104</t>
-        </is>
-      </c>
-      <c r="M7" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="N7" t="inlineStr">
-        <is>
-          <t>70</t>
-        </is>
-      </c>
-      <c r="O7" t="inlineStr">
-        <is>
-          <t>30</t>
-        </is>
-      </c>
-      <c r="P7" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="Q7" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="S7" t="inlineStr">
-        <is>
-          <t>28-April-2026</t>
         </is>
       </c>
       <c r="T7" t="inlineStr">
@@ -1743,87 +1743,87 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
+          <t>01-May-2026</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>residentui</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>33</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
           <t>30-April-2026</t>
         </is>
       </c>
-      <c r="B8" t="inlineStr">
+      <c r="K8" t="inlineStr">
         <is>
           <t>residentui</t>
         </is>
       </c>
-      <c r="C8" t="inlineStr">
+      <c r="L8" t="inlineStr">
         <is>
           <t>33</t>
         </is>
       </c>
-      <c r="D8" t="inlineStr">
+      <c r="M8" t="inlineStr">
         <is>
           <t>12</t>
         </is>
       </c>
-      <c r="E8" t="inlineStr">
+      <c r="N8" t="inlineStr">
         <is>
           <t>5</t>
         </is>
       </c>
-      <c r="F8" t="inlineStr">
+      <c r="O8" t="inlineStr">
         <is>
           <t>16</t>
         </is>
       </c>
-      <c r="G8" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H8" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="J8" t="inlineStr">
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Q8" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="S8" t="inlineStr">
         <is>
           <t>29-April-2026</t>
-        </is>
-      </c>
-      <c r="K8" t="inlineStr">
-        <is>
-          <t>residentui</t>
-        </is>
-      </c>
-      <c r="L8" t="inlineStr">
-        <is>
-          <t>33</t>
-        </is>
-      </c>
-      <c r="M8" t="inlineStr">
-        <is>
-          <t>12</t>
-        </is>
-      </c>
-      <c r="N8" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="O8" t="inlineStr">
-        <is>
-          <t>16</t>
-        </is>
-      </c>
-      <c r="P8" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="Q8" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="S8" t="inlineStr">
-        <is>
-          <t>28-April-2026</t>
         </is>
       </c>
       <c r="T8" t="inlineStr">

--- a/minio-report-tracker/xlxs/collab.xlsx
+++ b/minio-report-tracker/xlxs/collab.xlsx
@@ -614,10 +614,10 @@
     <col width="12" customWidth="1" min="11" max="11"/>
     <col width="5" customWidth="1" min="12" max="12"/>
     <col width="5" customWidth="1" min="13" max="13"/>
-    <col width="5" customWidth="1" min="14" max="14"/>
-    <col width="5" customWidth="1" min="15" max="15"/>
-    <col width="5" customWidth="1" min="16" max="16"/>
-    <col width="5" customWidth="1" min="17" max="17"/>
+    <col width="4" customWidth="1" min="14" max="14"/>
+    <col width="4" customWidth="1" min="15" max="15"/>
+    <col width="4" customWidth="1" min="16" max="16"/>
+    <col width="4" customWidth="1" min="17" max="17"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -705,77 +705,77 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
+          <t>05-May-2026</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>auth</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>254</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>142</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>72</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>40</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
           <t>04-May-2026</t>
         </is>
       </c>
-      <c r="B2" t="inlineStr">
+      <c r="K2" t="inlineStr">
         <is>
           <t>auth</t>
         </is>
       </c>
-      <c r="C2" t="inlineStr">
+      <c r="L2" t="inlineStr">
         <is>
           <t>254</t>
         </is>
       </c>
-      <c r="D2" t="inlineStr">
+      <c r="M2" t="inlineStr">
         <is>
           <t>140</t>
         </is>
       </c>
-      <c r="E2" t="inlineStr">
+      <c r="N2" t="inlineStr">
         <is>
           <t>72</t>
         </is>
       </c>
-      <c r="F2" t="inlineStr">
+      <c r="O2" t="inlineStr">
         <is>
           <t>42</t>
         </is>
       </c>
-      <c r="G2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="J2" t="inlineStr">
-        <is>
-          <t>01-May-2026</t>
-        </is>
-      </c>
-      <c r="K2" t="inlineStr">
-        <is>
-          <t>esignet</t>
-        </is>
-      </c>
-      <c r="L2" t="inlineStr">
-        <is>
-          <t>375</t>
-        </is>
-      </c>
-      <c r="M2" t="inlineStr">
-        <is>
-          <t>243</t>
-        </is>
-      </c>
-      <c r="N2" t="inlineStr">
-        <is>
-          <t>58</t>
-        </is>
-      </c>
-      <c r="O2" t="inlineStr">
-        <is>
-          <t>47</t>
-        </is>
-      </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>27</t>
+          <t>0</t>
         </is>
       </c>
       <c r="Q2" t="inlineStr">
@@ -787,77 +787,77 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
+          <t>05-May-2026</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>esignet</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>375</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>276</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>43</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>29</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>27</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
           <t>04-May-2026</t>
         </is>
       </c>
-      <c r="B3" t="inlineStr">
+      <c r="K3" t="inlineStr">
         <is>
           <t>esignet</t>
         </is>
       </c>
-      <c r="C3" t="inlineStr">
+      <c r="L3" t="inlineStr">
         <is>
           <t>375</t>
         </is>
       </c>
-      <c r="D3" t="inlineStr">
+      <c r="M3" t="inlineStr">
         <is>
           <t>264</t>
         </is>
       </c>
-      <c r="E3" t="inlineStr">
+      <c r="N3" t="inlineStr">
         <is>
           <t>37</t>
         </is>
       </c>
-      <c r="F3" t="inlineStr">
+      <c r="O3" t="inlineStr">
         <is>
           <t>47</t>
         </is>
       </c>
-      <c r="G3" t="inlineStr">
+      <c r="P3" t="inlineStr">
         <is>
           <t>27</t>
-        </is>
-      </c>
-      <c r="H3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="J3" t="inlineStr">
-        <is>
-          <t>01-May-2026</t>
-        </is>
-      </c>
-      <c r="K3" t="inlineStr">
-        <is>
-          <t>injiverify</t>
-        </is>
-      </c>
-      <c r="L3" t="inlineStr">
-        <is>
-          <t>53</t>
-        </is>
-      </c>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="N3" t="inlineStr">
-        <is>
-          <t>23</t>
-        </is>
-      </c>
-      <c r="O3" t="inlineStr">
-        <is>
-          <t>30</t>
-        </is>
-      </c>
-      <c r="P3" t="inlineStr">
-        <is>
-          <t>0</t>
         </is>
       </c>
       <c r="Q3" t="inlineStr">
@@ -869,154 +869,154 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
+          <t>05-May-2026</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>idrepo</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>152</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>101</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>51</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
           <t>04-May-2026</t>
         </is>
       </c>
-      <c r="B4" t="inlineStr">
+      <c r="K4" t="inlineStr">
         <is>
           <t>idrepo</t>
         </is>
       </c>
-      <c r="C4" t="inlineStr">
+      <c r="L4" t="inlineStr">
         <is>
           <t>152</t>
         </is>
       </c>
-      <c r="D4" t="inlineStr">
+      <c r="M4" t="inlineStr">
         <is>
           <t>101</t>
         </is>
       </c>
-      <c r="E4" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F4" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="G4" t="inlineStr">
+      <c r="N4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P4" t="inlineStr">
         <is>
           <t>51</t>
         </is>
       </c>
-      <c r="H4" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="J4" t="inlineStr">
-        <is>
-          <t>01-May-2026</t>
-        </is>
-      </c>
-      <c r="K4" t="inlineStr">
-        <is>
-          <t>prereg</t>
-        </is>
-      </c>
-      <c r="L4" t="inlineStr">
-        <is>
-          <t>104</t>
-        </is>
-      </c>
-      <c r="M4" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="N4" t="inlineStr">
-        <is>
-          <t>70</t>
-        </is>
-      </c>
-      <c r="O4" t="inlineStr">
-        <is>
-          <t>30</t>
-        </is>
-      </c>
-      <c r="P4" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
       <c r="Q4" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
+          <t>05-May-2026</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>injiverify</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>53</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>23</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
           <t>04-May-2026</t>
         </is>
       </c>
-      <c r="B5" t="inlineStr">
+      <c r="K5" t="inlineStr">
         <is>
           <t>injiverify</t>
         </is>
       </c>
-      <c r="C5" t="inlineStr">
+      <c r="L5" t="inlineStr">
         <is>
           <t>53</t>
         </is>
       </c>
-      <c r="D5" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="E5" t="inlineStr">
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="N5" t="inlineStr">
         <is>
           <t>23</t>
         </is>
       </c>
-      <c r="F5" t="inlineStr">
+      <c r="O5" t="inlineStr">
         <is>
           <t>30</t>
-        </is>
-      </c>
-      <c r="G5" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H5" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="J5" t="inlineStr">
-        <is>
-          <t>01-May-2026</t>
-        </is>
-      </c>
-      <c r="K5" t="inlineStr">
-        <is>
-          <t>residentui</t>
-        </is>
-      </c>
-      <c r="L5" t="inlineStr">
-        <is>
-          <t>33</t>
-        </is>
-      </c>
-      <c r="M5" t="inlineStr">
-        <is>
-          <t>12</t>
-        </is>
-      </c>
-      <c r="N5" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="O5" t="inlineStr">
-        <is>
-          <t>16</t>
         </is>
       </c>
       <c r="P5" t="inlineStr">
@@ -1033,199 +1033,247 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
+          <t>05-May-2026</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>mimoto</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>79</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>58</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
           <t>04-May-2026</t>
         </is>
       </c>
-      <c r="B6" t="inlineStr">
+      <c r="K6" t="inlineStr">
         <is>
           <t>mimoto</t>
         </is>
       </c>
-      <c r="C6" t="inlineStr">
+      <c r="L6" t="inlineStr">
         <is>
           <t>79</t>
         </is>
       </c>
-      <c r="D6" t="inlineStr">
+      <c r="M6" t="inlineStr">
         <is>
           <t>59</t>
         </is>
       </c>
-      <c r="E6" t="inlineStr">
+      <c r="N6" t="inlineStr">
         <is>
           <t>4</t>
         </is>
       </c>
-      <c r="F6" t="inlineStr">
+      <c r="O6" t="inlineStr">
         <is>
           <t>4</t>
         </is>
       </c>
-      <c r="G6" t="inlineStr">
+      <c r="P6" t="inlineStr">
         <is>
           <t>10</t>
         </is>
       </c>
-      <c r="H6" t="inlineStr">
+      <c r="Q6" t="inlineStr">
         <is>
           <t>2</t>
         </is>
-      </c>
-      <c r="J6" t="n">
-        <v/>
-      </c>
-      <c r="K6" t="n">
-        <v/>
-      </c>
-      <c r="L6" t="n">
-        <v/>
-      </c>
-      <c r="M6" t="n">
-        <v/>
-      </c>
-      <c r="N6" t="n">
-        <v/>
-      </c>
-      <c r="O6" t="n">
-        <v/>
-      </c>
-      <c r="P6" t="n">
-        <v/>
-      </c>
-      <c r="Q6" t="n">
-        <v/>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
+          <t>05-May-2026</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>prereg</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>104</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>70</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
           <t>04-May-2026</t>
         </is>
       </c>
-      <c r="B7" t="inlineStr">
+      <c r="K7" t="inlineStr">
         <is>
           <t>prereg</t>
         </is>
       </c>
-      <c r="C7" t="inlineStr">
+      <c r="L7" t="inlineStr">
         <is>
           <t>104</t>
         </is>
       </c>
-      <c r="D7" t="inlineStr">
+      <c r="M7" t="inlineStr">
         <is>
           <t>3</t>
         </is>
       </c>
-      <c r="E7" t="inlineStr">
+      <c r="N7" t="inlineStr">
         <is>
           <t>70</t>
         </is>
       </c>
-      <c r="F7" t="inlineStr">
+      <c r="O7" t="inlineStr">
         <is>
           <t>30</t>
         </is>
       </c>
-      <c r="G7" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H7" t="inlineStr">
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Q7" t="inlineStr">
         <is>
           <t>1</t>
         </is>
-      </c>
-      <c r="J7" t="n">
-        <v/>
-      </c>
-      <c r="K7" t="n">
-        <v/>
-      </c>
-      <c r="L7" t="n">
-        <v/>
-      </c>
-      <c r="M7" t="n">
-        <v/>
-      </c>
-      <c r="N7" t="n">
-        <v/>
-      </c>
-      <c r="O7" t="n">
-        <v/>
-      </c>
-      <c r="P7" t="n">
-        <v/>
-      </c>
-      <c r="Q7" t="n">
-        <v/>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
+          <t>05-May-2026</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>residentui</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>33</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
           <t>04-May-2026</t>
         </is>
       </c>
-      <c r="B8" t="inlineStr">
+      <c r="K8" t="inlineStr">
         <is>
           <t>residentui</t>
         </is>
       </c>
-      <c r="C8" t="inlineStr">
+      <c r="L8" t="inlineStr">
         <is>
           <t>33</t>
         </is>
       </c>
-      <c r="D8" t="inlineStr">
+      <c r="M8" t="inlineStr">
         <is>
           <t>12</t>
         </is>
       </c>
-      <c r="E8" t="inlineStr">
+      <c r="N8" t="inlineStr">
         <is>
           <t>5</t>
         </is>
       </c>
-      <c r="F8" t="inlineStr">
+      <c r="O8" t="inlineStr">
         <is>
           <t>16</t>
         </is>
       </c>
-      <c r="G8" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H8" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="J8" t="n">
-        <v/>
-      </c>
-      <c r="K8" t="n">
-        <v/>
-      </c>
-      <c r="L8" t="n">
-        <v/>
-      </c>
-      <c r="M8" t="n">
-        <v/>
-      </c>
-      <c r="N8" t="n">
-        <v/>
-      </c>
-      <c r="O8" t="n">
-        <v/>
-      </c>
-      <c r="P8" t="n">
-        <v/>
-      </c>
-      <c r="Q8" t="n">
-        <v/>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Q8" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
     </row>
   </sheetData>

--- a/minio-report-tracker/xlxs/collab.xlsx
+++ b/minio-report-tracker/xlxs/collab.xlsx
@@ -598,7 +598,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q8"/>
+  <dimension ref="A1:Z8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -618,6 +618,15 @@
     <col width="4" customWidth="1" min="15" max="15"/>
     <col width="4" customWidth="1" min="16" max="16"/>
     <col width="4" customWidth="1" min="17" max="17"/>
+    <col width="2" customWidth="1" min="18" max="18"/>
+    <col width="13" customWidth="1" min="19" max="19"/>
+    <col width="12" customWidth="1" min="20" max="20"/>
+    <col width="5" customWidth="1" min="21" max="21"/>
+    <col width="5" customWidth="1" min="22" max="22"/>
+    <col width="4" customWidth="1" min="23" max="23"/>
+    <col width="4" customWidth="1" min="24" max="24"/>
+    <col width="4" customWidth="1" min="25" max="25"/>
+    <col width="4" customWidth="1" min="26" max="26"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -701,84 +710,164 @@
           <t>KI</t>
         </is>
       </c>
+      <c r="S1" s="1" t="inlineStr">
+        <is>
+          <t>Date</t>
+        </is>
+      </c>
+      <c r="T1" s="1" t="inlineStr">
+        <is>
+          <t>Module</t>
+        </is>
+      </c>
+      <c r="U1" s="1" t="inlineStr">
+        <is>
+          <t>T</t>
+        </is>
+      </c>
+      <c r="V1" s="1" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
+      <c r="W1" s="1" t="inlineStr">
+        <is>
+          <t>S</t>
+        </is>
+      </c>
+      <c r="X1" s="1" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
+      <c r="Y1" s="1" t="inlineStr">
+        <is>
+          <t>I</t>
+        </is>
+      </c>
+      <c r="Z1" s="1" t="inlineStr">
+        <is>
+          <t>KI</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
+          <t>06-May-2026</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>auth</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>254</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>142</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>72</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>40</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
           <t>05-May-2026</t>
         </is>
       </c>
-      <c r="B2" t="inlineStr">
+      <c r="K2" t="inlineStr">
         <is>
           <t>auth</t>
         </is>
       </c>
-      <c r="C2" t="inlineStr">
+      <c r="L2" t="inlineStr">
         <is>
           <t>254</t>
         </is>
       </c>
-      <c r="D2" t="inlineStr">
+      <c r="M2" t="inlineStr">
         <is>
           <t>142</t>
         </is>
       </c>
-      <c r="E2" t="inlineStr">
+      <c r="N2" t="inlineStr">
         <is>
           <t>72</t>
         </is>
       </c>
-      <c r="F2" t="inlineStr">
+      <c r="O2" t="inlineStr">
         <is>
           <t>40</t>
         </is>
       </c>
-      <c r="G2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="J2" t="inlineStr">
+      <c r="P2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Q2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="S2" t="inlineStr">
         <is>
           <t>04-May-2026</t>
         </is>
       </c>
-      <c r="K2" t="inlineStr">
+      <c r="T2" t="inlineStr">
         <is>
           <t>auth</t>
         </is>
       </c>
-      <c r="L2" t="inlineStr">
+      <c r="U2" t="inlineStr">
         <is>
           <t>254</t>
         </is>
       </c>
-      <c r="M2" t="inlineStr">
+      <c r="V2" t="inlineStr">
         <is>
           <t>140</t>
         </is>
       </c>
-      <c r="N2" t="inlineStr">
+      <c r="W2" t="inlineStr">
         <is>
           <t>72</t>
         </is>
       </c>
-      <c r="O2" t="inlineStr">
+      <c r="X2" t="inlineStr">
         <is>
           <t>42</t>
         </is>
       </c>
-      <c r="P2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="Q2" t="inlineStr">
+      <c r="Y2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Z2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
@@ -787,80 +876,120 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
+          <t>06-May-2026</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>esignet</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>375</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>257</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>35</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>56</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>27</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
           <t>05-May-2026</t>
         </is>
       </c>
-      <c r="B3" t="inlineStr">
+      <c r="K3" t="inlineStr">
         <is>
           <t>esignet</t>
         </is>
       </c>
-      <c r="C3" t="inlineStr">
+      <c r="L3" t="inlineStr">
         <is>
           <t>375</t>
         </is>
       </c>
-      <c r="D3" t="inlineStr">
+      <c r="M3" t="inlineStr">
         <is>
           <t>276</t>
         </is>
       </c>
-      <c r="E3" t="inlineStr">
+      <c r="N3" t="inlineStr">
         <is>
           <t>43</t>
         </is>
       </c>
-      <c r="F3" t="inlineStr">
+      <c r="O3" t="inlineStr">
         <is>
           <t>29</t>
         </is>
       </c>
-      <c r="G3" t="inlineStr">
+      <c r="P3" t="inlineStr">
         <is>
           <t>27</t>
         </is>
       </c>
-      <c r="H3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="J3" t="inlineStr">
+      <c r="Q3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="S3" t="inlineStr">
         <is>
           <t>04-May-2026</t>
         </is>
       </c>
-      <c r="K3" t="inlineStr">
+      <c r="T3" t="inlineStr">
         <is>
           <t>esignet</t>
         </is>
       </c>
-      <c r="L3" t="inlineStr">
+      <c r="U3" t="inlineStr">
         <is>
           <t>375</t>
         </is>
       </c>
-      <c r="M3" t="inlineStr">
+      <c r="V3" t="inlineStr">
         <is>
           <t>264</t>
         </is>
       </c>
-      <c r="N3" t="inlineStr">
+      <c r="W3" t="inlineStr">
         <is>
           <t>37</t>
         </is>
       </c>
-      <c r="O3" t="inlineStr">
+      <c r="X3" t="inlineStr">
         <is>
           <t>47</t>
         </is>
       </c>
-      <c r="P3" t="inlineStr">
+      <c r="Y3" t="inlineStr">
         <is>
           <t>27</t>
         </is>
       </c>
-      <c r="Q3" t="inlineStr">
+      <c r="Z3" t="inlineStr">
         <is>
           <t>0</t>
         </is>
@@ -869,80 +998,120 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
+          <t>06-May-2026</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>idrepo</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>152</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>101</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>51</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
           <t>05-May-2026</t>
         </is>
       </c>
-      <c r="B4" t="inlineStr">
+      <c r="K4" t="inlineStr">
         <is>
           <t>idrepo</t>
         </is>
       </c>
-      <c r="C4" t="inlineStr">
+      <c r="L4" t="inlineStr">
         <is>
           <t>152</t>
         </is>
       </c>
-      <c r="D4" t="inlineStr">
+      <c r="M4" t="inlineStr">
         <is>
           <t>101</t>
         </is>
       </c>
-      <c r="E4" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F4" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="G4" t="inlineStr">
+      <c r="N4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P4" t="inlineStr">
         <is>
           <t>51</t>
         </is>
       </c>
-      <c r="H4" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="J4" t="inlineStr">
+      <c r="Q4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="S4" t="inlineStr">
         <is>
           <t>04-May-2026</t>
         </is>
       </c>
-      <c r="K4" t="inlineStr">
+      <c r="T4" t="inlineStr">
         <is>
           <t>idrepo</t>
         </is>
       </c>
-      <c r="L4" t="inlineStr">
+      <c r="U4" t="inlineStr">
         <is>
           <t>152</t>
         </is>
       </c>
-      <c r="M4" t="inlineStr">
+      <c r="V4" t="inlineStr">
         <is>
           <t>101</t>
         </is>
       </c>
-      <c r="N4" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="O4" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="P4" t="inlineStr">
+      <c r="W4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="X4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Y4" t="inlineStr">
         <is>
           <t>51</t>
         </is>
       </c>
-      <c r="Q4" t="inlineStr">
+      <c r="Z4" t="inlineStr">
         <is>
           <t>0</t>
         </is>
@@ -951,80 +1120,120 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
+          <t>06-May-2026</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>injiverify</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>53</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>23</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
           <t>05-May-2026</t>
         </is>
       </c>
-      <c r="B5" t="inlineStr">
+      <c r="K5" t="inlineStr">
         <is>
           <t>injiverify</t>
         </is>
       </c>
-      <c r="C5" t="inlineStr">
+      <c r="L5" t="inlineStr">
         <is>
           <t>53</t>
         </is>
       </c>
-      <c r="D5" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="E5" t="inlineStr">
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="N5" t="inlineStr">
         <is>
           <t>23</t>
         </is>
       </c>
-      <c r="F5" t="inlineStr">
+      <c r="O5" t="inlineStr">
         <is>
           <t>30</t>
         </is>
       </c>
-      <c r="G5" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H5" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="J5" t="inlineStr">
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Q5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="S5" t="inlineStr">
         <is>
           <t>04-May-2026</t>
         </is>
       </c>
-      <c r="K5" t="inlineStr">
+      <c r="T5" t="inlineStr">
         <is>
           <t>injiverify</t>
         </is>
       </c>
-      <c r="L5" t="inlineStr">
+      <c r="U5" t="inlineStr">
         <is>
           <t>53</t>
         </is>
       </c>
-      <c r="M5" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="N5" t="inlineStr">
+      <c r="V5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="W5" t="inlineStr">
         <is>
           <t>23</t>
         </is>
       </c>
-      <c r="O5" t="inlineStr">
+      <c r="X5" t="inlineStr">
         <is>
           <t>30</t>
         </is>
       </c>
-      <c r="P5" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="Q5" t="inlineStr">
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Z5" t="inlineStr">
         <is>
           <t>0</t>
         </is>
@@ -1033,80 +1242,120 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
+          <t>06-May-2026</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>mimoto</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>79</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>59</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
           <t>05-May-2026</t>
         </is>
       </c>
-      <c r="B6" t="inlineStr">
+      <c r="K6" t="inlineStr">
         <is>
           <t>mimoto</t>
         </is>
       </c>
-      <c r="C6" t="inlineStr">
+      <c r="L6" t="inlineStr">
         <is>
           <t>79</t>
         </is>
       </c>
-      <c r="D6" t="inlineStr">
+      <c r="M6" t="inlineStr">
         <is>
           <t>58</t>
         </is>
       </c>
-      <c r="E6" t="inlineStr">
+      <c r="N6" t="inlineStr">
         <is>
           <t>4</t>
         </is>
       </c>
-      <c r="F6" t="inlineStr">
+      <c r="O6" t="inlineStr">
         <is>
           <t>5</t>
         </is>
       </c>
-      <c r="G6" t="inlineStr">
+      <c r="P6" t="inlineStr">
         <is>
           <t>10</t>
         </is>
       </c>
-      <c r="H6" t="inlineStr">
+      <c r="Q6" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="J6" t="inlineStr">
+      <c r="S6" t="inlineStr">
         <is>
           <t>04-May-2026</t>
         </is>
       </c>
-      <c r="K6" t="inlineStr">
+      <c r="T6" t="inlineStr">
         <is>
           <t>mimoto</t>
         </is>
       </c>
-      <c r="L6" t="inlineStr">
+      <c r="U6" t="inlineStr">
         <is>
           <t>79</t>
         </is>
       </c>
-      <c r="M6" t="inlineStr">
+      <c r="V6" t="inlineStr">
         <is>
           <t>59</t>
         </is>
       </c>
-      <c r="N6" t="inlineStr">
+      <c r="W6" t="inlineStr">
         <is>
           <t>4</t>
         </is>
       </c>
-      <c r="O6" t="inlineStr">
+      <c r="X6" t="inlineStr">
         <is>
           <t>4</t>
         </is>
       </c>
-      <c r="P6" t="inlineStr">
+      <c r="Y6" t="inlineStr">
         <is>
           <t>10</t>
         </is>
       </c>
-      <c r="Q6" t="inlineStr">
+      <c r="Z6" t="inlineStr">
         <is>
           <t>2</t>
         </is>
@@ -1115,80 +1364,120 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
+          <t>06-May-2026</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>prereg</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>104</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>70</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
           <t>05-May-2026</t>
         </is>
       </c>
-      <c r="B7" t="inlineStr">
+      <c r="K7" t="inlineStr">
         <is>
           <t>prereg</t>
         </is>
       </c>
-      <c r="C7" t="inlineStr">
+      <c r="L7" t="inlineStr">
         <is>
           <t>104</t>
         </is>
       </c>
-      <c r="D7" t="inlineStr">
+      <c r="M7" t="inlineStr">
         <is>
           <t>3</t>
         </is>
       </c>
-      <c r="E7" t="inlineStr">
+      <c r="N7" t="inlineStr">
         <is>
           <t>70</t>
         </is>
       </c>
-      <c r="F7" t="inlineStr">
+      <c r="O7" t="inlineStr">
         <is>
           <t>30</t>
         </is>
       </c>
-      <c r="G7" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H7" t="inlineStr">
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Q7" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="J7" t="inlineStr">
+      <c r="S7" t="inlineStr">
         <is>
           <t>04-May-2026</t>
         </is>
       </c>
-      <c r="K7" t="inlineStr">
+      <c r="T7" t="inlineStr">
         <is>
           <t>prereg</t>
         </is>
       </c>
-      <c r="L7" t="inlineStr">
+      <c r="U7" t="inlineStr">
         <is>
           <t>104</t>
         </is>
       </c>
-      <c r="M7" t="inlineStr">
+      <c r="V7" t="inlineStr">
         <is>
           <t>3</t>
         </is>
       </c>
-      <c r="N7" t="inlineStr">
+      <c r="W7" t="inlineStr">
         <is>
           <t>70</t>
         </is>
       </c>
-      <c r="O7" t="inlineStr">
+      <c r="X7" t="inlineStr">
         <is>
           <t>30</t>
         </is>
       </c>
-      <c r="P7" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="Q7" t="inlineStr">
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Z7" t="inlineStr">
         <is>
           <t>1</t>
         </is>
@@ -1197,80 +1486,120 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
+          <t>06-May-2026</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>residentui</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>33</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
           <t>05-May-2026</t>
         </is>
       </c>
-      <c r="B8" t="inlineStr">
+      <c r="K8" t="inlineStr">
         <is>
           <t>residentui</t>
         </is>
       </c>
-      <c r="C8" t="inlineStr">
+      <c r="L8" t="inlineStr">
         <is>
           <t>33</t>
         </is>
       </c>
-      <c r="D8" t="inlineStr">
+      <c r="M8" t="inlineStr">
         <is>
           <t>12</t>
         </is>
       </c>
-      <c r="E8" t="inlineStr">
+      <c r="N8" t="inlineStr">
         <is>
           <t>5</t>
         </is>
       </c>
-      <c r="F8" t="inlineStr">
+      <c r="O8" t="inlineStr">
         <is>
           <t>16</t>
         </is>
       </c>
-      <c r="G8" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H8" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="J8" t="inlineStr">
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Q8" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="S8" t="inlineStr">
         <is>
           <t>04-May-2026</t>
         </is>
       </c>
-      <c r="K8" t="inlineStr">
+      <c r="T8" t="inlineStr">
         <is>
           <t>residentui</t>
         </is>
       </c>
-      <c r="L8" t="inlineStr">
+      <c r="U8" t="inlineStr">
         <is>
           <t>33</t>
         </is>
       </c>
-      <c r="M8" t="inlineStr">
+      <c r="V8" t="inlineStr">
         <is>
           <t>12</t>
         </is>
       </c>
-      <c r="N8" t="inlineStr">
+      <c r="W8" t="inlineStr">
         <is>
           <t>5</t>
         </is>
       </c>
-      <c r="O8" t="inlineStr">
+      <c r="X8" t="inlineStr">
         <is>
           <t>16</t>
         </is>
       </c>
-      <c r="P8" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="Q8" t="inlineStr">
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Z8" t="inlineStr">
         <is>
           <t>0</t>
         </is>

--- a/minio-report-tracker/xlxs/collab.xlsx
+++ b/minio-report-tracker/xlxs/collab.xlsx
@@ -598,7 +598,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Z8"/>
+  <dimension ref="A1:AI8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -627,6 +627,15 @@
     <col width="4" customWidth="1" min="24" max="24"/>
     <col width="4" customWidth="1" min="25" max="25"/>
     <col width="4" customWidth="1" min="26" max="26"/>
+    <col width="2" customWidth="1" min="27" max="27"/>
+    <col width="13" customWidth="1" min="28" max="28"/>
+    <col width="12" customWidth="1" min="29" max="29"/>
+    <col width="5" customWidth="1" min="30" max="30"/>
+    <col width="5" customWidth="1" min="31" max="31"/>
+    <col width="5" customWidth="1" min="32" max="32"/>
+    <col width="5" customWidth="1" min="33" max="33"/>
+    <col width="5" customWidth="1" min="34" max="34"/>
+    <col width="5" customWidth="1" min="35" max="35"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -750,124 +759,204 @@
           <t>KI</t>
         </is>
       </c>
+      <c r="AB1" s="1" t="inlineStr">
+        <is>
+          <t>Date</t>
+        </is>
+      </c>
+      <c r="AC1" s="1" t="inlineStr">
+        <is>
+          <t>Module</t>
+        </is>
+      </c>
+      <c r="AD1" s="1" t="inlineStr">
+        <is>
+          <t>T</t>
+        </is>
+      </c>
+      <c r="AE1" s="1" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
+      <c r="AF1" s="1" t="inlineStr">
+        <is>
+          <t>S</t>
+        </is>
+      </c>
+      <c r="AG1" s="1" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
+      <c r="AH1" s="1" t="inlineStr">
+        <is>
+          <t>I</t>
+        </is>
+      </c>
+      <c r="AI1" s="1" t="inlineStr">
+        <is>
+          <t>KI</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
+          <t>07-May-2026</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>auth</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>254</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>186</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>62</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
           <t>06-May-2026</t>
         </is>
       </c>
-      <c r="B2" t="inlineStr">
+      <c r="K2" t="inlineStr">
         <is>
           <t>auth</t>
         </is>
       </c>
-      <c r="C2" t="inlineStr">
+      <c r="L2" t="inlineStr">
         <is>
           <t>254</t>
         </is>
       </c>
-      <c r="D2" t="inlineStr">
+      <c r="M2" t="inlineStr">
         <is>
           <t>142</t>
         </is>
       </c>
-      <c r="E2" t="inlineStr">
+      <c r="N2" t="inlineStr">
         <is>
           <t>72</t>
         </is>
       </c>
-      <c r="F2" t="inlineStr">
+      <c r="O2" t="inlineStr">
         <is>
           <t>40</t>
         </is>
       </c>
-      <c r="G2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="J2" t="inlineStr">
+      <c r="P2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Q2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="S2" t="inlineStr">
         <is>
           <t>05-May-2026</t>
         </is>
       </c>
-      <c r="K2" t="inlineStr">
+      <c r="T2" t="inlineStr">
         <is>
           <t>auth</t>
         </is>
       </c>
-      <c r="L2" t="inlineStr">
+      <c r="U2" t="inlineStr">
         <is>
           <t>254</t>
         </is>
       </c>
-      <c r="M2" t="inlineStr">
+      <c r="V2" t="inlineStr">
         <is>
           <t>142</t>
         </is>
       </c>
-      <c r="N2" t="inlineStr">
+      <c r="W2" t="inlineStr">
         <is>
           <t>72</t>
         </is>
       </c>
-      <c r="O2" t="inlineStr">
+      <c r="X2" t="inlineStr">
         <is>
           <t>40</t>
         </is>
       </c>
-      <c r="P2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="Q2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="S2" t="inlineStr">
+      <c r="Y2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Z2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB2" t="inlineStr">
         <is>
           <t>04-May-2026</t>
         </is>
       </c>
-      <c r="T2" t="inlineStr">
-        <is>
-          <t>auth</t>
-        </is>
-      </c>
-      <c r="U2" t="inlineStr">
-        <is>
-          <t>254</t>
-        </is>
-      </c>
-      <c r="V2" t="inlineStr">
-        <is>
-          <t>140</t>
-        </is>
-      </c>
-      <c r="W2" t="inlineStr">
-        <is>
-          <t>72</t>
-        </is>
-      </c>
-      <c r="X2" t="inlineStr">
-        <is>
-          <t>42</t>
-        </is>
-      </c>
-      <c r="Y2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="Z2" t="inlineStr">
+      <c r="AC2" t="inlineStr">
+        <is>
+          <t>esignet</t>
+        </is>
+      </c>
+      <c r="AD2" t="inlineStr">
+        <is>
+          <t>375</t>
+        </is>
+      </c>
+      <c r="AE2" t="inlineStr">
+        <is>
+          <t>264</t>
+        </is>
+      </c>
+      <c r="AF2" t="inlineStr">
+        <is>
+          <t>37</t>
+        </is>
+      </c>
+      <c r="AG2" t="inlineStr">
+        <is>
+          <t>47</t>
+        </is>
+      </c>
+      <c r="AH2" t="inlineStr">
+        <is>
+          <t>27</t>
+        </is>
+      </c>
+      <c r="AI2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
@@ -876,120 +965,160 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
+          <t>07-May-2026</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>esignet</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>375</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>270</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>42</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>36</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>27</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
           <t>06-May-2026</t>
         </is>
       </c>
-      <c r="B3" t="inlineStr">
+      <c r="K3" t="inlineStr">
         <is>
           <t>esignet</t>
         </is>
       </c>
-      <c r="C3" t="inlineStr">
+      <c r="L3" t="inlineStr">
         <is>
           <t>375</t>
         </is>
       </c>
-      <c r="D3" t="inlineStr">
+      <c r="M3" t="inlineStr">
         <is>
           <t>257</t>
         </is>
       </c>
-      <c r="E3" t="inlineStr">
+      <c r="N3" t="inlineStr">
         <is>
           <t>35</t>
         </is>
       </c>
-      <c r="F3" t="inlineStr">
+      <c r="O3" t="inlineStr">
         <is>
           <t>56</t>
         </is>
       </c>
-      <c r="G3" t="inlineStr">
+      <c r="P3" t="inlineStr">
         <is>
           <t>27</t>
         </is>
       </c>
-      <c r="H3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="J3" t="inlineStr">
+      <c r="Q3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="S3" t="inlineStr">
         <is>
           <t>05-May-2026</t>
         </is>
       </c>
-      <c r="K3" t="inlineStr">
+      <c r="T3" t="inlineStr">
         <is>
           <t>esignet</t>
         </is>
       </c>
-      <c r="L3" t="inlineStr">
+      <c r="U3" t="inlineStr">
         <is>
           <t>375</t>
         </is>
       </c>
-      <c r="M3" t="inlineStr">
+      <c r="V3" t="inlineStr">
         <is>
           <t>276</t>
         </is>
       </c>
-      <c r="N3" t="inlineStr">
+      <c r="W3" t="inlineStr">
         <is>
           <t>43</t>
         </is>
       </c>
-      <c r="O3" t="inlineStr">
+      <c r="X3" t="inlineStr">
         <is>
           <t>29</t>
         </is>
       </c>
-      <c r="P3" t="inlineStr">
+      <c r="Y3" t="inlineStr">
         <is>
           <t>27</t>
         </is>
       </c>
-      <c r="Q3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="S3" t="inlineStr">
+      <c r="Z3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB3" t="inlineStr">
         <is>
           <t>04-May-2026</t>
         </is>
       </c>
-      <c r="T3" t="inlineStr">
-        <is>
-          <t>esignet</t>
-        </is>
-      </c>
-      <c r="U3" t="inlineStr">
-        <is>
-          <t>375</t>
-        </is>
-      </c>
-      <c r="V3" t="inlineStr">
-        <is>
-          <t>264</t>
-        </is>
-      </c>
-      <c r="W3" t="inlineStr">
-        <is>
-          <t>37</t>
-        </is>
-      </c>
-      <c r="X3" t="inlineStr">
-        <is>
-          <t>47</t>
-        </is>
-      </c>
-      <c r="Y3" t="inlineStr">
-        <is>
-          <t>27</t>
-        </is>
-      </c>
-      <c r="Z3" t="inlineStr">
+      <c r="AC3" t="inlineStr">
+        <is>
+          <t>injiverify</t>
+        </is>
+      </c>
+      <c r="AD3" t="inlineStr">
+        <is>
+          <t>53</t>
+        </is>
+      </c>
+      <c r="AE3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AF3" t="inlineStr">
+        <is>
+          <t>23</t>
+        </is>
+      </c>
+      <c r="AG3" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="AH3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AI3" t="inlineStr">
         <is>
           <t>0</t>
         </is>
@@ -998,242 +1127,322 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
+          <t>07-May-2026</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>idrepo</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>152</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>101</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>51</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
           <t>06-May-2026</t>
         </is>
       </c>
-      <c r="B4" t="inlineStr">
+      <c r="K4" t="inlineStr">
         <is>
           <t>idrepo</t>
         </is>
       </c>
-      <c r="C4" t="inlineStr">
+      <c r="L4" t="inlineStr">
         <is>
           <t>152</t>
         </is>
       </c>
-      <c r="D4" t="inlineStr">
+      <c r="M4" t="inlineStr">
         <is>
           <t>101</t>
         </is>
       </c>
-      <c r="E4" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F4" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="G4" t="inlineStr">
+      <c r="N4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P4" t="inlineStr">
         <is>
           <t>51</t>
         </is>
       </c>
-      <c r="H4" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="J4" t="inlineStr">
+      <c r="Q4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="S4" t="inlineStr">
         <is>
           <t>05-May-2026</t>
         </is>
       </c>
-      <c r="K4" t="inlineStr">
+      <c r="T4" t="inlineStr">
         <is>
           <t>idrepo</t>
         </is>
       </c>
-      <c r="L4" t="inlineStr">
+      <c r="U4" t="inlineStr">
         <is>
           <t>152</t>
         </is>
       </c>
-      <c r="M4" t="inlineStr">
+      <c r="V4" t="inlineStr">
         <is>
           <t>101</t>
         </is>
       </c>
-      <c r="N4" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="O4" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="P4" t="inlineStr">
+      <c r="W4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="X4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Y4" t="inlineStr">
         <is>
           <t>51</t>
         </is>
       </c>
-      <c r="Q4" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="S4" t="inlineStr">
+      <c r="Z4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB4" t="inlineStr">
         <is>
           <t>04-May-2026</t>
         </is>
       </c>
-      <c r="T4" t="inlineStr">
-        <is>
-          <t>idrepo</t>
-        </is>
-      </c>
-      <c r="U4" t="inlineStr">
-        <is>
-          <t>152</t>
-        </is>
-      </c>
-      <c r="V4" t="inlineStr">
-        <is>
-          <t>101</t>
-        </is>
-      </c>
-      <c r="W4" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="X4" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="Y4" t="inlineStr">
-        <is>
-          <t>51</t>
-        </is>
-      </c>
-      <c r="Z4" t="inlineStr">
-        <is>
-          <t>0</t>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t>prereg</t>
+        </is>
+      </c>
+      <c r="AD4" t="inlineStr">
+        <is>
+          <t>104</t>
+        </is>
+      </c>
+      <c r="AE4" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AF4" t="inlineStr">
+        <is>
+          <t>70</t>
+        </is>
+      </c>
+      <c r="AG4" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="AH4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AI4" t="inlineStr">
+        <is>
+          <t>1</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
+          <t>07-May-2026</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>injiverify</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>53</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>23</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
           <t>06-May-2026</t>
         </is>
       </c>
-      <c r="B5" t="inlineStr">
+      <c r="K5" t="inlineStr">
         <is>
           <t>injiverify</t>
         </is>
       </c>
-      <c r="C5" t="inlineStr">
+      <c r="L5" t="inlineStr">
         <is>
           <t>53</t>
         </is>
       </c>
-      <c r="D5" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="E5" t="inlineStr">
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="N5" t="inlineStr">
         <is>
           <t>23</t>
         </is>
       </c>
-      <c r="F5" t="inlineStr">
+      <c r="O5" t="inlineStr">
         <is>
           <t>30</t>
         </is>
       </c>
-      <c r="G5" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H5" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="J5" t="inlineStr">
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Q5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="S5" t="inlineStr">
         <is>
           <t>05-May-2026</t>
         </is>
       </c>
-      <c r="K5" t="inlineStr">
+      <c r="T5" t="inlineStr">
         <is>
           <t>injiverify</t>
         </is>
       </c>
-      <c r="L5" t="inlineStr">
+      <c r="U5" t="inlineStr">
         <is>
           <t>53</t>
         </is>
       </c>
-      <c r="M5" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="N5" t="inlineStr">
+      <c r="V5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="W5" t="inlineStr">
         <is>
           <t>23</t>
         </is>
       </c>
-      <c r="O5" t="inlineStr">
+      <c r="X5" t="inlineStr">
         <is>
           <t>30</t>
         </is>
       </c>
-      <c r="P5" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="Q5" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="S5" t="inlineStr">
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Z5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB5" t="inlineStr">
         <is>
           <t>04-May-2026</t>
         </is>
       </c>
-      <c r="T5" t="inlineStr">
-        <is>
-          <t>injiverify</t>
-        </is>
-      </c>
-      <c r="U5" t="inlineStr">
-        <is>
-          <t>53</t>
-        </is>
-      </c>
-      <c r="V5" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="W5" t="inlineStr">
-        <is>
-          <t>23</t>
-        </is>
-      </c>
-      <c r="X5" t="inlineStr">
-        <is>
-          <t>30</t>
-        </is>
-      </c>
-      <c r="Y5" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="Z5" t="inlineStr">
+      <c r="AC5" t="inlineStr">
+        <is>
+          <t>residentui</t>
+        </is>
+      </c>
+      <c r="AD5" t="inlineStr">
+        <is>
+          <t>33</t>
+        </is>
+      </c>
+      <c r="AE5" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="AF5" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AG5" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="AH5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AI5" t="inlineStr">
         <is>
           <t>0</t>
         </is>
@@ -1242,358 +1451,406 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
+          <t>07-May-2026</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>mimoto</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>79</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>66</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
           <t>06-May-2026</t>
         </is>
       </c>
-      <c r="B6" t="inlineStr">
+      <c r="K6" t="inlineStr">
         <is>
           <t>mimoto</t>
         </is>
       </c>
-      <c r="C6" t="inlineStr">
+      <c r="L6" t="inlineStr">
         <is>
           <t>79</t>
         </is>
       </c>
-      <c r="D6" t="inlineStr">
+      <c r="M6" t="inlineStr">
         <is>
           <t>59</t>
         </is>
       </c>
-      <c r="E6" t="inlineStr">
+      <c r="N6" t="inlineStr">
         <is>
           <t>4</t>
         </is>
       </c>
-      <c r="F6" t="inlineStr">
+      <c r="O6" t="inlineStr">
         <is>
           <t>4</t>
         </is>
       </c>
-      <c r="G6" t="inlineStr">
+      <c r="P6" t="inlineStr">
         <is>
           <t>10</t>
         </is>
       </c>
-      <c r="H6" t="inlineStr">
+      <c r="Q6" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="J6" t="inlineStr">
+      <c r="S6" t="inlineStr">
         <is>
           <t>05-May-2026</t>
         </is>
       </c>
-      <c r="K6" t="inlineStr">
+      <c r="T6" t="inlineStr">
         <is>
           <t>mimoto</t>
         </is>
       </c>
-      <c r="L6" t="inlineStr">
+      <c r="U6" t="inlineStr">
         <is>
           <t>79</t>
         </is>
       </c>
-      <c r="M6" t="inlineStr">
+      <c r="V6" t="inlineStr">
         <is>
           <t>58</t>
         </is>
       </c>
-      <c r="N6" t="inlineStr">
+      <c r="W6" t="inlineStr">
         <is>
           <t>4</t>
         </is>
       </c>
-      <c r="O6" t="inlineStr">
+      <c r="X6" t="inlineStr">
         <is>
           <t>5</t>
         </is>
       </c>
-      <c r="P6" t="inlineStr">
+      <c r="Y6" t="inlineStr">
         <is>
           <t>10</t>
         </is>
       </c>
-      <c r="Q6" t="inlineStr">
+      <c r="Z6" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="S6" t="inlineStr">
-        <is>
-          <t>04-May-2026</t>
-        </is>
-      </c>
-      <c r="T6" t="inlineStr">
-        <is>
-          <t>mimoto</t>
-        </is>
-      </c>
-      <c r="U6" t="inlineStr">
-        <is>
-          <t>79</t>
-        </is>
-      </c>
-      <c r="V6" t="inlineStr">
-        <is>
-          <t>59</t>
-        </is>
-      </c>
-      <c r="W6" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="X6" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="Y6" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="Z6" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
+      <c r="AB6" t="n">
+        <v/>
+      </c>
+      <c r="AC6" t="n">
+        <v/>
+      </c>
+      <c r="AD6" t="n">
+        <v/>
+      </c>
+      <c r="AE6" t="n">
+        <v/>
+      </c>
+      <c r="AF6" t="n">
+        <v/>
+      </c>
+      <c r="AG6" t="n">
+        <v/>
+      </c>
+      <c r="AH6" t="n">
+        <v/>
+      </c>
+      <c r="AI6" t="n">
+        <v/>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
+          <t>07-May-2026</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>prereg</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>104</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>70</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
           <t>06-May-2026</t>
         </is>
       </c>
-      <c r="B7" t="inlineStr">
+      <c r="K7" t="inlineStr">
         <is>
           <t>prereg</t>
         </is>
       </c>
-      <c r="C7" t="inlineStr">
+      <c r="L7" t="inlineStr">
         <is>
           <t>104</t>
         </is>
       </c>
-      <c r="D7" t="inlineStr">
+      <c r="M7" t="inlineStr">
         <is>
           <t>3</t>
         </is>
       </c>
-      <c r="E7" t="inlineStr">
+      <c r="N7" t="inlineStr">
         <is>
           <t>70</t>
         </is>
       </c>
-      <c r="F7" t="inlineStr">
+      <c r="O7" t="inlineStr">
         <is>
           <t>30</t>
         </is>
       </c>
-      <c r="G7" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H7" t="inlineStr">
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Q7" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="J7" t="inlineStr">
+      <c r="S7" t="inlineStr">
         <is>
           <t>05-May-2026</t>
         </is>
       </c>
-      <c r="K7" t="inlineStr">
+      <c r="T7" t="inlineStr">
         <is>
           <t>prereg</t>
         </is>
       </c>
-      <c r="L7" t="inlineStr">
+      <c r="U7" t="inlineStr">
         <is>
           <t>104</t>
         </is>
       </c>
-      <c r="M7" t="inlineStr">
+      <c r="V7" t="inlineStr">
         <is>
           <t>3</t>
         </is>
       </c>
-      <c r="N7" t="inlineStr">
+      <c r="W7" t="inlineStr">
         <is>
           <t>70</t>
         </is>
       </c>
-      <c r="O7" t="inlineStr">
+      <c r="X7" t="inlineStr">
         <is>
           <t>30</t>
         </is>
       </c>
-      <c r="P7" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="Q7" t="inlineStr">
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Z7" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="S7" t="inlineStr">
-        <is>
-          <t>04-May-2026</t>
-        </is>
-      </c>
-      <c r="T7" t="inlineStr">
-        <is>
-          <t>prereg</t>
-        </is>
-      </c>
-      <c r="U7" t="inlineStr">
-        <is>
-          <t>104</t>
-        </is>
-      </c>
-      <c r="V7" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="W7" t="inlineStr">
-        <is>
-          <t>70</t>
-        </is>
-      </c>
-      <c r="X7" t="inlineStr">
-        <is>
-          <t>30</t>
-        </is>
-      </c>
-      <c r="Y7" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="Z7" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
+      <c r="AB7" t="n">
+        <v/>
+      </c>
+      <c r="AC7" t="n">
+        <v/>
+      </c>
+      <c r="AD7" t="n">
+        <v/>
+      </c>
+      <c r="AE7" t="n">
+        <v/>
+      </c>
+      <c r="AF7" t="n">
+        <v/>
+      </c>
+      <c r="AG7" t="n">
+        <v/>
+      </c>
+      <c r="AH7" t="n">
+        <v/>
+      </c>
+      <c r="AI7" t="n">
+        <v/>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
+          <t>07-May-2026</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>residentui</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>33</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
           <t>06-May-2026</t>
         </is>
       </c>
-      <c r="B8" t="inlineStr">
+      <c r="K8" t="inlineStr">
         <is>
           <t>residentui</t>
         </is>
       </c>
-      <c r="C8" t="inlineStr">
+      <c r="L8" t="inlineStr">
         <is>
           <t>33</t>
         </is>
       </c>
-      <c r="D8" t="inlineStr">
+      <c r="M8" t="inlineStr">
         <is>
           <t>12</t>
         </is>
       </c>
-      <c r="E8" t="inlineStr">
+      <c r="N8" t="inlineStr">
         <is>
           <t>5</t>
         </is>
       </c>
-      <c r="F8" t="inlineStr">
+      <c r="O8" t="inlineStr">
         <is>
           <t>16</t>
         </is>
       </c>
-      <c r="G8" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H8" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="J8" t="inlineStr">
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Q8" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="S8" t="inlineStr">
         <is>
           <t>05-May-2026</t>
         </is>
       </c>
-      <c r="K8" t="inlineStr">
+      <c r="T8" t="inlineStr">
         <is>
           <t>residentui</t>
         </is>
       </c>
-      <c r="L8" t="inlineStr">
+      <c r="U8" t="inlineStr">
         <is>
           <t>33</t>
         </is>
       </c>
-      <c r="M8" t="inlineStr">
+      <c r="V8" t="inlineStr">
         <is>
           <t>12</t>
         </is>
       </c>
-      <c r="N8" t="inlineStr">
+      <c r="W8" t="inlineStr">
         <is>
           <t>5</t>
         </is>
       </c>
-      <c r="O8" t="inlineStr">
+      <c r="X8" t="inlineStr">
         <is>
           <t>16</t>
         </is>
       </c>
-      <c r="P8" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="Q8" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="S8" t="inlineStr">
-        <is>
-          <t>04-May-2026</t>
-        </is>
-      </c>
-      <c r="T8" t="inlineStr">
-        <is>
-          <t>residentui</t>
-        </is>
-      </c>
-      <c r="U8" t="inlineStr">
-        <is>
-          <t>33</t>
-        </is>
-      </c>
-      <c r="V8" t="inlineStr">
-        <is>
-          <t>12</t>
-        </is>
-      </c>
-      <c r="W8" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="X8" t="inlineStr">
-        <is>
-          <t>16</t>
-        </is>
-      </c>
       <c r="Y8" t="inlineStr">
         <is>
           <t>0</t>
@@ -1603,6 +1860,30 @@
         <is>
           <t>0</t>
         </is>
+      </c>
+      <c r="AB8" t="n">
+        <v/>
+      </c>
+      <c r="AC8" t="n">
+        <v/>
+      </c>
+      <c r="AD8" t="n">
+        <v/>
+      </c>
+      <c r="AE8" t="n">
+        <v/>
+      </c>
+      <c r="AF8" t="n">
+        <v/>
+      </c>
+      <c r="AG8" t="n">
+        <v/>
+      </c>
+      <c r="AH8" t="n">
+        <v/>
+      </c>
+      <c r="AI8" t="n">
+        <v/>
       </c>
     </row>
   </sheetData>

--- a/minio-report-tracker/xlxs/collab.xlsx
+++ b/minio-report-tracker/xlxs/collab.xlsx
@@ -803,129 +803,129 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
+          <t>08-May-2026</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>auth</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>254</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>186</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>62</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
           <t>07-May-2026</t>
         </is>
       </c>
-      <c r="B2" t="inlineStr">
+      <c r="K2" t="inlineStr">
         <is>
           <t>auth</t>
         </is>
       </c>
-      <c r="C2" t="inlineStr">
+      <c r="L2" t="inlineStr">
         <is>
           <t>254</t>
         </is>
       </c>
-      <c r="D2" t="inlineStr">
+      <c r="M2" t="inlineStr">
         <is>
           <t>186</t>
         </is>
       </c>
-      <c r="E2" t="inlineStr">
+      <c r="N2" t="inlineStr">
         <is>
           <t>6</t>
         </is>
       </c>
-      <c r="F2" t="inlineStr">
+      <c r="O2" t="inlineStr">
         <is>
           <t>62</t>
         </is>
       </c>
-      <c r="G2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="J2" t="inlineStr">
+      <c r="P2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Q2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="S2" t="inlineStr">
         <is>
           <t>06-May-2026</t>
         </is>
       </c>
-      <c r="K2" t="inlineStr">
+      <c r="T2" t="inlineStr">
         <is>
           <t>auth</t>
         </is>
       </c>
-      <c r="L2" t="inlineStr">
+      <c r="U2" t="inlineStr">
         <is>
           <t>254</t>
         </is>
       </c>
-      <c r="M2" t="inlineStr">
+      <c r="V2" t="inlineStr">
         <is>
           <t>142</t>
         </is>
       </c>
-      <c r="N2" t="inlineStr">
+      <c r="W2" t="inlineStr">
         <is>
           <t>72</t>
         </is>
       </c>
-      <c r="O2" t="inlineStr">
+      <c r="X2" t="inlineStr">
         <is>
           <t>40</t>
         </is>
       </c>
-      <c r="P2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="Q2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="S2" t="inlineStr">
+      <c r="Y2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Z2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB2" t="inlineStr">
         <is>
           <t>05-May-2026</t>
         </is>
       </c>
-      <c r="T2" t="inlineStr">
-        <is>
-          <t>auth</t>
-        </is>
-      </c>
-      <c r="U2" t="inlineStr">
-        <is>
-          <t>254</t>
-        </is>
-      </c>
-      <c r="V2" t="inlineStr">
-        <is>
-          <t>142</t>
-        </is>
-      </c>
-      <c r="W2" t="inlineStr">
-        <is>
-          <t>72</t>
-        </is>
-      </c>
-      <c r="X2" t="inlineStr">
-        <is>
-          <t>40</t>
-        </is>
-      </c>
-      <c r="Y2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>04-May-2026</t>
-        </is>
-      </c>
       <c r="AC2" t="inlineStr">
         <is>
           <t>esignet</t>
@@ -938,17 +938,17 @@
       </c>
       <c r="AE2" t="inlineStr">
         <is>
-          <t>264</t>
+          <t>276</t>
         </is>
       </c>
       <c r="AF2" t="inlineStr">
         <is>
-          <t>37</t>
+          <t>43</t>
         </is>
       </c>
       <c r="AG2" t="inlineStr">
         <is>
-          <t>47</t>
+          <t>29</t>
         </is>
       </c>
       <c r="AH2" t="inlineStr">
@@ -965,127 +965,127 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
+          <t>08-May-2026</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>esignet</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>375</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>272</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>33</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>43</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>27</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
           <t>07-May-2026</t>
         </is>
       </c>
-      <c r="B3" t="inlineStr">
+      <c r="K3" t="inlineStr">
         <is>
           <t>esignet</t>
         </is>
       </c>
-      <c r="C3" t="inlineStr">
+      <c r="L3" t="inlineStr">
         <is>
           <t>375</t>
         </is>
       </c>
-      <c r="D3" t="inlineStr">
+      <c r="M3" t="inlineStr">
         <is>
           <t>270</t>
         </is>
       </c>
-      <c r="E3" t="inlineStr">
+      <c r="N3" t="inlineStr">
         <is>
           <t>42</t>
         </is>
       </c>
-      <c r="F3" t="inlineStr">
+      <c r="O3" t="inlineStr">
         <is>
           <t>36</t>
         </is>
       </c>
-      <c r="G3" t="inlineStr">
+      <c r="P3" t="inlineStr">
         <is>
           <t>27</t>
         </is>
       </c>
-      <c r="H3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="J3" t="inlineStr">
+      <c r="Q3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="S3" t="inlineStr">
         <is>
           <t>06-May-2026</t>
         </is>
       </c>
-      <c r="K3" t="inlineStr">
+      <c r="T3" t="inlineStr">
         <is>
           <t>esignet</t>
         </is>
       </c>
-      <c r="L3" t="inlineStr">
+      <c r="U3" t="inlineStr">
         <is>
           <t>375</t>
         </is>
       </c>
-      <c r="M3" t="inlineStr">
+      <c r="V3" t="inlineStr">
         <is>
           <t>257</t>
         </is>
       </c>
-      <c r="N3" t="inlineStr">
+      <c r="W3" t="inlineStr">
         <is>
           <t>35</t>
         </is>
       </c>
-      <c r="O3" t="inlineStr">
+      <c r="X3" t="inlineStr">
         <is>
           <t>56</t>
         </is>
       </c>
-      <c r="P3" t="inlineStr">
+      <c r="Y3" t="inlineStr">
         <is>
           <t>27</t>
         </is>
       </c>
-      <c r="Q3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="S3" t="inlineStr">
+      <c r="Z3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB3" t="inlineStr">
         <is>
           <t>05-May-2026</t>
-        </is>
-      </c>
-      <c r="T3" t="inlineStr">
-        <is>
-          <t>esignet</t>
-        </is>
-      </c>
-      <c r="U3" t="inlineStr">
-        <is>
-          <t>375</t>
-        </is>
-      </c>
-      <c r="V3" t="inlineStr">
-        <is>
-          <t>276</t>
-        </is>
-      </c>
-      <c r="W3" t="inlineStr">
-        <is>
-          <t>43</t>
-        </is>
-      </c>
-      <c r="X3" t="inlineStr">
-        <is>
-          <t>29</t>
-        </is>
-      </c>
-      <c r="Y3" t="inlineStr">
-        <is>
-          <t>27</t>
-        </is>
-      </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>04-May-2026</t>
         </is>
       </c>
       <c r="AC3" t="inlineStr">
@@ -1127,127 +1127,127 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
+          <t>08-May-2026</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>idrepo</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>152</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>101</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>51</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
           <t>07-May-2026</t>
         </is>
       </c>
-      <c r="B4" t="inlineStr">
+      <c r="K4" t="inlineStr">
         <is>
           <t>idrepo</t>
         </is>
       </c>
-      <c r="C4" t="inlineStr">
+      <c r="L4" t="inlineStr">
         <is>
           <t>152</t>
         </is>
       </c>
-      <c r="D4" t="inlineStr">
+      <c r="M4" t="inlineStr">
         <is>
           <t>101</t>
         </is>
       </c>
-      <c r="E4" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F4" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="G4" t="inlineStr">
+      <c r="N4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P4" t="inlineStr">
         <is>
           <t>51</t>
         </is>
       </c>
-      <c r="H4" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="J4" t="inlineStr">
+      <c r="Q4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="S4" t="inlineStr">
         <is>
           <t>06-May-2026</t>
         </is>
       </c>
-      <c r="K4" t="inlineStr">
+      <c r="T4" t="inlineStr">
         <is>
           <t>idrepo</t>
         </is>
       </c>
-      <c r="L4" t="inlineStr">
+      <c r="U4" t="inlineStr">
         <is>
           <t>152</t>
         </is>
       </c>
-      <c r="M4" t="inlineStr">
+      <c r="V4" t="inlineStr">
         <is>
           <t>101</t>
         </is>
       </c>
-      <c r="N4" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="O4" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="P4" t="inlineStr">
+      <c r="W4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="X4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Y4" t="inlineStr">
         <is>
           <t>51</t>
         </is>
       </c>
-      <c r="Q4" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="S4" t="inlineStr">
+      <c r="Z4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB4" t="inlineStr">
         <is>
           <t>05-May-2026</t>
-        </is>
-      </c>
-      <c r="T4" t="inlineStr">
-        <is>
-          <t>idrepo</t>
-        </is>
-      </c>
-      <c r="U4" t="inlineStr">
-        <is>
-          <t>152</t>
-        </is>
-      </c>
-      <c r="V4" t="inlineStr">
-        <is>
-          <t>101</t>
-        </is>
-      </c>
-      <c r="W4" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="X4" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="Y4" t="inlineStr">
-        <is>
-          <t>51</t>
-        </is>
-      </c>
-      <c r="Z4" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB4" t="inlineStr">
-        <is>
-          <t>04-May-2026</t>
         </is>
       </c>
       <c r="AC4" t="inlineStr">
@@ -1289,127 +1289,127 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
+          <t>08-May-2026</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>injiverify</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>53</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>23</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
           <t>07-May-2026</t>
         </is>
       </c>
-      <c r="B5" t="inlineStr">
+      <c r="K5" t="inlineStr">
         <is>
           <t>injiverify</t>
         </is>
       </c>
-      <c r="C5" t="inlineStr">
+      <c r="L5" t="inlineStr">
         <is>
           <t>53</t>
         </is>
       </c>
-      <c r="D5" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="E5" t="inlineStr">
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="N5" t="inlineStr">
         <is>
           <t>23</t>
         </is>
       </c>
-      <c r="F5" t="inlineStr">
+      <c r="O5" t="inlineStr">
         <is>
           <t>30</t>
         </is>
       </c>
-      <c r="G5" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H5" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="J5" t="inlineStr">
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Q5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="S5" t="inlineStr">
         <is>
           <t>06-May-2026</t>
         </is>
       </c>
-      <c r="K5" t="inlineStr">
+      <c r="T5" t="inlineStr">
         <is>
           <t>injiverify</t>
         </is>
       </c>
-      <c r="L5" t="inlineStr">
+      <c r="U5" t="inlineStr">
         <is>
           <t>53</t>
         </is>
       </c>
-      <c r="M5" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="N5" t="inlineStr">
+      <c r="V5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="W5" t="inlineStr">
         <is>
           <t>23</t>
         </is>
       </c>
-      <c r="O5" t="inlineStr">
+      <c r="X5" t="inlineStr">
         <is>
           <t>30</t>
         </is>
       </c>
-      <c r="P5" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="Q5" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="S5" t="inlineStr">
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Z5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB5" t="inlineStr">
         <is>
           <t>05-May-2026</t>
-        </is>
-      </c>
-      <c r="T5" t="inlineStr">
-        <is>
-          <t>injiverify</t>
-        </is>
-      </c>
-      <c r="U5" t="inlineStr">
-        <is>
-          <t>53</t>
-        </is>
-      </c>
-      <c r="V5" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="W5" t="inlineStr">
-        <is>
-          <t>23</t>
-        </is>
-      </c>
-      <c r="X5" t="inlineStr">
-        <is>
-          <t>30</t>
-        </is>
-      </c>
-      <c r="Y5" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="Z5" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB5" t="inlineStr">
-        <is>
-          <t>04-May-2026</t>
         </is>
       </c>
       <c r="AC5" t="inlineStr">
@@ -1451,112 +1451,112 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
+          <t>08-May-2026</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>mimoto</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>79</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>66</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
           <t>07-May-2026</t>
         </is>
       </c>
-      <c r="B6" t="inlineStr">
+      <c r="K6" t="inlineStr">
         <is>
           <t>mimoto</t>
         </is>
       </c>
-      <c r="C6" t="inlineStr">
+      <c r="L6" t="inlineStr">
         <is>
           <t>79</t>
         </is>
       </c>
-      <c r="D6" t="inlineStr">
+      <c r="M6" t="inlineStr">
         <is>
           <t>66</t>
         </is>
       </c>
-      <c r="E6" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F6" t="inlineStr">
+      <c r="N6" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O6" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="G6" t="inlineStr">
+      <c r="P6" t="inlineStr">
         <is>
           <t>10</t>
         </is>
       </c>
-      <c r="H6" t="inlineStr">
+      <c r="Q6" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="J6" t="inlineStr">
+      <c r="S6" t="inlineStr">
         <is>
           <t>06-May-2026</t>
         </is>
       </c>
-      <c r="K6" t="inlineStr">
+      <c r="T6" t="inlineStr">
         <is>
           <t>mimoto</t>
         </is>
       </c>
-      <c r="L6" t="inlineStr">
+      <c r="U6" t="inlineStr">
         <is>
           <t>79</t>
         </is>
       </c>
-      <c r="M6" t="inlineStr">
+      <c r="V6" t="inlineStr">
         <is>
           <t>59</t>
         </is>
       </c>
-      <c r="N6" t="inlineStr">
+      <c r="W6" t="inlineStr">
         <is>
           <t>4</t>
         </is>
       </c>
-      <c r="O6" t="inlineStr">
+      <c r="X6" t="inlineStr">
         <is>
           <t>4</t>
-        </is>
-      </c>
-      <c r="P6" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="Q6" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="S6" t="inlineStr">
-        <is>
-          <t>05-May-2026</t>
-        </is>
-      </c>
-      <c r="T6" t="inlineStr">
-        <is>
-          <t>mimoto</t>
-        </is>
-      </c>
-      <c r="U6" t="inlineStr">
-        <is>
-          <t>79</t>
-        </is>
-      </c>
-      <c r="V6" t="inlineStr">
-        <is>
-          <t>58</t>
-        </is>
-      </c>
-      <c r="W6" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="X6" t="inlineStr">
-        <is>
-          <t>5</t>
         </is>
       </c>
       <c r="Y6" t="inlineStr">
@@ -1597,87 +1597,87 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
+          <t>08-May-2026</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>prereg</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>104</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>70</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
           <t>07-May-2026</t>
         </is>
       </c>
-      <c r="B7" t="inlineStr">
+      <c r="K7" t="inlineStr">
         <is>
           <t>prereg</t>
         </is>
       </c>
-      <c r="C7" t="inlineStr">
+      <c r="L7" t="inlineStr">
         <is>
           <t>104</t>
         </is>
       </c>
-      <c r="D7" t="inlineStr">
+      <c r="M7" t="inlineStr">
         <is>
           <t>3</t>
         </is>
       </c>
-      <c r="E7" t="inlineStr">
+      <c r="N7" t="inlineStr">
         <is>
           <t>70</t>
         </is>
       </c>
-      <c r="F7" t="inlineStr">
+      <c r="O7" t="inlineStr">
         <is>
           <t>30</t>
         </is>
       </c>
-      <c r="G7" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H7" t="inlineStr">
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Q7" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="J7" t="inlineStr">
+      <c r="S7" t="inlineStr">
         <is>
           <t>06-May-2026</t>
-        </is>
-      </c>
-      <c r="K7" t="inlineStr">
-        <is>
-          <t>prereg</t>
-        </is>
-      </c>
-      <c r="L7" t="inlineStr">
-        <is>
-          <t>104</t>
-        </is>
-      </c>
-      <c r="M7" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="N7" t="inlineStr">
-        <is>
-          <t>70</t>
-        </is>
-      </c>
-      <c r="O7" t="inlineStr">
-        <is>
-          <t>30</t>
-        </is>
-      </c>
-      <c r="P7" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="Q7" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="S7" t="inlineStr">
-        <is>
-          <t>05-May-2026</t>
         </is>
       </c>
       <c r="T7" t="inlineStr">
@@ -1743,87 +1743,87 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
+          <t>08-May-2026</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>residentui</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>33</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
           <t>07-May-2026</t>
         </is>
       </c>
-      <c r="B8" t="inlineStr">
+      <c r="K8" t="inlineStr">
         <is>
           <t>residentui</t>
         </is>
       </c>
-      <c r="C8" t="inlineStr">
+      <c r="L8" t="inlineStr">
         <is>
           <t>33</t>
         </is>
       </c>
-      <c r="D8" t="inlineStr">
+      <c r="M8" t="inlineStr">
         <is>
           <t>12</t>
         </is>
       </c>
-      <c r="E8" t="inlineStr">
+      <c r="N8" t="inlineStr">
         <is>
           <t>5</t>
         </is>
       </c>
-      <c r="F8" t="inlineStr">
+      <c r="O8" t="inlineStr">
         <is>
           <t>16</t>
         </is>
       </c>
-      <c r="G8" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H8" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="J8" t="inlineStr">
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Q8" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="S8" t="inlineStr">
         <is>
           <t>06-May-2026</t>
-        </is>
-      </c>
-      <c r="K8" t="inlineStr">
-        <is>
-          <t>residentui</t>
-        </is>
-      </c>
-      <c r="L8" t="inlineStr">
-        <is>
-          <t>33</t>
-        </is>
-      </c>
-      <c r="M8" t="inlineStr">
-        <is>
-          <t>12</t>
-        </is>
-      </c>
-      <c r="N8" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="O8" t="inlineStr">
-        <is>
-          <t>16</t>
-        </is>
-      </c>
-      <c r="P8" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="Q8" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="S8" t="inlineStr">
-        <is>
-          <t>05-May-2026</t>
         </is>
       </c>
       <c r="T8" t="inlineStr">

--- a/minio-report-tracker/xlxs/collab.xlsx
+++ b/minio-report-tracker/xlxs/collab.xlsx
@@ -598,7 +598,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AI8"/>
+  <dimension ref="A1:Q8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -614,28 +614,10 @@
     <col width="12" customWidth="1" min="11" max="11"/>
     <col width="5" customWidth="1" min="12" max="12"/>
     <col width="5" customWidth="1" min="13" max="13"/>
-    <col width="4" customWidth="1" min="14" max="14"/>
-    <col width="4" customWidth="1" min="15" max="15"/>
-    <col width="4" customWidth="1" min="16" max="16"/>
-    <col width="4" customWidth="1" min="17" max="17"/>
-    <col width="2" customWidth="1" min="18" max="18"/>
-    <col width="13" customWidth="1" min="19" max="19"/>
-    <col width="12" customWidth="1" min="20" max="20"/>
-    <col width="5" customWidth="1" min="21" max="21"/>
-    <col width="5" customWidth="1" min="22" max="22"/>
-    <col width="4" customWidth="1" min="23" max="23"/>
-    <col width="4" customWidth="1" min="24" max="24"/>
-    <col width="4" customWidth="1" min="25" max="25"/>
-    <col width="4" customWidth="1" min="26" max="26"/>
-    <col width="2" customWidth="1" min="27" max="27"/>
-    <col width="13" customWidth="1" min="28" max="28"/>
-    <col width="12" customWidth="1" min="29" max="29"/>
-    <col width="5" customWidth="1" min="30" max="30"/>
-    <col width="5" customWidth="1" min="31" max="31"/>
-    <col width="5" customWidth="1" min="32" max="32"/>
-    <col width="5" customWidth="1" min="33" max="33"/>
-    <col width="5" customWidth="1" min="34" max="34"/>
-    <col width="5" customWidth="1" min="35" max="35"/>
+    <col width="5" customWidth="1" min="14" max="14"/>
+    <col width="5" customWidth="1" min="15" max="15"/>
+    <col width="5" customWidth="1" min="16" max="16"/>
+    <col width="5" customWidth="1" min="17" max="17"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -719,244 +701,84 @@
           <t>KI</t>
         </is>
       </c>
-      <c r="S1" s="1" t="inlineStr">
-        <is>
-          <t>Date</t>
-        </is>
-      </c>
-      <c r="T1" s="1" t="inlineStr">
-        <is>
-          <t>Module</t>
-        </is>
-      </c>
-      <c r="U1" s="1" t="inlineStr">
-        <is>
-          <t>T</t>
-        </is>
-      </c>
-      <c r="V1" s="1" t="inlineStr">
-        <is>
-          <t>P</t>
-        </is>
-      </c>
-      <c r="W1" s="1" t="inlineStr">
-        <is>
-          <t>S</t>
-        </is>
-      </c>
-      <c r="X1" s="1" t="inlineStr">
-        <is>
-          <t>F</t>
-        </is>
-      </c>
-      <c r="Y1" s="1" t="inlineStr">
-        <is>
-          <t>I</t>
-        </is>
-      </c>
-      <c r="Z1" s="1" t="inlineStr">
-        <is>
-          <t>KI</t>
-        </is>
-      </c>
-      <c r="AB1" s="1" t="inlineStr">
-        <is>
-          <t>Date</t>
-        </is>
-      </c>
-      <c r="AC1" s="1" t="inlineStr">
-        <is>
-          <t>Module</t>
-        </is>
-      </c>
-      <c r="AD1" s="1" t="inlineStr">
-        <is>
-          <t>T</t>
-        </is>
-      </c>
-      <c r="AE1" s="1" t="inlineStr">
-        <is>
-          <t>P</t>
-        </is>
-      </c>
-      <c r="AF1" s="1" t="inlineStr">
-        <is>
-          <t>S</t>
-        </is>
-      </c>
-      <c r="AG1" s="1" t="inlineStr">
-        <is>
-          <t>F</t>
-        </is>
-      </c>
-      <c r="AH1" s="1" t="inlineStr">
-        <is>
-          <t>I</t>
-        </is>
-      </c>
-      <c r="AI1" s="1" t="inlineStr">
-        <is>
-          <t>KI</t>
-        </is>
-      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
+          <t>11-May-2026</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>auth</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>254</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>186</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>62</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
           <t>08-May-2026</t>
         </is>
       </c>
-      <c r="B2" t="inlineStr">
-        <is>
-          <t>auth</t>
-        </is>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>254</t>
-        </is>
-      </c>
-      <c r="D2" t="inlineStr">
-        <is>
-          <t>186</t>
-        </is>
-      </c>
-      <c r="E2" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="F2" t="inlineStr">
-        <is>
-          <t>62</t>
-        </is>
-      </c>
-      <c r="G2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="J2" t="inlineStr">
-        <is>
-          <t>07-May-2026</t>
-        </is>
-      </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>auth</t>
+          <t>esignet</t>
         </is>
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>254</t>
+          <t>375</t>
         </is>
       </c>
       <c r="M2" t="inlineStr">
         <is>
-          <t>186</t>
+          <t>272</t>
         </is>
       </c>
       <c r="N2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>33</t>
         </is>
       </c>
       <c r="O2" t="inlineStr">
         <is>
-          <t>62</t>
+          <t>43</t>
         </is>
       </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>27</t>
         </is>
       </c>
       <c r="Q2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="S2" t="inlineStr">
-        <is>
-          <t>06-May-2026</t>
-        </is>
-      </c>
-      <c r="T2" t="inlineStr">
-        <is>
-          <t>auth</t>
-        </is>
-      </c>
-      <c r="U2" t="inlineStr">
-        <is>
-          <t>254</t>
-        </is>
-      </c>
-      <c r="V2" t="inlineStr">
-        <is>
-          <t>142</t>
-        </is>
-      </c>
-      <c r="W2" t="inlineStr">
-        <is>
-          <t>72</t>
-        </is>
-      </c>
-      <c r="X2" t="inlineStr">
-        <is>
-          <t>40</t>
-        </is>
-      </c>
-      <c r="Y2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>05-May-2026</t>
-        </is>
-      </c>
-      <c r="AC2" t="inlineStr">
-        <is>
-          <t>esignet</t>
-        </is>
-      </c>
-      <c r="AD2" t="inlineStr">
-        <is>
-          <t>375</t>
-        </is>
-      </c>
-      <c r="AE2" t="inlineStr">
-        <is>
-          <t>276</t>
-        </is>
-      </c>
-      <c r="AF2" t="inlineStr">
-        <is>
-          <t>43</t>
-        </is>
-      </c>
-      <c r="AG2" t="inlineStr">
-        <is>
-          <t>29</t>
-        </is>
-      </c>
-      <c r="AH2" t="inlineStr">
-        <is>
-          <t>27</t>
-        </is>
-      </c>
-      <c r="AI2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
@@ -965,160 +787,80 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
+          <t>11-May-2026</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>esignet</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>375</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>230</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>55</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>63</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>27</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
           <t>08-May-2026</t>
         </is>
       </c>
-      <c r="B3" t="inlineStr">
-        <is>
-          <t>esignet</t>
-        </is>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>375</t>
-        </is>
-      </c>
-      <c r="D3" t="inlineStr">
-        <is>
-          <t>272</t>
-        </is>
-      </c>
-      <c r="E3" t="inlineStr">
-        <is>
-          <t>33</t>
-        </is>
-      </c>
-      <c r="F3" t="inlineStr">
-        <is>
-          <t>43</t>
-        </is>
-      </c>
-      <c r="G3" t="inlineStr">
-        <is>
-          <t>27</t>
-        </is>
-      </c>
-      <c r="H3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="J3" t="inlineStr">
-        <is>
-          <t>07-May-2026</t>
-        </is>
-      </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>esignet</t>
+          <t>injiverify</t>
         </is>
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>375</t>
+          <t>53</t>
         </is>
       </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>270</t>
+          <t>0</t>
         </is>
       </c>
       <c r="N3" t="inlineStr">
         <is>
-          <t>42</t>
+          <t>23</t>
         </is>
       </c>
       <c r="O3" t="inlineStr">
         <is>
-          <t>36</t>
+          <t>30</t>
         </is>
       </c>
       <c r="P3" t="inlineStr">
         <is>
-          <t>27</t>
+          <t>0</t>
         </is>
       </c>
       <c r="Q3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="S3" t="inlineStr">
-        <is>
-          <t>06-May-2026</t>
-        </is>
-      </c>
-      <c r="T3" t="inlineStr">
-        <is>
-          <t>esignet</t>
-        </is>
-      </c>
-      <c r="U3" t="inlineStr">
-        <is>
-          <t>375</t>
-        </is>
-      </c>
-      <c r="V3" t="inlineStr">
-        <is>
-          <t>257</t>
-        </is>
-      </c>
-      <c r="W3" t="inlineStr">
-        <is>
-          <t>35</t>
-        </is>
-      </c>
-      <c r="X3" t="inlineStr">
-        <is>
-          <t>56</t>
-        </is>
-      </c>
-      <c r="Y3" t="inlineStr">
-        <is>
-          <t>27</t>
-        </is>
-      </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>05-May-2026</t>
-        </is>
-      </c>
-      <c r="AC3" t="inlineStr">
-        <is>
-          <t>injiverify</t>
-        </is>
-      </c>
-      <c r="AD3" t="inlineStr">
-        <is>
-          <t>53</t>
-        </is>
-      </c>
-      <c r="AE3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AF3" t="inlineStr">
-        <is>
-          <t>23</t>
-        </is>
-      </c>
-      <c r="AG3" t="inlineStr">
-        <is>
-          <t>30</t>
-        </is>
-      </c>
-      <c r="AH3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AI3" t="inlineStr">
         <is>
           <t>0</t>
         </is>
@@ -1127,160 +869,80 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
+          <t>11-May-2026</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>idrepo</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>152</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>101</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>51</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
           <t>08-May-2026</t>
         </is>
       </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>idrepo</t>
-        </is>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>152</t>
-        </is>
-      </c>
-      <c r="D4" t="inlineStr">
-        <is>
-          <t>101</t>
-        </is>
-      </c>
-      <c r="E4" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F4" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="G4" t="inlineStr">
-        <is>
-          <t>51</t>
-        </is>
-      </c>
-      <c r="H4" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="J4" t="inlineStr">
-        <is>
-          <t>07-May-2026</t>
-        </is>
-      </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>idrepo</t>
+          <t>prereg</t>
         </is>
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>152</t>
+          <t>104</t>
         </is>
       </c>
       <c r="M4" t="inlineStr">
         <is>
-          <t>101</t>
+          <t>3</t>
         </is>
       </c>
       <c r="N4" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>70</t>
         </is>
       </c>
       <c r="O4" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>30</t>
         </is>
       </c>
       <c r="P4" t="inlineStr">
         <is>
-          <t>51</t>
+          <t>0</t>
         </is>
       </c>
       <c r="Q4" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="S4" t="inlineStr">
-        <is>
-          <t>06-May-2026</t>
-        </is>
-      </c>
-      <c r="T4" t="inlineStr">
-        <is>
-          <t>idrepo</t>
-        </is>
-      </c>
-      <c r="U4" t="inlineStr">
-        <is>
-          <t>152</t>
-        </is>
-      </c>
-      <c r="V4" t="inlineStr">
-        <is>
-          <t>101</t>
-        </is>
-      </c>
-      <c r="W4" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="X4" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="Y4" t="inlineStr">
-        <is>
-          <t>51</t>
-        </is>
-      </c>
-      <c r="Z4" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB4" t="inlineStr">
-        <is>
-          <t>05-May-2026</t>
-        </is>
-      </c>
-      <c r="AC4" t="inlineStr">
-        <is>
-          <t>prereg</t>
-        </is>
-      </c>
-      <c r="AD4" t="inlineStr">
-        <is>
-          <t>104</t>
-        </is>
-      </c>
-      <c r="AE4" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="AF4" t="inlineStr">
-        <is>
-          <t>70</t>
-        </is>
-      </c>
-      <c r="AG4" t="inlineStr">
-        <is>
-          <t>30</t>
-        </is>
-      </c>
-      <c r="AH4" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AI4" t="inlineStr">
         <is>
           <t>1</t>
         </is>
@@ -1289,72 +951,72 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
+          <t>11-May-2026</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>injiverify</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>53</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>23</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
           <t>08-May-2026</t>
         </is>
       </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>injiverify</t>
-        </is>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>53</t>
-        </is>
-      </c>
-      <c r="D5" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="E5" t="inlineStr">
-        <is>
-          <t>23</t>
-        </is>
-      </c>
-      <c r="F5" t="inlineStr">
-        <is>
-          <t>30</t>
-        </is>
-      </c>
-      <c r="G5" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H5" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="J5" t="inlineStr">
-        <is>
-          <t>07-May-2026</t>
-        </is>
-      </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>injiverify</t>
+          <t>residentui</t>
         </is>
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>53</t>
+          <t>33</t>
         </is>
       </c>
       <c r="M5" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>12</t>
         </is>
       </c>
       <c r="N5" t="inlineStr">
         <is>
-          <t>23</t>
+          <t>5</t>
         </is>
       </c>
       <c r="O5" t="inlineStr">
         <is>
-          <t>30</t>
+          <t>16</t>
         </is>
       </c>
       <c r="P5" t="inlineStr">
@@ -1363,86 +1025,6 @@
         </is>
       </c>
       <c r="Q5" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="S5" t="inlineStr">
-        <is>
-          <t>06-May-2026</t>
-        </is>
-      </c>
-      <c r="T5" t="inlineStr">
-        <is>
-          <t>injiverify</t>
-        </is>
-      </c>
-      <c r="U5" t="inlineStr">
-        <is>
-          <t>53</t>
-        </is>
-      </c>
-      <c r="V5" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="W5" t="inlineStr">
-        <is>
-          <t>23</t>
-        </is>
-      </c>
-      <c r="X5" t="inlineStr">
-        <is>
-          <t>30</t>
-        </is>
-      </c>
-      <c r="Y5" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="Z5" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB5" t="inlineStr">
-        <is>
-          <t>05-May-2026</t>
-        </is>
-      </c>
-      <c r="AC5" t="inlineStr">
-        <is>
-          <t>residentui</t>
-        </is>
-      </c>
-      <c r="AD5" t="inlineStr">
-        <is>
-          <t>33</t>
-        </is>
-      </c>
-      <c r="AE5" t="inlineStr">
-        <is>
-          <t>12</t>
-        </is>
-      </c>
-      <c r="AF5" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="AG5" t="inlineStr">
-        <is>
-          <t>16</t>
-        </is>
-      </c>
-      <c r="AH5" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AI5" t="inlineStr">
         <is>
           <t>0</t>
         </is>
@@ -1451,7 +1033,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>08-May-2026</t>
+          <t>11-May-2026</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -1466,7 +1048,7 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>66</t>
+          <t>64</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -1476,7 +1058,7 @@
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>3</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
@@ -1489,115 +1071,35 @@
           <t>2</t>
         </is>
       </c>
-      <c r="J6" t="inlineStr">
-        <is>
-          <t>07-May-2026</t>
-        </is>
-      </c>
-      <c r="K6" t="inlineStr">
-        <is>
-          <t>mimoto</t>
-        </is>
-      </c>
-      <c r="L6" t="inlineStr">
-        <is>
-          <t>79</t>
-        </is>
-      </c>
-      <c r="M6" t="inlineStr">
-        <is>
-          <t>66</t>
-        </is>
-      </c>
-      <c r="N6" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="O6" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="P6" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="Q6" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="S6" t="inlineStr">
-        <is>
-          <t>06-May-2026</t>
-        </is>
-      </c>
-      <c r="T6" t="inlineStr">
-        <is>
-          <t>mimoto</t>
-        </is>
-      </c>
-      <c r="U6" t="inlineStr">
-        <is>
-          <t>79</t>
-        </is>
-      </c>
-      <c r="V6" t="inlineStr">
-        <is>
-          <t>59</t>
-        </is>
-      </c>
-      <c r="W6" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="X6" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="Y6" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="Z6" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="AB6" t="n">
-        <v/>
-      </c>
-      <c r="AC6" t="n">
-        <v/>
-      </c>
-      <c r="AD6" t="n">
-        <v/>
-      </c>
-      <c r="AE6" t="n">
-        <v/>
-      </c>
-      <c r="AF6" t="n">
-        <v/>
-      </c>
-      <c r="AG6" t="n">
-        <v/>
-      </c>
-      <c r="AH6" t="n">
-        <v/>
-      </c>
-      <c r="AI6" t="n">
+      <c r="J6" t="n">
+        <v/>
+      </c>
+      <c r="K6" t="n">
+        <v/>
+      </c>
+      <c r="L6" t="n">
+        <v/>
+      </c>
+      <c r="M6" t="n">
+        <v/>
+      </c>
+      <c r="N6" t="n">
+        <v/>
+      </c>
+      <c r="O6" t="n">
+        <v/>
+      </c>
+      <c r="P6" t="n">
+        <v/>
+      </c>
+      <c r="Q6" t="n">
         <v/>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>08-May-2026</t>
+          <t>11-May-2026</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -1635,115 +1137,35 @@
           <t>1</t>
         </is>
       </c>
-      <c r="J7" t="inlineStr">
-        <is>
-          <t>07-May-2026</t>
-        </is>
-      </c>
-      <c r="K7" t="inlineStr">
-        <is>
-          <t>prereg</t>
-        </is>
-      </c>
-      <c r="L7" t="inlineStr">
-        <is>
-          <t>104</t>
-        </is>
-      </c>
-      <c r="M7" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="N7" t="inlineStr">
-        <is>
-          <t>70</t>
-        </is>
-      </c>
-      <c r="O7" t="inlineStr">
-        <is>
-          <t>30</t>
-        </is>
-      </c>
-      <c r="P7" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="Q7" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="S7" t="inlineStr">
-        <is>
-          <t>06-May-2026</t>
-        </is>
-      </c>
-      <c r="T7" t="inlineStr">
-        <is>
-          <t>prereg</t>
-        </is>
-      </c>
-      <c r="U7" t="inlineStr">
-        <is>
-          <t>104</t>
-        </is>
-      </c>
-      <c r="V7" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="W7" t="inlineStr">
-        <is>
-          <t>70</t>
-        </is>
-      </c>
-      <c r="X7" t="inlineStr">
-        <is>
-          <t>30</t>
-        </is>
-      </c>
-      <c r="Y7" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="Z7" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="AB7" t="n">
-        <v/>
-      </c>
-      <c r="AC7" t="n">
-        <v/>
-      </c>
-      <c r="AD7" t="n">
-        <v/>
-      </c>
-      <c r="AE7" t="n">
-        <v/>
-      </c>
-      <c r="AF7" t="n">
-        <v/>
-      </c>
-      <c r="AG7" t="n">
-        <v/>
-      </c>
-      <c r="AH7" t="n">
-        <v/>
-      </c>
-      <c r="AI7" t="n">
+      <c r="J7" t="n">
+        <v/>
+      </c>
+      <c r="K7" t="n">
+        <v/>
+      </c>
+      <c r="L7" t="n">
+        <v/>
+      </c>
+      <c r="M7" t="n">
+        <v/>
+      </c>
+      <c r="N7" t="n">
+        <v/>
+      </c>
+      <c r="O7" t="n">
+        <v/>
+      </c>
+      <c r="P7" t="n">
+        <v/>
+      </c>
+      <c r="Q7" t="n">
         <v/>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>08-May-2026</t>
+          <t>11-May-2026</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1781,108 +1203,28 @@
           <t>0</t>
         </is>
       </c>
-      <c r="J8" t="inlineStr">
-        <is>
-          <t>07-May-2026</t>
-        </is>
-      </c>
-      <c r="K8" t="inlineStr">
-        <is>
-          <t>residentui</t>
-        </is>
-      </c>
-      <c r="L8" t="inlineStr">
-        <is>
-          <t>33</t>
-        </is>
-      </c>
-      <c r="M8" t="inlineStr">
-        <is>
-          <t>12</t>
-        </is>
-      </c>
-      <c r="N8" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="O8" t="inlineStr">
-        <is>
-          <t>16</t>
-        </is>
-      </c>
-      <c r="P8" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="Q8" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="S8" t="inlineStr">
-        <is>
-          <t>06-May-2026</t>
-        </is>
-      </c>
-      <c r="T8" t="inlineStr">
-        <is>
-          <t>residentui</t>
-        </is>
-      </c>
-      <c r="U8" t="inlineStr">
-        <is>
-          <t>33</t>
-        </is>
-      </c>
-      <c r="V8" t="inlineStr">
-        <is>
-          <t>12</t>
-        </is>
-      </c>
-      <c r="W8" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="X8" t="inlineStr">
-        <is>
-          <t>16</t>
-        </is>
-      </c>
-      <c r="Y8" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="Z8" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB8" t="n">
-        <v/>
-      </c>
-      <c r="AC8" t="n">
-        <v/>
-      </c>
-      <c r="AD8" t="n">
-        <v/>
-      </c>
-      <c r="AE8" t="n">
-        <v/>
-      </c>
-      <c r="AF8" t="n">
-        <v/>
-      </c>
-      <c r="AG8" t="n">
-        <v/>
-      </c>
-      <c r="AH8" t="n">
-        <v/>
-      </c>
-      <c r="AI8" t="n">
+      <c r="J8" t="n">
+        <v/>
+      </c>
+      <c r="K8" t="n">
+        <v/>
+      </c>
+      <c r="L8" t="n">
+        <v/>
+      </c>
+      <c r="M8" t="n">
+        <v/>
+      </c>
+      <c r="N8" t="n">
+        <v/>
+      </c>
+      <c r="O8" t="n">
+        <v/>
+      </c>
+      <c r="P8" t="n">
+        <v/>
+      </c>
+      <c r="Q8" t="n">
         <v/>
       </c>
     </row>

--- a/minio-report-tracker/xlxs/collab.xlsx
+++ b/minio-report-tracker/xlxs/collab.xlsx
@@ -614,10 +614,10 @@
     <col width="12" customWidth="1" min="11" max="11"/>
     <col width="5" customWidth="1" min="12" max="12"/>
     <col width="5" customWidth="1" min="13" max="13"/>
-    <col width="5" customWidth="1" min="14" max="14"/>
-    <col width="5" customWidth="1" min="15" max="15"/>
-    <col width="5" customWidth="1" min="16" max="16"/>
-    <col width="5" customWidth="1" min="17" max="17"/>
+    <col width="4" customWidth="1" min="14" max="14"/>
+    <col width="4" customWidth="1" min="15" max="15"/>
+    <col width="4" customWidth="1" min="16" max="16"/>
+    <col width="4" customWidth="1" min="17" max="17"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -705,77 +705,77 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
+          <t>12-May-2026</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>auth</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>254</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>186</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>62</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
           <t>11-May-2026</t>
         </is>
       </c>
-      <c r="B2" t="inlineStr">
+      <c r="K2" t="inlineStr">
         <is>
           <t>auth</t>
         </is>
       </c>
-      <c r="C2" t="inlineStr">
+      <c r="L2" t="inlineStr">
         <is>
           <t>254</t>
         </is>
       </c>
-      <c r="D2" t="inlineStr">
+      <c r="M2" t="inlineStr">
         <is>
           <t>186</t>
         </is>
       </c>
-      <c r="E2" t="inlineStr">
+      <c r="N2" t="inlineStr">
         <is>
           <t>6</t>
         </is>
       </c>
-      <c r="F2" t="inlineStr">
+      <c r="O2" t="inlineStr">
         <is>
           <t>62</t>
         </is>
       </c>
-      <c r="G2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="J2" t="inlineStr">
-        <is>
-          <t>08-May-2026</t>
-        </is>
-      </c>
-      <c r="K2" t="inlineStr">
-        <is>
-          <t>esignet</t>
-        </is>
-      </c>
-      <c r="L2" t="inlineStr">
-        <is>
-          <t>375</t>
-        </is>
-      </c>
-      <c r="M2" t="inlineStr">
-        <is>
-          <t>272</t>
-        </is>
-      </c>
-      <c r="N2" t="inlineStr">
-        <is>
-          <t>33</t>
-        </is>
-      </c>
-      <c r="O2" t="inlineStr">
-        <is>
-          <t>43</t>
-        </is>
-      </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>27</t>
+          <t>0</t>
         </is>
       </c>
       <c r="Q2" t="inlineStr">
@@ -787,77 +787,77 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
+          <t>12-May-2026</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>esignet</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>375</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>231</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>40</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>77</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>27</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
           <t>11-May-2026</t>
         </is>
       </c>
-      <c r="B3" t="inlineStr">
+      <c r="K3" t="inlineStr">
         <is>
           <t>esignet</t>
         </is>
       </c>
-      <c r="C3" t="inlineStr">
+      <c r="L3" t="inlineStr">
         <is>
           <t>375</t>
         </is>
       </c>
-      <c r="D3" t="inlineStr">
+      <c r="M3" t="inlineStr">
         <is>
           <t>230</t>
         </is>
       </c>
-      <c r="E3" t="inlineStr">
+      <c r="N3" t="inlineStr">
         <is>
           <t>55</t>
         </is>
       </c>
-      <c r="F3" t="inlineStr">
+      <c r="O3" t="inlineStr">
         <is>
           <t>63</t>
         </is>
       </c>
-      <c r="G3" t="inlineStr">
+      <c r="P3" t="inlineStr">
         <is>
           <t>27</t>
-        </is>
-      </c>
-      <c r="H3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="J3" t="inlineStr">
-        <is>
-          <t>08-May-2026</t>
-        </is>
-      </c>
-      <c r="K3" t="inlineStr">
-        <is>
-          <t>injiverify</t>
-        </is>
-      </c>
-      <c r="L3" t="inlineStr">
-        <is>
-          <t>53</t>
-        </is>
-      </c>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="N3" t="inlineStr">
-        <is>
-          <t>23</t>
-        </is>
-      </c>
-      <c r="O3" t="inlineStr">
-        <is>
-          <t>30</t>
-        </is>
-      </c>
-      <c r="P3" t="inlineStr">
-        <is>
-          <t>0</t>
         </is>
       </c>
       <c r="Q3" t="inlineStr">
@@ -869,154 +869,154 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
+          <t>12-May-2026</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>idrepo</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>152</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>51</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
           <t>11-May-2026</t>
         </is>
       </c>
-      <c r="B4" t="inlineStr">
+      <c r="K4" t="inlineStr">
         <is>
           <t>idrepo</t>
         </is>
       </c>
-      <c r="C4" t="inlineStr">
+      <c r="L4" t="inlineStr">
         <is>
           <t>152</t>
         </is>
       </c>
-      <c r="D4" t="inlineStr">
+      <c r="M4" t="inlineStr">
         <is>
           <t>101</t>
         </is>
       </c>
-      <c r="E4" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F4" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="G4" t="inlineStr">
+      <c r="N4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P4" t="inlineStr">
         <is>
           <t>51</t>
         </is>
       </c>
-      <c r="H4" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="J4" t="inlineStr">
-        <is>
-          <t>08-May-2026</t>
-        </is>
-      </c>
-      <c r="K4" t="inlineStr">
-        <is>
-          <t>prereg</t>
-        </is>
-      </c>
-      <c r="L4" t="inlineStr">
-        <is>
-          <t>104</t>
-        </is>
-      </c>
-      <c r="M4" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="N4" t="inlineStr">
-        <is>
-          <t>70</t>
-        </is>
-      </c>
-      <c r="O4" t="inlineStr">
-        <is>
-          <t>30</t>
-        </is>
-      </c>
-      <c r="P4" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
       <c r="Q4" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
+          <t>12-May-2026</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>injiverify</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>53</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>23</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
           <t>11-May-2026</t>
         </is>
       </c>
-      <c r="B5" t="inlineStr">
+      <c r="K5" t="inlineStr">
         <is>
           <t>injiverify</t>
         </is>
       </c>
-      <c r="C5" t="inlineStr">
+      <c r="L5" t="inlineStr">
         <is>
           <t>53</t>
         </is>
       </c>
-      <c r="D5" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="E5" t="inlineStr">
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="N5" t="inlineStr">
         <is>
           <t>23</t>
         </is>
       </c>
-      <c r="F5" t="inlineStr">
+      <c r="O5" t="inlineStr">
         <is>
           <t>30</t>
-        </is>
-      </c>
-      <c r="G5" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H5" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="J5" t="inlineStr">
-        <is>
-          <t>08-May-2026</t>
-        </is>
-      </c>
-      <c r="K5" t="inlineStr">
-        <is>
-          <t>residentui</t>
-        </is>
-      </c>
-      <c r="L5" t="inlineStr">
-        <is>
-          <t>33</t>
-        </is>
-      </c>
-      <c r="M5" t="inlineStr">
-        <is>
-          <t>12</t>
-        </is>
-      </c>
-      <c r="N5" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="O5" t="inlineStr">
-        <is>
-          <t>16</t>
         </is>
       </c>
       <c r="P5" t="inlineStr">
@@ -1033,199 +1033,247 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
+          <t>12-May-2026</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>mimoto</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>79</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>58</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
           <t>11-May-2026</t>
         </is>
       </c>
-      <c r="B6" t="inlineStr">
+      <c r="K6" t="inlineStr">
         <is>
           <t>mimoto</t>
         </is>
       </c>
-      <c r="C6" t="inlineStr">
+      <c r="L6" t="inlineStr">
         <is>
           <t>79</t>
         </is>
       </c>
-      <c r="D6" t="inlineStr">
+      <c r="M6" t="inlineStr">
         <is>
           <t>64</t>
         </is>
       </c>
-      <c r="E6" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F6" t="inlineStr">
+      <c r="N6" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O6" t="inlineStr">
         <is>
           <t>3</t>
         </is>
       </c>
-      <c r="G6" t="inlineStr">
+      <c r="P6" t="inlineStr">
         <is>
           <t>10</t>
         </is>
       </c>
-      <c r="H6" t="inlineStr">
+      <c r="Q6" t="inlineStr">
         <is>
           <t>2</t>
         </is>
-      </c>
-      <c r="J6" t="n">
-        <v/>
-      </c>
-      <c r="K6" t="n">
-        <v/>
-      </c>
-      <c r="L6" t="n">
-        <v/>
-      </c>
-      <c r="M6" t="n">
-        <v/>
-      </c>
-      <c r="N6" t="n">
-        <v/>
-      </c>
-      <c r="O6" t="n">
-        <v/>
-      </c>
-      <c r="P6" t="n">
-        <v/>
-      </c>
-      <c r="Q6" t="n">
-        <v/>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
+          <t>12-May-2026</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>prereg</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>104</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>70</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
           <t>11-May-2026</t>
         </is>
       </c>
-      <c r="B7" t="inlineStr">
+      <c r="K7" t="inlineStr">
         <is>
           <t>prereg</t>
         </is>
       </c>
-      <c r="C7" t="inlineStr">
+      <c r="L7" t="inlineStr">
         <is>
           <t>104</t>
         </is>
       </c>
-      <c r="D7" t="inlineStr">
+      <c r="M7" t="inlineStr">
         <is>
           <t>3</t>
         </is>
       </c>
-      <c r="E7" t="inlineStr">
+      <c r="N7" t="inlineStr">
         <is>
           <t>70</t>
         </is>
       </c>
-      <c r="F7" t="inlineStr">
+      <c r="O7" t="inlineStr">
         <is>
           <t>30</t>
         </is>
       </c>
-      <c r="G7" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H7" t="inlineStr">
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Q7" t="inlineStr">
         <is>
           <t>1</t>
         </is>
-      </c>
-      <c r="J7" t="n">
-        <v/>
-      </c>
-      <c r="K7" t="n">
-        <v/>
-      </c>
-      <c r="L7" t="n">
-        <v/>
-      </c>
-      <c r="M7" t="n">
-        <v/>
-      </c>
-      <c r="N7" t="n">
-        <v/>
-      </c>
-      <c r="O7" t="n">
-        <v/>
-      </c>
-      <c r="P7" t="n">
-        <v/>
-      </c>
-      <c r="Q7" t="n">
-        <v/>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
+          <t>12-May-2026</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>residentui</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>33</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
           <t>11-May-2026</t>
         </is>
       </c>
-      <c r="B8" t="inlineStr">
+      <c r="K8" t="inlineStr">
         <is>
           <t>residentui</t>
         </is>
       </c>
-      <c r="C8" t="inlineStr">
+      <c r="L8" t="inlineStr">
         <is>
           <t>33</t>
         </is>
       </c>
-      <c r="D8" t="inlineStr">
+      <c r="M8" t="inlineStr">
         <is>
           <t>12</t>
         </is>
       </c>
-      <c r="E8" t="inlineStr">
+      <c r="N8" t="inlineStr">
         <is>
           <t>5</t>
         </is>
       </c>
-      <c r="F8" t="inlineStr">
+      <c r="O8" t="inlineStr">
         <is>
           <t>16</t>
         </is>
       </c>
-      <c r="G8" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H8" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="J8" t="n">
-        <v/>
-      </c>
-      <c r="K8" t="n">
-        <v/>
-      </c>
-      <c r="L8" t="n">
-        <v/>
-      </c>
-      <c r="M8" t="n">
-        <v/>
-      </c>
-      <c r="N8" t="n">
-        <v/>
-      </c>
-      <c r="O8" t="n">
-        <v/>
-      </c>
-      <c r="P8" t="n">
-        <v/>
-      </c>
-      <c r="Q8" t="n">
-        <v/>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Q8" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
     </row>
   </sheetData>

--- a/minio-report-tracker/xlxs/collab.xlsx
+++ b/minio-report-tracker/xlxs/collab.xlsx
@@ -598,7 +598,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q8"/>
+  <dimension ref="A1:Z8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -618,6 +618,15 @@
     <col width="4" customWidth="1" min="15" max="15"/>
     <col width="4" customWidth="1" min="16" max="16"/>
     <col width="4" customWidth="1" min="17" max="17"/>
+    <col width="2" customWidth="1" min="18" max="18"/>
+    <col width="13" customWidth="1" min="19" max="19"/>
+    <col width="12" customWidth="1" min="20" max="20"/>
+    <col width="5" customWidth="1" min="21" max="21"/>
+    <col width="5" customWidth="1" min="22" max="22"/>
+    <col width="4" customWidth="1" min="23" max="23"/>
+    <col width="4" customWidth="1" min="24" max="24"/>
+    <col width="4" customWidth="1" min="25" max="25"/>
+    <col width="4" customWidth="1" min="26" max="26"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -701,84 +710,164 @@
           <t>KI</t>
         </is>
       </c>
+      <c r="S1" s="1" t="inlineStr">
+        <is>
+          <t>Date</t>
+        </is>
+      </c>
+      <c r="T1" s="1" t="inlineStr">
+        <is>
+          <t>Module</t>
+        </is>
+      </c>
+      <c r="U1" s="1" t="inlineStr">
+        <is>
+          <t>T</t>
+        </is>
+      </c>
+      <c r="V1" s="1" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
+      <c r="W1" s="1" t="inlineStr">
+        <is>
+          <t>S</t>
+        </is>
+      </c>
+      <c r="X1" s="1" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
+      <c r="Y1" s="1" t="inlineStr">
+        <is>
+          <t>I</t>
+        </is>
+      </c>
+      <c r="Z1" s="1" t="inlineStr">
+        <is>
+          <t>KI</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
+          <t>13-May-2026</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>auth</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>254</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>140</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>72</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>42</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
           <t>12-May-2026</t>
         </is>
       </c>
-      <c r="B2" t="inlineStr">
+      <c r="K2" t="inlineStr">
         <is>
           <t>auth</t>
         </is>
       </c>
-      <c r="C2" t="inlineStr">
+      <c r="L2" t="inlineStr">
         <is>
           <t>254</t>
         </is>
       </c>
-      <c r="D2" t="inlineStr">
+      <c r="M2" t="inlineStr">
         <is>
           <t>186</t>
         </is>
       </c>
-      <c r="E2" t="inlineStr">
+      <c r="N2" t="inlineStr">
         <is>
           <t>6</t>
         </is>
       </c>
-      <c r="F2" t="inlineStr">
+      <c r="O2" t="inlineStr">
         <is>
           <t>62</t>
         </is>
       </c>
-      <c r="G2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="J2" t="inlineStr">
+      <c r="P2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Q2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="S2" t="inlineStr">
         <is>
           <t>11-May-2026</t>
         </is>
       </c>
-      <c r="K2" t="inlineStr">
+      <c r="T2" t="inlineStr">
         <is>
           <t>auth</t>
         </is>
       </c>
-      <c r="L2" t="inlineStr">
+      <c r="U2" t="inlineStr">
         <is>
           <t>254</t>
         </is>
       </c>
-      <c r="M2" t="inlineStr">
+      <c r="V2" t="inlineStr">
         <is>
           <t>186</t>
         </is>
       </c>
-      <c r="N2" t="inlineStr">
+      <c r="W2" t="inlineStr">
         <is>
           <t>6</t>
         </is>
       </c>
-      <c r="O2" t="inlineStr">
+      <c r="X2" t="inlineStr">
         <is>
           <t>62</t>
         </is>
       </c>
-      <c r="P2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="Q2" t="inlineStr">
+      <c r="Y2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Z2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
@@ -787,80 +876,120 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
+          <t>13-May-2026</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>esignet</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>375</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>227</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>56</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>65</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>27</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
           <t>12-May-2026</t>
         </is>
       </c>
-      <c r="B3" t="inlineStr">
+      <c r="K3" t="inlineStr">
         <is>
           <t>esignet</t>
         </is>
       </c>
-      <c r="C3" t="inlineStr">
+      <c r="L3" t="inlineStr">
         <is>
           <t>375</t>
         </is>
       </c>
-      <c r="D3" t="inlineStr">
+      <c r="M3" t="inlineStr">
         <is>
           <t>231</t>
         </is>
       </c>
-      <c r="E3" t="inlineStr">
+      <c r="N3" t="inlineStr">
         <is>
           <t>40</t>
         </is>
       </c>
-      <c r="F3" t="inlineStr">
+      <c r="O3" t="inlineStr">
         <is>
           <t>77</t>
         </is>
       </c>
-      <c r="G3" t="inlineStr">
+      <c r="P3" t="inlineStr">
         <is>
           <t>27</t>
         </is>
       </c>
-      <c r="H3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="J3" t="inlineStr">
+      <c r="Q3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="S3" t="inlineStr">
         <is>
           <t>11-May-2026</t>
         </is>
       </c>
-      <c r="K3" t="inlineStr">
+      <c r="T3" t="inlineStr">
         <is>
           <t>esignet</t>
         </is>
       </c>
-      <c r="L3" t="inlineStr">
+      <c r="U3" t="inlineStr">
         <is>
           <t>375</t>
         </is>
       </c>
-      <c r="M3" t="inlineStr">
+      <c r="V3" t="inlineStr">
         <is>
           <t>230</t>
         </is>
       </c>
-      <c r="N3" t="inlineStr">
+      <c r="W3" t="inlineStr">
         <is>
           <t>55</t>
         </is>
       </c>
-      <c r="O3" t="inlineStr">
+      <c r="X3" t="inlineStr">
         <is>
           <t>63</t>
         </is>
       </c>
-      <c r="P3" t="inlineStr">
+      <c r="Y3" t="inlineStr">
         <is>
           <t>27</t>
         </is>
       </c>
-      <c r="Q3" t="inlineStr">
+      <c r="Z3" t="inlineStr">
         <is>
           <t>0</t>
         </is>
@@ -869,80 +998,120 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
+          <t>13-May-2026</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>idrepo</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>152</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>101</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>51</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
           <t>12-May-2026</t>
         </is>
       </c>
-      <c r="B4" t="inlineStr">
+      <c r="K4" t="inlineStr">
         <is>
           <t>idrepo</t>
         </is>
       </c>
-      <c r="C4" t="inlineStr">
+      <c r="L4" t="inlineStr">
         <is>
           <t>152</t>
         </is>
       </c>
-      <c r="D4" t="inlineStr">
+      <c r="M4" t="inlineStr">
         <is>
           <t>100</t>
         </is>
       </c>
-      <c r="E4" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F4" t="inlineStr">
+      <c r="N4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O4" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="G4" t="inlineStr">
+      <c r="P4" t="inlineStr">
         <is>
           <t>51</t>
         </is>
       </c>
-      <c r="H4" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="J4" t="inlineStr">
+      <c r="Q4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="S4" t="inlineStr">
         <is>
           <t>11-May-2026</t>
         </is>
       </c>
-      <c r="K4" t="inlineStr">
+      <c r="T4" t="inlineStr">
         <is>
           <t>idrepo</t>
         </is>
       </c>
-      <c r="L4" t="inlineStr">
+      <c r="U4" t="inlineStr">
         <is>
           <t>152</t>
         </is>
       </c>
-      <c r="M4" t="inlineStr">
+      <c r="V4" t="inlineStr">
         <is>
           <t>101</t>
         </is>
       </c>
-      <c r="N4" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="O4" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="P4" t="inlineStr">
+      <c r="W4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="X4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Y4" t="inlineStr">
         <is>
           <t>51</t>
         </is>
       </c>
-      <c r="Q4" t="inlineStr">
+      <c r="Z4" t="inlineStr">
         <is>
           <t>0</t>
         </is>
@@ -951,80 +1120,120 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
+          <t>13-May-2026</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>injiverify</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>53</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>23</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
           <t>12-May-2026</t>
         </is>
       </c>
-      <c r="B5" t="inlineStr">
+      <c r="K5" t="inlineStr">
         <is>
           <t>injiverify</t>
         </is>
       </c>
-      <c r="C5" t="inlineStr">
+      <c r="L5" t="inlineStr">
         <is>
           <t>53</t>
         </is>
       </c>
-      <c r="D5" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="E5" t="inlineStr">
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="N5" t="inlineStr">
         <is>
           <t>23</t>
         </is>
       </c>
-      <c r="F5" t="inlineStr">
+      <c r="O5" t="inlineStr">
         <is>
           <t>30</t>
         </is>
       </c>
-      <c r="G5" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H5" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="J5" t="inlineStr">
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Q5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="S5" t="inlineStr">
         <is>
           <t>11-May-2026</t>
         </is>
       </c>
-      <c r="K5" t="inlineStr">
+      <c r="T5" t="inlineStr">
         <is>
           <t>injiverify</t>
         </is>
       </c>
-      <c r="L5" t="inlineStr">
+      <c r="U5" t="inlineStr">
         <is>
           <t>53</t>
         </is>
       </c>
-      <c r="M5" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="N5" t="inlineStr">
+      <c r="V5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="W5" t="inlineStr">
         <is>
           <t>23</t>
         </is>
       </c>
-      <c r="O5" t="inlineStr">
+      <c r="X5" t="inlineStr">
         <is>
           <t>30</t>
         </is>
       </c>
-      <c r="P5" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="Q5" t="inlineStr">
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Z5" t="inlineStr">
         <is>
           <t>0</t>
         </is>
@@ -1033,80 +1242,120 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
+          <t>13-May-2026</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>mimoto</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>79</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>58</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
           <t>12-May-2026</t>
         </is>
       </c>
-      <c r="B6" t="inlineStr">
+      <c r="K6" t="inlineStr">
         <is>
           <t>mimoto</t>
         </is>
       </c>
-      <c r="C6" t="inlineStr">
+      <c r="L6" t="inlineStr">
         <is>
           <t>79</t>
         </is>
       </c>
-      <c r="D6" t="inlineStr">
+      <c r="M6" t="inlineStr">
         <is>
           <t>58</t>
         </is>
       </c>
-      <c r="E6" t="inlineStr">
+      <c r="N6" t="inlineStr">
         <is>
           <t>4</t>
         </is>
       </c>
-      <c r="F6" t="inlineStr">
+      <c r="O6" t="inlineStr">
         <is>
           <t>5</t>
         </is>
       </c>
-      <c r="G6" t="inlineStr">
+      <c r="P6" t="inlineStr">
         <is>
           <t>10</t>
         </is>
       </c>
-      <c r="H6" t="inlineStr">
+      <c r="Q6" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="J6" t="inlineStr">
+      <c r="S6" t="inlineStr">
         <is>
           <t>11-May-2026</t>
         </is>
       </c>
-      <c r="K6" t="inlineStr">
+      <c r="T6" t="inlineStr">
         <is>
           <t>mimoto</t>
         </is>
       </c>
-      <c r="L6" t="inlineStr">
+      <c r="U6" t="inlineStr">
         <is>
           <t>79</t>
         </is>
       </c>
-      <c r="M6" t="inlineStr">
+      <c r="V6" t="inlineStr">
         <is>
           <t>64</t>
         </is>
       </c>
-      <c r="N6" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="O6" t="inlineStr">
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="X6" t="inlineStr">
         <is>
           <t>3</t>
         </is>
       </c>
-      <c r="P6" t="inlineStr">
+      <c r="Y6" t="inlineStr">
         <is>
           <t>10</t>
         </is>
       </c>
-      <c r="Q6" t="inlineStr">
+      <c r="Z6" t="inlineStr">
         <is>
           <t>2</t>
         </is>
@@ -1115,80 +1364,120 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
+          <t>13-May-2026</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>prereg</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>104</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>70</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
           <t>12-May-2026</t>
         </is>
       </c>
-      <c r="B7" t="inlineStr">
+      <c r="K7" t="inlineStr">
         <is>
           <t>prereg</t>
         </is>
       </c>
-      <c r="C7" t="inlineStr">
+      <c r="L7" t="inlineStr">
         <is>
           <t>104</t>
         </is>
       </c>
-      <c r="D7" t="inlineStr">
+      <c r="M7" t="inlineStr">
         <is>
           <t>3</t>
         </is>
       </c>
-      <c r="E7" t="inlineStr">
+      <c r="N7" t="inlineStr">
         <is>
           <t>70</t>
         </is>
       </c>
-      <c r="F7" t="inlineStr">
+      <c r="O7" t="inlineStr">
         <is>
           <t>30</t>
         </is>
       </c>
-      <c r="G7" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H7" t="inlineStr">
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Q7" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="J7" t="inlineStr">
+      <c r="S7" t="inlineStr">
         <is>
           <t>11-May-2026</t>
         </is>
       </c>
-      <c r="K7" t="inlineStr">
+      <c r="T7" t="inlineStr">
         <is>
           <t>prereg</t>
         </is>
       </c>
-      <c r="L7" t="inlineStr">
+      <c r="U7" t="inlineStr">
         <is>
           <t>104</t>
         </is>
       </c>
-      <c r="M7" t="inlineStr">
+      <c r="V7" t="inlineStr">
         <is>
           <t>3</t>
         </is>
       </c>
-      <c r="N7" t="inlineStr">
+      <c r="W7" t="inlineStr">
         <is>
           <t>70</t>
         </is>
       </c>
-      <c r="O7" t="inlineStr">
+      <c r="X7" t="inlineStr">
         <is>
           <t>30</t>
         </is>
       </c>
-      <c r="P7" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="Q7" t="inlineStr">
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Z7" t="inlineStr">
         <is>
           <t>1</t>
         </is>
@@ -1197,80 +1486,120 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
+          <t>13-May-2026</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>residentui</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>33</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
           <t>12-May-2026</t>
         </is>
       </c>
-      <c r="B8" t="inlineStr">
+      <c r="K8" t="inlineStr">
         <is>
           <t>residentui</t>
         </is>
       </c>
-      <c r="C8" t="inlineStr">
+      <c r="L8" t="inlineStr">
         <is>
           <t>33</t>
         </is>
       </c>
-      <c r="D8" t="inlineStr">
+      <c r="M8" t="inlineStr">
         <is>
           <t>12</t>
         </is>
       </c>
-      <c r="E8" t="inlineStr">
+      <c r="N8" t="inlineStr">
         <is>
           <t>5</t>
         </is>
       </c>
-      <c r="F8" t="inlineStr">
+      <c r="O8" t="inlineStr">
         <is>
           <t>16</t>
         </is>
       </c>
-      <c r="G8" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H8" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="J8" t="inlineStr">
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Q8" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="S8" t="inlineStr">
         <is>
           <t>11-May-2026</t>
         </is>
       </c>
-      <c r="K8" t="inlineStr">
+      <c r="T8" t="inlineStr">
         <is>
           <t>residentui</t>
         </is>
       </c>
-      <c r="L8" t="inlineStr">
+      <c r="U8" t="inlineStr">
         <is>
           <t>33</t>
         </is>
       </c>
-      <c r="M8" t="inlineStr">
+      <c r="V8" t="inlineStr">
         <is>
           <t>12</t>
         </is>
       </c>
-      <c r="N8" t="inlineStr">
+      <c r="W8" t="inlineStr">
         <is>
           <t>5</t>
         </is>
       </c>
-      <c r="O8" t="inlineStr">
+      <c r="X8" t="inlineStr">
         <is>
           <t>16</t>
         </is>
       </c>
-      <c r="P8" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="Q8" t="inlineStr">
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Z8" t="inlineStr">
         <is>
           <t>0</t>
         </is>

--- a/minio-report-tracker/xlxs/collab.xlsx
+++ b/minio-report-tracker/xlxs/collab.xlsx
@@ -598,7 +598,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Z8"/>
+  <dimension ref="A1:AI8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -627,6 +627,15 @@
     <col width="4" customWidth="1" min="24" max="24"/>
     <col width="4" customWidth="1" min="25" max="25"/>
     <col width="4" customWidth="1" min="26" max="26"/>
+    <col width="2" customWidth="1" min="27" max="27"/>
+    <col width="13" customWidth="1" min="28" max="28"/>
+    <col width="12" customWidth="1" min="29" max="29"/>
+    <col width="5" customWidth="1" min="30" max="30"/>
+    <col width="5" customWidth="1" min="31" max="31"/>
+    <col width="5" customWidth="1" min="32" max="32"/>
+    <col width="5" customWidth="1" min="33" max="33"/>
+    <col width="5" customWidth="1" min="34" max="34"/>
+    <col width="5" customWidth="1" min="35" max="35"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -750,124 +759,204 @@
           <t>KI</t>
         </is>
       </c>
+      <c r="AB1" s="1" t="inlineStr">
+        <is>
+          <t>Date</t>
+        </is>
+      </c>
+      <c r="AC1" s="1" t="inlineStr">
+        <is>
+          <t>Module</t>
+        </is>
+      </c>
+      <c r="AD1" s="1" t="inlineStr">
+        <is>
+          <t>T</t>
+        </is>
+      </c>
+      <c r="AE1" s="1" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
+      <c r="AF1" s="1" t="inlineStr">
+        <is>
+          <t>S</t>
+        </is>
+      </c>
+      <c r="AG1" s="1" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
+      <c r="AH1" s="1" t="inlineStr">
+        <is>
+          <t>I</t>
+        </is>
+      </c>
+      <c r="AI1" s="1" t="inlineStr">
+        <is>
+          <t>KI</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
+          <t>14-May-2026</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>auth</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>254</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>142</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>72</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>40</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
           <t>13-May-2026</t>
         </is>
       </c>
-      <c r="B2" t="inlineStr">
+      <c r="K2" t="inlineStr">
         <is>
           <t>auth</t>
         </is>
       </c>
-      <c r="C2" t="inlineStr">
+      <c r="L2" t="inlineStr">
         <is>
           <t>254</t>
         </is>
       </c>
-      <c r="D2" t="inlineStr">
+      <c r="M2" t="inlineStr">
         <is>
           <t>140</t>
         </is>
       </c>
-      <c r="E2" t="inlineStr">
+      <c r="N2" t="inlineStr">
         <is>
           <t>72</t>
         </is>
       </c>
-      <c r="F2" t="inlineStr">
+      <c r="O2" t="inlineStr">
         <is>
           <t>42</t>
         </is>
       </c>
-      <c r="G2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="J2" t="inlineStr">
+      <c r="P2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Q2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="S2" t="inlineStr">
         <is>
           <t>12-May-2026</t>
         </is>
       </c>
-      <c r="K2" t="inlineStr">
+      <c r="T2" t="inlineStr">
         <is>
           <t>auth</t>
         </is>
       </c>
-      <c r="L2" t="inlineStr">
+      <c r="U2" t="inlineStr">
         <is>
           <t>254</t>
         </is>
       </c>
-      <c r="M2" t="inlineStr">
+      <c r="V2" t="inlineStr">
         <is>
           <t>186</t>
         </is>
       </c>
-      <c r="N2" t="inlineStr">
+      <c r="W2" t="inlineStr">
         <is>
           <t>6</t>
         </is>
       </c>
-      <c r="O2" t="inlineStr">
+      <c r="X2" t="inlineStr">
         <is>
           <t>62</t>
         </is>
       </c>
-      <c r="P2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="Q2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="S2" t="inlineStr">
+      <c r="Y2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Z2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB2" t="inlineStr">
         <is>
           <t>11-May-2026</t>
         </is>
       </c>
-      <c r="T2" t="inlineStr">
-        <is>
-          <t>auth</t>
-        </is>
-      </c>
-      <c r="U2" t="inlineStr">
-        <is>
-          <t>254</t>
-        </is>
-      </c>
-      <c r="V2" t="inlineStr">
-        <is>
-          <t>186</t>
-        </is>
-      </c>
-      <c r="W2" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="X2" t="inlineStr">
-        <is>
-          <t>62</t>
-        </is>
-      </c>
-      <c r="Y2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="Z2" t="inlineStr">
+      <c r="AC2" t="inlineStr">
+        <is>
+          <t>esignet</t>
+        </is>
+      </c>
+      <c r="AD2" t="inlineStr">
+        <is>
+          <t>375</t>
+        </is>
+      </c>
+      <c r="AE2" t="inlineStr">
+        <is>
+          <t>230</t>
+        </is>
+      </c>
+      <c r="AF2" t="inlineStr">
+        <is>
+          <t>55</t>
+        </is>
+      </c>
+      <c r="AG2" t="inlineStr">
+        <is>
+          <t>63</t>
+        </is>
+      </c>
+      <c r="AH2" t="inlineStr">
+        <is>
+          <t>27</t>
+        </is>
+      </c>
+      <c r="AI2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
@@ -876,120 +965,160 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
+          <t>14-May-2026</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>esignet</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>375</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>281</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>31</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>36</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>27</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
           <t>13-May-2026</t>
         </is>
       </c>
-      <c r="B3" t="inlineStr">
+      <c r="K3" t="inlineStr">
         <is>
           <t>esignet</t>
         </is>
       </c>
-      <c r="C3" t="inlineStr">
+      <c r="L3" t="inlineStr">
         <is>
           <t>375</t>
         </is>
       </c>
-      <c r="D3" t="inlineStr">
+      <c r="M3" t="inlineStr">
         <is>
           <t>227</t>
         </is>
       </c>
-      <c r="E3" t="inlineStr">
+      <c r="N3" t="inlineStr">
         <is>
           <t>56</t>
         </is>
       </c>
-      <c r="F3" t="inlineStr">
+      <c r="O3" t="inlineStr">
         <is>
           <t>65</t>
         </is>
       </c>
-      <c r="G3" t="inlineStr">
+      <c r="P3" t="inlineStr">
         <is>
           <t>27</t>
         </is>
       </c>
-      <c r="H3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="J3" t="inlineStr">
+      <c r="Q3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="S3" t="inlineStr">
         <is>
           <t>12-May-2026</t>
         </is>
       </c>
-      <c r="K3" t="inlineStr">
+      <c r="T3" t="inlineStr">
         <is>
           <t>esignet</t>
         </is>
       </c>
-      <c r="L3" t="inlineStr">
+      <c r="U3" t="inlineStr">
         <is>
           <t>375</t>
         </is>
       </c>
-      <c r="M3" t="inlineStr">
+      <c r="V3" t="inlineStr">
         <is>
           <t>231</t>
         </is>
       </c>
-      <c r="N3" t="inlineStr">
+      <c r="W3" t="inlineStr">
         <is>
           <t>40</t>
         </is>
       </c>
-      <c r="O3" t="inlineStr">
+      <c r="X3" t="inlineStr">
         <is>
           <t>77</t>
         </is>
       </c>
-      <c r="P3" t="inlineStr">
+      <c r="Y3" t="inlineStr">
         <is>
           <t>27</t>
         </is>
       </c>
-      <c r="Q3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="S3" t="inlineStr">
+      <c r="Z3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB3" t="inlineStr">
         <is>
           <t>11-May-2026</t>
         </is>
       </c>
-      <c r="T3" t="inlineStr">
-        <is>
-          <t>esignet</t>
-        </is>
-      </c>
-      <c r="U3" t="inlineStr">
-        <is>
-          <t>375</t>
-        </is>
-      </c>
-      <c r="V3" t="inlineStr">
-        <is>
-          <t>230</t>
-        </is>
-      </c>
-      <c r="W3" t="inlineStr">
-        <is>
-          <t>55</t>
-        </is>
-      </c>
-      <c r="X3" t="inlineStr">
-        <is>
-          <t>63</t>
-        </is>
-      </c>
-      <c r="Y3" t="inlineStr">
-        <is>
-          <t>27</t>
-        </is>
-      </c>
-      <c r="Z3" t="inlineStr">
+      <c r="AC3" t="inlineStr">
+        <is>
+          <t>injiverify</t>
+        </is>
+      </c>
+      <c r="AD3" t="inlineStr">
+        <is>
+          <t>53</t>
+        </is>
+      </c>
+      <c r="AE3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AF3" t="inlineStr">
+        <is>
+          <t>23</t>
+        </is>
+      </c>
+      <c r="AG3" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="AH3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AI3" t="inlineStr">
         <is>
           <t>0</t>
         </is>
@@ -998,242 +1127,322 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
+          <t>14-May-2026</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>idrepo</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>152</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>98</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>51</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
           <t>13-May-2026</t>
         </is>
       </c>
-      <c r="B4" t="inlineStr">
+      <c r="K4" t="inlineStr">
         <is>
           <t>idrepo</t>
         </is>
       </c>
-      <c r="C4" t="inlineStr">
+      <c r="L4" t="inlineStr">
         <is>
           <t>152</t>
         </is>
       </c>
-      <c r="D4" t="inlineStr">
+      <c r="M4" t="inlineStr">
         <is>
           <t>101</t>
         </is>
       </c>
-      <c r="E4" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F4" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="G4" t="inlineStr">
+      <c r="N4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P4" t="inlineStr">
         <is>
           <t>51</t>
         </is>
       </c>
-      <c r="H4" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="J4" t="inlineStr">
+      <c r="Q4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="S4" t="inlineStr">
         <is>
           <t>12-May-2026</t>
         </is>
       </c>
-      <c r="K4" t="inlineStr">
+      <c r="T4" t="inlineStr">
         <is>
           <t>idrepo</t>
         </is>
       </c>
-      <c r="L4" t="inlineStr">
+      <c r="U4" t="inlineStr">
         <is>
           <t>152</t>
         </is>
       </c>
-      <c r="M4" t="inlineStr">
+      <c r="V4" t="inlineStr">
         <is>
           <t>100</t>
         </is>
       </c>
-      <c r="N4" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="O4" t="inlineStr">
+      <c r="W4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="X4" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="P4" t="inlineStr">
+      <c r="Y4" t="inlineStr">
         <is>
           <t>51</t>
         </is>
       </c>
-      <c r="Q4" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="S4" t="inlineStr">
+      <c r="Z4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB4" t="inlineStr">
         <is>
           <t>11-May-2026</t>
         </is>
       </c>
-      <c r="T4" t="inlineStr">
-        <is>
-          <t>idrepo</t>
-        </is>
-      </c>
-      <c r="U4" t="inlineStr">
-        <is>
-          <t>152</t>
-        </is>
-      </c>
-      <c r="V4" t="inlineStr">
-        <is>
-          <t>101</t>
-        </is>
-      </c>
-      <c r="W4" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="X4" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="Y4" t="inlineStr">
-        <is>
-          <t>51</t>
-        </is>
-      </c>
-      <c r="Z4" t="inlineStr">
-        <is>
-          <t>0</t>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t>prereg</t>
+        </is>
+      </c>
+      <c r="AD4" t="inlineStr">
+        <is>
+          <t>104</t>
+        </is>
+      </c>
+      <c r="AE4" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AF4" t="inlineStr">
+        <is>
+          <t>70</t>
+        </is>
+      </c>
+      <c r="AG4" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="AH4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AI4" t="inlineStr">
+        <is>
+          <t>1</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
+          <t>14-May-2026</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>injiverify</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>53</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>23</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
           <t>13-May-2026</t>
         </is>
       </c>
-      <c r="B5" t="inlineStr">
+      <c r="K5" t="inlineStr">
         <is>
           <t>injiverify</t>
         </is>
       </c>
-      <c r="C5" t="inlineStr">
+      <c r="L5" t="inlineStr">
         <is>
           <t>53</t>
         </is>
       </c>
-      <c r="D5" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="E5" t="inlineStr">
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="N5" t="inlineStr">
         <is>
           <t>23</t>
         </is>
       </c>
-      <c r="F5" t="inlineStr">
+      <c r="O5" t="inlineStr">
         <is>
           <t>30</t>
         </is>
       </c>
-      <c r="G5" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H5" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="J5" t="inlineStr">
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Q5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="S5" t="inlineStr">
         <is>
           <t>12-May-2026</t>
         </is>
       </c>
-      <c r="K5" t="inlineStr">
+      <c r="T5" t="inlineStr">
         <is>
           <t>injiverify</t>
         </is>
       </c>
-      <c r="L5" t="inlineStr">
+      <c r="U5" t="inlineStr">
         <is>
           <t>53</t>
         </is>
       </c>
-      <c r="M5" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="N5" t="inlineStr">
+      <c r="V5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="W5" t="inlineStr">
         <is>
           <t>23</t>
         </is>
       </c>
-      <c r="O5" t="inlineStr">
+      <c r="X5" t="inlineStr">
         <is>
           <t>30</t>
         </is>
       </c>
-      <c r="P5" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="Q5" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="S5" t="inlineStr">
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Z5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB5" t="inlineStr">
         <is>
           <t>11-May-2026</t>
         </is>
       </c>
-      <c r="T5" t="inlineStr">
-        <is>
-          <t>injiverify</t>
-        </is>
-      </c>
-      <c r="U5" t="inlineStr">
-        <is>
-          <t>53</t>
-        </is>
-      </c>
-      <c r="V5" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="W5" t="inlineStr">
-        <is>
-          <t>23</t>
-        </is>
-      </c>
-      <c r="X5" t="inlineStr">
-        <is>
-          <t>30</t>
-        </is>
-      </c>
-      <c r="Y5" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="Z5" t="inlineStr">
+      <c r="AC5" t="inlineStr">
+        <is>
+          <t>residentui</t>
+        </is>
+      </c>
+      <c r="AD5" t="inlineStr">
+        <is>
+          <t>33</t>
+        </is>
+      </c>
+      <c r="AE5" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="AF5" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AG5" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="AH5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AI5" t="inlineStr">
         <is>
           <t>0</t>
         </is>
@@ -1242,358 +1451,406 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
+          <t>14-May-2026</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>mimoto</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>79</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>58</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
           <t>13-May-2026</t>
         </is>
       </c>
-      <c r="B6" t="inlineStr">
+      <c r="K6" t="inlineStr">
         <is>
           <t>mimoto</t>
         </is>
       </c>
-      <c r="C6" t="inlineStr">
+      <c r="L6" t="inlineStr">
         <is>
           <t>79</t>
         </is>
       </c>
-      <c r="D6" t="inlineStr">
+      <c r="M6" t="inlineStr">
         <is>
           <t>58</t>
         </is>
       </c>
-      <c r="E6" t="inlineStr">
+      <c r="N6" t="inlineStr">
         <is>
           <t>4</t>
         </is>
       </c>
-      <c r="F6" t="inlineStr">
+      <c r="O6" t="inlineStr">
         <is>
           <t>5</t>
         </is>
       </c>
-      <c r="G6" t="inlineStr">
+      <c r="P6" t="inlineStr">
         <is>
           <t>10</t>
         </is>
       </c>
-      <c r="H6" t="inlineStr">
+      <c r="Q6" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="J6" t="inlineStr">
+      <c r="S6" t="inlineStr">
         <is>
           <t>12-May-2026</t>
         </is>
       </c>
-      <c r="K6" t="inlineStr">
+      <c r="T6" t="inlineStr">
         <is>
           <t>mimoto</t>
         </is>
       </c>
-      <c r="L6" t="inlineStr">
+      <c r="U6" t="inlineStr">
         <is>
           <t>79</t>
         </is>
       </c>
-      <c r="M6" t="inlineStr">
+      <c r="V6" t="inlineStr">
         <is>
           <t>58</t>
         </is>
       </c>
-      <c r="N6" t="inlineStr">
+      <c r="W6" t="inlineStr">
         <is>
           <t>4</t>
         </is>
       </c>
-      <c r="O6" t="inlineStr">
+      <c r="X6" t="inlineStr">
         <is>
           <t>5</t>
         </is>
       </c>
-      <c r="P6" t="inlineStr">
+      <c r="Y6" t="inlineStr">
         <is>
           <t>10</t>
         </is>
       </c>
-      <c r="Q6" t="inlineStr">
+      <c r="Z6" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="S6" t="inlineStr">
-        <is>
-          <t>11-May-2026</t>
-        </is>
-      </c>
-      <c r="T6" t="inlineStr">
-        <is>
-          <t>mimoto</t>
-        </is>
-      </c>
-      <c r="U6" t="inlineStr">
-        <is>
-          <t>79</t>
-        </is>
-      </c>
-      <c r="V6" t="inlineStr">
-        <is>
-          <t>64</t>
-        </is>
-      </c>
-      <c r="W6" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="X6" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="Y6" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="Z6" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
+      <c r="AB6" t="n">
+        <v/>
+      </c>
+      <c r="AC6" t="n">
+        <v/>
+      </c>
+      <c r="AD6" t="n">
+        <v/>
+      </c>
+      <c r="AE6" t="n">
+        <v/>
+      </c>
+      <c r="AF6" t="n">
+        <v/>
+      </c>
+      <c r="AG6" t="n">
+        <v/>
+      </c>
+      <c r="AH6" t="n">
+        <v/>
+      </c>
+      <c r="AI6" t="n">
+        <v/>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
+          <t>14-May-2026</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>prereg</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>104</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>70</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
           <t>13-May-2026</t>
         </is>
       </c>
-      <c r="B7" t="inlineStr">
+      <c r="K7" t="inlineStr">
         <is>
           <t>prereg</t>
         </is>
       </c>
-      <c r="C7" t="inlineStr">
+      <c r="L7" t="inlineStr">
         <is>
           <t>104</t>
         </is>
       </c>
-      <c r="D7" t="inlineStr">
+      <c r="M7" t="inlineStr">
         <is>
           <t>3</t>
         </is>
       </c>
-      <c r="E7" t="inlineStr">
+      <c r="N7" t="inlineStr">
         <is>
           <t>70</t>
         </is>
       </c>
-      <c r="F7" t="inlineStr">
+      <c r="O7" t="inlineStr">
         <is>
           <t>30</t>
         </is>
       </c>
-      <c r="G7" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H7" t="inlineStr">
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Q7" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="J7" t="inlineStr">
+      <c r="S7" t="inlineStr">
         <is>
           <t>12-May-2026</t>
         </is>
       </c>
-      <c r="K7" t="inlineStr">
+      <c r="T7" t="inlineStr">
         <is>
           <t>prereg</t>
         </is>
       </c>
-      <c r="L7" t="inlineStr">
+      <c r="U7" t="inlineStr">
         <is>
           <t>104</t>
         </is>
       </c>
-      <c r="M7" t="inlineStr">
+      <c r="V7" t="inlineStr">
         <is>
           <t>3</t>
         </is>
       </c>
-      <c r="N7" t="inlineStr">
+      <c r="W7" t="inlineStr">
         <is>
           <t>70</t>
         </is>
       </c>
-      <c r="O7" t="inlineStr">
+      <c r="X7" t="inlineStr">
         <is>
           <t>30</t>
         </is>
       </c>
-      <c r="P7" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="Q7" t="inlineStr">
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Z7" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="S7" t="inlineStr">
-        <is>
-          <t>11-May-2026</t>
-        </is>
-      </c>
-      <c r="T7" t="inlineStr">
-        <is>
-          <t>prereg</t>
-        </is>
-      </c>
-      <c r="U7" t="inlineStr">
-        <is>
-          <t>104</t>
-        </is>
-      </c>
-      <c r="V7" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="W7" t="inlineStr">
-        <is>
-          <t>70</t>
-        </is>
-      </c>
-      <c r="X7" t="inlineStr">
-        <is>
-          <t>30</t>
-        </is>
-      </c>
-      <c r="Y7" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="Z7" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
+      <c r="AB7" t="n">
+        <v/>
+      </c>
+      <c r="AC7" t="n">
+        <v/>
+      </c>
+      <c r="AD7" t="n">
+        <v/>
+      </c>
+      <c r="AE7" t="n">
+        <v/>
+      </c>
+      <c r="AF7" t="n">
+        <v/>
+      </c>
+      <c r="AG7" t="n">
+        <v/>
+      </c>
+      <c r="AH7" t="n">
+        <v/>
+      </c>
+      <c r="AI7" t="n">
+        <v/>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
+          <t>14-May-2026</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>residentui</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>33</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
           <t>13-May-2026</t>
         </is>
       </c>
-      <c r="B8" t="inlineStr">
+      <c r="K8" t="inlineStr">
         <is>
           <t>residentui</t>
         </is>
       </c>
-      <c r="C8" t="inlineStr">
+      <c r="L8" t="inlineStr">
         <is>
           <t>33</t>
         </is>
       </c>
-      <c r="D8" t="inlineStr">
+      <c r="M8" t="inlineStr">
         <is>
           <t>12</t>
         </is>
       </c>
-      <c r="E8" t="inlineStr">
+      <c r="N8" t="inlineStr">
         <is>
           <t>5</t>
         </is>
       </c>
-      <c r="F8" t="inlineStr">
+      <c r="O8" t="inlineStr">
         <is>
           <t>16</t>
         </is>
       </c>
-      <c r="G8" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H8" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="J8" t="inlineStr">
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Q8" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="S8" t="inlineStr">
         <is>
           <t>12-May-2026</t>
         </is>
       </c>
-      <c r="K8" t="inlineStr">
+      <c r="T8" t="inlineStr">
         <is>
           <t>residentui</t>
         </is>
       </c>
-      <c r="L8" t="inlineStr">
+      <c r="U8" t="inlineStr">
         <is>
           <t>33</t>
         </is>
       </c>
-      <c r="M8" t="inlineStr">
+      <c r="V8" t="inlineStr">
         <is>
           <t>12</t>
         </is>
       </c>
-      <c r="N8" t="inlineStr">
+      <c r="W8" t="inlineStr">
         <is>
           <t>5</t>
         </is>
       </c>
-      <c r="O8" t="inlineStr">
+      <c r="X8" t="inlineStr">
         <is>
           <t>16</t>
         </is>
       </c>
-      <c r="P8" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="Q8" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="S8" t="inlineStr">
-        <is>
-          <t>11-May-2026</t>
-        </is>
-      </c>
-      <c r="T8" t="inlineStr">
-        <is>
-          <t>residentui</t>
-        </is>
-      </c>
-      <c r="U8" t="inlineStr">
-        <is>
-          <t>33</t>
-        </is>
-      </c>
-      <c r="V8" t="inlineStr">
-        <is>
-          <t>12</t>
-        </is>
-      </c>
-      <c r="W8" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="X8" t="inlineStr">
-        <is>
-          <t>16</t>
-        </is>
-      </c>
       <c r="Y8" t="inlineStr">
         <is>
           <t>0</t>
@@ -1603,6 +1860,30 @@
         <is>
           <t>0</t>
         </is>
+      </c>
+      <c r="AB8" t="n">
+        <v/>
+      </c>
+      <c r="AC8" t="n">
+        <v/>
+      </c>
+      <c r="AD8" t="n">
+        <v/>
+      </c>
+      <c r="AE8" t="n">
+        <v/>
+      </c>
+      <c r="AF8" t="n">
+        <v/>
+      </c>
+      <c r="AG8" t="n">
+        <v/>
+      </c>
+      <c r="AH8" t="n">
+        <v/>
+      </c>
+      <c r="AI8" t="n">
+        <v/>
       </c>
     </row>
   </sheetData>

--- a/minio-report-tracker/xlxs/collab.xlsx
+++ b/minio-report-tracker/xlxs/collab.xlsx
@@ -803,129 +803,129 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
+          <t>15-May-2026</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>auth</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>254</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>140</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>72</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>42</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
           <t>14-May-2026</t>
         </is>
       </c>
-      <c r="B2" t="inlineStr">
+      <c r="K2" t="inlineStr">
         <is>
           <t>auth</t>
         </is>
       </c>
-      <c r="C2" t="inlineStr">
+      <c r="L2" t="inlineStr">
         <is>
           <t>254</t>
         </is>
       </c>
-      <c r="D2" t="inlineStr">
+      <c r="M2" t="inlineStr">
         <is>
           <t>142</t>
         </is>
       </c>
-      <c r="E2" t="inlineStr">
+      <c r="N2" t="inlineStr">
         <is>
           <t>72</t>
         </is>
       </c>
-      <c r="F2" t="inlineStr">
+      <c r="O2" t="inlineStr">
         <is>
           <t>40</t>
         </is>
       </c>
-      <c r="G2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="J2" t="inlineStr">
+      <c r="P2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Q2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="S2" t="inlineStr">
         <is>
           <t>13-May-2026</t>
         </is>
       </c>
-      <c r="K2" t="inlineStr">
+      <c r="T2" t="inlineStr">
         <is>
           <t>auth</t>
         </is>
       </c>
-      <c r="L2" t="inlineStr">
+      <c r="U2" t="inlineStr">
         <is>
           <t>254</t>
         </is>
       </c>
-      <c r="M2" t="inlineStr">
+      <c r="V2" t="inlineStr">
         <is>
           <t>140</t>
         </is>
       </c>
-      <c r="N2" t="inlineStr">
+      <c r="W2" t="inlineStr">
         <is>
           <t>72</t>
         </is>
       </c>
-      <c r="O2" t="inlineStr">
+      <c r="X2" t="inlineStr">
         <is>
           <t>42</t>
         </is>
       </c>
-      <c r="P2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="Q2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="S2" t="inlineStr">
+      <c r="Y2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Z2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB2" t="inlineStr">
         <is>
           <t>12-May-2026</t>
         </is>
       </c>
-      <c r="T2" t="inlineStr">
-        <is>
-          <t>auth</t>
-        </is>
-      </c>
-      <c r="U2" t="inlineStr">
-        <is>
-          <t>254</t>
-        </is>
-      </c>
-      <c r="V2" t="inlineStr">
-        <is>
-          <t>186</t>
-        </is>
-      </c>
-      <c r="W2" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="X2" t="inlineStr">
-        <is>
-          <t>62</t>
-        </is>
-      </c>
-      <c r="Y2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>11-May-2026</t>
-        </is>
-      </c>
       <c r="AC2" t="inlineStr">
         <is>
           <t>esignet</t>
@@ -938,17 +938,17 @@
       </c>
       <c r="AE2" t="inlineStr">
         <is>
-          <t>230</t>
+          <t>231</t>
         </is>
       </c>
       <c r="AF2" t="inlineStr">
         <is>
-          <t>55</t>
+          <t>40</t>
         </is>
       </c>
       <c r="AG2" t="inlineStr">
         <is>
-          <t>63</t>
+          <t>77</t>
         </is>
       </c>
       <c r="AH2" t="inlineStr">
@@ -965,127 +965,127 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
+          <t>15-May-2026</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>esignet</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>375</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>287</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>18</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>43</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>27</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
           <t>14-May-2026</t>
         </is>
       </c>
-      <c r="B3" t="inlineStr">
+      <c r="K3" t="inlineStr">
         <is>
           <t>esignet</t>
         </is>
       </c>
-      <c r="C3" t="inlineStr">
+      <c r="L3" t="inlineStr">
         <is>
           <t>375</t>
         </is>
       </c>
-      <c r="D3" t="inlineStr">
+      <c r="M3" t="inlineStr">
         <is>
           <t>281</t>
         </is>
       </c>
-      <c r="E3" t="inlineStr">
+      <c r="N3" t="inlineStr">
         <is>
           <t>31</t>
         </is>
       </c>
-      <c r="F3" t="inlineStr">
+      <c r="O3" t="inlineStr">
         <is>
           <t>36</t>
         </is>
       </c>
-      <c r="G3" t="inlineStr">
+      <c r="P3" t="inlineStr">
         <is>
           <t>27</t>
         </is>
       </c>
-      <c r="H3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="J3" t="inlineStr">
+      <c r="Q3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="S3" t="inlineStr">
         <is>
           <t>13-May-2026</t>
         </is>
       </c>
-      <c r="K3" t="inlineStr">
+      <c r="T3" t="inlineStr">
         <is>
           <t>esignet</t>
         </is>
       </c>
-      <c r="L3" t="inlineStr">
+      <c r="U3" t="inlineStr">
         <is>
           <t>375</t>
         </is>
       </c>
-      <c r="M3" t="inlineStr">
+      <c r="V3" t="inlineStr">
         <is>
           <t>227</t>
         </is>
       </c>
-      <c r="N3" t="inlineStr">
+      <c r="W3" t="inlineStr">
         <is>
           <t>56</t>
         </is>
       </c>
-      <c r="O3" t="inlineStr">
+      <c r="X3" t="inlineStr">
         <is>
           <t>65</t>
         </is>
       </c>
-      <c r="P3" t="inlineStr">
+      <c r="Y3" t="inlineStr">
         <is>
           <t>27</t>
         </is>
       </c>
-      <c r="Q3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="S3" t="inlineStr">
+      <c r="Z3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB3" t="inlineStr">
         <is>
           <t>12-May-2026</t>
-        </is>
-      </c>
-      <c r="T3" t="inlineStr">
-        <is>
-          <t>esignet</t>
-        </is>
-      </c>
-      <c r="U3" t="inlineStr">
-        <is>
-          <t>375</t>
-        </is>
-      </c>
-      <c r="V3" t="inlineStr">
-        <is>
-          <t>231</t>
-        </is>
-      </c>
-      <c r="W3" t="inlineStr">
-        <is>
-          <t>40</t>
-        </is>
-      </c>
-      <c r="X3" t="inlineStr">
-        <is>
-          <t>77</t>
-        </is>
-      </c>
-      <c r="Y3" t="inlineStr">
-        <is>
-          <t>27</t>
-        </is>
-      </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>11-May-2026</t>
         </is>
       </c>
       <c r="AC3" t="inlineStr">
@@ -1127,127 +1127,127 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
+          <t>15-May-2026</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>idrepo</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>152</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>101</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>51</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
           <t>14-May-2026</t>
         </is>
       </c>
-      <c r="B4" t="inlineStr">
+      <c r="K4" t="inlineStr">
         <is>
           <t>idrepo</t>
         </is>
       </c>
-      <c r="C4" t="inlineStr">
+      <c r="L4" t="inlineStr">
         <is>
           <t>152</t>
         </is>
       </c>
-      <c r="D4" t="inlineStr">
+      <c r="M4" t="inlineStr">
         <is>
           <t>98</t>
         </is>
       </c>
-      <c r="E4" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F4" t="inlineStr">
+      <c r="N4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O4" t="inlineStr">
         <is>
           <t>3</t>
         </is>
       </c>
-      <c r="G4" t="inlineStr">
+      <c r="P4" t="inlineStr">
         <is>
           <t>51</t>
         </is>
       </c>
-      <c r="H4" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="J4" t="inlineStr">
+      <c r="Q4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="S4" t="inlineStr">
         <is>
           <t>13-May-2026</t>
         </is>
       </c>
-      <c r="K4" t="inlineStr">
+      <c r="T4" t="inlineStr">
         <is>
           <t>idrepo</t>
         </is>
       </c>
-      <c r="L4" t="inlineStr">
+      <c r="U4" t="inlineStr">
         <is>
           <t>152</t>
         </is>
       </c>
-      <c r="M4" t="inlineStr">
+      <c r="V4" t="inlineStr">
         <is>
           <t>101</t>
         </is>
       </c>
-      <c r="N4" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="O4" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="P4" t="inlineStr">
+      <c r="W4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="X4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Y4" t="inlineStr">
         <is>
           <t>51</t>
         </is>
       </c>
-      <c r="Q4" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="S4" t="inlineStr">
+      <c r="Z4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB4" t="inlineStr">
         <is>
           <t>12-May-2026</t>
-        </is>
-      </c>
-      <c r="T4" t="inlineStr">
-        <is>
-          <t>idrepo</t>
-        </is>
-      </c>
-      <c r="U4" t="inlineStr">
-        <is>
-          <t>152</t>
-        </is>
-      </c>
-      <c r="V4" t="inlineStr">
-        <is>
-          <t>100</t>
-        </is>
-      </c>
-      <c r="W4" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="X4" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="Y4" t="inlineStr">
-        <is>
-          <t>51</t>
-        </is>
-      </c>
-      <c r="Z4" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB4" t="inlineStr">
-        <is>
-          <t>11-May-2026</t>
         </is>
       </c>
       <c r="AC4" t="inlineStr">
@@ -1289,127 +1289,127 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
+          <t>15-May-2026</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>injiverify</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>53</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>23</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
           <t>14-May-2026</t>
         </is>
       </c>
-      <c r="B5" t="inlineStr">
+      <c r="K5" t="inlineStr">
         <is>
           <t>injiverify</t>
         </is>
       </c>
-      <c r="C5" t="inlineStr">
+      <c r="L5" t="inlineStr">
         <is>
           <t>53</t>
         </is>
       </c>
-      <c r="D5" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="E5" t="inlineStr">
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="N5" t="inlineStr">
         <is>
           <t>23</t>
         </is>
       </c>
-      <c r="F5" t="inlineStr">
+      <c r="O5" t="inlineStr">
         <is>
           <t>30</t>
         </is>
       </c>
-      <c r="G5" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H5" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="J5" t="inlineStr">
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Q5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="S5" t="inlineStr">
         <is>
           <t>13-May-2026</t>
         </is>
       </c>
-      <c r="K5" t="inlineStr">
+      <c r="T5" t="inlineStr">
         <is>
           <t>injiverify</t>
         </is>
       </c>
-      <c r="L5" t="inlineStr">
+      <c r="U5" t="inlineStr">
         <is>
           <t>53</t>
         </is>
       </c>
-      <c r="M5" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="N5" t="inlineStr">
+      <c r="V5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="W5" t="inlineStr">
         <is>
           <t>23</t>
         </is>
       </c>
-      <c r="O5" t="inlineStr">
+      <c r="X5" t="inlineStr">
         <is>
           <t>30</t>
         </is>
       </c>
-      <c r="P5" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="Q5" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="S5" t="inlineStr">
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Z5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB5" t="inlineStr">
         <is>
           <t>12-May-2026</t>
-        </is>
-      </c>
-      <c r="T5" t="inlineStr">
-        <is>
-          <t>injiverify</t>
-        </is>
-      </c>
-      <c r="U5" t="inlineStr">
-        <is>
-          <t>53</t>
-        </is>
-      </c>
-      <c r="V5" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="W5" t="inlineStr">
-        <is>
-          <t>23</t>
-        </is>
-      </c>
-      <c r="X5" t="inlineStr">
-        <is>
-          <t>30</t>
-        </is>
-      </c>
-      <c r="Y5" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="Z5" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB5" t="inlineStr">
-        <is>
-          <t>11-May-2026</t>
         </is>
       </c>
       <c r="AC5" t="inlineStr">
@@ -1451,87 +1451,87 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
+          <t>15-May-2026</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>mimoto</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>79</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>58</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
           <t>14-May-2026</t>
         </is>
       </c>
-      <c r="B6" t="inlineStr">
+      <c r="K6" t="inlineStr">
         <is>
           <t>mimoto</t>
         </is>
       </c>
-      <c r="C6" t="inlineStr">
+      <c r="L6" t="inlineStr">
         <is>
           <t>79</t>
         </is>
       </c>
-      <c r="D6" t="inlineStr">
+      <c r="M6" t="inlineStr">
         <is>
           <t>58</t>
         </is>
       </c>
-      <c r="E6" t="inlineStr">
+      <c r="N6" t="inlineStr">
         <is>
           <t>4</t>
         </is>
       </c>
-      <c r="F6" t="inlineStr">
+      <c r="O6" t="inlineStr">
         <is>
           <t>5</t>
         </is>
       </c>
-      <c r="G6" t="inlineStr">
+      <c r="P6" t="inlineStr">
         <is>
           <t>10</t>
         </is>
       </c>
-      <c r="H6" t="inlineStr">
+      <c r="Q6" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="J6" t="inlineStr">
+      <c r="S6" t="inlineStr">
         <is>
           <t>13-May-2026</t>
-        </is>
-      </c>
-      <c r="K6" t="inlineStr">
-        <is>
-          <t>mimoto</t>
-        </is>
-      </c>
-      <c r="L6" t="inlineStr">
-        <is>
-          <t>79</t>
-        </is>
-      </c>
-      <c r="M6" t="inlineStr">
-        <is>
-          <t>58</t>
-        </is>
-      </c>
-      <c r="N6" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="O6" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="P6" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="Q6" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="S6" t="inlineStr">
-        <is>
-          <t>12-May-2026</t>
         </is>
       </c>
       <c r="T6" t="inlineStr">
@@ -1597,87 +1597,87 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
+          <t>15-May-2026</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>prereg</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>104</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>70</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
           <t>14-May-2026</t>
         </is>
       </c>
-      <c r="B7" t="inlineStr">
+      <c r="K7" t="inlineStr">
         <is>
           <t>prereg</t>
         </is>
       </c>
-      <c r="C7" t="inlineStr">
+      <c r="L7" t="inlineStr">
         <is>
           <t>104</t>
         </is>
       </c>
-      <c r="D7" t="inlineStr">
+      <c r="M7" t="inlineStr">
         <is>
           <t>3</t>
         </is>
       </c>
-      <c r="E7" t="inlineStr">
+      <c r="N7" t="inlineStr">
         <is>
           <t>70</t>
         </is>
       </c>
-      <c r="F7" t="inlineStr">
+      <c r="O7" t="inlineStr">
         <is>
           <t>30</t>
         </is>
       </c>
-      <c r="G7" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H7" t="inlineStr">
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Q7" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="J7" t="inlineStr">
+      <c r="S7" t="inlineStr">
         <is>
           <t>13-May-2026</t>
-        </is>
-      </c>
-      <c r="K7" t="inlineStr">
-        <is>
-          <t>prereg</t>
-        </is>
-      </c>
-      <c r="L7" t="inlineStr">
-        <is>
-          <t>104</t>
-        </is>
-      </c>
-      <c r="M7" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="N7" t="inlineStr">
-        <is>
-          <t>70</t>
-        </is>
-      </c>
-      <c r="O7" t="inlineStr">
-        <is>
-          <t>30</t>
-        </is>
-      </c>
-      <c r="P7" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="Q7" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="S7" t="inlineStr">
-        <is>
-          <t>12-May-2026</t>
         </is>
       </c>
       <c r="T7" t="inlineStr">
@@ -1743,87 +1743,87 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
+          <t>15-May-2026</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>residentui</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>33</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
           <t>14-May-2026</t>
         </is>
       </c>
-      <c r="B8" t="inlineStr">
+      <c r="K8" t="inlineStr">
         <is>
           <t>residentui</t>
         </is>
       </c>
-      <c r="C8" t="inlineStr">
+      <c r="L8" t="inlineStr">
         <is>
           <t>33</t>
         </is>
       </c>
-      <c r="D8" t="inlineStr">
+      <c r="M8" t="inlineStr">
         <is>
           <t>12</t>
         </is>
       </c>
-      <c r="E8" t="inlineStr">
+      <c r="N8" t="inlineStr">
         <is>
           <t>5</t>
         </is>
       </c>
-      <c r="F8" t="inlineStr">
+      <c r="O8" t="inlineStr">
         <is>
           <t>16</t>
         </is>
       </c>
-      <c r="G8" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H8" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="J8" t="inlineStr">
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Q8" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="S8" t="inlineStr">
         <is>
           <t>13-May-2026</t>
-        </is>
-      </c>
-      <c r="K8" t="inlineStr">
-        <is>
-          <t>residentui</t>
-        </is>
-      </c>
-      <c r="L8" t="inlineStr">
-        <is>
-          <t>33</t>
-        </is>
-      </c>
-      <c r="M8" t="inlineStr">
-        <is>
-          <t>12</t>
-        </is>
-      </c>
-      <c r="N8" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="O8" t="inlineStr">
-        <is>
-          <t>16</t>
-        </is>
-      </c>
-      <c r="P8" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="Q8" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="S8" t="inlineStr">
-        <is>
-          <t>12-May-2026</t>
         </is>
       </c>
       <c r="T8" t="inlineStr">

--- a/minio-report-tracker/xlxs/collab.xlsx
+++ b/minio-report-tracker/xlxs/collab.xlsx
@@ -598,7 +598,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AI8"/>
+  <dimension ref="A1:Q8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -614,28 +614,10 @@
     <col width="12" customWidth="1" min="11" max="11"/>
     <col width="5" customWidth="1" min="12" max="12"/>
     <col width="5" customWidth="1" min="13" max="13"/>
-    <col width="4" customWidth="1" min="14" max="14"/>
-    <col width="4" customWidth="1" min="15" max="15"/>
-    <col width="4" customWidth="1" min="16" max="16"/>
-    <col width="4" customWidth="1" min="17" max="17"/>
-    <col width="2" customWidth="1" min="18" max="18"/>
-    <col width="13" customWidth="1" min="19" max="19"/>
-    <col width="12" customWidth="1" min="20" max="20"/>
-    <col width="5" customWidth="1" min="21" max="21"/>
-    <col width="5" customWidth="1" min="22" max="22"/>
-    <col width="4" customWidth="1" min="23" max="23"/>
-    <col width="4" customWidth="1" min="24" max="24"/>
-    <col width="4" customWidth="1" min="25" max="25"/>
-    <col width="4" customWidth="1" min="26" max="26"/>
-    <col width="2" customWidth="1" min="27" max="27"/>
-    <col width="13" customWidth="1" min="28" max="28"/>
-    <col width="12" customWidth="1" min="29" max="29"/>
-    <col width="5" customWidth="1" min="30" max="30"/>
-    <col width="5" customWidth="1" min="31" max="31"/>
-    <col width="5" customWidth="1" min="32" max="32"/>
-    <col width="5" customWidth="1" min="33" max="33"/>
-    <col width="5" customWidth="1" min="34" max="34"/>
-    <col width="5" customWidth="1" min="35" max="35"/>
+    <col width="5" customWidth="1" min="14" max="14"/>
+    <col width="5" customWidth="1" min="15" max="15"/>
+    <col width="5" customWidth="1" min="16" max="16"/>
+    <col width="5" customWidth="1" min="17" max="17"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -719,244 +701,84 @@
           <t>KI</t>
         </is>
       </c>
-      <c r="S1" s="1" t="inlineStr">
-        <is>
-          <t>Date</t>
-        </is>
-      </c>
-      <c r="T1" s="1" t="inlineStr">
-        <is>
-          <t>Module</t>
-        </is>
-      </c>
-      <c r="U1" s="1" t="inlineStr">
-        <is>
-          <t>T</t>
-        </is>
-      </c>
-      <c r="V1" s="1" t="inlineStr">
-        <is>
-          <t>P</t>
-        </is>
-      </c>
-      <c r="W1" s="1" t="inlineStr">
-        <is>
-          <t>S</t>
-        </is>
-      </c>
-      <c r="X1" s="1" t="inlineStr">
-        <is>
-          <t>F</t>
-        </is>
-      </c>
-      <c r="Y1" s="1" t="inlineStr">
-        <is>
-          <t>I</t>
-        </is>
-      </c>
-      <c r="Z1" s="1" t="inlineStr">
-        <is>
-          <t>KI</t>
-        </is>
-      </c>
-      <c r="AB1" s="1" t="inlineStr">
-        <is>
-          <t>Date</t>
-        </is>
-      </c>
-      <c r="AC1" s="1" t="inlineStr">
-        <is>
-          <t>Module</t>
-        </is>
-      </c>
-      <c r="AD1" s="1" t="inlineStr">
-        <is>
-          <t>T</t>
-        </is>
-      </c>
-      <c r="AE1" s="1" t="inlineStr">
-        <is>
-          <t>P</t>
-        </is>
-      </c>
-      <c r="AF1" s="1" t="inlineStr">
-        <is>
-          <t>S</t>
-        </is>
-      </c>
-      <c r="AG1" s="1" t="inlineStr">
-        <is>
-          <t>F</t>
-        </is>
-      </c>
-      <c r="AH1" s="1" t="inlineStr">
-        <is>
-          <t>I</t>
-        </is>
-      </c>
-      <c r="AI1" s="1" t="inlineStr">
-        <is>
-          <t>KI</t>
-        </is>
-      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
+          <t>18-May-2026</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>auth</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>254</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>115</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>72</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>67</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
           <t>15-May-2026</t>
         </is>
       </c>
-      <c r="B2" t="inlineStr">
-        <is>
-          <t>auth</t>
-        </is>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>254</t>
-        </is>
-      </c>
-      <c r="D2" t="inlineStr">
-        <is>
-          <t>140</t>
-        </is>
-      </c>
-      <c r="E2" t="inlineStr">
-        <is>
-          <t>72</t>
-        </is>
-      </c>
-      <c r="F2" t="inlineStr">
-        <is>
-          <t>42</t>
-        </is>
-      </c>
-      <c r="G2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="J2" t="inlineStr">
-        <is>
-          <t>14-May-2026</t>
-        </is>
-      </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>auth</t>
+          <t>esignet</t>
         </is>
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>254</t>
+          <t>375</t>
         </is>
       </c>
       <c r="M2" t="inlineStr">
         <is>
-          <t>142</t>
+          <t>287</t>
         </is>
       </c>
       <c r="N2" t="inlineStr">
         <is>
-          <t>72</t>
+          <t>18</t>
         </is>
       </c>
       <c r="O2" t="inlineStr">
         <is>
-          <t>40</t>
+          <t>43</t>
         </is>
       </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>27</t>
         </is>
       </c>
       <c r="Q2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="S2" t="inlineStr">
-        <is>
-          <t>13-May-2026</t>
-        </is>
-      </c>
-      <c r="T2" t="inlineStr">
-        <is>
-          <t>auth</t>
-        </is>
-      </c>
-      <c r="U2" t="inlineStr">
-        <is>
-          <t>254</t>
-        </is>
-      </c>
-      <c r="V2" t="inlineStr">
-        <is>
-          <t>140</t>
-        </is>
-      </c>
-      <c r="W2" t="inlineStr">
-        <is>
-          <t>72</t>
-        </is>
-      </c>
-      <c r="X2" t="inlineStr">
-        <is>
-          <t>42</t>
-        </is>
-      </c>
-      <c r="Y2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>12-May-2026</t>
-        </is>
-      </c>
-      <c r="AC2" t="inlineStr">
-        <is>
-          <t>esignet</t>
-        </is>
-      </c>
-      <c r="AD2" t="inlineStr">
-        <is>
-          <t>375</t>
-        </is>
-      </c>
-      <c r="AE2" t="inlineStr">
-        <is>
-          <t>231</t>
-        </is>
-      </c>
-      <c r="AF2" t="inlineStr">
-        <is>
-          <t>40</t>
-        </is>
-      </c>
-      <c r="AG2" t="inlineStr">
-        <is>
-          <t>77</t>
-        </is>
-      </c>
-      <c r="AH2" t="inlineStr">
-        <is>
-          <t>27</t>
-        </is>
-      </c>
-      <c r="AI2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
@@ -965,160 +787,80 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
+          <t>18-May-2026</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>esignet</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>375</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>258</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>43</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>47</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>27</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
           <t>15-May-2026</t>
         </is>
       </c>
-      <c r="B3" t="inlineStr">
-        <is>
-          <t>esignet</t>
-        </is>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>375</t>
-        </is>
-      </c>
-      <c r="D3" t="inlineStr">
-        <is>
-          <t>287</t>
-        </is>
-      </c>
-      <c r="E3" t="inlineStr">
-        <is>
-          <t>18</t>
-        </is>
-      </c>
-      <c r="F3" t="inlineStr">
-        <is>
-          <t>43</t>
-        </is>
-      </c>
-      <c r="G3" t="inlineStr">
-        <is>
-          <t>27</t>
-        </is>
-      </c>
-      <c r="H3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="J3" t="inlineStr">
-        <is>
-          <t>14-May-2026</t>
-        </is>
-      </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>esignet</t>
+          <t>injiverify</t>
         </is>
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>375</t>
+          <t>53</t>
         </is>
       </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>281</t>
+          <t>0</t>
         </is>
       </c>
       <c r="N3" t="inlineStr">
         <is>
-          <t>31</t>
+          <t>23</t>
         </is>
       </c>
       <c r="O3" t="inlineStr">
         <is>
-          <t>36</t>
+          <t>30</t>
         </is>
       </c>
       <c r="P3" t="inlineStr">
         <is>
-          <t>27</t>
+          <t>0</t>
         </is>
       </c>
       <c r="Q3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="S3" t="inlineStr">
-        <is>
-          <t>13-May-2026</t>
-        </is>
-      </c>
-      <c r="T3" t="inlineStr">
-        <is>
-          <t>esignet</t>
-        </is>
-      </c>
-      <c r="U3" t="inlineStr">
-        <is>
-          <t>375</t>
-        </is>
-      </c>
-      <c r="V3" t="inlineStr">
-        <is>
-          <t>227</t>
-        </is>
-      </c>
-      <c r="W3" t="inlineStr">
-        <is>
-          <t>56</t>
-        </is>
-      </c>
-      <c r="X3" t="inlineStr">
-        <is>
-          <t>65</t>
-        </is>
-      </c>
-      <c r="Y3" t="inlineStr">
-        <is>
-          <t>27</t>
-        </is>
-      </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>12-May-2026</t>
-        </is>
-      </c>
-      <c r="AC3" t="inlineStr">
-        <is>
-          <t>injiverify</t>
-        </is>
-      </c>
-      <c r="AD3" t="inlineStr">
-        <is>
-          <t>53</t>
-        </is>
-      </c>
-      <c r="AE3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AF3" t="inlineStr">
-        <is>
-          <t>23</t>
-        </is>
-      </c>
-      <c r="AG3" t="inlineStr">
-        <is>
-          <t>30</t>
-        </is>
-      </c>
-      <c r="AH3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AI3" t="inlineStr">
         <is>
           <t>0</t>
         </is>
@@ -1127,160 +869,80 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
+          <t>18-May-2026</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>idrepo</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>152</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>101</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>51</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
           <t>15-May-2026</t>
         </is>
       </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>idrepo</t>
-        </is>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>152</t>
-        </is>
-      </c>
-      <c r="D4" t="inlineStr">
-        <is>
-          <t>101</t>
-        </is>
-      </c>
-      <c r="E4" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F4" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="G4" t="inlineStr">
-        <is>
-          <t>51</t>
-        </is>
-      </c>
-      <c r="H4" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="J4" t="inlineStr">
-        <is>
-          <t>14-May-2026</t>
-        </is>
-      </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>idrepo</t>
+          <t>prereg</t>
         </is>
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>152</t>
+          <t>104</t>
         </is>
       </c>
       <c r="M4" t="inlineStr">
         <is>
-          <t>98</t>
+          <t>3</t>
         </is>
       </c>
       <c r="N4" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>70</t>
         </is>
       </c>
       <c r="O4" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>30</t>
         </is>
       </c>
       <c r="P4" t="inlineStr">
         <is>
-          <t>51</t>
+          <t>0</t>
         </is>
       </c>
       <c r="Q4" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="S4" t="inlineStr">
-        <is>
-          <t>13-May-2026</t>
-        </is>
-      </c>
-      <c r="T4" t="inlineStr">
-        <is>
-          <t>idrepo</t>
-        </is>
-      </c>
-      <c r="U4" t="inlineStr">
-        <is>
-          <t>152</t>
-        </is>
-      </c>
-      <c r="V4" t="inlineStr">
-        <is>
-          <t>101</t>
-        </is>
-      </c>
-      <c r="W4" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="X4" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="Y4" t="inlineStr">
-        <is>
-          <t>51</t>
-        </is>
-      </c>
-      <c r="Z4" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB4" t="inlineStr">
-        <is>
-          <t>12-May-2026</t>
-        </is>
-      </c>
-      <c r="AC4" t="inlineStr">
-        <is>
-          <t>prereg</t>
-        </is>
-      </c>
-      <c r="AD4" t="inlineStr">
-        <is>
-          <t>104</t>
-        </is>
-      </c>
-      <c r="AE4" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="AF4" t="inlineStr">
-        <is>
-          <t>70</t>
-        </is>
-      </c>
-      <c r="AG4" t="inlineStr">
-        <is>
-          <t>30</t>
-        </is>
-      </c>
-      <c r="AH4" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AI4" t="inlineStr">
         <is>
           <t>1</t>
         </is>
@@ -1289,72 +951,72 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
+          <t>18-May-2026</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>injiverify</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>53</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>23</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
           <t>15-May-2026</t>
         </is>
       </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>injiverify</t>
-        </is>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>53</t>
-        </is>
-      </c>
-      <c r="D5" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="E5" t="inlineStr">
-        <is>
-          <t>23</t>
-        </is>
-      </c>
-      <c r="F5" t="inlineStr">
-        <is>
-          <t>30</t>
-        </is>
-      </c>
-      <c r="G5" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H5" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="J5" t="inlineStr">
-        <is>
-          <t>14-May-2026</t>
-        </is>
-      </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>injiverify</t>
+          <t>residentui</t>
         </is>
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>53</t>
+          <t>33</t>
         </is>
       </c>
       <c r="M5" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>12</t>
         </is>
       </c>
       <c r="N5" t="inlineStr">
         <is>
-          <t>23</t>
+          <t>5</t>
         </is>
       </c>
       <c r="O5" t="inlineStr">
         <is>
-          <t>30</t>
+          <t>16</t>
         </is>
       </c>
       <c r="P5" t="inlineStr">
@@ -1363,86 +1025,6 @@
         </is>
       </c>
       <c r="Q5" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="S5" t="inlineStr">
-        <is>
-          <t>13-May-2026</t>
-        </is>
-      </c>
-      <c r="T5" t="inlineStr">
-        <is>
-          <t>injiverify</t>
-        </is>
-      </c>
-      <c r="U5" t="inlineStr">
-        <is>
-          <t>53</t>
-        </is>
-      </c>
-      <c r="V5" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="W5" t="inlineStr">
-        <is>
-          <t>23</t>
-        </is>
-      </c>
-      <c r="X5" t="inlineStr">
-        <is>
-          <t>30</t>
-        </is>
-      </c>
-      <c r="Y5" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="Z5" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB5" t="inlineStr">
-        <is>
-          <t>12-May-2026</t>
-        </is>
-      </c>
-      <c r="AC5" t="inlineStr">
-        <is>
-          <t>residentui</t>
-        </is>
-      </c>
-      <c r="AD5" t="inlineStr">
-        <is>
-          <t>33</t>
-        </is>
-      </c>
-      <c r="AE5" t="inlineStr">
-        <is>
-          <t>12</t>
-        </is>
-      </c>
-      <c r="AF5" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="AG5" t="inlineStr">
-        <is>
-          <t>16</t>
-        </is>
-      </c>
-      <c r="AH5" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AI5" t="inlineStr">
         <is>
           <t>0</t>
         </is>
@@ -1451,7 +1033,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>15-May-2026</t>
+          <t>18-May-2026</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -1466,17 +1048,17 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>58</t>
+          <t>63</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>2</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>2</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
@@ -1489,115 +1071,35 @@
           <t>2</t>
         </is>
       </c>
-      <c r="J6" t="inlineStr">
-        <is>
-          <t>14-May-2026</t>
-        </is>
-      </c>
-      <c r="K6" t="inlineStr">
-        <is>
-          <t>mimoto</t>
-        </is>
-      </c>
-      <c r="L6" t="inlineStr">
-        <is>
-          <t>79</t>
-        </is>
-      </c>
-      <c r="M6" t="inlineStr">
-        <is>
-          <t>58</t>
-        </is>
-      </c>
-      <c r="N6" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="O6" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="P6" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="Q6" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="S6" t="inlineStr">
-        <is>
-          <t>13-May-2026</t>
-        </is>
-      </c>
-      <c r="T6" t="inlineStr">
-        <is>
-          <t>mimoto</t>
-        </is>
-      </c>
-      <c r="U6" t="inlineStr">
-        <is>
-          <t>79</t>
-        </is>
-      </c>
-      <c r="V6" t="inlineStr">
-        <is>
-          <t>58</t>
-        </is>
-      </c>
-      <c r="W6" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="X6" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="Y6" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="Z6" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="AB6" t="n">
-        <v/>
-      </c>
-      <c r="AC6" t="n">
-        <v/>
-      </c>
-      <c r="AD6" t="n">
-        <v/>
-      </c>
-      <c r="AE6" t="n">
-        <v/>
-      </c>
-      <c r="AF6" t="n">
-        <v/>
-      </c>
-      <c r="AG6" t="n">
-        <v/>
-      </c>
-      <c r="AH6" t="n">
-        <v/>
-      </c>
-      <c r="AI6" t="n">
+      <c r="J6" t="n">
+        <v/>
+      </c>
+      <c r="K6" t="n">
+        <v/>
+      </c>
+      <c r="L6" t="n">
+        <v/>
+      </c>
+      <c r="M6" t="n">
+        <v/>
+      </c>
+      <c r="N6" t="n">
+        <v/>
+      </c>
+      <c r="O6" t="n">
+        <v/>
+      </c>
+      <c r="P6" t="n">
+        <v/>
+      </c>
+      <c r="Q6" t="n">
         <v/>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>15-May-2026</t>
+          <t>18-May-2026</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -1635,115 +1137,35 @@
           <t>1</t>
         </is>
       </c>
-      <c r="J7" t="inlineStr">
-        <is>
-          <t>14-May-2026</t>
-        </is>
-      </c>
-      <c r="K7" t="inlineStr">
-        <is>
-          <t>prereg</t>
-        </is>
-      </c>
-      <c r="L7" t="inlineStr">
-        <is>
-          <t>104</t>
-        </is>
-      </c>
-      <c r="M7" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="N7" t="inlineStr">
-        <is>
-          <t>70</t>
-        </is>
-      </c>
-      <c r="O7" t="inlineStr">
-        <is>
-          <t>30</t>
-        </is>
-      </c>
-      <c r="P7" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="Q7" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="S7" t="inlineStr">
-        <is>
-          <t>13-May-2026</t>
-        </is>
-      </c>
-      <c r="T7" t="inlineStr">
-        <is>
-          <t>prereg</t>
-        </is>
-      </c>
-      <c r="U7" t="inlineStr">
-        <is>
-          <t>104</t>
-        </is>
-      </c>
-      <c r="V7" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="W7" t="inlineStr">
-        <is>
-          <t>70</t>
-        </is>
-      </c>
-      <c r="X7" t="inlineStr">
-        <is>
-          <t>30</t>
-        </is>
-      </c>
-      <c r="Y7" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="Z7" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="AB7" t="n">
-        <v/>
-      </c>
-      <c r="AC7" t="n">
-        <v/>
-      </c>
-      <c r="AD7" t="n">
-        <v/>
-      </c>
-      <c r="AE7" t="n">
-        <v/>
-      </c>
-      <c r="AF7" t="n">
-        <v/>
-      </c>
-      <c r="AG7" t="n">
-        <v/>
-      </c>
-      <c r="AH7" t="n">
-        <v/>
-      </c>
-      <c r="AI7" t="n">
+      <c r="J7" t="n">
+        <v/>
+      </c>
+      <c r="K7" t="n">
+        <v/>
+      </c>
+      <c r="L7" t="n">
+        <v/>
+      </c>
+      <c r="M7" t="n">
+        <v/>
+      </c>
+      <c r="N7" t="n">
+        <v/>
+      </c>
+      <c r="O7" t="n">
+        <v/>
+      </c>
+      <c r="P7" t="n">
+        <v/>
+      </c>
+      <c r="Q7" t="n">
         <v/>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>15-May-2026</t>
+          <t>18-May-2026</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1781,108 +1203,28 @@
           <t>0</t>
         </is>
       </c>
-      <c r="J8" t="inlineStr">
-        <is>
-          <t>14-May-2026</t>
-        </is>
-      </c>
-      <c r="K8" t="inlineStr">
-        <is>
-          <t>residentui</t>
-        </is>
-      </c>
-      <c r="L8" t="inlineStr">
-        <is>
-          <t>33</t>
-        </is>
-      </c>
-      <c r="M8" t="inlineStr">
-        <is>
-          <t>12</t>
-        </is>
-      </c>
-      <c r="N8" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="O8" t="inlineStr">
-        <is>
-          <t>16</t>
-        </is>
-      </c>
-      <c r="P8" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="Q8" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="S8" t="inlineStr">
-        <is>
-          <t>13-May-2026</t>
-        </is>
-      </c>
-      <c r="T8" t="inlineStr">
-        <is>
-          <t>residentui</t>
-        </is>
-      </c>
-      <c r="U8" t="inlineStr">
-        <is>
-          <t>33</t>
-        </is>
-      </c>
-      <c r="V8" t="inlineStr">
-        <is>
-          <t>12</t>
-        </is>
-      </c>
-      <c r="W8" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="X8" t="inlineStr">
-        <is>
-          <t>16</t>
-        </is>
-      </c>
-      <c r="Y8" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="Z8" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB8" t="n">
-        <v/>
-      </c>
-      <c r="AC8" t="n">
-        <v/>
-      </c>
-      <c r="AD8" t="n">
-        <v/>
-      </c>
-      <c r="AE8" t="n">
-        <v/>
-      </c>
-      <c r="AF8" t="n">
-        <v/>
-      </c>
-      <c r="AG8" t="n">
-        <v/>
-      </c>
-      <c r="AH8" t="n">
-        <v/>
-      </c>
-      <c r="AI8" t="n">
+      <c r="J8" t="n">
+        <v/>
+      </c>
+      <c r="K8" t="n">
+        <v/>
+      </c>
+      <c r="L8" t="n">
+        <v/>
+      </c>
+      <c r="M8" t="n">
+        <v/>
+      </c>
+      <c r="N8" t="n">
+        <v/>
+      </c>
+      <c r="O8" t="n">
+        <v/>
+      </c>
+      <c r="P8" t="n">
+        <v/>
+      </c>
+      <c r="Q8" t="n">
         <v/>
       </c>
     </row>

--- a/minio-report-tracker/xlxs/collab.xlsx
+++ b/minio-report-tracker/xlxs/collab.xlsx
@@ -614,10 +614,10 @@
     <col width="12" customWidth="1" min="11" max="11"/>
     <col width="5" customWidth="1" min="12" max="12"/>
     <col width="5" customWidth="1" min="13" max="13"/>
-    <col width="5" customWidth="1" min="14" max="14"/>
-    <col width="5" customWidth="1" min="15" max="15"/>
-    <col width="5" customWidth="1" min="16" max="16"/>
-    <col width="5" customWidth="1" min="17" max="17"/>
+    <col width="4" customWidth="1" min="14" max="14"/>
+    <col width="4" customWidth="1" min="15" max="15"/>
+    <col width="4" customWidth="1" min="16" max="16"/>
+    <col width="4" customWidth="1" min="17" max="17"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -705,77 +705,77 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
+          <t>19-May-2026</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>auth</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>254</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>142</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>72</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>40</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
           <t>18-May-2026</t>
         </is>
       </c>
-      <c r="B2" t="inlineStr">
+      <c r="K2" t="inlineStr">
         <is>
           <t>auth</t>
         </is>
       </c>
-      <c r="C2" t="inlineStr">
+      <c r="L2" t="inlineStr">
         <is>
           <t>254</t>
         </is>
       </c>
-      <c r="D2" t="inlineStr">
+      <c r="M2" t="inlineStr">
         <is>
           <t>115</t>
         </is>
       </c>
-      <c r="E2" t="inlineStr">
+      <c r="N2" t="inlineStr">
         <is>
           <t>72</t>
         </is>
       </c>
-      <c r="F2" t="inlineStr">
+      <c r="O2" t="inlineStr">
         <is>
           <t>67</t>
         </is>
       </c>
-      <c r="G2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="J2" t="inlineStr">
-        <is>
-          <t>15-May-2026</t>
-        </is>
-      </c>
-      <c r="K2" t="inlineStr">
-        <is>
-          <t>esignet</t>
-        </is>
-      </c>
-      <c r="L2" t="inlineStr">
-        <is>
-          <t>375</t>
-        </is>
-      </c>
-      <c r="M2" t="inlineStr">
-        <is>
-          <t>287</t>
-        </is>
-      </c>
-      <c r="N2" t="inlineStr">
-        <is>
-          <t>18</t>
-        </is>
-      </c>
-      <c r="O2" t="inlineStr">
-        <is>
-          <t>43</t>
-        </is>
-      </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>27</t>
+          <t>0</t>
         </is>
       </c>
       <c r="Q2" t="inlineStr">
@@ -787,77 +787,77 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
+          <t>19-May-2026</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>esignet</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>375</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>280</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>37</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>31</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>27</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
           <t>18-May-2026</t>
         </is>
       </c>
-      <c r="B3" t="inlineStr">
+      <c r="K3" t="inlineStr">
         <is>
           <t>esignet</t>
         </is>
       </c>
-      <c r="C3" t="inlineStr">
+      <c r="L3" t="inlineStr">
         <is>
           <t>375</t>
         </is>
       </c>
-      <c r="D3" t="inlineStr">
+      <c r="M3" t="inlineStr">
         <is>
           <t>258</t>
         </is>
       </c>
-      <c r="E3" t="inlineStr">
+      <c r="N3" t="inlineStr">
         <is>
           <t>43</t>
         </is>
       </c>
-      <c r="F3" t="inlineStr">
+      <c r="O3" t="inlineStr">
         <is>
           <t>47</t>
         </is>
       </c>
-      <c r="G3" t="inlineStr">
+      <c r="P3" t="inlineStr">
         <is>
           <t>27</t>
-        </is>
-      </c>
-      <c r="H3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="J3" t="inlineStr">
-        <is>
-          <t>15-May-2026</t>
-        </is>
-      </c>
-      <c r="K3" t="inlineStr">
-        <is>
-          <t>injiverify</t>
-        </is>
-      </c>
-      <c r="L3" t="inlineStr">
-        <is>
-          <t>53</t>
-        </is>
-      </c>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="N3" t="inlineStr">
-        <is>
-          <t>23</t>
-        </is>
-      </c>
-      <c r="O3" t="inlineStr">
-        <is>
-          <t>30</t>
-        </is>
-      </c>
-      <c r="P3" t="inlineStr">
-        <is>
-          <t>0</t>
         </is>
       </c>
       <c r="Q3" t="inlineStr">
@@ -869,154 +869,154 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
+          <t>19-May-2026</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>idrepo</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>152</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>101</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>51</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
           <t>18-May-2026</t>
         </is>
       </c>
-      <c r="B4" t="inlineStr">
+      <c r="K4" t="inlineStr">
         <is>
           <t>idrepo</t>
         </is>
       </c>
-      <c r="C4" t="inlineStr">
+      <c r="L4" t="inlineStr">
         <is>
           <t>152</t>
         </is>
       </c>
-      <c r="D4" t="inlineStr">
+      <c r="M4" t="inlineStr">
         <is>
           <t>101</t>
         </is>
       </c>
-      <c r="E4" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F4" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="G4" t="inlineStr">
+      <c r="N4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P4" t="inlineStr">
         <is>
           <t>51</t>
         </is>
       </c>
-      <c r="H4" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="J4" t="inlineStr">
-        <is>
-          <t>15-May-2026</t>
-        </is>
-      </c>
-      <c r="K4" t="inlineStr">
-        <is>
-          <t>prereg</t>
-        </is>
-      </c>
-      <c r="L4" t="inlineStr">
-        <is>
-          <t>104</t>
-        </is>
-      </c>
-      <c r="M4" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="N4" t="inlineStr">
-        <is>
-          <t>70</t>
-        </is>
-      </c>
-      <c r="O4" t="inlineStr">
-        <is>
-          <t>30</t>
-        </is>
-      </c>
-      <c r="P4" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
       <c r="Q4" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
+          <t>19-May-2026</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>injiverify</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>53</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>23</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
           <t>18-May-2026</t>
         </is>
       </c>
-      <c r="B5" t="inlineStr">
+      <c r="K5" t="inlineStr">
         <is>
           <t>injiverify</t>
         </is>
       </c>
-      <c r="C5" t="inlineStr">
+      <c r="L5" t="inlineStr">
         <is>
           <t>53</t>
         </is>
       </c>
-      <c r="D5" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="E5" t="inlineStr">
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="N5" t="inlineStr">
         <is>
           <t>23</t>
         </is>
       </c>
-      <c r="F5" t="inlineStr">
+      <c r="O5" t="inlineStr">
         <is>
           <t>30</t>
-        </is>
-      </c>
-      <c r="G5" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H5" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="J5" t="inlineStr">
-        <is>
-          <t>15-May-2026</t>
-        </is>
-      </c>
-      <c r="K5" t="inlineStr">
-        <is>
-          <t>residentui</t>
-        </is>
-      </c>
-      <c r="L5" t="inlineStr">
-        <is>
-          <t>33</t>
-        </is>
-      </c>
-      <c r="M5" t="inlineStr">
-        <is>
-          <t>12</t>
-        </is>
-      </c>
-      <c r="N5" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="O5" t="inlineStr">
-        <is>
-          <t>16</t>
         </is>
       </c>
       <c r="P5" t="inlineStr">
@@ -1033,199 +1033,247 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
+          <t>19-May-2026</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>mimoto</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>79</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>58</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
           <t>18-May-2026</t>
         </is>
       </c>
-      <c r="B6" t="inlineStr">
+      <c r="K6" t="inlineStr">
         <is>
           <t>mimoto</t>
         </is>
       </c>
-      <c r="C6" t="inlineStr">
+      <c r="L6" t="inlineStr">
         <is>
           <t>79</t>
         </is>
       </c>
-      <c r="D6" t="inlineStr">
+      <c r="M6" t="inlineStr">
         <is>
           <t>63</t>
         </is>
       </c>
-      <c r="E6" t="inlineStr">
+      <c r="N6" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="F6" t="inlineStr">
+      <c r="O6" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="G6" t="inlineStr">
+      <c r="P6" t="inlineStr">
         <is>
           <t>10</t>
         </is>
       </c>
-      <c r="H6" t="inlineStr">
+      <c r="Q6" t="inlineStr">
         <is>
           <t>2</t>
         </is>
-      </c>
-      <c r="J6" t="n">
-        <v/>
-      </c>
-      <c r="K6" t="n">
-        <v/>
-      </c>
-      <c r="L6" t="n">
-        <v/>
-      </c>
-      <c r="M6" t="n">
-        <v/>
-      </c>
-      <c r="N6" t="n">
-        <v/>
-      </c>
-      <c r="O6" t="n">
-        <v/>
-      </c>
-      <c r="P6" t="n">
-        <v/>
-      </c>
-      <c r="Q6" t="n">
-        <v/>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
+          <t>19-May-2026</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>prereg</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>104</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>70</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
           <t>18-May-2026</t>
         </is>
       </c>
-      <c r="B7" t="inlineStr">
+      <c r="K7" t="inlineStr">
         <is>
           <t>prereg</t>
         </is>
       </c>
-      <c r="C7" t="inlineStr">
+      <c r="L7" t="inlineStr">
         <is>
           <t>104</t>
         </is>
       </c>
-      <c r="D7" t="inlineStr">
+      <c r="M7" t="inlineStr">
         <is>
           <t>3</t>
         </is>
       </c>
-      <c r="E7" t="inlineStr">
+      <c r="N7" t="inlineStr">
         <is>
           <t>70</t>
         </is>
       </c>
-      <c r="F7" t="inlineStr">
+      <c r="O7" t="inlineStr">
         <is>
           <t>30</t>
         </is>
       </c>
-      <c r="G7" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H7" t="inlineStr">
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Q7" t="inlineStr">
         <is>
           <t>1</t>
         </is>
-      </c>
-      <c r="J7" t="n">
-        <v/>
-      </c>
-      <c r="K7" t="n">
-        <v/>
-      </c>
-      <c r="L7" t="n">
-        <v/>
-      </c>
-      <c r="M7" t="n">
-        <v/>
-      </c>
-      <c r="N7" t="n">
-        <v/>
-      </c>
-      <c r="O7" t="n">
-        <v/>
-      </c>
-      <c r="P7" t="n">
-        <v/>
-      </c>
-      <c r="Q7" t="n">
-        <v/>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
+          <t>19-May-2026</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>residentui</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>33</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
           <t>18-May-2026</t>
         </is>
       </c>
-      <c r="B8" t="inlineStr">
+      <c r="K8" t="inlineStr">
         <is>
           <t>residentui</t>
         </is>
       </c>
-      <c r="C8" t="inlineStr">
+      <c r="L8" t="inlineStr">
         <is>
           <t>33</t>
         </is>
       </c>
-      <c r="D8" t="inlineStr">
+      <c r="M8" t="inlineStr">
         <is>
           <t>12</t>
         </is>
       </c>
-      <c r="E8" t="inlineStr">
+      <c r="N8" t="inlineStr">
         <is>
           <t>5</t>
         </is>
       </c>
-      <c r="F8" t="inlineStr">
+      <c r="O8" t="inlineStr">
         <is>
           <t>16</t>
         </is>
       </c>
-      <c r="G8" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H8" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="J8" t="n">
-        <v/>
-      </c>
-      <c r="K8" t="n">
-        <v/>
-      </c>
-      <c r="L8" t="n">
-        <v/>
-      </c>
-      <c r="M8" t="n">
-        <v/>
-      </c>
-      <c r="N8" t="n">
-        <v/>
-      </c>
-      <c r="O8" t="n">
-        <v/>
-      </c>
-      <c r="P8" t="n">
-        <v/>
-      </c>
-      <c r="Q8" t="n">
-        <v/>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Q8" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
     </row>
   </sheetData>

--- a/minio-report-tracker/xlxs/collab.xlsx
+++ b/minio-report-tracker/xlxs/collab.xlsx
@@ -598,7 +598,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q8"/>
+  <dimension ref="A1:Z8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -618,6 +618,15 @@
     <col width="4" customWidth="1" min="15" max="15"/>
     <col width="4" customWidth="1" min="16" max="16"/>
     <col width="4" customWidth="1" min="17" max="17"/>
+    <col width="2" customWidth="1" min="18" max="18"/>
+    <col width="13" customWidth="1" min="19" max="19"/>
+    <col width="12" customWidth="1" min="20" max="20"/>
+    <col width="5" customWidth="1" min="21" max="21"/>
+    <col width="5" customWidth="1" min="22" max="22"/>
+    <col width="4" customWidth="1" min="23" max="23"/>
+    <col width="4" customWidth="1" min="24" max="24"/>
+    <col width="4" customWidth="1" min="25" max="25"/>
+    <col width="4" customWidth="1" min="26" max="26"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -701,84 +710,164 @@
           <t>KI</t>
         </is>
       </c>
+      <c r="S1" s="1" t="inlineStr">
+        <is>
+          <t>Date</t>
+        </is>
+      </c>
+      <c r="T1" s="1" t="inlineStr">
+        <is>
+          <t>Module</t>
+        </is>
+      </c>
+      <c r="U1" s="1" t="inlineStr">
+        <is>
+          <t>T</t>
+        </is>
+      </c>
+      <c r="V1" s="1" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
+      <c r="W1" s="1" t="inlineStr">
+        <is>
+          <t>S</t>
+        </is>
+      </c>
+      <c r="X1" s="1" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
+      <c r="Y1" s="1" t="inlineStr">
+        <is>
+          <t>I</t>
+        </is>
+      </c>
+      <c r="Z1" s="1" t="inlineStr">
+        <is>
+          <t>KI</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
+          <t>20-May-2026</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>auth</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>254</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>186</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>62</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
           <t>19-May-2026</t>
         </is>
       </c>
-      <c r="B2" t="inlineStr">
+      <c r="K2" t="inlineStr">
         <is>
           <t>auth</t>
         </is>
       </c>
-      <c r="C2" t="inlineStr">
+      <c r="L2" t="inlineStr">
         <is>
           <t>254</t>
         </is>
       </c>
-      <c r="D2" t="inlineStr">
+      <c r="M2" t="inlineStr">
         <is>
           <t>142</t>
         </is>
       </c>
-      <c r="E2" t="inlineStr">
+      <c r="N2" t="inlineStr">
         <is>
           <t>72</t>
         </is>
       </c>
-      <c r="F2" t="inlineStr">
+      <c r="O2" t="inlineStr">
         <is>
           <t>40</t>
         </is>
       </c>
-      <c r="G2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="J2" t="inlineStr">
+      <c r="P2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Q2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="S2" t="inlineStr">
         <is>
           <t>18-May-2026</t>
         </is>
       </c>
-      <c r="K2" t="inlineStr">
+      <c r="T2" t="inlineStr">
         <is>
           <t>auth</t>
         </is>
       </c>
-      <c r="L2" t="inlineStr">
+      <c r="U2" t="inlineStr">
         <is>
           <t>254</t>
         </is>
       </c>
-      <c r="M2" t="inlineStr">
+      <c r="V2" t="inlineStr">
         <is>
           <t>115</t>
         </is>
       </c>
-      <c r="N2" t="inlineStr">
+      <c r="W2" t="inlineStr">
         <is>
           <t>72</t>
         </is>
       </c>
-      <c r="O2" t="inlineStr">
+      <c r="X2" t="inlineStr">
         <is>
           <t>67</t>
         </is>
       </c>
-      <c r="P2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="Q2" t="inlineStr">
+      <c r="Y2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Z2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
@@ -787,80 +876,120 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
+          <t>20-May-2026</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>esignet</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>375</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>281</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>33</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>34</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>27</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
           <t>19-May-2026</t>
         </is>
       </c>
-      <c r="B3" t="inlineStr">
+      <c r="K3" t="inlineStr">
         <is>
           <t>esignet</t>
         </is>
       </c>
-      <c r="C3" t="inlineStr">
+      <c r="L3" t="inlineStr">
         <is>
           <t>375</t>
         </is>
       </c>
-      <c r="D3" t="inlineStr">
+      <c r="M3" t="inlineStr">
         <is>
           <t>280</t>
         </is>
       </c>
-      <c r="E3" t="inlineStr">
+      <c r="N3" t="inlineStr">
         <is>
           <t>37</t>
         </is>
       </c>
-      <c r="F3" t="inlineStr">
+      <c r="O3" t="inlineStr">
         <is>
           <t>31</t>
         </is>
       </c>
-      <c r="G3" t="inlineStr">
+      <c r="P3" t="inlineStr">
         <is>
           <t>27</t>
         </is>
       </c>
-      <c r="H3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="J3" t="inlineStr">
+      <c r="Q3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="S3" t="inlineStr">
         <is>
           <t>18-May-2026</t>
         </is>
       </c>
-      <c r="K3" t="inlineStr">
+      <c r="T3" t="inlineStr">
         <is>
           <t>esignet</t>
         </is>
       </c>
-      <c r="L3" t="inlineStr">
+      <c r="U3" t="inlineStr">
         <is>
           <t>375</t>
         </is>
       </c>
-      <c r="M3" t="inlineStr">
+      <c r="V3" t="inlineStr">
         <is>
           <t>258</t>
         </is>
       </c>
-      <c r="N3" t="inlineStr">
+      <c r="W3" t="inlineStr">
         <is>
           <t>43</t>
         </is>
       </c>
-      <c r="O3" t="inlineStr">
+      <c r="X3" t="inlineStr">
         <is>
           <t>47</t>
         </is>
       </c>
-      <c r="P3" t="inlineStr">
+      <c r="Y3" t="inlineStr">
         <is>
           <t>27</t>
         </is>
       </c>
-      <c r="Q3" t="inlineStr">
+      <c r="Z3" t="inlineStr">
         <is>
           <t>0</t>
         </is>
@@ -869,80 +998,120 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
+          <t>20-May-2026</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>idrepo</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>152</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>101</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>51</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
           <t>19-May-2026</t>
         </is>
       </c>
-      <c r="B4" t="inlineStr">
+      <c r="K4" t="inlineStr">
         <is>
           <t>idrepo</t>
         </is>
       </c>
-      <c r="C4" t="inlineStr">
+      <c r="L4" t="inlineStr">
         <is>
           <t>152</t>
         </is>
       </c>
-      <c r="D4" t="inlineStr">
+      <c r="M4" t="inlineStr">
         <is>
           <t>101</t>
         </is>
       </c>
-      <c r="E4" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F4" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="G4" t="inlineStr">
+      <c r="N4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P4" t="inlineStr">
         <is>
           <t>51</t>
         </is>
       </c>
-      <c r="H4" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="J4" t="inlineStr">
+      <c r="Q4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="S4" t="inlineStr">
         <is>
           <t>18-May-2026</t>
         </is>
       </c>
-      <c r="K4" t="inlineStr">
+      <c r="T4" t="inlineStr">
         <is>
           <t>idrepo</t>
         </is>
       </c>
-      <c r="L4" t="inlineStr">
+      <c r="U4" t="inlineStr">
         <is>
           <t>152</t>
         </is>
       </c>
-      <c r="M4" t="inlineStr">
+      <c r="V4" t="inlineStr">
         <is>
           <t>101</t>
         </is>
       </c>
-      <c r="N4" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="O4" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="P4" t="inlineStr">
+      <c r="W4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="X4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Y4" t="inlineStr">
         <is>
           <t>51</t>
         </is>
       </c>
-      <c r="Q4" t="inlineStr">
+      <c r="Z4" t="inlineStr">
         <is>
           <t>0</t>
         </is>
@@ -951,80 +1120,120 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
+          <t>20-May-2026</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>injiverify</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>53</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>23</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
           <t>19-May-2026</t>
         </is>
       </c>
-      <c r="B5" t="inlineStr">
+      <c r="K5" t="inlineStr">
         <is>
           <t>injiverify</t>
         </is>
       </c>
-      <c r="C5" t="inlineStr">
+      <c r="L5" t="inlineStr">
         <is>
           <t>53</t>
         </is>
       </c>
-      <c r="D5" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="E5" t="inlineStr">
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="N5" t="inlineStr">
         <is>
           <t>23</t>
         </is>
       </c>
-      <c r="F5" t="inlineStr">
+      <c r="O5" t="inlineStr">
         <is>
           <t>30</t>
         </is>
       </c>
-      <c r="G5" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H5" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="J5" t="inlineStr">
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Q5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="S5" t="inlineStr">
         <is>
           <t>18-May-2026</t>
         </is>
       </c>
-      <c r="K5" t="inlineStr">
+      <c r="T5" t="inlineStr">
         <is>
           <t>injiverify</t>
         </is>
       </c>
-      <c r="L5" t="inlineStr">
+      <c r="U5" t="inlineStr">
         <is>
           <t>53</t>
         </is>
       </c>
-      <c r="M5" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="N5" t="inlineStr">
+      <c r="V5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="W5" t="inlineStr">
         <is>
           <t>23</t>
         </is>
       </c>
-      <c r="O5" t="inlineStr">
+      <c r="X5" t="inlineStr">
         <is>
           <t>30</t>
         </is>
       </c>
-      <c r="P5" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="Q5" t="inlineStr">
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Z5" t="inlineStr">
         <is>
           <t>0</t>
         </is>
@@ -1033,80 +1242,120 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
+          <t>20-May-2026</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>mimoto</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>79</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>59</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
           <t>19-May-2026</t>
         </is>
       </c>
-      <c r="B6" t="inlineStr">
+      <c r="K6" t="inlineStr">
         <is>
           <t>mimoto</t>
         </is>
       </c>
-      <c r="C6" t="inlineStr">
+      <c r="L6" t="inlineStr">
         <is>
           <t>79</t>
         </is>
       </c>
-      <c r="D6" t="inlineStr">
+      <c r="M6" t="inlineStr">
         <is>
           <t>58</t>
         </is>
       </c>
-      <c r="E6" t="inlineStr">
+      <c r="N6" t="inlineStr">
         <is>
           <t>4</t>
         </is>
       </c>
-      <c r="F6" t="inlineStr">
+      <c r="O6" t="inlineStr">
         <is>
           <t>5</t>
         </is>
       </c>
-      <c r="G6" t="inlineStr">
+      <c r="P6" t="inlineStr">
         <is>
           <t>10</t>
         </is>
       </c>
-      <c r="H6" t="inlineStr">
+      <c r="Q6" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="J6" t="inlineStr">
+      <c r="S6" t="inlineStr">
         <is>
           <t>18-May-2026</t>
         </is>
       </c>
-      <c r="K6" t="inlineStr">
+      <c r="T6" t="inlineStr">
         <is>
           <t>mimoto</t>
         </is>
       </c>
-      <c r="L6" t="inlineStr">
+      <c r="U6" t="inlineStr">
         <is>
           <t>79</t>
         </is>
       </c>
-      <c r="M6" t="inlineStr">
+      <c r="V6" t="inlineStr">
         <is>
           <t>63</t>
         </is>
       </c>
-      <c r="N6" t="inlineStr">
+      <c r="W6" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="O6" t="inlineStr">
+      <c r="X6" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="P6" t="inlineStr">
+      <c r="Y6" t="inlineStr">
         <is>
           <t>10</t>
         </is>
       </c>
-      <c r="Q6" t="inlineStr">
+      <c r="Z6" t="inlineStr">
         <is>
           <t>2</t>
         </is>
@@ -1115,80 +1364,120 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
+          <t>20-May-2026</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>prereg</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>104</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>70</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
           <t>19-May-2026</t>
         </is>
       </c>
-      <c r="B7" t="inlineStr">
+      <c r="K7" t="inlineStr">
         <is>
           <t>prereg</t>
         </is>
       </c>
-      <c r="C7" t="inlineStr">
+      <c r="L7" t="inlineStr">
         <is>
           <t>104</t>
         </is>
       </c>
-      <c r="D7" t="inlineStr">
+      <c r="M7" t="inlineStr">
         <is>
           <t>3</t>
         </is>
       </c>
-      <c r="E7" t="inlineStr">
+      <c r="N7" t="inlineStr">
         <is>
           <t>70</t>
         </is>
       </c>
-      <c r="F7" t="inlineStr">
+      <c r="O7" t="inlineStr">
         <is>
           <t>30</t>
         </is>
       </c>
-      <c r="G7" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H7" t="inlineStr">
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Q7" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="J7" t="inlineStr">
+      <c r="S7" t="inlineStr">
         <is>
           <t>18-May-2026</t>
         </is>
       </c>
-      <c r="K7" t="inlineStr">
+      <c r="T7" t="inlineStr">
         <is>
           <t>prereg</t>
         </is>
       </c>
-      <c r="L7" t="inlineStr">
+      <c r="U7" t="inlineStr">
         <is>
           <t>104</t>
         </is>
       </c>
-      <c r="M7" t="inlineStr">
+      <c r="V7" t="inlineStr">
         <is>
           <t>3</t>
         </is>
       </c>
-      <c r="N7" t="inlineStr">
+      <c r="W7" t="inlineStr">
         <is>
           <t>70</t>
         </is>
       </c>
-      <c r="O7" t="inlineStr">
+      <c r="X7" t="inlineStr">
         <is>
           <t>30</t>
         </is>
       </c>
-      <c r="P7" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="Q7" t="inlineStr">
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Z7" t="inlineStr">
         <is>
           <t>1</t>
         </is>
@@ -1197,80 +1486,120 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
+          <t>20-May-2026</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>residentui</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>33</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
           <t>19-May-2026</t>
         </is>
       </c>
-      <c r="B8" t="inlineStr">
+      <c r="K8" t="inlineStr">
         <is>
           <t>residentui</t>
         </is>
       </c>
-      <c r="C8" t="inlineStr">
+      <c r="L8" t="inlineStr">
         <is>
           <t>33</t>
         </is>
       </c>
-      <c r="D8" t="inlineStr">
+      <c r="M8" t="inlineStr">
         <is>
           <t>12</t>
         </is>
       </c>
-      <c r="E8" t="inlineStr">
+      <c r="N8" t="inlineStr">
         <is>
           <t>5</t>
         </is>
       </c>
-      <c r="F8" t="inlineStr">
+      <c r="O8" t="inlineStr">
         <is>
           <t>16</t>
         </is>
       </c>
-      <c r="G8" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H8" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="J8" t="inlineStr">
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Q8" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="S8" t="inlineStr">
         <is>
           <t>18-May-2026</t>
         </is>
       </c>
-      <c r="K8" t="inlineStr">
+      <c r="T8" t="inlineStr">
         <is>
           <t>residentui</t>
         </is>
       </c>
-      <c r="L8" t="inlineStr">
+      <c r="U8" t="inlineStr">
         <is>
           <t>33</t>
         </is>
       </c>
-      <c r="M8" t="inlineStr">
+      <c r="V8" t="inlineStr">
         <is>
           <t>12</t>
         </is>
       </c>
-      <c r="N8" t="inlineStr">
+      <c r="W8" t="inlineStr">
         <is>
           <t>5</t>
         </is>
       </c>
-      <c r="O8" t="inlineStr">
+      <c r="X8" t="inlineStr">
         <is>
           <t>16</t>
         </is>
       </c>
-      <c r="P8" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="Q8" t="inlineStr">
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Z8" t="inlineStr">
         <is>
           <t>0</t>
         </is>

--- a/minio-report-tracker/xlxs/collab.xlsx
+++ b/minio-report-tracker/xlxs/collab.xlsx
@@ -598,7 +598,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Z8"/>
+  <dimension ref="A1:AI8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -627,6 +627,15 @@
     <col width="4" customWidth="1" min="24" max="24"/>
     <col width="4" customWidth="1" min="25" max="25"/>
     <col width="4" customWidth="1" min="26" max="26"/>
+    <col width="2" customWidth="1" min="27" max="27"/>
+    <col width="13" customWidth="1" min="28" max="28"/>
+    <col width="12" customWidth="1" min="29" max="29"/>
+    <col width="5" customWidth="1" min="30" max="30"/>
+    <col width="5" customWidth="1" min="31" max="31"/>
+    <col width="5" customWidth="1" min="32" max="32"/>
+    <col width="5" customWidth="1" min="33" max="33"/>
+    <col width="5" customWidth="1" min="34" max="34"/>
+    <col width="5" customWidth="1" min="35" max="35"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -750,124 +759,204 @@
           <t>KI</t>
         </is>
       </c>
+      <c r="AB1" s="1" t="inlineStr">
+        <is>
+          <t>Date</t>
+        </is>
+      </c>
+      <c r="AC1" s="1" t="inlineStr">
+        <is>
+          <t>Module</t>
+        </is>
+      </c>
+      <c r="AD1" s="1" t="inlineStr">
+        <is>
+          <t>T</t>
+        </is>
+      </c>
+      <c r="AE1" s="1" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
+      <c r="AF1" s="1" t="inlineStr">
+        <is>
+          <t>S</t>
+        </is>
+      </c>
+      <c r="AG1" s="1" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
+      <c r="AH1" s="1" t="inlineStr">
+        <is>
+          <t>I</t>
+        </is>
+      </c>
+      <c r="AI1" s="1" t="inlineStr">
+        <is>
+          <t>KI</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
+          <t>21-May-2026</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>auth</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>254</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>140</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>72</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>42</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
           <t>20-May-2026</t>
         </is>
       </c>
-      <c r="B2" t="inlineStr">
+      <c r="K2" t="inlineStr">
         <is>
           <t>auth</t>
         </is>
       </c>
-      <c r="C2" t="inlineStr">
+      <c r="L2" t="inlineStr">
         <is>
           <t>254</t>
         </is>
       </c>
-      <c r="D2" t="inlineStr">
+      <c r="M2" t="inlineStr">
         <is>
           <t>186</t>
         </is>
       </c>
-      <c r="E2" t="inlineStr">
+      <c r="N2" t="inlineStr">
         <is>
           <t>6</t>
         </is>
       </c>
-      <c r="F2" t="inlineStr">
+      <c r="O2" t="inlineStr">
         <is>
           <t>62</t>
         </is>
       </c>
-      <c r="G2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="J2" t="inlineStr">
+      <c r="P2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Q2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="S2" t="inlineStr">
         <is>
           <t>19-May-2026</t>
         </is>
       </c>
-      <c r="K2" t="inlineStr">
+      <c r="T2" t="inlineStr">
         <is>
           <t>auth</t>
         </is>
       </c>
-      <c r="L2" t="inlineStr">
+      <c r="U2" t="inlineStr">
         <is>
           <t>254</t>
         </is>
       </c>
-      <c r="M2" t="inlineStr">
+      <c r="V2" t="inlineStr">
         <is>
           <t>142</t>
         </is>
       </c>
-      <c r="N2" t="inlineStr">
+      <c r="W2" t="inlineStr">
         <is>
           <t>72</t>
         </is>
       </c>
-      <c r="O2" t="inlineStr">
+      <c r="X2" t="inlineStr">
         <is>
           <t>40</t>
         </is>
       </c>
-      <c r="P2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="Q2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="S2" t="inlineStr">
+      <c r="Y2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Z2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB2" t="inlineStr">
         <is>
           <t>18-May-2026</t>
         </is>
       </c>
-      <c r="T2" t="inlineStr">
-        <is>
-          <t>auth</t>
-        </is>
-      </c>
-      <c r="U2" t="inlineStr">
-        <is>
-          <t>254</t>
-        </is>
-      </c>
-      <c r="V2" t="inlineStr">
-        <is>
-          <t>115</t>
-        </is>
-      </c>
-      <c r="W2" t="inlineStr">
-        <is>
-          <t>72</t>
-        </is>
-      </c>
-      <c r="X2" t="inlineStr">
-        <is>
-          <t>67</t>
-        </is>
-      </c>
-      <c r="Y2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="Z2" t="inlineStr">
+      <c r="AC2" t="inlineStr">
+        <is>
+          <t>esignet</t>
+        </is>
+      </c>
+      <c r="AD2" t="inlineStr">
+        <is>
+          <t>375</t>
+        </is>
+      </c>
+      <c r="AE2" t="inlineStr">
+        <is>
+          <t>258</t>
+        </is>
+      </c>
+      <c r="AF2" t="inlineStr">
+        <is>
+          <t>43</t>
+        </is>
+      </c>
+      <c r="AG2" t="inlineStr">
+        <is>
+          <t>47</t>
+        </is>
+      </c>
+      <c r="AH2" t="inlineStr">
+        <is>
+          <t>27</t>
+        </is>
+      </c>
+      <c r="AI2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
@@ -876,120 +965,160 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
+          <t>21-May-2026</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>esignet</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>375</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>267</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>28</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>53</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>27</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
           <t>20-May-2026</t>
         </is>
       </c>
-      <c r="B3" t="inlineStr">
+      <c r="K3" t="inlineStr">
         <is>
           <t>esignet</t>
         </is>
       </c>
-      <c r="C3" t="inlineStr">
+      <c r="L3" t="inlineStr">
         <is>
           <t>375</t>
         </is>
       </c>
-      <c r="D3" t="inlineStr">
+      <c r="M3" t="inlineStr">
         <is>
           <t>281</t>
         </is>
       </c>
-      <c r="E3" t="inlineStr">
+      <c r="N3" t="inlineStr">
         <is>
           <t>33</t>
         </is>
       </c>
-      <c r="F3" t="inlineStr">
+      <c r="O3" t="inlineStr">
         <is>
           <t>34</t>
         </is>
       </c>
-      <c r="G3" t="inlineStr">
+      <c r="P3" t="inlineStr">
         <is>
           <t>27</t>
         </is>
       </c>
-      <c r="H3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="J3" t="inlineStr">
+      <c r="Q3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="S3" t="inlineStr">
         <is>
           <t>19-May-2026</t>
         </is>
       </c>
-      <c r="K3" t="inlineStr">
+      <c r="T3" t="inlineStr">
         <is>
           <t>esignet</t>
         </is>
       </c>
-      <c r="L3" t="inlineStr">
+      <c r="U3" t="inlineStr">
         <is>
           <t>375</t>
         </is>
       </c>
-      <c r="M3" t="inlineStr">
+      <c r="V3" t="inlineStr">
         <is>
           <t>280</t>
         </is>
       </c>
-      <c r="N3" t="inlineStr">
+      <c r="W3" t="inlineStr">
         <is>
           <t>37</t>
         </is>
       </c>
-      <c r="O3" t="inlineStr">
+      <c r="X3" t="inlineStr">
         <is>
           <t>31</t>
         </is>
       </c>
-      <c r="P3" t="inlineStr">
+      <c r="Y3" t="inlineStr">
         <is>
           <t>27</t>
         </is>
       </c>
-      <c r="Q3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="S3" t="inlineStr">
+      <c r="Z3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB3" t="inlineStr">
         <is>
           <t>18-May-2026</t>
         </is>
       </c>
-      <c r="T3" t="inlineStr">
-        <is>
-          <t>esignet</t>
-        </is>
-      </c>
-      <c r="U3" t="inlineStr">
-        <is>
-          <t>375</t>
-        </is>
-      </c>
-      <c r="V3" t="inlineStr">
-        <is>
-          <t>258</t>
-        </is>
-      </c>
-      <c r="W3" t="inlineStr">
-        <is>
-          <t>43</t>
-        </is>
-      </c>
-      <c r="X3" t="inlineStr">
-        <is>
-          <t>47</t>
-        </is>
-      </c>
-      <c r="Y3" t="inlineStr">
-        <is>
-          <t>27</t>
-        </is>
-      </c>
-      <c r="Z3" t="inlineStr">
+      <c r="AC3" t="inlineStr">
+        <is>
+          <t>injiverify</t>
+        </is>
+      </c>
+      <c r="AD3" t="inlineStr">
+        <is>
+          <t>53</t>
+        </is>
+      </c>
+      <c r="AE3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AF3" t="inlineStr">
+        <is>
+          <t>23</t>
+        </is>
+      </c>
+      <c r="AG3" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="AH3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AI3" t="inlineStr">
         <is>
           <t>0</t>
         </is>
@@ -998,242 +1127,322 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
+          <t>21-May-2026</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>idrepo</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>152</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>101</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>51</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
           <t>20-May-2026</t>
         </is>
       </c>
-      <c r="B4" t="inlineStr">
+      <c r="K4" t="inlineStr">
         <is>
           <t>idrepo</t>
         </is>
       </c>
-      <c r="C4" t="inlineStr">
+      <c r="L4" t="inlineStr">
         <is>
           <t>152</t>
         </is>
       </c>
-      <c r="D4" t="inlineStr">
+      <c r="M4" t="inlineStr">
         <is>
           <t>101</t>
         </is>
       </c>
-      <c r="E4" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F4" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="G4" t="inlineStr">
+      <c r="N4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P4" t="inlineStr">
         <is>
           <t>51</t>
         </is>
       </c>
-      <c r="H4" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="J4" t="inlineStr">
+      <c r="Q4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="S4" t="inlineStr">
         <is>
           <t>19-May-2026</t>
         </is>
       </c>
-      <c r="K4" t="inlineStr">
+      <c r="T4" t="inlineStr">
         <is>
           <t>idrepo</t>
         </is>
       </c>
-      <c r="L4" t="inlineStr">
+      <c r="U4" t="inlineStr">
         <is>
           <t>152</t>
         </is>
       </c>
-      <c r="M4" t="inlineStr">
+      <c r="V4" t="inlineStr">
         <is>
           <t>101</t>
         </is>
       </c>
-      <c r="N4" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="O4" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="P4" t="inlineStr">
+      <c r="W4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="X4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Y4" t="inlineStr">
         <is>
           <t>51</t>
         </is>
       </c>
-      <c r="Q4" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="S4" t="inlineStr">
+      <c r="Z4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB4" t="inlineStr">
         <is>
           <t>18-May-2026</t>
         </is>
       </c>
-      <c r="T4" t="inlineStr">
-        <is>
-          <t>idrepo</t>
-        </is>
-      </c>
-      <c r="U4" t="inlineStr">
-        <is>
-          <t>152</t>
-        </is>
-      </c>
-      <c r="V4" t="inlineStr">
-        <is>
-          <t>101</t>
-        </is>
-      </c>
-      <c r="W4" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="X4" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="Y4" t="inlineStr">
-        <is>
-          <t>51</t>
-        </is>
-      </c>
-      <c r="Z4" t="inlineStr">
-        <is>
-          <t>0</t>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t>prereg</t>
+        </is>
+      </c>
+      <c r="AD4" t="inlineStr">
+        <is>
+          <t>104</t>
+        </is>
+      </c>
+      <c r="AE4" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AF4" t="inlineStr">
+        <is>
+          <t>70</t>
+        </is>
+      </c>
+      <c r="AG4" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="AH4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AI4" t="inlineStr">
+        <is>
+          <t>1</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
+          <t>21-May-2026</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>injiverify</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>53</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>23</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
           <t>20-May-2026</t>
         </is>
       </c>
-      <c r="B5" t="inlineStr">
+      <c r="K5" t="inlineStr">
         <is>
           <t>injiverify</t>
         </is>
       </c>
-      <c r="C5" t="inlineStr">
+      <c r="L5" t="inlineStr">
         <is>
           <t>53</t>
         </is>
       </c>
-      <c r="D5" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="E5" t="inlineStr">
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="N5" t="inlineStr">
         <is>
           <t>23</t>
         </is>
       </c>
-      <c r="F5" t="inlineStr">
+      <c r="O5" t="inlineStr">
         <is>
           <t>30</t>
         </is>
       </c>
-      <c r="G5" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H5" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="J5" t="inlineStr">
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Q5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="S5" t="inlineStr">
         <is>
           <t>19-May-2026</t>
         </is>
       </c>
-      <c r="K5" t="inlineStr">
+      <c r="T5" t="inlineStr">
         <is>
           <t>injiverify</t>
         </is>
       </c>
-      <c r="L5" t="inlineStr">
+      <c r="U5" t="inlineStr">
         <is>
           <t>53</t>
         </is>
       </c>
-      <c r="M5" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="N5" t="inlineStr">
+      <c r="V5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="W5" t="inlineStr">
         <is>
           <t>23</t>
         </is>
       </c>
-      <c r="O5" t="inlineStr">
+      <c r="X5" t="inlineStr">
         <is>
           <t>30</t>
         </is>
       </c>
-      <c r="P5" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="Q5" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="S5" t="inlineStr">
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Z5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB5" t="inlineStr">
         <is>
           <t>18-May-2026</t>
         </is>
       </c>
-      <c r="T5" t="inlineStr">
-        <is>
-          <t>injiverify</t>
-        </is>
-      </c>
-      <c r="U5" t="inlineStr">
-        <is>
-          <t>53</t>
-        </is>
-      </c>
-      <c r="V5" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="W5" t="inlineStr">
-        <is>
-          <t>23</t>
-        </is>
-      </c>
-      <c r="X5" t="inlineStr">
-        <is>
-          <t>30</t>
-        </is>
-      </c>
-      <c r="Y5" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="Z5" t="inlineStr">
+      <c r="AC5" t="inlineStr">
+        <is>
+          <t>residentui</t>
+        </is>
+      </c>
+      <c r="AD5" t="inlineStr">
+        <is>
+          <t>33</t>
+        </is>
+      </c>
+      <c r="AE5" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="AF5" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AG5" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="AH5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AI5" t="inlineStr">
         <is>
           <t>0</t>
         </is>
@@ -1242,358 +1451,406 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
+          <t>21-May-2026</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>mimoto</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>79</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>66</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
           <t>20-May-2026</t>
         </is>
       </c>
-      <c r="B6" t="inlineStr">
+      <c r="K6" t="inlineStr">
         <is>
           <t>mimoto</t>
         </is>
       </c>
-      <c r="C6" t="inlineStr">
+      <c r="L6" t="inlineStr">
         <is>
           <t>79</t>
         </is>
       </c>
-      <c r="D6" t="inlineStr">
+      <c r="M6" t="inlineStr">
         <is>
           <t>59</t>
         </is>
       </c>
-      <c r="E6" t="inlineStr">
+      <c r="N6" t="inlineStr">
         <is>
           <t>4</t>
         </is>
       </c>
-      <c r="F6" t="inlineStr">
+      <c r="O6" t="inlineStr">
         <is>
           <t>4</t>
         </is>
       </c>
-      <c r="G6" t="inlineStr">
+      <c r="P6" t="inlineStr">
         <is>
           <t>10</t>
         </is>
       </c>
-      <c r="H6" t="inlineStr">
+      <c r="Q6" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="J6" t="inlineStr">
+      <c r="S6" t="inlineStr">
         <is>
           <t>19-May-2026</t>
         </is>
       </c>
-      <c r="K6" t="inlineStr">
+      <c r="T6" t="inlineStr">
         <is>
           <t>mimoto</t>
         </is>
       </c>
-      <c r="L6" t="inlineStr">
+      <c r="U6" t="inlineStr">
         <is>
           <t>79</t>
         </is>
       </c>
-      <c r="M6" t="inlineStr">
+      <c r="V6" t="inlineStr">
         <is>
           <t>58</t>
         </is>
       </c>
-      <c r="N6" t="inlineStr">
+      <c r="W6" t="inlineStr">
         <is>
           <t>4</t>
         </is>
       </c>
-      <c r="O6" t="inlineStr">
+      <c r="X6" t="inlineStr">
         <is>
           <t>5</t>
         </is>
       </c>
-      <c r="P6" t="inlineStr">
+      <c r="Y6" t="inlineStr">
         <is>
           <t>10</t>
         </is>
       </c>
-      <c r="Q6" t="inlineStr">
+      <c r="Z6" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="S6" t="inlineStr">
-        <is>
-          <t>18-May-2026</t>
-        </is>
-      </c>
-      <c r="T6" t="inlineStr">
-        <is>
-          <t>mimoto</t>
-        </is>
-      </c>
-      <c r="U6" t="inlineStr">
-        <is>
-          <t>79</t>
-        </is>
-      </c>
-      <c r="V6" t="inlineStr">
-        <is>
-          <t>63</t>
-        </is>
-      </c>
-      <c r="W6" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="X6" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="Y6" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="Z6" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
+      <c r="AB6" t="n">
+        <v/>
+      </c>
+      <c r="AC6" t="n">
+        <v/>
+      </c>
+      <c r="AD6" t="n">
+        <v/>
+      </c>
+      <c r="AE6" t="n">
+        <v/>
+      </c>
+      <c r="AF6" t="n">
+        <v/>
+      </c>
+      <c r="AG6" t="n">
+        <v/>
+      </c>
+      <c r="AH6" t="n">
+        <v/>
+      </c>
+      <c r="AI6" t="n">
+        <v/>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
+          <t>21-May-2026</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>prereg</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>104</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>70</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
           <t>20-May-2026</t>
         </is>
       </c>
-      <c r="B7" t="inlineStr">
+      <c r="K7" t="inlineStr">
         <is>
           <t>prereg</t>
         </is>
       </c>
-      <c r="C7" t="inlineStr">
+      <c r="L7" t="inlineStr">
         <is>
           <t>104</t>
         </is>
       </c>
-      <c r="D7" t="inlineStr">
+      <c r="M7" t="inlineStr">
         <is>
           <t>3</t>
         </is>
       </c>
-      <c r="E7" t="inlineStr">
+      <c r="N7" t="inlineStr">
         <is>
           <t>70</t>
         </is>
       </c>
-      <c r="F7" t="inlineStr">
+      <c r="O7" t="inlineStr">
         <is>
           <t>30</t>
         </is>
       </c>
-      <c r="G7" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H7" t="inlineStr">
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Q7" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="J7" t="inlineStr">
+      <c r="S7" t="inlineStr">
         <is>
           <t>19-May-2026</t>
         </is>
       </c>
-      <c r="K7" t="inlineStr">
+      <c r="T7" t="inlineStr">
         <is>
           <t>prereg</t>
         </is>
       </c>
-      <c r="L7" t="inlineStr">
+      <c r="U7" t="inlineStr">
         <is>
           <t>104</t>
         </is>
       </c>
-      <c r="M7" t="inlineStr">
+      <c r="V7" t="inlineStr">
         <is>
           <t>3</t>
         </is>
       </c>
-      <c r="N7" t="inlineStr">
+      <c r="W7" t="inlineStr">
         <is>
           <t>70</t>
         </is>
       </c>
-      <c r="O7" t="inlineStr">
+      <c r="X7" t="inlineStr">
         <is>
           <t>30</t>
         </is>
       </c>
-      <c r="P7" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="Q7" t="inlineStr">
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Z7" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="S7" t="inlineStr">
-        <is>
-          <t>18-May-2026</t>
-        </is>
-      </c>
-      <c r="T7" t="inlineStr">
-        <is>
-          <t>prereg</t>
-        </is>
-      </c>
-      <c r="U7" t="inlineStr">
-        <is>
-          <t>104</t>
-        </is>
-      </c>
-      <c r="V7" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="W7" t="inlineStr">
-        <is>
-          <t>70</t>
-        </is>
-      </c>
-      <c r="X7" t="inlineStr">
-        <is>
-          <t>30</t>
-        </is>
-      </c>
-      <c r="Y7" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="Z7" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
+      <c r="AB7" t="n">
+        <v/>
+      </c>
+      <c r="AC7" t="n">
+        <v/>
+      </c>
+      <c r="AD7" t="n">
+        <v/>
+      </c>
+      <c r="AE7" t="n">
+        <v/>
+      </c>
+      <c r="AF7" t="n">
+        <v/>
+      </c>
+      <c r="AG7" t="n">
+        <v/>
+      </c>
+      <c r="AH7" t="n">
+        <v/>
+      </c>
+      <c r="AI7" t="n">
+        <v/>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
+          <t>21-May-2026</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>residentui</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>33</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
           <t>20-May-2026</t>
         </is>
       </c>
-      <c r="B8" t="inlineStr">
+      <c r="K8" t="inlineStr">
         <is>
           <t>residentui</t>
         </is>
       </c>
-      <c r="C8" t="inlineStr">
+      <c r="L8" t="inlineStr">
         <is>
           <t>33</t>
         </is>
       </c>
-      <c r="D8" t="inlineStr">
+      <c r="M8" t="inlineStr">
         <is>
           <t>12</t>
         </is>
       </c>
-      <c r="E8" t="inlineStr">
+      <c r="N8" t="inlineStr">
         <is>
           <t>5</t>
         </is>
       </c>
-      <c r="F8" t="inlineStr">
+      <c r="O8" t="inlineStr">
         <is>
           <t>16</t>
         </is>
       </c>
-      <c r="G8" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H8" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="J8" t="inlineStr">
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Q8" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="S8" t="inlineStr">
         <is>
           <t>19-May-2026</t>
         </is>
       </c>
-      <c r="K8" t="inlineStr">
+      <c r="T8" t="inlineStr">
         <is>
           <t>residentui</t>
         </is>
       </c>
-      <c r="L8" t="inlineStr">
+      <c r="U8" t="inlineStr">
         <is>
           <t>33</t>
         </is>
       </c>
-      <c r="M8" t="inlineStr">
+      <c r="V8" t="inlineStr">
         <is>
           <t>12</t>
         </is>
       </c>
-      <c r="N8" t="inlineStr">
+      <c r="W8" t="inlineStr">
         <is>
           <t>5</t>
         </is>
       </c>
-      <c r="O8" t="inlineStr">
+      <c r="X8" t="inlineStr">
         <is>
           <t>16</t>
         </is>
       </c>
-      <c r="P8" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="Q8" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="S8" t="inlineStr">
-        <is>
-          <t>18-May-2026</t>
-        </is>
-      </c>
-      <c r="T8" t="inlineStr">
-        <is>
-          <t>residentui</t>
-        </is>
-      </c>
-      <c r="U8" t="inlineStr">
-        <is>
-          <t>33</t>
-        </is>
-      </c>
-      <c r="V8" t="inlineStr">
-        <is>
-          <t>12</t>
-        </is>
-      </c>
-      <c r="W8" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="X8" t="inlineStr">
-        <is>
-          <t>16</t>
-        </is>
-      </c>
       <c r="Y8" t="inlineStr">
         <is>
           <t>0</t>
@@ -1603,6 +1860,30 @@
         <is>
           <t>0</t>
         </is>
+      </c>
+      <c r="AB8" t="n">
+        <v/>
+      </c>
+      <c r="AC8" t="n">
+        <v/>
+      </c>
+      <c r="AD8" t="n">
+        <v/>
+      </c>
+      <c r="AE8" t="n">
+        <v/>
+      </c>
+      <c r="AF8" t="n">
+        <v/>
+      </c>
+      <c r="AG8" t="n">
+        <v/>
+      </c>
+      <c r="AH8" t="n">
+        <v/>
+      </c>
+      <c r="AI8" t="n">
+        <v/>
       </c>
     </row>
   </sheetData>

--- a/minio-report-tracker/xlxs/collab.xlsx
+++ b/minio-report-tracker/xlxs/collab.xlsx
@@ -803,129 +803,129 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
+          <t>22-May-2026</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>auth</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>254</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>142</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>72</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>40</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
           <t>21-May-2026</t>
         </is>
       </c>
-      <c r="B2" t="inlineStr">
+      <c r="K2" t="inlineStr">
         <is>
           <t>auth</t>
         </is>
       </c>
-      <c r="C2" t="inlineStr">
+      <c r="L2" t="inlineStr">
         <is>
           <t>254</t>
         </is>
       </c>
-      <c r="D2" t="inlineStr">
+      <c r="M2" t="inlineStr">
         <is>
           <t>140</t>
         </is>
       </c>
-      <c r="E2" t="inlineStr">
+      <c r="N2" t="inlineStr">
         <is>
           <t>72</t>
         </is>
       </c>
-      <c r="F2" t="inlineStr">
+      <c r="O2" t="inlineStr">
         <is>
           <t>42</t>
         </is>
       </c>
-      <c r="G2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="J2" t="inlineStr">
+      <c r="P2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Q2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="S2" t="inlineStr">
         <is>
           <t>20-May-2026</t>
         </is>
       </c>
-      <c r="K2" t="inlineStr">
+      <c r="T2" t="inlineStr">
         <is>
           <t>auth</t>
         </is>
       </c>
-      <c r="L2" t="inlineStr">
+      <c r="U2" t="inlineStr">
         <is>
           <t>254</t>
         </is>
       </c>
-      <c r="M2" t="inlineStr">
+      <c r="V2" t="inlineStr">
         <is>
           <t>186</t>
         </is>
       </c>
-      <c r="N2" t="inlineStr">
+      <c r="W2" t="inlineStr">
         <is>
           <t>6</t>
         </is>
       </c>
-      <c r="O2" t="inlineStr">
+      <c r="X2" t="inlineStr">
         <is>
           <t>62</t>
         </is>
       </c>
-      <c r="P2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="Q2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="S2" t="inlineStr">
+      <c r="Y2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Z2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB2" t="inlineStr">
         <is>
           <t>19-May-2026</t>
         </is>
       </c>
-      <c r="T2" t="inlineStr">
-        <is>
-          <t>auth</t>
-        </is>
-      </c>
-      <c r="U2" t="inlineStr">
-        <is>
-          <t>254</t>
-        </is>
-      </c>
-      <c r="V2" t="inlineStr">
-        <is>
-          <t>142</t>
-        </is>
-      </c>
-      <c r="W2" t="inlineStr">
-        <is>
-          <t>72</t>
-        </is>
-      </c>
-      <c r="X2" t="inlineStr">
-        <is>
-          <t>40</t>
-        </is>
-      </c>
-      <c r="Y2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>18-May-2026</t>
-        </is>
-      </c>
       <c r="AC2" t="inlineStr">
         <is>
           <t>esignet</t>
@@ -938,17 +938,17 @@
       </c>
       <c r="AE2" t="inlineStr">
         <is>
-          <t>258</t>
+          <t>280</t>
         </is>
       </c>
       <c r="AF2" t="inlineStr">
         <is>
-          <t>43</t>
+          <t>37</t>
         </is>
       </c>
       <c r="AG2" t="inlineStr">
         <is>
-          <t>47</t>
+          <t>31</t>
         </is>
       </c>
       <c r="AH2" t="inlineStr">
@@ -965,127 +965,127 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
+          <t>22-May-2026</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>esignet</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>375</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>249</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>52</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>47</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>27</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
           <t>21-May-2026</t>
         </is>
       </c>
-      <c r="B3" t="inlineStr">
+      <c r="K3" t="inlineStr">
         <is>
           <t>esignet</t>
         </is>
       </c>
-      <c r="C3" t="inlineStr">
+      <c r="L3" t="inlineStr">
         <is>
           <t>375</t>
         </is>
       </c>
-      <c r="D3" t="inlineStr">
+      <c r="M3" t="inlineStr">
         <is>
           <t>267</t>
         </is>
       </c>
-      <c r="E3" t="inlineStr">
+      <c r="N3" t="inlineStr">
         <is>
           <t>28</t>
         </is>
       </c>
-      <c r="F3" t="inlineStr">
+      <c r="O3" t="inlineStr">
         <is>
           <t>53</t>
         </is>
       </c>
-      <c r="G3" t="inlineStr">
+      <c r="P3" t="inlineStr">
         <is>
           <t>27</t>
         </is>
       </c>
-      <c r="H3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="J3" t="inlineStr">
+      <c r="Q3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="S3" t="inlineStr">
         <is>
           <t>20-May-2026</t>
         </is>
       </c>
-      <c r="K3" t="inlineStr">
+      <c r="T3" t="inlineStr">
         <is>
           <t>esignet</t>
         </is>
       </c>
-      <c r="L3" t="inlineStr">
+      <c r="U3" t="inlineStr">
         <is>
           <t>375</t>
         </is>
       </c>
-      <c r="M3" t="inlineStr">
+      <c r="V3" t="inlineStr">
         <is>
           <t>281</t>
         </is>
       </c>
-      <c r="N3" t="inlineStr">
+      <c r="W3" t="inlineStr">
         <is>
           <t>33</t>
         </is>
       </c>
-      <c r="O3" t="inlineStr">
+      <c r="X3" t="inlineStr">
         <is>
           <t>34</t>
         </is>
       </c>
-      <c r="P3" t="inlineStr">
+      <c r="Y3" t="inlineStr">
         <is>
           <t>27</t>
         </is>
       </c>
-      <c r="Q3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="S3" t="inlineStr">
+      <c r="Z3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB3" t="inlineStr">
         <is>
           <t>19-May-2026</t>
-        </is>
-      </c>
-      <c r="T3" t="inlineStr">
-        <is>
-          <t>esignet</t>
-        </is>
-      </c>
-      <c r="U3" t="inlineStr">
-        <is>
-          <t>375</t>
-        </is>
-      </c>
-      <c r="V3" t="inlineStr">
-        <is>
-          <t>280</t>
-        </is>
-      </c>
-      <c r="W3" t="inlineStr">
-        <is>
-          <t>37</t>
-        </is>
-      </c>
-      <c r="X3" t="inlineStr">
-        <is>
-          <t>31</t>
-        </is>
-      </c>
-      <c r="Y3" t="inlineStr">
-        <is>
-          <t>27</t>
-        </is>
-      </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>18-May-2026</t>
         </is>
       </c>
       <c r="AC3" t="inlineStr">
@@ -1127,127 +1127,127 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
+          <t>22-May-2026</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>idrepo</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>152</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>101</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>51</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
           <t>21-May-2026</t>
         </is>
       </c>
-      <c r="B4" t="inlineStr">
+      <c r="K4" t="inlineStr">
         <is>
           <t>idrepo</t>
         </is>
       </c>
-      <c r="C4" t="inlineStr">
+      <c r="L4" t="inlineStr">
         <is>
           <t>152</t>
         </is>
       </c>
-      <c r="D4" t="inlineStr">
+      <c r="M4" t="inlineStr">
         <is>
           <t>101</t>
         </is>
       </c>
-      <c r="E4" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F4" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="G4" t="inlineStr">
+      <c r="N4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P4" t="inlineStr">
         <is>
           <t>51</t>
         </is>
       </c>
-      <c r="H4" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="J4" t="inlineStr">
+      <c r="Q4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="S4" t="inlineStr">
         <is>
           <t>20-May-2026</t>
         </is>
       </c>
-      <c r="K4" t="inlineStr">
+      <c r="T4" t="inlineStr">
         <is>
           <t>idrepo</t>
         </is>
       </c>
-      <c r="L4" t="inlineStr">
+      <c r="U4" t="inlineStr">
         <is>
           <t>152</t>
         </is>
       </c>
-      <c r="M4" t="inlineStr">
+      <c r="V4" t="inlineStr">
         <is>
           <t>101</t>
         </is>
       </c>
-      <c r="N4" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="O4" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="P4" t="inlineStr">
+      <c r="W4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="X4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Y4" t="inlineStr">
         <is>
           <t>51</t>
         </is>
       </c>
-      <c r="Q4" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="S4" t="inlineStr">
+      <c r="Z4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB4" t="inlineStr">
         <is>
           <t>19-May-2026</t>
-        </is>
-      </c>
-      <c r="T4" t="inlineStr">
-        <is>
-          <t>idrepo</t>
-        </is>
-      </c>
-      <c r="U4" t="inlineStr">
-        <is>
-          <t>152</t>
-        </is>
-      </c>
-      <c r="V4" t="inlineStr">
-        <is>
-          <t>101</t>
-        </is>
-      </c>
-      <c r="W4" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="X4" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="Y4" t="inlineStr">
-        <is>
-          <t>51</t>
-        </is>
-      </c>
-      <c r="Z4" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB4" t="inlineStr">
-        <is>
-          <t>18-May-2026</t>
         </is>
       </c>
       <c r="AC4" t="inlineStr">
@@ -1289,127 +1289,127 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
+          <t>22-May-2026</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>injiverify</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>53</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>23</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
           <t>21-May-2026</t>
         </is>
       </c>
-      <c r="B5" t="inlineStr">
+      <c r="K5" t="inlineStr">
         <is>
           <t>injiverify</t>
         </is>
       </c>
-      <c r="C5" t="inlineStr">
+      <c r="L5" t="inlineStr">
         <is>
           <t>53</t>
         </is>
       </c>
-      <c r="D5" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="E5" t="inlineStr">
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="N5" t="inlineStr">
         <is>
           <t>23</t>
         </is>
       </c>
-      <c r="F5" t="inlineStr">
+      <c r="O5" t="inlineStr">
         <is>
           <t>30</t>
         </is>
       </c>
-      <c r="G5" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H5" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="J5" t="inlineStr">
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Q5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="S5" t="inlineStr">
         <is>
           <t>20-May-2026</t>
         </is>
       </c>
-      <c r="K5" t="inlineStr">
+      <c r="T5" t="inlineStr">
         <is>
           <t>injiverify</t>
         </is>
       </c>
-      <c r="L5" t="inlineStr">
+      <c r="U5" t="inlineStr">
         <is>
           <t>53</t>
         </is>
       </c>
-      <c r="M5" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="N5" t="inlineStr">
+      <c r="V5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="W5" t="inlineStr">
         <is>
           <t>23</t>
         </is>
       </c>
-      <c r="O5" t="inlineStr">
+      <c r="X5" t="inlineStr">
         <is>
           <t>30</t>
         </is>
       </c>
-      <c r="P5" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="Q5" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="S5" t="inlineStr">
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Z5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB5" t="inlineStr">
         <is>
           <t>19-May-2026</t>
-        </is>
-      </c>
-      <c r="T5" t="inlineStr">
-        <is>
-          <t>injiverify</t>
-        </is>
-      </c>
-      <c r="U5" t="inlineStr">
-        <is>
-          <t>53</t>
-        </is>
-      </c>
-      <c r="V5" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="W5" t="inlineStr">
-        <is>
-          <t>23</t>
-        </is>
-      </c>
-      <c r="X5" t="inlineStr">
-        <is>
-          <t>30</t>
-        </is>
-      </c>
-      <c r="Y5" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="Z5" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB5" t="inlineStr">
-        <is>
-          <t>18-May-2026</t>
         </is>
       </c>
       <c r="AC5" t="inlineStr">
@@ -1451,112 +1451,112 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
+          <t>22-May-2026</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>mimoto</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>79</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>66</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
           <t>21-May-2026</t>
         </is>
       </c>
-      <c r="B6" t="inlineStr">
+      <c r="K6" t="inlineStr">
         <is>
           <t>mimoto</t>
         </is>
       </c>
-      <c r="C6" t="inlineStr">
+      <c r="L6" t="inlineStr">
         <is>
           <t>79</t>
         </is>
       </c>
-      <c r="D6" t="inlineStr">
+      <c r="M6" t="inlineStr">
         <is>
           <t>66</t>
         </is>
       </c>
-      <c r="E6" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F6" t="inlineStr">
+      <c r="N6" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O6" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="G6" t="inlineStr">
+      <c r="P6" t="inlineStr">
         <is>
           <t>10</t>
         </is>
       </c>
-      <c r="H6" t="inlineStr">
+      <c r="Q6" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="J6" t="inlineStr">
+      <c r="S6" t="inlineStr">
         <is>
           <t>20-May-2026</t>
         </is>
       </c>
-      <c r="K6" t="inlineStr">
+      <c r="T6" t="inlineStr">
         <is>
           <t>mimoto</t>
         </is>
       </c>
-      <c r="L6" t="inlineStr">
+      <c r="U6" t="inlineStr">
         <is>
           <t>79</t>
         </is>
       </c>
-      <c r="M6" t="inlineStr">
+      <c r="V6" t="inlineStr">
         <is>
           <t>59</t>
         </is>
       </c>
-      <c r="N6" t="inlineStr">
+      <c r="W6" t="inlineStr">
         <is>
           <t>4</t>
         </is>
       </c>
-      <c r="O6" t="inlineStr">
+      <c r="X6" t="inlineStr">
         <is>
           <t>4</t>
-        </is>
-      </c>
-      <c r="P6" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="Q6" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="S6" t="inlineStr">
-        <is>
-          <t>19-May-2026</t>
-        </is>
-      </c>
-      <c r="T6" t="inlineStr">
-        <is>
-          <t>mimoto</t>
-        </is>
-      </c>
-      <c r="U6" t="inlineStr">
-        <is>
-          <t>79</t>
-        </is>
-      </c>
-      <c r="V6" t="inlineStr">
-        <is>
-          <t>58</t>
-        </is>
-      </c>
-      <c r="W6" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="X6" t="inlineStr">
-        <is>
-          <t>5</t>
         </is>
       </c>
       <c r="Y6" t="inlineStr">
@@ -1597,87 +1597,87 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
+          <t>22-May-2026</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>prereg</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>104</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>70</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
           <t>21-May-2026</t>
         </is>
       </c>
-      <c r="B7" t="inlineStr">
+      <c r="K7" t="inlineStr">
         <is>
           <t>prereg</t>
         </is>
       </c>
-      <c r="C7" t="inlineStr">
+      <c r="L7" t="inlineStr">
         <is>
           <t>104</t>
         </is>
       </c>
-      <c r="D7" t="inlineStr">
+      <c r="M7" t="inlineStr">
         <is>
           <t>3</t>
         </is>
       </c>
-      <c r="E7" t="inlineStr">
+      <c r="N7" t="inlineStr">
         <is>
           <t>70</t>
         </is>
       </c>
-      <c r="F7" t="inlineStr">
+      <c r="O7" t="inlineStr">
         <is>
           <t>30</t>
         </is>
       </c>
-      <c r="G7" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H7" t="inlineStr">
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Q7" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="J7" t="inlineStr">
+      <c r="S7" t="inlineStr">
         <is>
           <t>20-May-2026</t>
-        </is>
-      </c>
-      <c r="K7" t="inlineStr">
-        <is>
-          <t>prereg</t>
-        </is>
-      </c>
-      <c r="L7" t="inlineStr">
-        <is>
-          <t>104</t>
-        </is>
-      </c>
-      <c r="M7" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="N7" t="inlineStr">
-        <is>
-          <t>70</t>
-        </is>
-      </c>
-      <c r="O7" t="inlineStr">
-        <is>
-          <t>30</t>
-        </is>
-      </c>
-      <c r="P7" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="Q7" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="S7" t="inlineStr">
-        <is>
-          <t>19-May-2026</t>
         </is>
       </c>
       <c r="T7" t="inlineStr">
@@ -1743,87 +1743,87 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
+          <t>22-May-2026</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>residentui</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>33</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
           <t>21-May-2026</t>
         </is>
       </c>
-      <c r="B8" t="inlineStr">
+      <c r="K8" t="inlineStr">
         <is>
           <t>residentui</t>
         </is>
       </c>
-      <c r="C8" t="inlineStr">
+      <c r="L8" t="inlineStr">
         <is>
           <t>33</t>
         </is>
       </c>
-      <c r="D8" t="inlineStr">
+      <c r="M8" t="inlineStr">
         <is>
           <t>12</t>
         </is>
       </c>
-      <c r="E8" t="inlineStr">
+      <c r="N8" t="inlineStr">
         <is>
           <t>5</t>
         </is>
       </c>
-      <c r="F8" t="inlineStr">
+      <c r="O8" t="inlineStr">
         <is>
           <t>16</t>
         </is>
       </c>
-      <c r="G8" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H8" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="J8" t="inlineStr">
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Q8" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="S8" t="inlineStr">
         <is>
           <t>20-May-2026</t>
-        </is>
-      </c>
-      <c r="K8" t="inlineStr">
-        <is>
-          <t>residentui</t>
-        </is>
-      </c>
-      <c r="L8" t="inlineStr">
-        <is>
-          <t>33</t>
-        </is>
-      </c>
-      <c r="M8" t="inlineStr">
-        <is>
-          <t>12</t>
-        </is>
-      </c>
-      <c r="N8" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="O8" t="inlineStr">
-        <is>
-          <t>16</t>
-        </is>
-      </c>
-      <c r="P8" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="Q8" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="S8" t="inlineStr">
-        <is>
-          <t>19-May-2026</t>
         </is>
       </c>
       <c r="T8" t="inlineStr">
